--- a/mapping_datasul_full.xlsx
+++ b/mapping_datasul_full.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T228"/>
+  <dimension ref="A1:U228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,30 +502,35 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
+          <t>catalog_distinct_coverage</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>catalog_confidence</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>llm_data_confidence</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>llm_final_confidence</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>reviewer_status</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>correct_client_column</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>reviewer_note</t>
         </is>
@@ -569,21 +574,22 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>All candidates exhibit semantic header conflicts or lack relevant data evidence.</t>
+          <t>All candidates exhibit semantic conflicts or lack relevant data evidence.</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
-      <c r="R2" t="inlineStr"/>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -629,21 +635,22 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>The name 'Base CPRB' closely matches 'Base CBS' and has a high name confidence, despite all values being zero.</t>
+          <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
-      <c r="P3" t="n">
-        <v>0.8787</v>
-      </c>
+      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>0.8787</v>
-      </c>
-      <c r="R3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -666,10 +673,10 @@
         <v>0.8605</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8282</v>
+        <v>0.8283</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0323</v>
+        <v>0.0322</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -695,15 +702,16 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
-      <c r="R4" t="inlineStr"/>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -726,7 +734,7 @@
         <v>0.8766</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8394</v>
+        <v>0.8395</v>
       </c>
       <c r="G5" t="n">
         <v>0.0371</v>
@@ -749,21 +757,22 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Both columns are numeric and all-zero, but 'Valor CPRB' is a tax-related field conflicting with 'Valor CBS'.</t>
+          <t>Both columns are numeric and contain only zeros, but 'Valor CPRB' conflicts with the tax family of 'Valor CBS'.</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
         <v>0.8766</v>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -809,15 +818,16 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
+      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
-      <c r="R6" t="inlineStr"/>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -869,15 +879,16 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
-      <c r="P7" t="n">
-        <v>0.8437</v>
-      </c>
+      <c r="P7" t="inlineStr"/>
       <c r="Q7" t="n">
         <v>0.8437</v>
       </c>
-      <c r="R7" t="inlineStr"/>
+      <c r="R7" t="n">
+        <v>0.8437</v>
+      </c>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -917,21 +928,22 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>All candidates exhibit semantic header conflicts and lack distinctive sample evidence.</t>
+          <t>All candidates exhibit semantic-role conflicts and lack distinctive evidence.</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
+      <c r="P8" t="inlineStr"/>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
-      <c r="R8" t="inlineStr"/>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -971,21 +983,22 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the tax family, indicating they do not align with the expected role of 'Tipo de Imposto IBSM'.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
+      <c r="P9" t="inlineStr"/>
       <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="inlineStr"/>
+        <v>0.8443000000000001</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.8443000000000001</v>
+      </c>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1037,15 +1050,16 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
+      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
-      <c r="R10" t="inlineStr"/>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1065,19 +1079,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.8531</v>
+        <v>0.853</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8531</v>
+        <v>0.853</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8531</v>
+        <v>0.853</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1097,15 +1111,16 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
+      <c r="P11" t="inlineStr"/>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
-      <c r="R11" t="inlineStr"/>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1131,7 +1146,7 @@
         <v>0.8693</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0142</v>
+        <v>0.0143</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1157,15 +1172,16 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
+      <c r="P12" t="inlineStr"/>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
-      <c r="R12" t="inlineStr"/>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1211,15 +1227,16 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
+      <c r="P13" t="inlineStr"/>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
-      <c r="R13" t="inlineStr"/>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1265,15 +1282,16 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
+      <c r="P14" t="inlineStr"/>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
-      <c r="R14" t="inlineStr"/>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1287,7 +1305,7 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
-        <v>0.8617</v>
+        <v>0.8618</v>
       </c>
       <c r="F15" t="n">
         <v>0.8473000000000001</v>
@@ -1313,21 +1331,22 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>All candidates exhibit semantic header conflicts and lack distinctive non-zero evidence.</t>
+          <t>All candidates exhibit semantic-role conflicts and lack distinctive non-zero evidence.</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
+      <c r="P15" t="inlineStr"/>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
-      <c r="R15" t="inlineStr"/>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1347,7 +1366,7 @@
         <v>0.8366</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0148</v>
+        <v>0.0147</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1373,15 +1392,16 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
+      <c r="P16" t="inlineStr"/>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
-      <c r="R16" t="inlineStr"/>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1433,15 +1453,16 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
+      <c r="P17" t="inlineStr"/>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
-      <c r="R17" t="inlineStr"/>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1461,19 +1482,19 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.849</v>
+        <v>0.8489</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.849</v>
+        <v>0.8489</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0.849</v>
+        <v>0.8489</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1493,15 +1514,16 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
+      <c r="P18" t="inlineStr"/>
       <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
         <v>0.8555</v>
       </c>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1553,15 +1575,16 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
+      <c r="P19" t="inlineStr"/>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
-      <c r="R19" t="inlineStr"/>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1581,19 +1604,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.8522999999999999</v>
+        <v>0.8522</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.8522999999999999</v>
+        <v>0.8522</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8522999999999999</v>
+        <v>0.8522</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1613,15 +1636,16 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
+      <c r="P20" t="inlineStr"/>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
-      <c r="R20" t="inlineStr"/>
+      <c r="R20" t="n">
+        <v>0.861</v>
+      </c>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1638,7 +1662,7 @@
         <v>0.8466</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8464</v>
+        <v>0.8465</v>
       </c>
       <c r="G21" t="n">
         <v>0.0002</v>
@@ -1661,21 +1685,22 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the tax-family context, indicating they do not align with 'Outras IBS'.</t>
+          <t>All candidates have semantic header conflicts with the tax-family context, indicating they do not align with the 'Outras IBS' column.</t>
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
+      <c r="P21" t="inlineStr"/>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
-      <c r="R21" t="inlineStr"/>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1689,7 +1714,7 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>0.8659</v>
+        <v>0.866</v>
       </c>
       <c r="F22" t="n">
         <v>0.8485</v>
@@ -1715,21 +1740,22 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>All candidates have semantic-role conflicts and provide no valid evidence.</t>
+          <t>All candidates exhibit semantic header conflicts and lack distinctive non-zero evidence.</t>
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
+      <c r="P22" t="inlineStr"/>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
-      <c r="R22" t="inlineStr"/>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1740,28 +1766,22 @@
           <t>Tipo de Imposto IS</t>
         </is>
       </c>
-      <c r="C23" t="n">
-        <v>157</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Sit.Trib.ISS</t>
-        </is>
-      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
-        <v>0.8501</v>
+        <v>0.8541</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8541</v>
+        <v>0.8502</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.004</v>
+        <v>0.004</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8501</v>
+        <v>0</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1770,26 +1790,27 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>no_match</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>The header 'Sit.Trib.ISS' aligns with the tax status role, despite all values being zero.</t>
+          <t>No viable candidates due to lack of relevant data and semantic conflicts.</t>
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
-      <c r="P23" t="n">
-        <v>0.8501</v>
-      </c>
+      <c r="P23" t="inlineStr"/>
       <c r="Q23" t="n">
-        <v>0.8501</v>
-      </c>
-      <c r="R23" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1835,21 +1856,22 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>The column 'Vlr Base IPI' has a higher name confidence and contains mixed numeric values, indicating it may represent a base value, unlike the all-zero candidates.</t>
+          <t>The column 'Vlr Base IPI' has a higher name confidence and contains varied non-zero samples, indicating it may represent a base value.</t>
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
-      <c r="P24" t="n">
-        <v>0.8801</v>
-      </c>
+      <c r="P24" t="inlineStr"/>
       <c r="Q24" t="n">
         <v>0.8801</v>
       </c>
-      <c r="R24" t="inlineStr"/>
+      <c r="R24" t="n">
+        <v>0.8801</v>
+      </c>
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1872,7 +1894,7 @@
         <v>0.8672</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8633999999999999</v>
+        <v>0.8633</v>
       </c>
       <c r="G25" t="n">
         <v>0.0038</v>
@@ -1895,21 +1917,22 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>The candidate 'Aliq ICMS So' has a high name confidence but both columns contain only zeros, indicating no valid data to support a mapping.</t>
+          <t>The candidate 'Aliq ICMS So' has a high name confidence but lacks distinctive sample overlap and all values are zero.</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
+      <c r="P25" t="inlineStr"/>
       <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
         <v>0.8672</v>
       </c>
-      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1921,27 +1944,27 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Vlr Isen ICM</t>
+          <t>Vlr ICMS Com</t>
         </is>
       </c>
       <c r="E26" t="n">
+        <v>0.8348</v>
+      </c>
+      <c r="F26" t="n">
         <v>0.8721</v>
       </c>
-      <c r="F26" t="n">
-        <v>0.8703</v>
-      </c>
       <c r="G26" t="n">
-        <v>0.0018</v>
+        <v>-0.0373</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0.8721</v>
+        <v>0.8348</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1955,21 +1978,22 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
+          <t>The name 'Vlr ICMS Com' closely relates to tax values, and while both columns show high zero fractions, the name suggests a relevant tax context.</t>
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
+      <c r="P26" t="inlineStr"/>
       <c r="Q26" t="n">
-        <v>0.8721</v>
-      </c>
-      <c r="R26" t="inlineStr"/>
+        <v>0.8348</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.8348</v>
+      </c>
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1986,7 +2010,7 @@
         <v>0.8626</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8401999999999999</v>
+        <v>0.8401</v>
       </c>
       <c r="G27" t="n">
         <v>0.0225</v>
@@ -2009,21 +2033,22 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>All candidates have semantic-role conflicts or all-zero evidence, indicating no suitable mapping.</t>
+          <t>All candidates exhibit semantic-role conflicts or lack relevant data evidence.</t>
         </is>
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
+      <c r="P27" t="inlineStr"/>
       <c r="Q27" t="n">
-        <v>0.8626</v>
-      </c>
-      <c r="R27" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2069,15 +2094,16 @@
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
+      <c r="P28" t="inlineStr"/>
       <c r="Q28" t="n">
-        <v>0.8552999999999999</v>
-      </c>
-      <c r="R28" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2091,10 +2117,10 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="n">
-        <v>0.8331</v>
+        <v>0.8332000000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8325</v>
+        <v>0.8326</v>
       </c>
       <c r="G29" t="n">
         <v>0.0005999999999999999</v>
@@ -2123,15 +2149,16 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
+      <c r="P29" t="inlineStr"/>
       <c r="Q29" t="n">
         <v>0</v>
       </c>
-      <c r="R29" t="inlineStr"/>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2145,13 +2172,13 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="n">
-        <v>0.7521</v>
+        <v>0.7519</v>
       </c>
       <c r="F30" t="n">
         <v>0.8106</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.0585</v>
+        <v>-0.0587</v>
       </c>
       <c r="H30" t="n">
         <v>0.84</v>
@@ -2177,15 +2204,16 @@
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
-      <c r="P30" t="n">
-        <v>0.7521</v>
-      </c>
+      <c r="P30" t="inlineStr"/>
       <c r="Q30" t="n">
-        <v>0.7521</v>
-      </c>
-      <c r="R30" t="inlineStr"/>
+        <v>0.7519</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.7519</v>
+      </c>
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2205,10 +2233,10 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.8612</v>
+        <v>0.8611</v>
       </c>
       <c r="F31" t="n">
-        <v>0.8182</v>
+        <v>0.8181</v>
       </c>
       <c r="G31" t="n">
         <v>0.043</v>
@@ -2217,7 +2245,7 @@
         <v>0.84</v>
       </c>
       <c r="I31" t="n">
-        <v>0.8612</v>
+        <v>0.8611</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -2231,21 +2259,22 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>The header 'Data Emissão' closely matches 'Data de lançamento' in meaning, both representing dates related to invoices.</t>
+          <t>The header 'Data Emissão' closely matches 'Data de lançamento' in meaning, both representing dates related to document issuance.</t>
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
-      <c r="P31" t="n">
-        <v>0.8612</v>
-      </c>
+      <c r="P31" t="inlineStr"/>
       <c r="Q31" t="n">
-        <v>0.8612</v>
-      </c>
-      <c r="R31" t="inlineStr"/>
+        <v>0.8611</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.8611</v>
+      </c>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2291,15 +2320,16 @@
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
-      <c r="P32" t="n">
-        <v>0.8414</v>
-      </c>
+      <c r="P32" t="inlineStr"/>
       <c r="Q32" t="n">
         <v>0.8414</v>
       </c>
-      <c r="R32" t="inlineStr"/>
+      <c r="R32" t="n">
+        <v>0.8414</v>
+      </c>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2322,38 +2352,45 @@
         <v>0.9176</v>
       </c>
       <c r="F33" t="n">
-        <v>0.8361</v>
+        <v>0.8362000000000001</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0815</v>
-      </c>
-      <c r="H33" t="inlineStr"/>
+        <v>0.0814</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
       <c r="I33" t="n">
         <v>0.9176</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>data</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>review</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Accepted from header similarity with a clear lead over the runner-up.</t>
+          <t>'Nota Fiscal' has no populated rows, so it cannot be this column's source however well the headers match. Not accepted.</t>
         </is>
       </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
+      <c r="Q33" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.9</v>
+      </c>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2373,7 +2410,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.9111</v>
+        <v>0.9112</v>
       </c>
       <c r="F34" t="n">
         <v>0.926</v>
@@ -2405,15 +2442,16 @@
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
-      <c r="P34" t="n">
-        <v>0.9111</v>
-      </c>
+      <c r="P34" t="inlineStr"/>
       <c r="Q34" t="n">
-        <v>0.9111</v>
-      </c>
-      <c r="R34" t="inlineStr"/>
+        <v>0.9112</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0.9112</v>
+      </c>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2445,7 +2483,7 @@
         <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>0.9408</v>
+        <v>0.9407</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2459,7 +2497,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Versioned official cfop codes cover 100.0% of nonblank values and uniquely identify this candidate among the available columns.</t>
+          <t>Versioned official cfop codes cover 100.0% of the 62 distinct codes used (100.0% of rows) and uniquely identify this candidate among the available columns.</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2470,14 +2508,15 @@
       <c r="N35" t="n">
         <v>1</v>
       </c>
-      <c r="O35" t="n">
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="n">
         <v>1</v>
       </c>
-      <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2497,19 +2536,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.8816000000000001</v>
+        <v>0.8815</v>
       </c>
       <c r="F36" t="n">
         <v>0.872</v>
       </c>
       <c r="G36" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0095</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0.8816000000000001</v>
+        <v>0.8815</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2529,15 +2568,16 @@
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
+      <c r="P36" t="inlineStr"/>
       <c r="Q36" t="n">
         <v>0</v>
       </c>
-      <c r="R36" t="inlineStr"/>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2577,21 +2617,22 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>No suitable candidate matches the semantic role of 'ID parceiro' based on name and data evidence.</t>
+          <t>The candidate 'ID Tributos' has a different semantic role and no distinctive sample overlap with 'ID parceiro', indicating no mapping.</t>
         </is>
       </c>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
+      <c r="P37" t="inlineStr"/>
       <c r="Q37" t="n">
         <v>0</v>
       </c>
-      <c r="R37" t="inlineStr"/>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2605,16 +2646,16 @@
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.8494</v>
       </c>
       <c r="F38" t="n">
-        <v>0.8494</v>
+        <v>0.8461</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.0314</v>
+        <v>0.0032</v>
       </c>
       <c r="H38" t="n">
-        <v>0.171</v>
+        <v>0.4054</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -2637,15 +2678,16 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
-      <c r="P38" t="n">
-        <v>0.8179999999999999</v>
-      </c>
+      <c r="P38" t="inlineStr"/>
       <c r="Q38" t="n">
-        <v>0.8179999999999999</v>
-      </c>
-      <c r="R38" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0.8494</v>
+      </c>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2659,13 +2701,13 @@
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="n">
-        <v>0.8024</v>
+        <v>0.8285</v>
       </c>
       <c r="F39" t="n">
-        <v>0.858</v>
+        <v>0.8581</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.0556</v>
+        <v>-0.0296</v>
       </c>
       <c r="H39" t="n">
         <v>0.4227</v>
@@ -2691,15 +2733,16 @@
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
-      <c r="P39" t="n">
-        <v>0.8024</v>
-      </c>
+      <c r="P39" t="inlineStr"/>
       <c r="Q39" t="n">
-        <v>0.8024</v>
-      </c>
-      <c r="R39" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0.5</v>
+      </c>
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2713,13 +2756,13 @@
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="n">
-        <v>0.7938</v>
+        <v>0.7937</v>
       </c>
       <c r="F40" t="n">
         <v>0.8041</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.0103</v>
+        <v>-0.0104</v>
       </c>
       <c r="H40" t="n">
         <v>0.45</v>
@@ -2745,15 +2788,16 @@
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
-      <c r="P40" t="n">
-        <v>0.7938</v>
-      </c>
+      <c r="P40" t="inlineStr"/>
       <c r="Q40" t="n">
-        <v>0.7938</v>
-      </c>
-      <c r="R40" t="inlineStr"/>
+        <v>0.7937</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0.7937</v>
+      </c>
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2805,15 +2849,16 @@
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
-      <c r="P41" t="n">
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="R41" t="n">
         <v>0.88</v>
       </c>
-      <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2868,6 +2913,7 @@
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2922,6 +2968,7 @@
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2935,7 +2982,7 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="n">
-        <v>0.9154</v>
+        <v>0.9155</v>
       </c>
       <c r="F44" t="n">
         <v>0.9122</v>
@@ -2967,15 +3014,16 @@
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
-      <c r="P44" t="n">
-        <v>0.99</v>
-      </c>
+      <c r="P44" t="inlineStr"/>
       <c r="Q44" t="n">
-        <v>0.9154</v>
-      </c>
-      <c r="R44" t="inlineStr"/>
+        <v>0.1</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0.9155</v>
+      </c>
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3021,15 +3069,16 @@
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
-      <c r="P45" t="n">
-        <v>0.874</v>
-      </c>
+      <c r="P45" t="inlineStr"/>
       <c r="Q45" t="n">
         <v>0.874</v>
       </c>
-      <c r="R45" t="inlineStr"/>
+      <c r="R45" t="n">
+        <v>0.874</v>
+      </c>
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3043,16 +3092,16 @@
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="n">
-        <v>0.9164</v>
+        <v>0.8991</v>
       </c>
       <c r="F46" t="n">
-        <v>0.8991</v>
+        <v>0.8871</v>
       </c>
       <c r="G46" t="n">
-        <v>0.0173</v>
+        <v>0.012</v>
       </c>
       <c r="H46" t="n">
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
@@ -3069,21 +3118,22 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>The candidate 'Vlr Out ICMS' has a semantic header conflict and does not align with the expected role of 'Outras ICMS'.</t>
         </is>
       </c>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
-      <c r="P46" t="n">
-        <v>0.9164</v>
-      </c>
+      <c r="P46" t="inlineStr"/>
       <c r="Q46" t="n">
-        <v>0.9164</v>
-      </c>
-      <c r="R46" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3129,21 +3179,22 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>The candidate 'Vlr Isen ICM' has a compatible numeric type and no semantic header conflict, making it the best match despite the low distinctive sample overlap.</t>
+          <t>The candidate 'Vlr Isen ICM' has a compatible numeric type and no semantic header conflict.</t>
         </is>
       </c>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
-      <c r="P47" t="n">
-        <v>0.8691</v>
-      </c>
+      <c r="P47" t="inlineStr"/>
       <c r="Q47" t="n">
         <v>0.8691</v>
       </c>
-      <c r="R47" t="inlineStr"/>
+      <c r="R47" t="n">
+        <v>0.8691</v>
+      </c>
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3166,7 +3217,7 @@
         <v>0.8731</v>
       </c>
       <c r="F48" t="n">
-        <v>0.853</v>
+        <v>0.8529</v>
       </c>
       <c r="G48" t="n">
         <v>0.0202</v>
@@ -3195,15 +3246,16 @@
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
-      <c r="P48" t="n">
-        <v>0</v>
-      </c>
+      <c r="P48" t="inlineStr"/>
       <c r="Q48" t="n">
         <v>0</v>
       </c>
-      <c r="R48" t="inlineStr"/>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3255,15 +3307,16 @@
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
-      <c r="P49" t="n">
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="n">
         <v>0.9979</v>
       </c>
-      <c r="Q49" t="n">
+      <c r="R49" t="n">
         <v>0.9491000000000001</v>
       </c>
-      <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3318,6 +3371,7 @@
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3363,15 +3417,16 @@
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
-      <c r="P51" t="n">
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="n">
         <v>0.091</v>
       </c>
-      <c r="Q51" t="n">
+      <c r="R51" t="n">
         <v>0.9011</v>
       </c>
-      <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3391,7 +3446,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.898</v>
+        <v>0.8981</v>
       </c>
       <c r="F52" t="n">
         <v>0.878</v>
@@ -3403,7 +3458,7 @@
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>0.898</v>
+        <v>0.8981</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -3417,21 +3472,22 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>The header 'IPI Pauta' aligns with the tax context of 'Outras IPI', despite all-zero evidence.</t>
+          <t>The header 'IPI Pauta' aligns with the tax context of 'Outras IPI', despite both having all-zero evidence.</t>
         </is>
       </c>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
-      <c r="P52" t="n">
-        <v>0</v>
-      </c>
+      <c r="P52" t="inlineStr"/>
       <c r="Q52" t="n">
-        <v>0.898</v>
-      </c>
-      <c r="R52" t="inlineStr"/>
+        <v>0.8981</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0.8981</v>
+      </c>
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3477,21 +3533,22 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>The name 'Base Pis' closely matches 'Base PIS' with high name confidence, but the data shows a high zero fraction and low distinctive sample overlap.</t>
+          <t>The name 'Base Pis' closely matches 'Base PIS' with high name confidence, and while the numeric evidence is weak, the profile similarity is very high.</t>
         </is>
       </c>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
-      <c r="P53" t="n">
-        <v>0.909</v>
-      </c>
+      <c r="P53" t="inlineStr"/>
       <c r="Q53" t="n">
         <v>0.909</v>
       </c>
-      <c r="R53" t="inlineStr"/>
+      <c r="R53" t="n">
+        <v>0.954</v>
+      </c>
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -3514,10 +3571,10 @@
         <v>1</v>
       </c>
       <c r="F54" t="n">
-        <v>0.921</v>
+        <v>0.9211</v>
       </c>
       <c r="G54" t="n">
-        <v>0.079</v>
+        <v>0.0789</v>
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="n">
@@ -3546,6 +3603,7 @@
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -3568,10 +3626,10 @@
         <v>1</v>
       </c>
       <c r="F55" t="n">
-        <v>0.9262</v>
+        <v>0.9263</v>
       </c>
       <c r="G55" t="n">
-        <v>0.0738</v>
+        <v>0.0737</v>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="n">
@@ -3600,6 +3658,7 @@
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -3622,10 +3681,10 @@
         <v>1</v>
       </c>
       <c r="F56" t="n">
-        <v>0.8996</v>
+        <v>0.8995</v>
       </c>
       <c r="G56" t="n">
-        <v>0.1004</v>
+        <v>0.1005</v>
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="n">
@@ -3654,6 +3713,7 @@
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3708,6 +3768,7 @@
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3762,6 +3823,7 @@
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3784,10 +3846,10 @@
         <v>0.853</v>
       </c>
       <c r="F59" t="n">
-        <v>0.8487</v>
+        <v>0.8486</v>
       </c>
       <c r="G59" t="n">
-        <v>0.0043</v>
+        <v>0.0044</v>
       </c>
       <c r="H59" t="n">
         <v>0.2513</v>
@@ -3807,21 +3869,22 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>The header 'Obs Liv. Fis' aligns with the sample values indicating observations related to invoices, despite a lower name confidence.</t>
+          <t>The header 'Obs Liv. Fis' suggests observational notes, which aligns with the 'Observações' column's content.</t>
         </is>
       </c>
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
-      <c r="P59" t="n">
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q59" t="n">
+      <c r="R59" t="n">
         <v>0.826</v>
       </c>
-      <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3873,15 +3936,16 @@
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
-      <c r="P60" t="n">
-        <v>0.8768</v>
-      </c>
+      <c r="P60" t="inlineStr"/>
       <c r="Q60" t="n">
-        <v>0.8768</v>
-      </c>
-      <c r="R60" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0.88</v>
+      </c>
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -3892,22 +3956,28 @@
           <t>Ctg.nota fiscal</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
+      <c r="C61" t="n">
+        <v>280</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Nota Fiscal</t>
+        </is>
+      </c>
       <c r="E61" t="n">
-        <v>0.8376</v>
+        <v>0.9093</v>
       </c>
       <c r="F61" t="n">
-        <v>0.8497</v>
+        <v>0.8498</v>
       </c>
       <c r="G61" t="n">
-        <v>-0.0122</v>
+        <v>0.0595</v>
       </c>
       <c r="H61" t="n">
-        <v>0.2633</v>
+        <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>0.9093</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -3916,26 +3986,27 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>review</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>'Nota Fiscal' has no populated rows, so it cannot be this column's source however well the headers match. Not accepted.</t>
         </is>
       </c>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
-      <c r="P61" t="n">
-        <v>0.8376</v>
-      </c>
+      <c r="P61" t="inlineStr"/>
       <c r="Q61" t="n">
-        <v>0.8376</v>
-      </c>
-      <c r="R61" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0.9</v>
+      </c>
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -3981,21 +4052,22 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>The header 'Data Emissão' closely matches the semantic role of 'Data documento' and both have similar datetime profiles.</t>
+          <t>The header 'Data Emissão' closely matches the semantic role of 'Data documento' with strong datetime evidence.</t>
         </is>
       </c>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
-      <c r="P62" t="n">
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="n">
         <v>0.8752</v>
       </c>
-      <c r="Q62" t="n">
+      <c r="R62" t="n">
         <v>0.8794999999999999</v>
       </c>
-      <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -4035,21 +4107,22 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>No suitable candidate matches the semantic role of 'Criado por' based on the evidence provided.</t>
+          <t>No suitable candidate matches the semantic role of 'Criado por'.</t>
         </is>
       </c>
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
-      <c r="P63" t="n">
-        <v>0</v>
-      </c>
+      <c r="P63" t="inlineStr"/>
       <c r="Q63" t="n">
-        <v>0.7499</v>
-      </c>
-      <c r="R63" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0</v>
+      </c>
       <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -4089,21 +4162,22 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>No candidate column matches the semantic role of 'Modificado por'.</t>
+          <t>No suitable candidate matches the semantic role of 'Modificado por'.</t>
         </is>
       </c>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
-      <c r="P64" t="n">
-        <v>0</v>
-      </c>
+      <c r="P64" t="inlineStr"/>
       <c r="Q64" t="n">
         <v>0</v>
       </c>
-      <c r="R64" t="inlineStr"/>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
       <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -4117,13 +4191,13 @@
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="n">
-        <v>0.8098</v>
+        <v>0.8379</v>
       </c>
       <c r="F65" t="n">
-        <v>0.8379</v>
+        <v>0.8155</v>
       </c>
       <c r="G65" t="n">
-        <v>-0.0282</v>
+        <v>0.0224</v>
       </c>
       <c r="H65" t="n">
         <v>0.45</v>
@@ -4149,15 +4223,16 @@
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
-      <c r="P65" t="n">
-        <v>0.8098</v>
-      </c>
+      <c r="P65" t="inlineStr"/>
       <c r="Q65" t="n">
-        <v>0.8098</v>
-      </c>
-      <c r="R65" t="inlineStr"/>
+        <v>0.8379</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0.8379</v>
+      </c>
       <c r="S65" t="inlineStr"/>
       <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -4203,21 +4278,22 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>The header 'NF Original' closely matches the semantic role of 'Nº doc.original Cabeçalho' and has a high numeric fraction with consistent sample values.</t>
+          <t>The column 'NF Original' has a high name confidence and matches the numeric format of invoice document numbers.</t>
         </is>
       </c>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
-      <c r="P66" t="n">
-        <v>0.845</v>
-      </c>
+      <c r="P66" t="inlineStr"/>
       <c r="Q66" t="n">
         <v>0.845</v>
       </c>
-      <c r="R66" t="inlineStr"/>
+      <c r="R66" t="n">
+        <v>0.845</v>
+      </c>
       <c r="S66" t="inlineStr"/>
       <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -4263,21 +4339,22 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>The candidate 'NF Original' has a strong numeric profile with a consistent length of 9 digits, aligning well with the 'Nº doc.original' which also appears to represent a document number.</t>
+          <t>The candidate 'NF Original' closely matches the document ID role of 'Nº doc.original' with strong numeric evidence.</t>
         </is>
       </c>
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
-      <c r="P67" t="n">
-        <v>0.9</v>
-      </c>
+      <c r="P67" t="inlineStr"/>
       <c r="Q67" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="R67" t="inlineStr"/>
+        <v>0.8584000000000001</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0.8584000000000001</v>
+      </c>
       <c r="S67" t="inlineStr"/>
       <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -4288,8 +4365,14 @@
           <t>Código da situação do documento</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr"/>
-      <c r="D68" t="inlineStr"/>
+      <c r="C68" t="n">
+        <v>270</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Cód Sit SN</t>
+        </is>
+      </c>
       <c r="E68" t="n">
         <v>0.8507</v>
       </c>
@@ -4297,13 +4380,13 @@
         <v>0.8332000000000001</v>
       </c>
       <c r="G68" t="n">
-        <v>0.0175</v>
+        <v>0.0176</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>0.8507</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -4312,26 +4395,27 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>review</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>No suitable candidate matches the semantic role of the document situation code, as all candidates either lack data or conflict with the expected role.</t>
+          <t>The candidate column has no non-empty values, making it incompatible despite a reasonable name match.</t>
         </is>
       </c>
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
-      <c r="P68" t="n">
-        <v>0</v>
-      </c>
+      <c r="P68" t="inlineStr"/>
       <c r="Q68" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" t="n">
         <v>0.8507</v>
       </c>
-      <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr"/>
       <c r="T68" t="inlineStr"/>
+      <c r="U68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -4348,7 +4432,7 @@
         <v>0.8661</v>
       </c>
       <c r="F69" t="n">
-        <v>0.8498</v>
+        <v>0.8497</v>
       </c>
       <c r="G69" t="n">
         <v>0.0163</v>
@@ -4371,21 +4455,22 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>All candidates have empty or all-zero evidence, making them unsuitable for mapping.</t>
+          <t>All candidates have empty or all-zero evidence, providing no support for a mapping.</t>
         </is>
       </c>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
-      <c r="P69" t="n">
-        <v>0</v>
-      </c>
+      <c r="P69" t="inlineStr"/>
       <c r="Q69" t="n">
         <v>0</v>
       </c>
-      <c r="R69" t="inlineStr"/>
+      <c r="R69" t="n">
+        <v>0</v>
+      </c>
       <c r="S69" t="inlineStr"/>
       <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -4405,7 +4490,7 @@
         <v>0.7958</v>
       </c>
       <c r="G70" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.0083</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -4431,15 +4516,16 @@
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
-      <c r="P70" t="n">
-        <v>0</v>
-      </c>
+      <c r="P70" t="inlineStr"/>
       <c r="Q70" t="n">
         <v>0</v>
       </c>
-      <c r="R70" t="inlineStr"/>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
       <c r="S70" t="inlineStr"/>
       <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -4462,7 +4548,7 @@
         <v>0.8597</v>
       </c>
       <c r="F71" t="n">
-        <v>0.8532999999999999</v>
+        <v>0.8532</v>
       </c>
       <c r="G71" t="n">
         <v>0.0064</v>
@@ -4491,15 +4577,16 @@
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
-      <c r="P71" t="n">
-        <v>0</v>
-      </c>
+      <c r="P71" t="inlineStr"/>
       <c r="Q71" t="n">
         <v>0</v>
       </c>
-      <c r="R71" t="inlineStr"/>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
       <c r="S71" t="inlineStr"/>
       <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -4551,15 +4638,16 @@
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
-      <c r="P72" t="n">
-        <v>0</v>
-      </c>
+      <c r="P72" t="inlineStr"/>
       <c r="Q72" t="n">
-        <v>0.8615</v>
-      </c>
-      <c r="R72" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0.8614000000000001</v>
+      </c>
       <c r="S72" t="inlineStr"/>
       <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -4573,13 +4661,13 @@
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="n">
-        <v>0.7998</v>
+        <v>0.7991</v>
       </c>
       <c r="F73" t="n">
-        <v>0.849</v>
+        <v>0.8494</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.0491</v>
+        <v>-0.0503</v>
       </c>
       <c r="H73" t="n">
         <v>0.84</v>
@@ -4605,15 +4693,16 @@
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
-      <c r="P73" t="n">
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="n">
         <v>0.9667</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0.849</v>
-      </c>
-      <c r="R73" t="inlineStr"/>
+      <c r="R73" t="n">
+        <v>0.8494</v>
+      </c>
       <c r="S73" t="inlineStr"/>
       <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -4625,28 +4714,28 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NF Original</t>
+          <t>Item NF Orig</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.8375</v>
+        <v>0.8758</v>
       </c>
       <c r="F74" t="n">
+        <v>0.8493000000000001</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.0265</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="I74" t="n">
         <v>0.8758</v>
       </c>
-      <c r="G74" t="n">
-        <v>-0.0383</v>
-      </c>
-      <c r="H74" t="n">
-        <v>0.3167</v>
-      </c>
-      <c r="I74" t="n">
-        <v>0.8375</v>
-      </c>
       <c r="J74" t="inlineStr">
         <is>
           <t>data</t>
@@ -4659,21 +4748,22 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>The candidate 'NF Original' has a strong numeric profile and a high name confidence, aligning well with the expected format of an invoice item reference.</t>
+          <t>The candidate 'Item NF Orig' has a high name confidence and numeric profile similarity, but lacks distinctive sample overlap.</t>
         </is>
       </c>
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr"/>
-      <c r="P74" t="n">
-        <v>0.8</v>
-      </c>
+      <c r="P74" t="inlineStr"/>
       <c r="Q74" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="R74" t="inlineStr"/>
+        <v>0.65</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0.75</v>
+      </c>
       <c r="S74" t="inlineStr"/>
       <c r="T74" t="inlineStr"/>
+      <c r="U74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -4690,10 +4780,10 @@
         <v>0.8007</v>
       </c>
       <c r="F75" t="n">
-        <v>0.7953</v>
+        <v>0.7974</v>
       </c>
       <c r="G75" t="n">
-        <v>0.0054</v>
+        <v>0.0033</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -4713,21 +4803,22 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>No candidate column matches the semantic role of 'Mensagem' based on header and data evidence.</t>
+          <t>No suitable candidate matches the semantic role of 'Mensagem' based on the provided evidence.</t>
         </is>
       </c>
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
-      <c r="P75" t="n">
-        <v>0</v>
-      </c>
+      <c r="P75" t="inlineStr"/>
       <c r="Q75" t="n">
         <v>0</v>
       </c>
-      <c r="R75" t="inlineStr"/>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
       <c r="S75" t="inlineStr"/>
       <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -4744,10 +4835,10 @@
         <v>0.8042</v>
       </c>
       <c r="F76" t="n">
-        <v>0.8024</v>
+        <v>0.8025</v>
       </c>
       <c r="G76" t="n">
-        <v>0.0018</v>
+        <v>0.0017</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -4767,21 +4858,22 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>No suitable candidate found due to lack of relevant data evidence.</t>
+          <t>All candidates have insufficient evidence or conflicting roles, making a mapping unsupported.</t>
         </is>
       </c>
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
-      <c r="P76" t="n">
-        <v>0</v>
-      </c>
+      <c r="P76" t="inlineStr"/>
       <c r="Q76" t="n">
         <v>0</v>
       </c>
-      <c r="R76" t="inlineStr"/>
+      <c r="R76" t="n">
+        <v>0</v>
+      </c>
       <c r="S76" t="inlineStr"/>
       <c r="T76" t="inlineStr"/>
+      <c r="U76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -4798,7 +4890,7 @@
         <v>0.8317</v>
       </c>
       <c r="F77" t="n">
-        <v>0.8231000000000001</v>
+        <v>0.823</v>
       </c>
       <c r="G77" t="n">
         <v>0.0086</v>
@@ -4821,21 +4913,22 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>The candidate 'Doc. Fiscal' does not match the numeric format and content of 'Domicílio fiscal', which consists of 7-digit numbers.</t>
+          <t>The candidate 'Doc. Fiscal' has a different numeric format and length compared to 'Domicílio fiscal', indicating a mismatch.</t>
         </is>
       </c>
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
-      <c r="P77" t="n">
-        <v>0</v>
-      </c>
+      <c r="P77" t="inlineStr"/>
       <c r="Q77" t="n">
         <v>0</v>
       </c>
-      <c r="R77" t="inlineStr"/>
+      <c r="R77" t="n">
+        <v>0</v>
+      </c>
       <c r="S77" t="inlineStr"/>
       <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -4846,22 +4939,28 @@
           <t>Modelo nota fiscal</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr"/>
-      <c r="D78" t="inlineStr"/>
+      <c r="C78" t="n">
+        <v>280</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Nota Fiscal</t>
+        </is>
+      </c>
       <c r="E78" t="n">
-        <v>0.8229</v>
+        <v>0.9081</v>
       </c>
       <c r="F78" t="n">
-        <v>0.8305</v>
+        <v>0.8306</v>
       </c>
       <c r="G78" t="n">
-        <v>-0.0077</v>
+        <v>0.0775</v>
       </c>
       <c r="H78" t="n">
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>0</v>
+        <v>0.9081</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -4870,26 +4969,27 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>review</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>'Nota Fiscal' has no populated rows, so it cannot be this column's source however well the headers match. Not accepted.</t>
         </is>
       </c>
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
-      <c r="P78" t="n">
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="n">
         <v>0.9199000000000001</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="R78" t="inlineStr"/>
+      <c r="R78" t="n">
+        <v>0.914</v>
+      </c>
       <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr"/>
+      <c r="U78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -4901,27 +5001,27 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>10</v>
+        <v>116</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Cód. Serviço</t>
+          <t>Num. RPS</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.8831</v>
+        <v>0.8129</v>
       </c>
       <c r="F79" t="n">
-        <v>0.8361</v>
+        <v>0.883</v>
       </c>
       <c r="G79" t="n">
-        <v>0.047</v>
+        <v>-0.0702</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>0.8831</v>
+        <v>0.8129</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -4935,21 +5035,22 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>The header 'Cód. Serviço' closely matches the semantic role of 'Nº de serviço' and has informative data.</t>
+          <t>The header 'Num. RPS' closely aligns with the semantic role of 'Nº de serviço' and has informative data evidence.</t>
         </is>
       </c>
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
-      <c r="P79" t="n">
-        <v>0.8831</v>
-      </c>
+      <c r="P79" t="inlineStr"/>
       <c r="Q79" t="n">
-        <v>0.8831</v>
-      </c>
-      <c r="R79" t="inlineStr"/>
+        <v>0.8129</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0.8129</v>
+      </c>
       <c r="S79" t="inlineStr"/>
       <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -4989,21 +5090,22 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>All candidate columns have insufficient evidence or semantic conflicts, making them incompatible.</t>
         </is>
       </c>
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
-      <c r="P80" t="n">
-        <v>0.8447</v>
-      </c>
+      <c r="P80" t="inlineStr"/>
       <c r="Q80" t="n">
-        <v>0.8447</v>
-      </c>
-      <c r="R80" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0</v>
+      </c>
       <c r="S80" t="inlineStr"/>
       <c r="T80" t="inlineStr"/>
+      <c r="U80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -5017,16 +5119,16 @@
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="n">
-        <v>0.8238</v>
+        <v>0.8079</v>
       </c>
       <c r="F81" t="n">
         <v>0.842</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.0182</v>
+        <v>-0.0342</v>
       </c>
       <c r="H81" t="n">
-        <v>0.375</v>
+        <v>0.84</v>
       </c>
       <c r="I81" t="n">
         <v>0</v>
@@ -5049,15 +5151,16 @@
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
-      <c r="P81" t="n">
-        <v>0.8238</v>
-      </c>
+      <c r="P81" t="inlineStr"/>
       <c r="Q81" t="n">
-        <v>0.8238</v>
-      </c>
-      <c r="R81" t="inlineStr"/>
+        <v>0.8079</v>
+      </c>
+      <c r="R81" t="n">
+        <v>0.825</v>
+      </c>
       <c r="S81" t="inlineStr"/>
       <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -5074,10 +5177,10 @@
         <v>0.7775</v>
       </c>
       <c r="F82" t="n">
-        <v>0.7871</v>
+        <v>0.7881</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.0097</v>
+        <v>-0.0106</v>
       </c>
       <c r="H82" t="n">
         <v>0.7266</v>
@@ -5103,15 +5206,16 @@
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
-      <c r="P82" t="n">
-        <v>0.7266</v>
-      </c>
+      <c r="P82" t="inlineStr"/>
       <c r="Q82" t="n">
-        <v>0.7566000000000001</v>
-      </c>
-      <c r="R82" t="inlineStr"/>
+        <v>0.7775</v>
+      </c>
+      <c r="R82" t="n">
+        <v>0.7775</v>
+      </c>
       <c r="S82" t="inlineStr"/>
       <c r="T82" t="inlineStr"/>
+      <c r="U82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -5125,13 +5229,13 @@
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="n">
-        <v>0.8112</v>
+        <v>0.8279</v>
       </c>
       <c r="F83" t="n">
-        <v>0.8322000000000001</v>
+        <v>0.8323</v>
       </c>
       <c r="G83" t="n">
-        <v>-0.021</v>
+        <v>-0.0044</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -5157,15 +5261,16 @@
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
-      <c r="P83" t="n">
-        <v>0.8112</v>
-      </c>
+      <c r="P83" t="inlineStr"/>
       <c r="Q83" t="n">
-        <v>0.8112</v>
-      </c>
-      <c r="R83" t="inlineStr"/>
+        <v>0.8279</v>
+      </c>
+      <c r="R83" t="n">
+        <v>0.8279</v>
+      </c>
       <c r="S83" t="inlineStr"/>
       <c r="T83" t="inlineStr"/>
+      <c r="U83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -5179,10 +5284,10 @@
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="n">
-        <v>0.7959000000000001</v>
+        <v>0.7961</v>
       </c>
       <c r="F84" t="n">
-        <v>0.7909</v>
+        <v>0.7911</v>
       </c>
       <c r="G84" t="n">
         <v>0.005</v>
@@ -5205,21 +5310,22 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>All candidates have zero values and lack distinctive content to support a mapping.</t>
+          <t>All candidates have zero values and lack distinctive evidence to support a mapping.</t>
         </is>
       </c>
       <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
-      <c r="P84" t="n">
-        <v>0</v>
-      </c>
+      <c r="P84" t="inlineStr"/>
       <c r="Q84" t="n">
-        <v>0.7751</v>
-      </c>
-      <c r="R84" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="R84" t="n">
+        <v>0</v>
+      </c>
       <c r="S84" t="inlineStr"/>
       <c r="T84" t="inlineStr"/>
+      <c r="U84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -5233,10 +5339,10 @@
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="n">
-        <v>0.79</v>
+        <v>0.7903</v>
       </c>
       <c r="F85" t="n">
-        <v>0.7982</v>
+        <v>0.7983</v>
       </c>
       <c r="G85" t="n">
         <v>-0.0081</v>
@@ -5265,15 +5371,16 @@
       <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
-      <c r="P85" t="n">
-        <v>0.79</v>
-      </c>
+      <c r="P85" t="inlineStr"/>
       <c r="Q85" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="R85" t="inlineStr"/>
+        <v>0.7903</v>
+      </c>
+      <c r="R85" t="n">
+        <v>0.7903</v>
+      </c>
       <c r="S85" t="inlineStr"/>
       <c r="T85" t="inlineStr"/>
+      <c r="U85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -5287,13 +5394,13 @@
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="n">
-        <v>0.8451</v>
+        <v>0.8458</v>
       </c>
       <c r="F86" t="n">
-        <v>0.8381999999999999</v>
+        <v>0.8383</v>
       </c>
       <c r="G86" t="n">
-        <v>0.0069</v>
+        <v>0.0075</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -5313,21 +5420,22 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>All candidates have insufficient evidence or semantic conflicts, making a valid mapping impossible.</t>
+          <t>All candidates have insufficient evidence or semantic conflicts, making a mapping unsupported.</t>
         </is>
       </c>
       <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
-      <c r="P86" t="n">
-        <v>0</v>
-      </c>
+      <c r="P86" t="inlineStr"/>
       <c r="Q86" t="n">
         <v>0</v>
       </c>
-      <c r="R86" t="inlineStr"/>
+      <c r="R86" t="n">
+        <v>0</v>
+      </c>
       <c r="S86" t="inlineStr"/>
       <c r="T86" t="inlineStr"/>
+      <c r="U86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -5347,7 +5455,7 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.8827</v>
+        <v>0.8826000000000001</v>
       </c>
       <c r="F87" t="n">
         <v>0.8787</v>
@@ -5359,7 +5467,7 @@
         <v>0.84</v>
       </c>
       <c r="I87" t="n">
-        <v>0.8827</v>
+        <v>0.8826000000000001</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -5373,21 +5481,22 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>The name 'Antecip.ICMS' aligns closely with the tax type, and there is no semantic conflict.</t>
+          <t>The name 'Antecip.ICMS' aligns closely with the tax type, and the profile shows valid numeric data without semantic conflicts.</t>
         </is>
       </c>
       <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
-      <c r="P87" t="n">
-        <v>0.8827</v>
-      </c>
+      <c r="P87" t="inlineStr"/>
       <c r="Q87" t="n">
-        <v>0.8827</v>
-      </c>
-      <c r="R87" t="inlineStr"/>
+        <v>0.8826000000000001</v>
+      </c>
+      <c r="R87" t="n">
+        <v>0.8826000000000001</v>
+      </c>
       <c r="S87" t="inlineStr"/>
       <c r="T87" t="inlineStr"/>
+      <c r="U87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -5433,21 +5542,22 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>The name 'Antecip.ICMS' closely relates to ICMS tax, but lacks sufficient distinctive sample overlap and has a lower numeric range compared to 'Base Reduzida ICMS'.</t>
+          <t>The name 'Antecip.ICMS' closely relates to the 'Base Reduzida ICMS' and has a high name confidence, despite limited numeric evidence.</t>
         </is>
       </c>
       <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr"/>
-      <c r="P88" t="n">
-        <v>0.75</v>
-      </c>
+      <c r="P88" t="inlineStr"/>
       <c r="Q88" t="n">
         <v>0.8724</v>
       </c>
-      <c r="R88" t="inlineStr"/>
+      <c r="R88" t="n">
+        <v>0.8724</v>
+      </c>
       <c r="S88" t="inlineStr"/>
       <c r="T88" t="inlineStr"/>
+      <c r="U88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -5464,7 +5574,7 @@
         <v>0.8306</v>
       </c>
       <c r="F89" t="n">
-        <v>0.8295</v>
+        <v>0.8294</v>
       </c>
       <c r="G89" t="n">
         <v>0.0012</v>
@@ -5487,21 +5597,22 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>All candidates have a tax-family conflict with ICAP and are not semantically compatible.</t>
+          <t>All candidates have a tax-family conflict with ICAP and ICMS, indicating incompatible semantic roles.</t>
         </is>
       </c>
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr"/>
-      <c r="P89" t="n">
-        <v>0</v>
-      </c>
+      <c r="P89" t="inlineStr"/>
       <c r="Q89" t="n">
         <v>0</v>
       </c>
-      <c r="R89" t="inlineStr"/>
+      <c r="R89" t="n">
+        <v>0</v>
+      </c>
       <c r="S89" t="inlineStr"/>
       <c r="T89" t="inlineStr"/>
+      <c r="U89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -5547,15 +5658,16 @@
       <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr"/>
-      <c r="P90" t="n">
-        <v>0</v>
-      </c>
+      <c r="P90" t="inlineStr"/>
       <c r="Q90" t="n">
+        <v>0</v>
+      </c>
+      <c r="R90" t="n">
         <v>0.8544</v>
       </c>
-      <c r="R90" t="inlineStr"/>
       <c r="S90" t="inlineStr"/>
       <c r="T90" t="inlineStr"/>
+      <c r="U90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -5595,21 +5707,22 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>All candidates have a semantic header conflict with the target column and provide no distinctive evidence.</t>
+          <t>All candidates have semantic header conflicts with the original column and provide no distinctive or valid data evidence.</t>
         </is>
       </c>
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr"/>
-      <c r="P91" t="n">
-        <v>0</v>
-      </c>
+      <c r="P91" t="inlineStr"/>
       <c r="Q91" t="n">
         <v>0</v>
       </c>
-      <c r="R91" t="inlineStr"/>
+      <c r="R91" t="n">
+        <v>0</v>
+      </c>
       <c r="S91" t="inlineStr"/>
       <c r="T91" t="inlineStr"/>
+      <c r="U91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -5655,15 +5768,16 @@
       <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr"/>
-      <c r="P92" t="n">
-        <v>0</v>
-      </c>
+      <c r="P92" t="inlineStr"/>
       <c r="Q92" t="n">
         <v>0</v>
       </c>
-      <c r="R92" t="inlineStr"/>
+      <c r="R92" t="n">
+        <v>0</v>
+      </c>
       <c r="S92" t="inlineStr"/>
       <c r="T92" t="inlineStr"/>
+      <c r="U92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -5680,7 +5794,7 @@
         <v>0.8462</v>
       </c>
       <c r="F93" t="n">
-        <v>0.8383</v>
+        <v>0.8384</v>
       </c>
       <c r="G93" t="n">
         <v>0.0078</v>
@@ -5703,21 +5817,22 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>All candidates have significant semantic header conflicts with the expected tax type.</t>
+          <t>All candidates exhibit semantic header conflicts with the expected tax type, and the evidence quality is insufficient.</t>
         </is>
       </c>
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr"/>
-      <c r="P93" t="n">
-        <v>0</v>
-      </c>
+      <c r="P93" t="inlineStr"/>
       <c r="Q93" t="n">
         <v>0</v>
       </c>
-      <c r="R93" t="inlineStr"/>
+      <c r="R93" t="n">
+        <v>0</v>
+      </c>
       <c r="S93" t="inlineStr"/>
       <c r="T93" t="inlineStr"/>
+      <c r="U93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -5737,19 +5852,19 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.8617</v>
+        <v>0.8618</v>
       </c>
       <c r="F94" t="n">
         <v>0.8565</v>
       </c>
       <c r="G94" t="n">
-        <v>0.0052</v>
+        <v>0.0053</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>0.8617</v>
+        <v>0.8618</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -5769,15 +5884,16 @@
       <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr"/>
-      <c r="P94" t="n">
-        <v>0</v>
-      </c>
+      <c r="P94" t="inlineStr"/>
       <c r="Q94" t="n">
         <v>0</v>
       </c>
-      <c r="R94" t="inlineStr"/>
+      <c r="R94" t="n">
+        <v>0</v>
+      </c>
       <c r="S94" t="inlineStr"/>
       <c r="T94" t="inlineStr"/>
+      <c r="U94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -5788,28 +5904,22 @@
           <t>Aliquota ICEP</t>
         </is>
       </c>
-      <c r="C95" t="n">
-        <v>245</v>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Alíquota CPR</t>
-        </is>
-      </c>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr"/>
       <c r="E95" t="n">
-        <v>0.8475</v>
+        <v>0.8618</v>
       </c>
       <c r="F95" t="n">
-        <v>0</v>
+        <v>0.8552</v>
       </c>
       <c r="G95" t="n">
-        <v>0.8475</v>
+        <v>0.0066</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>0.8475</v>
+        <v>0</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -5818,26 +5928,27 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>no_match</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr"/>
-      <c r="P95" t="n">
-        <v>0</v>
-      </c>
+      <c r="P95" t="inlineStr"/>
       <c r="Q95" t="n">
         <v>0</v>
       </c>
-      <c r="R95" t="inlineStr"/>
+      <c r="R95" t="n">
+        <v>0.8618</v>
+      </c>
       <c r="S95" t="inlineStr"/>
       <c r="T95" t="inlineStr"/>
+      <c r="U95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -5877,21 +5988,22 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>All candidates exhibit semantic header conflicts or lack relevant data evidence.</t>
+          <t>All candidates exhibit semantic header conflicts and lack distinctive row evidence.</t>
         </is>
       </c>
       <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr"/>
-      <c r="P96" t="n">
-        <v>0</v>
-      </c>
+      <c r="P96" t="inlineStr"/>
       <c r="Q96" t="n">
         <v>0</v>
       </c>
-      <c r="R96" t="inlineStr"/>
+      <c r="R96" t="n">
+        <v>0</v>
+      </c>
       <c r="S96" t="inlineStr"/>
       <c r="T96" t="inlineStr"/>
+      <c r="U96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -5943,15 +6055,16 @@
       <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr"/>
-      <c r="P97" t="n">
-        <v>0</v>
-      </c>
+      <c r="P97" t="inlineStr"/>
       <c r="Q97" t="n">
         <v>0</v>
       </c>
-      <c r="R97" t="inlineStr"/>
+      <c r="R97" t="n">
+        <v>0</v>
+      </c>
       <c r="S97" t="inlineStr"/>
       <c r="T97" t="inlineStr"/>
+      <c r="U97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -5965,13 +6078,13 @@
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="n">
-        <v>0.8421999999999999</v>
+        <v>0.8419</v>
       </c>
       <c r="F98" t="n">
-        <v>0.8409</v>
+        <v>0.8405</v>
       </c>
       <c r="G98" t="n">
-        <v>0.0013</v>
+        <v>0.0014</v>
       </c>
       <c r="H98" t="n">
         <v>0</v>
@@ -5991,21 +6104,22 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>All candidates exhibit semantic-role conflicts or lack distinctive evidence, making them unsuitable for mapping.</t>
+          <t>All candidates exhibit semantic header conflicts and lack distinctive non-zero evidence.</t>
         </is>
       </c>
       <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr"/>
       <c r="O98" t="inlineStr"/>
-      <c r="P98" t="n">
-        <v>0</v>
-      </c>
+      <c r="P98" t="inlineStr"/>
       <c r="Q98" t="n">
         <v>0</v>
       </c>
-      <c r="R98" t="inlineStr"/>
+      <c r="R98" t="n">
+        <v>0</v>
+      </c>
       <c r="S98" t="inlineStr"/>
       <c r="T98" t="inlineStr"/>
+      <c r="U98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -6019,7 +6133,7 @@
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="n">
-        <v>0.8389</v>
+        <v>0.839</v>
       </c>
       <c r="F99" t="n">
         <v>0.8258</v>
@@ -6045,21 +6159,22 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with ICMS, and the evidence quality is insufficient.</t>
+          <t>All candidates have a tax-family conflict with ICMS, indicating they do not semantically match the required ICSP type.</t>
         </is>
       </c>
       <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr"/>
       <c r="O99" t="inlineStr"/>
-      <c r="P99" t="n">
-        <v>0</v>
-      </c>
+      <c r="P99" t="inlineStr"/>
       <c r="Q99" t="n">
         <v>0</v>
       </c>
-      <c r="R99" t="inlineStr"/>
+      <c r="R99" t="n">
+        <v>0</v>
+      </c>
       <c r="S99" t="inlineStr"/>
       <c r="T99" t="inlineStr"/>
+      <c r="U99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -6079,19 +6194,19 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.8561</v>
+        <v>0.8562</v>
       </c>
       <c r="F100" t="n">
-        <v>0.849</v>
+        <v>0.8489</v>
       </c>
       <c r="G100" t="n">
-        <v>0.0072</v>
+        <v>0.0073</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>0.8561</v>
+        <v>0.8562</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -6111,15 +6226,16 @@
       <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr"/>
       <c r="O100" t="inlineStr"/>
-      <c r="P100" t="n">
-        <v>0</v>
-      </c>
+      <c r="P100" t="inlineStr"/>
       <c r="Q100" t="n">
         <v>0</v>
       </c>
-      <c r="R100" t="inlineStr"/>
+      <c r="R100" t="n">
+        <v>0</v>
+      </c>
       <c r="S100" t="inlineStr"/>
       <c r="T100" t="inlineStr"/>
+      <c r="U100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -6139,19 +6255,19 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.8712</v>
+        <v>0.8713</v>
       </c>
       <c r="F101" t="n">
         <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>0.8712</v>
+        <v>0.8713</v>
       </c>
       <c r="H101" t="n">
         <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>0.8712</v>
+        <v>0.8713</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -6171,15 +6287,16 @@
       <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr"/>
       <c r="O101" t="inlineStr"/>
-      <c r="P101" t="n">
-        <v>0</v>
-      </c>
+      <c r="P101" t="inlineStr"/>
       <c r="Q101" t="n">
         <v>0</v>
       </c>
-      <c r="R101" t="inlineStr"/>
+      <c r="R101" t="n">
+        <v>0</v>
+      </c>
       <c r="S101" t="inlineStr"/>
       <c r="T101" t="inlineStr"/>
+      <c r="U101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -6225,21 +6342,22 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
+          <t>The candidate 'Vlr Isen ICM' has a high name confidence and no semantic header conflict, despite the weak data evidence.</t>
         </is>
       </c>
       <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr"/>
       <c r="O102" t="inlineStr"/>
-      <c r="P102" t="n">
-        <v>0</v>
-      </c>
+      <c r="P102" t="inlineStr"/>
       <c r="Q102" t="n">
         <v>0</v>
       </c>
-      <c r="R102" t="inlineStr"/>
+      <c r="R102" t="n">
+        <v>0.8829</v>
+      </c>
       <c r="S102" t="inlineStr"/>
       <c r="T102" t="inlineStr"/>
+      <c r="U102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -6253,13 +6371,13 @@
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="n">
-        <v>0.8487</v>
+        <v>0.8486</v>
       </c>
       <c r="F103" t="n">
         <v>0</v>
       </c>
       <c r="G103" t="n">
-        <v>0.8487</v>
+        <v>0.8486</v>
       </c>
       <c r="H103" t="n">
         <v>0</v>
@@ -6285,15 +6403,16 @@
       <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr"/>
       <c r="O103" t="inlineStr"/>
-      <c r="P103" t="n">
-        <v>0</v>
-      </c>
+      <c r="P103" t="inlineStr"/>
       <c r="Q103" t="n">
         <v>0</v>
       </c>
-      <c r="R103" t="inlineStr"/>
+      <c r="R103" t="n">
+        <v>0</v>
+      </c>
       <c r="S103" t="inlineStr"/>
       <c r="T103" t="inlineStr"/>
+      <c r="U103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -6345,15 +6464,16 @@
       <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr"/>
       <c r="O104" t="inlineStr"/>
-      <c r="P104" t="n">
-        <v>0</v>
-      </c>
+      <c r="P104" t="inlineStr"/>
       <c r="Q104" t="n">
         <v>0</v>
       </c>
-      <c r="R104" t="inlineStr"/>
+      <c r="R104" t="n">
+        <v>0</v>
+      </c>
       <c r="S104" t="inlineStr"/>
       <c r="T104" t="inlineStr"/>
+      <c r="U104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -6367,7 +6487,7 @@
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="n">
-        <v>0.8404</v>
+        <v>0.8405</v>
       </c>
       <c r="F105" t="n">
         <v>0.84</v>
@@ -6393,21 +6513,22 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>All candidates exhibit semantic conflicts and contain only zeros, providing no valid mapping evidence.</t>
+          <t>All candidates exhibit semantic header conflicts and lack distinctive row evidence.</t>
         </is>
       </c>
       <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr"/>
-      <c r="P105" t="n">
-        <v>0</v>
-      </c>
+      <c r="P105" t="inlineStr"/>
       <c r="Q105" t="n">
         <v>0</v>
       </c>
-      <c r="R105" t="inlineStr"/>
+      <c r="R105" t="n">
+        <v>0</v>
+      </c>
       <c r="S105" t="inlineStr"/>
       <c r="T105" t="inlineStr"/>
+      <c r="U105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -6453,15 +6574,16 @@
       <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
       <c r="O106" t="inlineStr"/>
-      <c r="P106" t="n">
-        <v>0</v>
-      </c>
+      <c r="P106" t="inlineStr"/>
       <c r="Q106" t="n">
         <v>0</v>
       </c>
-      <c r="R106" t="inlineStr"/>
+      <c r="R106" t="n">
+        <v>0</v>
+      </c>
       <c r="S106" t="inlineStr"/>
       <c r="T106" t="inlineStr"/>
+      <c r="U106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -6478,10 +6600,10 @@
         <v>0.8474</v>
       </c>
       <c r="F107" t="n">
-        <v>0.8611</v>
+        <v>0</v>
       </c>
       <c r="G107" t="n">
-        <v>-0.0136</v>
+        <v>0.8474</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -6501,21 +6623,22 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>All candidates have semantic-role conflicts and insufficient distinctive data evidence.</t>
         </is>
       </c>
       <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr"/>
-      <c r="P107" t="n">
-        <v>0.997</v>
-      </c>
+      <c r="P107" t="inlineStr"/>
       <c r="Q107" t="n">
-        <v>0.8474</v>
-      </c>
-      <c r="R107" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="R107" t="n">
+        <v>0</v>
+      </c>
       <c r="S107" t="inlineStr"/>
       <c r="T107" t="inlineStr"/>
+      <c r="U107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -6538,7 +6661,7 @@
         <v>0.856</v>
       </c>
       <c r="F108" t="n">
-        <v>0.8835</v>
+        <v>0.8836000000000001</v>
       </c>
       <c r="G108" t="n">
         <v>-0.0276</v>
@@ -6561,21 +6684,22 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>The candidate 'Difal ICMS' has a relevant name match and a profile indicating mixed numeric values, unlike the all-zero profile of the model column.</t>
+          <t>The candidate 'Difal ICMS' does not match the expected role of 'Aliquota DIF_ALIQ' as it represents a different tax type.</t>
         </is>
       </c>
       <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr"/>
       <c r="O108" t="inlineStr"/>
-      <c r="P108" t="n">
-        <v>0</v>
-      </c>
+      <c r="P108" t="inlineStr"/>
       <c r="Q108" t="n">
+        <v>0</v>
+      </c>
+      <c r="R108" t="n">
         <v>0.856</v>
       </c>
-      <c r="R108" t="inlineStr"/>
       <c r="S108" t="inlineStr"/>
       <c r="T108" t="inlineStr"/>
+      <c r="U108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -6592,10 +6716,10 @@
         <v>0.84</v>
       </c>
       <c r="F109" t="n">
-        <v>0.8522999999999999</v>
+        <v>0.8637</v>
       </c>
       <c r="G109" t="n">
-        <v>-0.0123</v>
+        <v>-0.0236</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -6621,15 +6745,16 @@
       <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr"/>
-      <c r="P109" t="n">
-        <v>0.84</v>
-      </c>
+      <c r="P109" t="inlineStr"/>
       <c r="Q109" t="n">
         <v>0.84</v>
       </c>
-      <c r="R109" t="inlineStr"/>
+      <c r="R109" t="n">
+        <v>0.84</v>
+      </c>
       <c r="S109" t="inlineStr"/>
       <c r="T109" t="inlineStr"/>
+      <c r="U109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -6641,27 +6766,27 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>99</v>
+        <v>247</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Aliq. COFINS</t>
+          <t>Difal ICMS</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.8598</v>
+        <v>0.8536</v>
       </c>
       <c r="F110" t="n">
-        <v>0.8559</v>
+        <v>0</v>
       </c>
       <c r="G110" t="n">
-        <v>0.0039</v>
+        <v>0.8536</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
       </c>
       <c r="I110" t="n">
-        <v>0.8598</v>
+        <v>0.8536</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
@@ -6675,21 +6800,22 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
+          <t>The strongest header candidate has weak row evidence; preserve the name-based mapping for review instead of replacing it with a merely similar value shape.</t>
         </is>
       </c>
       <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
       <c r="O110" t="inlineStr"/>
-      <c r="P110" t="n">
-        <v>0</v>
-      </c>
+      <c r="P110" t="inlineStr"/>
       <c r="Q110" t="n">
         <v>0</v>
       </c>
-      <c r="R110" t="inlineStr"/>
+      <c r="R110" t="n">
+        <v>0</v>
+      </c>
       <c r="S110" t="inlineStr"/>
       <c r="T110" t="inlineStr"/>
+      <c r="U110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -6700,14 +6826,8 @@
           <t>Outras DIF_ALIQ</t>
         </is>
       </c>
-      <c r="C111" t="n">
-        <v>99</v>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>Aliq. COFINS</t>
-        </is>
-      </c>
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" t="inlineStr"/>
       <c r="E111" t="n">
         <v>0.8688</v>
       </c>
@@ -6721,7 +6841,7 @@
         <v>0</v>
       </c>
       <c r="I111" t="n">
-        <v>0.8688</v>
+        <v>0</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
@@ -6730,26 +6850,27 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>no_match</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>The candidate 'Aliq. COFINS' has a significant zero fraction and does not align with the all-zero evidence of 'Outras DIF_ALIQ'.</t>
+          <t>All candidates exhibit semantic-role conflicts and lack distinctive evidence.</t>
         </is>
       </c>
       <c r="M111" t="inlineStr"/>
       <c r="N111" t="inlineStr"/>
       <c r="O111" t="inlineStr"/>
-      <c r="P111" t="n">
-        <v>0</v>
-      </c>
+      <c r="P111" t="inlineStr"/>
       <c r="Q111" t="n">
-        <v>0.8688</v>
-      </c>
-      <c r="R111" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="R111" t="n">
+        <v>0</v>
+      </c>
       <c r="S111" t="inlineStr"/>
       <c r="T111" t="inlineStr"/>
+      <c r="U111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -6760,28 +6881,22 @@
           <t>Base Reduzida DIF_ALIQ</t>
         </is>
       </c>
-      <c r="C112" t="n">
-        <v>99</v>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>Aliq. COFINS</t>
-        </is>
-      </c>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="inlineStr"/>
       <c r="E112" t="n">
-        <v>0.8363</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="F112" t="n">
-        <v>0.8308</v>
+        <v>0</v>
       </c>
       <c r="G112" t="n">
-        <v>0.0055</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
       </c>
       <c r="I112" t="n">
-        <v>0.8363</v>
+        <v>0</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
@@ -6790,26 +6905,27 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>no_match</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
+          <t>All candidates exhibit semantic-role conflicts with the target column, indicating incompatible mappings.</t>
         </is>
       </c>
       <c r="M112" t="inlineStr"/>
       <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr"/>
-      <c r="P112" t="n">
-        <v>0</v>
-      </c>
+      <c r="P112" t="inlineStr"/>
       <c r="Q112" t="n">
         <v>0</v>
       </c>
-      <c r="R112" t="inlineStr"/>
+      <c r="R112" t="n">
+        <v>0</v>
+      </c>
       <c r="S112" t="inlineStr"/>
       <c r="T112" t="inlineStr"/>
+      <c r="U112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -6855,21 +6971,22 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>The candidate 'Base FCP Cmp' has a high name confidence but all values are zero, indicating no valid mapping.</t>
+          <t>The candidate 'Base FCP Cmp' has a high name confidence and no semantic header conflict, despite all-zero evidence.</t>
         </is>
       </c>
       <c r="M113" t="inlineStr"/>
       <c r="N113" t="inlineStr"/>
       <c r="O113" t="inlineStr"/>
-      <c r="P113" t="n">
-        <v>0</v>
-      </c>
+      <c r="P113" t="inlineStr"/>
       <c r="Q113" t="n">
+        <v>0</v>
+      </c>
+      <c r="R113" t="n">
         <v>0.893</v>
       </c>
-      <c r="R113" t="inlineStr"/>
       <c r="S113" t="inlineStr"/>
       <c r="T113" t="inlineStr"/>
+      <c r="U113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -6915,21 +7032,22 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>The candidate 'Aliq FECP' has a high name confidence and matches the semantic role, despite all values being zero.</t>
+          <t>The candidate 'Aliq FECP' closely matches the semantic role of 'Aliquota ICMS_FECP' with high name confidence, despite all values being zero.</t>
         </is>
       </c>
       <c r="M114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
       <c r="O114" t="inlineStr"/>
-      <c r="P114" t="n">
-        <v>0</v>
-      </c>
+      <c r="P114" t="inlineStr"/>
       <c r="Q114" t="n">
         <v>0.8905999999999999</v>
       </c>
-      <c r="R114" t="inlineStr"/>
+      <c r="R114" t="n">
+        <v>0.8905999999999999</v>
+      </c>
       <c r="S114" t="inlineStr"/>
       <c r="T114" t="inlineStr"/>
+      <c r="U114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -6975,21 +7093,22 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>The name 'Vlr ICMS Com' is the closest match to 'Valor ICMS_FECP' and has a higher unique count and informative sample values.</t>
+          <t>The name 'Vlr ICMS Com' closely relates to the tax value context of 'Valor ICMS_FECP', and it has a higher unique count and informative evidence.</t>
         </is>
       </c>
       <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr"/>
       <c r="O115" t="inlineStr"/>
-      <c r="P115" t="n">
-        <v>0.8948</v>
-      </c>
+      <c r="P115" t="inlineStr"/>
       <c r="Q115" t="n">
         <v>0.8948</v>
       </c>
-      <c r="R115" t="inlineStr"/>
+      <c r="R115" t="n">
+        <v>0.8948</v>
+      </c>
       <c r="S115" t="inlineStr"/>
       <c r="T115" t="inlineStr"/>
+      <c r="U115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -7009,7 +7128,7 @@
         <v>0.8747</v>
       </c>
       <c r="G116" t="n">
-        <v>-0.0223</v>
+        <v>-0.0224</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
@@ -7035,15 +7154,16 @@
       <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
       <c r="O116" t="inlineStr"/>
-      <c r="P116" t="n">
-        <v>0.8522999999999999</v>
-      </c>
+      <c r="P116" t="inlineStr"/>
       <c r="Q116" t="n">
         <v>0.8522999999999999</v>
       </c>
-      <c r="R116" t="inlineStr"/>
+      <c r="R116" t="n">
+        <v>0.8522999999999999</v>
+      </c>
       <c r="S116" t="inlineStr"/>
       <c r="T116" t="inlineStr"/>
+      <c r="U116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -7063,19 +7183,19 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0.8759</v>
+        <v>0.8747</v>
       </c>
       <c r="F117" t="n">
-        <v>0.8731</v>
+        <v>0.872</v>
       </c>
       <c r="G117" t="n">
-        <v>0.0028</v>
+        <v>0.0026</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
       </c>
       <c r="I117" t="n">
-        <v>0.8759</v>
+        <v>0.8747</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -7089,21 +7209,22 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>The candidate has a semantic header conflict and all-zero evidence, indicating it does not support a mapping.</t>
+          <t>The name 'BC ICMS Efet' aligns with the tax context, and there is no semantic conflict.</t>
         </is>
       </c>
       <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr"/>
-      <c r="P117" t="n">
-        <v>0</v>
-      </c>
+      <c r="P117" t="inlineStr"/>
       <c r="Q117" t="n">
-        <v>0.8759</v>
-      </c>
-      <c r="R117" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.8747</v>
+      </c>
       <c r="S117" t="inlineStr"/>
       <c r="T117" t="inlineStr"/>
+      <c r="U117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -7123,7 +7244,7 @@
         <v>0.851</v>
       </c>
       <c r="G118" t="n">
-        <v>0.0098</v>
+        <v>0.0097</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
@@ -7143,21 +7264,22 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>All candidates exhibit semantic-role conflicts or lack distinctive evidence.</t>
+          <t>All candidates exhibit semantic-role conflicts and lack distinctive row evidence.</t>
         </is>
       </c>
       <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr"/>
       <c r="O118" t="inlineStr"/>
-      <c r="P118" t="n">
-        <v>0</v>
-      </c>
+      <c r="P118" t="inlineStr"/>
       <c r="Q118" t="n">
         <v>0</v>
       </c>
-      <c r="R118" t="inlineStr"/>
+      <c r="R118" t="n">
+        <v>0</v>
+      </c>
       <c r="S118" t="inlineStr"/>
       <c r="T118" t="inlineStr"/>
+      <c r="U118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -7203,21 +7325,22 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>The candidate 'IPI Pauta' has a high name confidence but lacks distinctive sample evidence, and the all-zero profile indicates no valid data.</t>
+          <t>The candidate 'IPI Pauta' has a high name confidence but lacks distinctive data evidence, making it a weak match.</t>
         </is>
       </c>
       <c r="M119" t="inlineStr"/>
       <c r="N119" t="inlineStr"/>
       <c r="O119" t="inlineStr"/>
-      <c r="P119" t="n">
-        <v>0</v>
-      </c>
+      <c r="P119" t="inlineStr"/>
       <c r="Q119" t="n">
+        <v>0</v>
+      </c>
+      <c r="R119" t="n">
         <v>0.8718</v>
       </c>
-      <c r="R119" t="inlineStr"/>
       <c r="S119" t="inlineStr"/>
       <c r="T119" t="inlineStr"/>
+      <c r="U119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -7237,19 +7360,19 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.8935</v>
+        <v>0.8934</v>
       </c>
       <c r="F120" t="n">
         <v>0.8421</v>
       </c>
       <c r="G120" t="n">
-        <v>0.0514</v>
+        <v>0.0513</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
       </c>
       <c r="I120" t="n">
-        <v>0.8935</v>
+        <v>0.8934</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
@@ -7269,15 +7392,16 @@
       <c r="M120" t="inlineStr"/>
       <c r="N120" t="inlineStr"/>
       <c r="O120" t="inlineStr"/>
-      <c r="P120" t="n">
-        <v>0.8358</v>
-      </c>
+      <c r="P120" t="inlineStr"/>
       <c r="Q120" t="n">
         <v>0.8358</v>
       </c>
-      <c r="R120" t="inlineStr"/>
+      <c r="R120" t="n">
+        <v>0.8358</v>
+      </c>
       <c r="S120" t="inlineStr"/>
       <c r="T120" t="inlineStr"/>
+      <c r="U120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -7329,15 +7453,16 @@
       <c r="M121" t="inlineStr"/>
       <c r="N121" t="inlineStr"/>
       <c r="O121" t="inlineStr"/>
-      <c r="P121" t="n">
-        <v>0.8784999999999999</v>
-      </c>
+      <c r="P121" t="inlineStr"/>
       <c r="Q121" t="n">
         <v>0.8784999999999999</v>
       </c>
-      <c r="R121" t="inlineStr"/>
+      <c r="R121" t="n">
+        <v>0.8784999999999999</v>
+      </c>
       <c r="S121" t="inlineStr"/>
       <c r="T121" t="inlineStr"/>
+      <c r="U121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -7363,7 +7488,7 @@
         <v>0.8625</v>
       </c>
       <c r="G122" t="n">
-        <v>0.0248</v>
+        <v>0.0247</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
@@ -7383,21 +7508,22 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>The candidate 'Cofins Pauta' has a high name confidence but all values are zero, indicating no valid mapping.</t>
+          <t>The candidate 'Cofins Pauta' has a high name confidence but all values are zero, indicating no actual data.</t>
         </is>
       </c>
       <c r="M122" t="inlineStr"/>
       <c r="N122" t="inlineStr"/>
       <c r="O122" t="inlineStr"/>
-      <c r="P122" t="n">
-        <v>0</v>
-      </c>
+      <c r="P122" t="inlineStr"/>
       <c r="Q122" t="n">
+        <v>0</v>
+      </c>
+      <c r="R122" t="n">
         <v>0.8872</v>
       </c>
-      <c r="R122" t="inlineStr"/>
       <c r="S122" t="inlineStr"/>
       <c r="T122" t="inlineStr"/>
+      <c r="U122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -7417,19 +7543,19 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0.856</v>
+        <v>0.8559</v>
       </c>
       <c r="F123" t="n">
         <v>0</v>
       </c>
       <c r="G123" t="n">
-        <v>0.856</v>
+        <v>0.8559</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
       </c>
       <c r="I123" t="n">
-        <v>0.856</v>
+        <v>0.8559</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
@@ -7449,15 +7575,16 @@
       <c r="M123" t="inlineStr"/>
       <c r="N123" t="inlineStr"/>
       <c r="O123" t="inlineStr"/>
-      <c r="P123" t="n">
-        <v>0</v>
-      </c>
+      <c r="P123" t="inlineStr"/>
       <c r="Q123" t="n">
         <v>0</v>
       </c>
-      <c r="R123" t="inlineStr"/>
+      <c r="R123" t="n">
+        <v>0</v>
+      </c>
       <c r="S123" t="inlineStr"/>
       <c r="T123" t="inlineStr"/>
+      <c r="U123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -7471,10 +7598,10 @@
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="n">
-        <v>0.8848</v>
+        <v>0.8847</v>
       </c>
       <c r="F124" t="n">
-        <v>0.8729</v>
+        <v>0.8728</v>
       </c>
       <c r="G124" t="n">
         <v>0.0119</v>
@@ -7497,21 +7624,22 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>All candidates have semantic-role conflicts or all-zero evidence, making them unsuitable for mapping.</t>
+          <t>All candidates exhibit semantic-role conflicts or all-zero evidence, indicating no suitable mapping.</t>
         </is>
       </c>
       <c r="M124" t="inlineStr"/>
       <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr"/>
-      <c r="P124" t="n">
-        <v>0</v>
-      </c>
+      <c r="P124" t="inlineStr"/>
       <c r="Q124" t="n">
-        <v>0.8848</v>
-      </c>
-      <c r="R124" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0</v>
+      </c>
       <c r="S124" t="inlineStr"/>
       <c r="T124" t="inlineStr"/>
+      <c r="U124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -7531,7 +7659,7 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>0.8868</v>
+        <v>0.8867</v>
       </c>
       <c r="F125" t="n">
         <v>0.8735000000000001</v>
@@ -7543,7 +7671,7 @@
         <v>0</v>
       </c>
       <c r="I125" t="n">
-        <v>0.8868</v>
+        <v>0.8867</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
@@ -7557,21 +7685,22 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>The header 'PIS Pauta' is closely related to 'Outras PIS', but both have all-zero evidence, making the mapping uncertain.</t>
+          <t>The name 'PIS Pauta' closely aligns with 'Outras PIS', despite both having all-zero evidence.</t>
         </is>
       </c>
       <c r="M125" t="inlineStr"/>
       <c r="N125" t="inlineStr"/>
       <c r="O125" t="inlineStr"/>
-      <c r="P125" t="n">
-        <v>0</v>
-      </c>
+      <c r="P125" t="inlineStr"/>
       <c r="Q125" t="n">
-        <v>0.8868</v>
-      </c>
-      <c r="R125" t="inlineStr"/>
+        <v>0.8867</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.8867</v>
+      </c>
       <c r="S125" t="inlineStr"/>
       <c r="T125" t="inlineStr"/>
+      <c r="U125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -7582,28 +7711,22 @@
           <t>Tipo de Imposto PIS</t>
         </is>
       </c>
-      <c r="C126" t="n">
-        <v>146</v>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>Sit.Trib.PIS</t>
-        </is>
-      </c>
+      <c r="C126" t="inlineStr"/>
+      <c r="D126" t="inlineStr"/>
       <c r="E126" t="n">
-        <v>0.886</v>
+        <v>0.8502</v>
       </c>
       <c r="F126" t="n">
         <v>0.894</v>
       </c>
       <c r="G126" t="n">
-        <v>-0.0081</v>
+        <v>-0.0438</v>
       </c>
       <c r="H126" t="n">
-        <v>0.175</v>
+        <v>0.0601</v>
       </c>
       <c r="I126" t="n">
-        <v>0.886</v>
+        <v>0</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
@@ -7612,26 +7735,27 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>no_match</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>The name 'Sit.Trib.PIS' closely aligns with 'Tipo de Imposto PIS' and has a strong name confidence, despite some numeric content.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M126" t="inlineStr"/>
       <c r="N126" t="inlineStr"/>
       <c r="O126" t="inlineStr"/>
-      <c r="P126" t="n">
-        <v>0.886</v>
-      </c>
+      <c r="P126" t="inlineStr"/>
       <c r="Q126" t="n">
-        <v>0.886</v>
-      </c>
-      <c r="R126" t="inlineStr"/>
+        <v>0.8502</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.8502</v>
+      </c>
       <c r="S126" t="inlineStr"/>
       <c r="T126" t="inlineStr"/>
+      <c r="U126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -7645,7 +7769,7 @@
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="n">
-        <v>0.8999</v>
+        <v>0.9</v>
       </c>
       <c r="F127" t="n">
         <v>0.8962</v>
@@ -7677,15 +7801,16 @@
       <c r="M127" t="inlineStr"/>
       <c r="N127" t="inlineStr"/>
       <c r="O127" t="inlineStr"/>
-      <c r="P127" t="n">
-        <v>0</v>
-      </c>
+      <c r="P127" t="inlineStr"/>
       <c r="Q127" t="n">
-        <v>0.8999</v>
-      </c>
-      <c r="R127" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.9</v>
+      </c>
       <c r="S127" t="inlineStr"/>
       <c r="T127" t="inlineStr"/>
+      <c r="U127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -7731,21 +7856,22 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>The candidate 'Recolhe ISS' has a high name confidence and relevant content indicating a tax type related to ISS.</t>
+          <t>The candidate 'Recolhe ISS' has the highest name confidence and aligns with the tax type, despite the lack of distinctive sample overlap.</t>
         </is>
       </c>
       <c r="M128" t="inlineStr"/>
       <c r="N128" t="inlineStr"/>
       <c r="O128" t="inlineStr"/>
-      <c r="P128" t="n">
-        <v>0.882</v>
-      </c>
+      <c r="P128" t="inlineStr"/>
       <c r="Q128" t="n">
         <v>0.882</v>
       </c>
-      <c r="R128" t="inlineStr"/>
+      <c r="R128" t="n">
+        <v>0.882</v>
+      </c>
       <c r="S128" t="inlineStr"/>
       <c r="T128" t="inlineStr"/>
+      <c r="U128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -7768,7 +7894,7 @@
         <v>0.8771</v>
       </c>
       <c r="F129" t="n">
-        <v>0.8797</v>
+        <v>0.8798</v>
       </c>
       <c r="G129" t="n">
         <v>-0.0027</v>
@@ -7791,21 +7917,22 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>The name 'ISS Mat.' closely aligns with 'Base ISS' and both have similar numeric profiles, despite all values being zero.</t>
+          <t>The name 'ISS Mat.' closely aligns with 'Base ISS' and both have identical numeric profiles, despite all values being zero.</t>
         </is>
       </c>
       <c r="M129" t="inlineStr"/>
       <c r="N129" t="inlineStr"/>
       <c r="O129" t="inlineStr"/>
-      <c r="P129" t="n">
-        <v>0.8771</v>
-      </c>
+      <c r="P129" t="inlineStr"/>
       <c r="Q129" t="n">
         <v>0.8771</v>
       </c>
-      <c r="R129" t="inlineStr"/>
+      <c r="R129" t="n">
+        <v>0.8771</v>
+      </c>
       <c r="S129" t="inlineStr"/>
       <c r="T129" t="inlineStr"/>
+      <c r="U129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -7825,19 +7952,19 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>0.8939</v>
+        <v>0.8938</v>
       </c>
       <c r="F130" t="n">
         <v>0.8915999999999999</v>
       </c>
       <c r="G130" t="n">
-        <v>0.0023</v>
+        <v>0.0022</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
       </c>
       <c r="I130" t="n">
-        <v>0.8939</v>
+        <v>0.8938</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
@@ -7851,21 +7978,22 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>The candidate 'Alq.ISS CPM' has a high name confidence and matches the expected integer type, despite all values being zero.</t>
+          <t>Both columns represent ISS tax rates, but all values are zero, limiting evidence for a strong mapping.</t>
         </is>
       </c>
       <c r="M130" t="inlineStr"/>
       <c r="N130" t="inlineStr"/>
       <c r="O130" t="inlineStr"/>
-      <c r="P130" t="n">
-        <v>0</v>
-      </c>
+      <c r="P130" t="inlineStr"/>
       <c r="Q130" t="n">
-        <v>0.8939</v>
-      </c>
-      <c r="R130" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.8938</v>
+      </c>
       <c r="S130" t="inlineStr"/>
       <c r="T130" t="inlineStr"/>
+      <c r="U130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -7917,15 +8045,16 @@
       <c r="M131" t="inlineStr"/>
       <c r="N131" t="inlineStr"/>
       <c r="O131" t="inlineStr"/>
-      <c r="P131" t="n">
-        <v>0.8663</v>
-      </c>
+      <c r="P131" t="inlineStr"/>
       <c r="Q131" t="n">
         <v>0.8663</v>
       </c>
-      <c r="R131" t="inlineStr"/>
+      <c r="R131" t="n">
+        <v>0.8663</v>
+      </c>
       <c r="S131" t="inlineStr"/>
       <c r="T131" t="inlineStr"/>
+      <c r="U131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -7936,22 +8065,28 @@
           <t>Isentas ISS</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr"/>
-      <c r="D132" t="inlineStr"/>
+      <c r="C132" t="n">
+        <v>122</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>ISS Mat.</t>
+        </is>
+      </c>
       <c r="E132" t="n">
+        <v>0.8718</v>
+      </c>
+      <c r="F132" t="n">
         <v>0.8815</v>
       </c>
-      <c r="F132" t="n">
-        <v>0.8814</v>
-      </c>
       <c r="G132" t="n">
-        <v>0.0001</v>
+        <v>-0.0097</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
       </c>
       <c r="I132" t="n">
-        <v>0</v>
+        <v>0.8718</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
@@ -7960,26 +8095,27 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>review</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>All candidates have significant semantic conflicts or lack relevant data evidence.</t>
+          <t>The header 'ISS Mat.' closely matches the tax exemption context of 'Isentas ISS' despite both having all-zero values.</t>
         </is>
       </c>
       <c r="M132" t="inlineStr"/>
       <c r="N132" t="inlineStr"/>
       <c r="O132" t="inlineStr"/>
-      <c r="P132" t="n">
-        <v>0</v>
-      </c>
+      <c r="P132" t="inlineStr"/>
       <c r="Q132" t="n">
-        <v>0</v>
-      </c>
-      <c r="R132" t="inlineStr"/>
+        <v>0.8718</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.8718</v>
+      </c>
       <c r="S132" t="inlineStr"/>
       <c r="T132" t="inlineStr"/>
+      <c r="U132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -7990,13 +8126,19 @@
           <t>Outras ISS</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr"/>
-      <c r="D133" t="inlineStr"/>
+      <c r="C133" t="n">
+        <v>115</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Recolhe ISS</t>
+        </is>
+      </c>
       <c r="E133" t="n">
-        <v>0.892</v>
+        <v>0.8919</v>
       </c>
       <c r="F133" t="n">
-        <v>0.8756</v>
+        <v>0.8754999999999999</v>
       </c>
       <c r="G133" t="n">
         <v>0.0164</v>
@@ -8005,7 +8147,7 @@
         <v>0</v>
       </c>
       <c r="I133" t="n">
-        <v>0</v>
+        <v>0.8919</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -8014,26 +8156,27 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>review</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>All candidates have significant semantic conflicts or lack relevant data evidence.</t>
+          <t>The candidate 'Recolhe ISS' has a high name confidence but lacks any numeric evidence, making it incompatible with 'Outras ISS'.</t>
         </is>
       </c>
       <c r="M133" t="inlineStr"/>
       <c r="N133" t="inlineStr"/>
       <c r="O133" t="inlineStr"/>
-      <c r="P133" t="n">
-        <v>0</v>
-      </c>
+      <c r="P133" t="inlineStr"/>
       <c r="Q133" t="n">
         <v>0</v>
       </c>
-      <c r="R133" t="inlineStr"/>
+      <c r="R133" t="n">
+        <v>0.8919</v>
+      </c>
       <c r="S133" t="inlineStr"/>
       <c r="T133" t="inlineStr"/>
+      <c r="U133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -8047,13 +8190,13 @@
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="n">
-        <v>0.8449</v>
+        <v>0.8457</v>
       </c>
       <c r="F134" t="n">
-        <v>0.8769</v>
+        <v>0.8774</v>
       </c>
       <c r="G134" t="n">
-        <v>-0.032</v>
+        <v>-0.0317</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -8079,15 +8222,16 @@
       <c r="M134" t="inlineStr"/>
       <c r="N134" t="inlineStr"/>
       <c r="O134" t="inlineStr"/>
-      <c r="P134" t="n">
-        <v>0.8449</v>
-      </c>
+      <c r="P134" t="inlineStr"/>
       <c r="Q134" t="n">
-        <v>0.8449</v>
-      </c>
-      <c r="R134" t="inlineStr"/>
+        <v>0.8457</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.8457</v>
+      </c>
       <c r="S134" t="inlineStr"/>
       <c r="T134" t="inlineStr"/>
+      <c r="U134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -8139,15 +8283,16 @@
       <c r="M135" t="inlineStr"/>
       <c r="N135" t="inlineStr"/>
       <c r="O135" t="inlineStr"/>
-      <c r="P135" t="n">
-        <v>0.9431</v>
-      </c>
+      <c r="P135" t="inlineStr"/>
       <c r="Q135" t="n">
         <v>0.9431</v>
       </c>
-      <c r="R135" t="inlineStr"/>
+      <c r="R135" t="n">
+        <v>0.9431</v>
+      </c>
       <c r="S135" t="inlineStr"/>
       <c r="T135" t="inlineStr"/>
+      <c r="U135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -8193,21 +8338,22 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>The candidate 'Aliq. FCP ST' has a high name confidence and no semantic header conflict, aligning closely with the tax qualifier role.</t>
+          <t>The candidate 'Aliq. FCP ST' has a high name confidence and no semantic header conflict.</t>
         </is>
       </c>
       <c r="M136" t="inlineStr"/>
       <c r="N136" t="inlineStr"/>
       <c r="O136" t="inlineStr"/>
-      <c r="P136" t="n">
-        <v>0.8806</v>
-      </c>
+      <c r="P136" t="inlineStr"/>
       <c r="Q136" t="n">
         <v>0.8806</v>
       </c>
-      <c r="R136" t="inlineStr"/>
+      <c r="R136" t="n">
+        <v>0.8806</v>
+      </c>
       <c r="S136" t="inlineStr"/>
       <c r="T136" t="inlineStr"/>
+      <c r="U136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -8247,21 +8393,22 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>All candidates have a semantic header conflict and provide no distinctive row evidence.</t>
+          <t>All candidates exhibit a tax-qualifier conflict and contain only zeros, providing no valid mapping evidence.</t>
         </is>
       </c>
       <c r="M137" t="inlineStr"/>
       <c r="N137" t="inlineStr"/>
       <c r="O137" t="inlineStr"/>
-      <c r="P137" t="n">
-        <v>0</v>
-      </c>
+      <c r="P137" t="inlineStr"/>
       <c r="Q137" t="n">
         <v>0</v>
       </c>
-      <c r="R137" t="inlineStr"/>
+      <c r="R137" t="n">
+        <v>0</v>
+      </c>
       <c r="S137" t="inlineStr"/>
       <c r="T137" t="inlineStr"/>
+      <c r="U137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -8307,21 +8454,22 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>The candidate 'V.FECP-ST/MT' has a high name confidence and matches the tax type, despite all values being zero.</t>
+          <t>The candidate 'V.FECP-ST/MT' has a high name confidence and no semantic conflicts, but both columns contain only zeros, limiting data evidence.</t>
         </is>
       </c>
       <c r="M138" t="inlineStr"/>
       <c r="N138" t="inlineStr"/>
       <c r="O138" t="inlineStr"/>
-      <c r="P138" t="n">
-        <v>0</v>
-      </c>
+      <c r="P138" t="inlineStr"/>
       <c r="Q138" t="n">
+        <v>0</v>
+      </c>
+      <c r="R138" t="n">
         <v>0.8653999999999999</v>
       </c>
-      <c r="R138" t="inlineStr"/>
       <c r="S138" t="inlineStr"/>
       <c r="T138" t="inlineStr"/>
+      <c r="U138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -8332,14 +8480,8 @@
           <t>Outras FECP_ST</t>
         </is>
       </c>
-      <c r="C139" t="n">
-        <v>214</v>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>V.FECP-ST/MT</t>
-        </is>
-      </c>
+      <c r="C139" t="inlineStr"/>
+      <c r="D139" t="inlineStr"/>
       <c r="E139" t="n">
         <v>0.886</v>
       </c>
@@ -8353,7 +8495,7 @@
         <v>0</v>
       </c>
       <c r="I139" t="n">
-        <v>0.886</v>
+        <v>0</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
@@ -8362,26 +8504,27 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>no_match</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>The candidate 'V.FECP-ST/MT' has a high name confidence and no semantic header conflict, despite all values being zero.</t>
+          <t>All candidates have semantic conflicts or lack distinctive evidence.</t>
         </is>
       </c>
       <c r="M139" t="inlineStr"/>
       <c r="N139" t="inlineStr"/>
       <c r="O139" t="inlineStr"/>
-      <c r="P139" t="n">
-        <v>0</v>
-      </c>
+      <c r="P139" t="inlineStr"/>
       <c r="Q139" t="n">
-        <v>0.886</v>
-      </c>
-      <c r="R139" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0</v>
+      </c>
       <c r="S139" t="inlineStr"/>
       <c r="T139" t="inlineStr"/>
+      <c r="U139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -8421,21 +8564,22 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>All candidates exhibit semantic-role conflicts and provide no distinctive evidence.</t>
+          <t>All candidates exhibit semantic header conflicts and lack distinctive sample evidence.</t>
         </is>
       </c>
       <c r="M140" t="inlineStr"/>
       <c r="N140" t="inlineStr"/>
       <c r="O140" t="inlineStr"/>
-      <c r="P140" t="n">
-        <v>0</v>
-      </c>
+      <c r="P140" t="inlineStr"/>
       <c r="Q140" t="n">
         <v>0</v>
       </c>
-      <c r="R140" t="inlineStr"/>
+      <c r="R140" t="n">
+        <v>0</v>
+      </c>
       <c r="S140" t="inlineStr"/>
       <c r="T140" t="inlineStr"/>
+      <c r="U140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -8487,15 +8631,16 @@
       <c r="M141" t="inlineStr"/>
       <c r="N141" t="inlineStr"/>
       <c r="O141" t="inlineStr"/>
-      <c r="P141" t="n">
-        <v>0.8672</v>
-      </c>
+      <c r="P141" t="inlineStr"/>
       <c r="Q141" t="n">
         <v>0.8672</v>
       </c>
-      <c r="R141" t="inlineStr"/>
+      <c r="R141" t="n">
+        <v>0.8672</v>
+      </c>
       <c r="S141" t="inlineStr"/>
       <c r="T141" t="inlineStr"/>
+      <c r="U141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -8521,7 +8666,7 @@
         <v>0.908</v>
       </c>
       <c r="G142" t="n">
-        <v>-0.0129</v>
+        <v>-0.0128</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -8547,15 +8692,16 @@
       <c r="M142" t="inlineStr"/>
       <c r="N142" t="inlineStr"/>
       <c r="O142" t="inlineStr"/>
-      <c r="P142" t="n">
+      <c r="P142" t="inlineStr"/>
+      <c r="Q142" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="R142" t="n">
         <v>0.8951</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0.8951</v>
-      </c>
-      <c r="R142" t="inlineStr"/>
       <c r="S142" t="inlineStr"/>
       <c r="T142" t="inlineStr"/>
+      <c r="U142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -8575,19 +8721,19 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>0.8942</v>
+        <v>0.8941</v>
       </c>
       <c r="F143" t="n">
         <v>0.8922</v>
       </c>
       <c r="G143" t="n">
-        <v>0.0019</v>
+        <v>0.002</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
       </c>
       <c r="I143" t="n">
-        <v>0.8942</v>
+        <v>0.8941</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
@@ -8601,21 +8747,22 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>The name 'ICMS ST Ant.' closely aligns with 'Aliquota ICMS_ST' despite a lack of distinctive sample overlap, and no semantic header conflict.</t>
+          <t>The name 'ICMS ST Ant.' closely aligns with 'Aliquota ICMS_ST' and has no semantic conflicts.</t>
         </is>
       </c>
       <c r="M143" t="inlineStr"/>
       <c r="N143" t="inlineStr"/>
       <c r="O143" t="inlineStr"/>
-      <c r="P143" t="n">
-        <v>0.8942</v>
-      </c>
+      <c r="P143" t="inlineStr"/>
       <c r="Q143" t="n">
-        <v>0.8942</v>
-      </c>
-      <c r="R143" t="inlineStr"/>
+        <v>0.8941</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.8941</v>
+      </c>
       <c r="S143" t="inlineStr"/>
       <c r="T143" t="inlineStr"/>
+      <c r="U143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -8635,7 +8782,7 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>0.8848</v>
+        <v>0.8847</v>
       </c>
       <c r="F144" t="n">
         <v>0.8745000000000001</v>
@@ -8647,7 +8794,7 @@
         <v>0</v>
       </c>
       <c r="I144" t="n">
-        <v>0.8848</v>
+        <v>0.8847</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
@@ -8661,21 +8808,22 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>The candidate 'B.ICMS ST An' has the highest name confidence and no semantic header conflict.</t>
+          <t>The candidate 'B.ICMS ST An' has a high name confidence and no semantic conflicts, aligning with the tax situation of ICMS ST.</t>
         </is>
       </c>
       <c r="M144" t="inlineStr"/>
       <c r="N144" t="inlineStr"/>
       <c r="O144" t="inlineStr"/>
-      <c r="P144" t="n">
-        <v>0</v>
-      </c>
+      <c r="P144" t="inlineStr"/>
       <c r="Q144" t="n">
-        <v>0.8848</v>
-      </c>
-      <c r="R144" t="inlineStr"/>
+        <v>0.8847</v>
+      </c>
+      <c r="R144" t="n">
+        <v>0.8847</v>
+      </c>
       <c r="S144" t="inlineStr"/>
       <c r="T144" t="inlineStr"/>
+      <c r="U144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -8721,15 +8869,16 @@
       <c r="M145" t="inlineStr"/>
       <c r="N145" t="inlineStr"/>
       <c r="O145" t="inlineStr"/>
-      <c r="P145" t="n">
-        <v>0</v>
-      </c>
+      <c r="P145" t="inlineStr"/>
       <c r="Q145" t="n">
+        <v>0</v>
+      </c>
+      <c r="R145" t="n">
         <v>0.882</v>
       </c>
-      <c r="R145" t="inlineStr"/>
       <c r="S145" t="inlineStr"/>
       <c r="T145" t="inlineStr"/>
+      <c r="U145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -8743,13 +8892,13 @@
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="n">
-        <v>0.8426</v>
+        <v>0.8425</v>
       </c>
       <c r="F146" t="n">
-        <v>0.7483</v>
+        <v>0.7494</v>
       </c>
       <c r="G146" t="n">
-        <v>0.09420000000000001</v>
+        <v>0.0931</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -8769,21 +8918,22 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>All candidates have semantic header conflicts and lack distinctive sample overlap, indicating no suitable mapping.</t>
         </is>
       </c>
       <c r="M146" t="inlineStr"/>
       <c r="N146" t="inlineStr"/>
       <c r="O146" t="inlineStr"/>
-      <c r="P146" t="n">
-        <v>0.8426</v>
-      </c>
+      <c r="P146" t="inlineStr"/>
       <c r="Q146" t="n">
-        <v>0.8426</v>
-      </c>
-      <c r="R146" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="R146" t="n">
+        <v>0.8487</v>
+      </c>
       <c r="S146" t="inlineStr"/>
       <c r="T146" t="inlineStr"/>
+      <c r="U146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -8797,13 +8947,13 @@
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="n">
-        <v>0.8249</v>
+        <v>0.8248</v>
       </c>
       <c r="F147" t="n">
         <v>0.8243</v>
       </c>
       <c r="G147" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0005</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
@@ -8829,15 +8979,16 @@
       <c r="M147" t="inlineStr"/>
       <c r="N147" t="inlineStr"/>
       <c r="O147" t="inlineStr"/>
-      <c r="P147" t="n">
-        <v>0.8249</v>
-      </c>
+      <c r="P147" t="inlineStr"/>
       <c r="Q147" t="n">
-        <v>0.8249</v>
-      </c>
-      <c r="R147" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="R147" t="n">
+        <v>0.8248</v>
+      </c>
       <c r="S147" t="inlineStr"/>
       <c r="T147" t="inlineStr"/>
+      <c r="U147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -8877,21 +9028,22 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>No viable candidates match the semantic role of 'Municipio Inicio' as all candidates are related to tax situations or codes.</t>
+          <t>No viable candidates match the semantic role of 'Municipio Inicio' as all candidates pertain to tax situations or codes.</t>
         </is>
       </c>
       <c r="M148" t="inlineStr"/>
       <c r="N148" t="inlineStr"/>
       <c r="O148" t="inlineStr"/>
-      <c r="P148" t="n">
-        <v>0</v>
-      </c>
+      <c r="P148" t="inlineStr"/>
       <c r="Q148" t="n">
         <v>0</v>
       </c>
-      <c r="R148" t="inlineStr"/>
+      <c r="R148" t="n">
+        <v>0</v>
+      </c>
       <c r="S148" t="inlineStr"/>
       <c r="T148" t="inlineStr"/>
+      <c r="U148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -8908,7 +9060,7 @@
         <v>0.8372000000000001</v>
       </c>
       <c r="F149" t="n">
-        <v>0.8067</v>
+        <v>0.8068</v>
       </c>
       <c r="G149" t="n">
         <v>0.0304</v>
@@ -8937,15 +9089,16 @@
       <c r="M149" t="inlineStr"/>
       <c r="N149" t="inlineStr"/>
       <c r="O149" t="inlineStr"/>
-      <c r="P149" t="n">
-        <v>0.8372000000000001</v>
-      </c>
+      <c r="P149" t="inlineStr"/>
       <c r="Q149" t="n">
         <v>0.8372000000000001</v>
       </c>
-      <c r="R149" t="inlineStr"/>
+      <c r="R149" t="n">
+        <v>0.8372000000000001</v>
+      </c>
       <c r="S149" t="inlineStr"/>
       <c r="T149" t="inlineStr"/>
+      <c r="U149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -8959,13 +9112,13 @@
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="n">
-        <v>0.7112000000000001</v>
+        <v>0.7113</v>
       </c>
       <c r="F150" t="n">
         <v>0.768</v>
       </c>
       <c r="G150" t="n">
-        <v>-0.0568</v>
+        <v>-0.0567</v>
       </c>
       <c r="H150" t="n">
         <v>0.1633</v>
@@ -8991,15 +9144,16 @@
       <c r="M150" t="inlineStr"/>
       <c r="N150" t="inlineStr"/>
       <c r="O150" t="inlineStr"/>
-      <c r="P150" t="n">
-        <v>0.7112000000000001</v>
-      </c>
+      <c r="P150" t="inlineStr"/>
       <c r="Q150" t="n">
-        <v>0.7112000000000001</v>
-      </c>
-      <c r="R150" t="inlineStr"/>
+        <v>0.7113</v>
+      </c>
+      <c r="R150" t="n">
+        <v>0.7113</v>
+      </c>
       <c r="S150" t="inlineStr"/>
       <c r="T150" t="inlineStr"/>
+      <c r="U150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -9039,21 +9193,22 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>All candidate columns contain non-empty values, but none align semantically with 'Exercício', which is empty.</t>
+          <t>All candidates have insufficient evidence and do not align semantically with the 'Exercício' column.</t>
         </is>
       </c>
       <c r="M151" t="inlineStr"/>
       <c r="N151" t="inlineStr"/>
       <c r="O151" t="inlineStr"/>
-      <c r="P151" t="n">
-        <v>0</v>
-      </c>
+      <c r="P151" t="inlineStr"/>
       <c r="Q151" t="n">
-        <v>0.8145</v>
-      </c>
-      <c r="R151" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="R151" t="n">
+        <v>0</v>
+      </c>
       <c r="S151" t="inlineStr"/>
       <c r="T151" t="inlineStr"/>
+      <c r="U151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -9067,7 +9222,7 @@
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="n">
-        <v>0.8033</v>
+        <v>0.8034</v>
       </c>
       <c r="F152" t="n">
         <v>0.8159999999999999</v>
@@ -9099,15 +9254,16 @@
       <c r="M152" t="inlineStr"/>
       <c r="N152" t="inlineStr"/>
       <c r="O152" t="inlineStr"/>
-      <c r="P152" t="n">
-        <v>0</v>
-      </c>
+      <c r="P152" t="inlineStr"/>
       <c r="Q152" t="n">
-        <v>0.8033</v>
-      </c>
-      <c r="R152" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="R152" t="n">
+        <v>0.8034</v>
+      </c>
       <c r="S152" t="inlineStr"/>
       <c r="T152" t="inlineStr"/>
+      <c r="U152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -9121,7 +9277,7 @@
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="n">
-        <v>0.7964</v>
+        <v>0.7963</v>
       </c>
       <c r="F153" t="n">
         <v>0.7881</v>
@@ -9153,15 +9309,16 @@
       <c r="M153" t="inlineStr"/>
       <c r="N153" t="inlineStr"/>
       <c r="O153" t="inlineStr"/>
-      <c r="P153" t="n">
-        <v>0</v>
-      </c>
+      <c r="P153" t="inlineStr"/>
       <c r="Q153" t="n">
-        <v>0.7964</v>
-      </c>
-      <c r="R153" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="R153" t="n">
+        <v>0.7963</v>
+      </c>
       <c r="S153" t="inlineStr"/>
       <c r="T153" t="inlineStr"/>
+      <c r="U153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -9178,10 +9335,10 @@
         <v>0.8688</v>
       </c>
       <c r="F154" t="n">
-        <v>0.8321</v>
+        <v>0.832</v>
       </c>
       <c r="G154" t="n">
-        <v>0.0367</v>
+        <v>0.0368</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -9201,21 +9358,22 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>All candidates have empty profiles and no distinctive content to support a mapping.</t>
+          <t>All candidate columns have empty profiles and lack distinctive content to support a mapping.</t>
         </is>
       </c>
       <c r="M154" t="inlineStr"/>
       <c r="N154" t="inlineStr"/>
       <c r="O154" t="inlineStr"/>
-      <c r="P154" t="n">
-        <v>0</v>
-      </c>
+      <c r="P154" t="inlineStr"/>
       <c r="Q154" t="n">
-        <v>0.8688</v>
-      </c>
-      <c r="R154" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="R154" t="n">
+        <v>0</v>
+      </c>
       <c r="S154" t="inlineStr"/>
       <c r="T154" t="inlineStr"/>
+      <c r="U154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -9255,21 +9413,22 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>All candidate columns contain no valid data, making them incompatible with the 'Domicílio Fiscal' requirement.</t>
+          <t>All candidate columns lack sufficient non-empty data to establish a meaningful mapping.</t>
         </is>
       </c>
       <c r="M155" t="inlineStr"/>
       <c r="N155" t="inlineStr"/>
       <c r="O155" t="inlineStr"/>
-      <c r="P155" t="n">
-        <v>0</v>
-      </c>
+      <c r="P155" t="inlineStr"/>
       <c r="Q155" t="n">
         <v>0</v>
       </c>
-      <c r="R155" t="inlineStr"/>
+      <c r="R155" t="n">
+        <v>0</v>
+      </c>
       <c r="S155" t="inlineStr"/>
       <c r="T155" t="inlineStr"/>
+      <c r="U155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -9286,10 +9445,10 @@
         <v>0.8388</v>
       </c>
       <c r="F156" t="n">
-        <v>0.8838</v>
+        <v>0.8841</v>
       </c>
       <c r="G156" t="n">
-        <v>-0.045</v>
+        <v>-0.0453</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -9315,15 +9474,16 @@
       <c r="M156" t="inlineStr"/>
       <c r="N156" t="inlineStr"/>
       <c r="O156" t="inlineStr"/>
-      <c r="P156" t="n">
-        <v>0.8388</v>
-      </c>
+      <c r="P156" t="inlineStr"/>
       <c r="Q156" t="n">
         <v>0.8388</v>
       </c>
-      <c r="R156" t="inlineStr"/>
+      <c r="R156" t="n">
+        <v>0.8388</v>
+      </c>
       <c r="S156" t="inlineStr"/>
       <c r="T156" t="inlineStr"/>
+      <c r="U156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -9343,7 +9503,7 @@
         <v>0.8413</v>
       </c>
       <c r="G157" t="n">
-        <v>0.0089</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -9369,15 +9529,16 @@
       <c r="M157" t="inlineStr"/>
       <c r="N157" t="inlineStr"/>
       <c r="O157" t="inlineStr"/>
-      <c r="P157" t="n">
-        <v>0</v>
-      </c>
+      <c r="P157" t="inlineStr"/>
       <c r="Q157" t="n">
         <v>0</v>
       </c>
-      <c r="R157" t="inlineStr"/>
+      <c r="R157" t="n">
+        <v>0</v>
+      </c>
       <c r="S157" t="inlineStr"/>
       <c r="T157" t="inlineStr"/>
+      <c r="U157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -9388,23 +9549,29 @@
           <t>Dest.</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr"/>
-      <c r="D158" t="inlineStr"/>
+      <c r="C158" t="n">
+        <v>252</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Cliente Dest</t>
+        </is>
+      </c>
       <c r="E158" t="n">
-        <v>0.772</v>
+        <v>0.8815</v>
       </c>
       <c r="F158" t="n">
+        <v>0.8586</v>
+      </c>
+      <c r="G158" t="n">
+        <v>0.0229</v>
+      </c>
+      <c r="H158" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="I158" t="n">
         <v>0.8815</v>
       </c>
-      <c r="G158" t="n">
-        <v>-0.1095</v>
-      </c>
-      <c r="H158" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="I158" t="n">
-        <v>0</v>
-      </c>
       <c r="J158" t="inlineStr">
         <is>
           <t>data</t>
@@ -9412,26 +9579,27 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>review</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>The header 'Cliente Dest' suggests a destination client, aligning with the numeric values indicating a destination code.</t>
         </is>
       </c>
       <c r="M158" t="inlineStr"/>
       <c r="N158" t="inlineStr"/>
       <c r="O158" t="inlineStr"/>
-      <c r="P158" t="n">
-        <v>0.9</v>
-      </c>
+      <c r="P158" t="inlineStr"/>
       <c r="Q158" t="n">
-        <v>0.885</v>
-      </c>
-      <c r="R158" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="R158" t="n">
+        <v>0.8815</v>
+      </c>
       <c r="S158" t="inlineStr"/>
       <c r="T158" t="inlineStr"/>
+      <c r="U158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -9454,10 +9622,10 @@
         <v>0.8584000000000001</v>
       </c>
       <c r="F159" t="n">
-        <v>0.8557</v>
+        <v>0.8558</v>
       </c>
       <c r="G159" t="n">
-        <v>0.0027</v>
+        <v>0.0026</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -9483,15 +9651,16 @@
       <c r="M159" t="inlineStr"/>
       <c r="N159" t="inlineStr"/>
       <c r="O159" t="inlineStr"/>
-      <c r="P159" t="n">
-        <v>0</v>
-      </c>
+      <c r="P159" t="inlineStr"/>
       <c r="Q159" t="n">
         <v>0</v>
       </c>
-      <c r="R159" t="inlineStr"/>
+      <c r="R159" t="n">
+        <v>0</v>
+      </c>
       <c r="S159" t="inlineStr"/>
       <c r="T159" t="inlineStr"/>
+      <c r="U159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -9505,13 +9674,13 @@
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="n">
-        <v>0.8307</v>
+        <v>0.8309</v>
       </c>
       <c r="F160" t="n">
         <v>0.8465</v>
       </c>
       <c r="G160" t="n">
-        <v>-0.0158</v>
+        <v>-0.0157</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -9537,15 +9706,16 @@
       <c r="M160" t="inlineStr"/>
       <c r="N160" t="inlineStr"/>
       <c r="O160" t="inlineStr"/>
-      <c r="P160" t="n">
-        <v>0.8307</v>
-      </c>
+      <c r="P160" t="inlineStr"/>
       <c r="Q160" t="n">
-        <v>0.8307</v>
-      </c>
-      <c r="R160" t="inlineStr"/>
+        <v>0.8309</v>
+      </c>
+      <c r="R160" t="n">
+        <v>0.8309</v>
+      </c>
       <c r="S160" t="inlineStr"/>
       <c r="T160" t="inlineStr"/>
+      <c r="U160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -9585,21 +9755,22 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>No suitable candidate found due to lack of evidence in the 'Ordem' column.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M161" t="inlineStr"/>
       <c r="N161" t="inlineStr"/>
       <c r="O161" t="inlineStr"/>
-      <c r="P161" t="n">
-        <v>0</v>
-      </c>
+      <c r="P161" t="inlineStr"/>
       <c r="Q161" t="n">
-        <v>0</v>
-      </c>
-      <c r="R161" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="R161" t="n">
+        <v>0.8152</v>
+      </c>
       <c r="S161" t="inlineStr"/>
       <c r="T161" t="inlineStr"/>
+      <c r="U161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -9654,6 +9825,7 @@
       <c r="R162" t="inlineStr"/>
       <c r="S162" t="inlineStr"/>
       <c r="T162" t="inlineStr"/>
+      <c r="U162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -9699,15 +9871,16 @@
       <c r="M163" t="inlineStr"/>
       <c r="N163" t="inlineStr"/>
       <c r="O163" t="inlineStr"/>
-      <c r="P163" t="n">
-        <v>0</v>
-      </c>
+      <c r="P163" t="inlineStr"/>
       <c r="Q163" t="n">
         <v>0</v>
       </c>
-      <c r="R163" t="inlineStr"/>
+      <c r="R163" t="n">
+        <v>0</v>
+      </c>
       <c r="S163" t="inlineStr"/>
       <c r="T163" t="inlineStr"/>
+      <c r="U163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -9753,15 +9926,16 @@
       <c r="M164" t="inlineStr"/>
       <c r="N164" t="inlineStr"/>
       <c r="O164" t="inlineStr"/>
-      <c r="P164" t="n">
-        <v>0</v>
-      </c>
+      <c r="P164" t="inlineStr"/>
       <c r="Q164" t="n">
+        <v>0</v>
+      </c>
+      <c r="R164" t="n">
         <v>0.8007</v>
       </c>
-      <c r="R164" t="inlineStr"/>
       <c r="S164" t="inlineStr"/>
       <c r="T164" t="inlineStr"/>
+      <c r="U164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -9775,13 +9949,13 @@
       <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="n">
+        <v>0.7877</v>
+      </c>
+      <c r="F165" t="n">
         <v>0.7975</v>
       </c>
-      <c r="F165" t="n">
-        <v>0.7904</v>
-      </c>
       <c r="G165" t="n">
-        <v>0.0071</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -9801,21 +9975,22 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>The candidate columns contain numeric values, but none align semantically with the empty 'Nº material antigo' header.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M165" t="inlineStr"/>
       <c r="N165" t="inlineStr"/>
       <c r="O165" t="inlineStr"/>
-      <c r="P165" t="n">
-        <v>0</v>
-      </c>
+      <c r="P165" t="inlineStr"/>
       <c r="Q165" t="n">
-        <v>0.7975</v>
-      </c>
-      <c r="R165" t="inlineStr"/>
+        <v>0.7877</v>
+      </c>
+      <c r="R165" t="n">
+        <v>0.7877</v>
+      </c>
       <c r="S165" t="inlineStr"/>
       <c r="T165" t="inlineStr"/>
+      <c r="U165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -9870,6 +10045,7 @@
       <c r="R166" t="inlineStr"/>
       <c r="S166" t="inlineStr"/>
       <c r="T166" t="inlineStr"/>
+      <c r="U166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -9880,28 +10056,22 @@
           <t>Número do NFC-e SAT</t>
         </is>
       </c>
-      <c r="C167" t="n">
-        <v>5</v>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>Série NF</t>
-        </is>
-      </c>
+      <c r="C167" t="inlineStr"/>
+      <c r="D167" t="inlineStr"/>
       <c r="E167" t="n">
+        <v>0.8295</v>
+      </c>
+      <c r="F167" t="n">
         <v>0.8205</v>
       </c>
-      <c r="F167" t="n">
-        <v>0.8298</v>
-      </c>
       <c r="G167" t="n">
-        <v>-0.009299999999999999</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H167" t="n">
         <v>0</v>
       </c>
       <c r="I167" t="n">
-        <v>0.8205</v>
+        <v>0</v>
       </c>
       <c r="J167" t="inlineStr">
         <is>
@@ -9910,26 +10080,27 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>no_match</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>The header 'Série NF' closely matches the semantic role of 'Número do NFC-e SAT' and has informative data evidence.</t>
+          <t>All candidates have empty evidence with no distinctive samples or valid data.</t>
         </is>
       </c>
       <c r="M167" t="inlineStr"/>
       <c r="N167" t="inlineStr"/>
       <c r="O167" t="inlineStr"/>
-      <c r="P167" t="n">
-        <v>0.8205</v>
-      </c>
+      <c r="P167" t="inlineStr"/>
       <c r="Q167" t="n">
-        <v>0.8205</v>
-      </c>
-      <c r="R167" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="R167" t="n">
+        <v>0</v>
+      </c>
       <c r="S167" t="inlineStr"/>
       <c r="T167" t="inlineStr"/>
+      <c r="U167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -9943,16 +10114,16 @@
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="n">
-        <v>0.8345</v>
+        <v>0.8053</v>
       </c>
       <c r="F168" t="n">
-        <v>0.8321</v>
+        <v>0.8344</v>
       </c>
       <c r="G168" t="n">
-        <v>0.0024</v>
+        <v>-0.0291</v>
       </c>
       <c r="H168" t="n">
-        <v>0.3375</v>
+        <v>0.84</v>
       </c>
       <c r="I168" t="n">
         <v>0</v>
@@ -9975,15 +10146,16 @@
       <c r="M168" t="inlineStr"/>
       <c r="N168" t="inlineStr"/>
       <c r="O168" t="inlineStr"/>
-      <c r="P168" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="P168" t="inlineStr"/>
       <c r="Q168" t="n">
-        <v>0.8345</v>
-      </c>
-      <c r="R168" t="inlineStr"/>
+        <v>0.97</v>
+      </c>
+      <c r="R168" t="n">
+        <v>0.83</v>
+      </c>
       <c r="S168" t="inlineStr"/>
       <c r="T168" t="inlineStr"/>
+      <c r="U168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -10035,15 +10207,16 @@
       <c r="M169" t="inlineStr"/>
       <c r="N169" t="inlineStr"/>
       <c r="O169" t="inlineStr"/>
-      <c r="P169" t="n">
-        <v>0.8512999999999999</v>
-      </c>
+      <c r="P169" t="inlineStr"/>
       <c r="Q169" t="n">
         <v>0.8512999999999999</v>
       </c>
-      <c r="R169" t="inlineStr"/>
+      <c r="R169" t="n">
+        <v>0.8512999999999999</v>
+      </c>
       <c r="S169" t="inlineStr"/>
       <c r="T169" t="inlineStr"/>
+      <c r="U169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -10089,21 +10262,22 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>The candidate 'Base FCP Cmp' has a high name confidence and no semantic conflicts, aligning closely with the tax base context.</t>
+          <t>The name 'Base FCP Cmp' closely aligns with 'Base de Cálculo ICOP FECP' and both have all-zero evidence, but the name confidence is the highest among candidates.</t>
         </is>
       </c>
       <c r="M170" t="inlineStr"/>
       <c r="N170" t="inlineStr"/>
       <c r="O170" t="inlineStr"/>
-      <c r="P170" t="n">
-        <v>0.9036</v>
-      </c>
+      <c r="P170" t="inlineStr"/>
       <c r="Q170" t="n">
         <v>0.9036</v>
       </c>
-      <c r="R170" t="inlineStr"/>
+      <c r="R170" t="n">
+        <v>0.9036</v>
+      </c>
       <c r="S170" t="inlineStr"/>
       <c r="T170" t="inlineStr"/>
+      <c r="U170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -10155,15 +10329,16 @@
       <c r="M171" t="inlineStr"/>
       <c r="N171" t="inlineStr"/>
       <c r="O171" t="inlineStr"/>
-      <c r="P171" t="n">
-        <v>0.8787</v>
-      </c>
+      <c r="P171" t="inlineStr"/>
       <c r="Q171" t="n">
         <v>0.8787</v>
       </c>
-      <c r="R171" t="inlineStr"/>
+      <c r="R171" t="n">
+        <v>0.8787</v>
+      </c>
       <c r="S171" t="inlineStr"/>
       <c r="T171" t="inlineStr"/>
+      <c r="U171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -10186,10 +10361,10 @@
         <v>0.9402</v>
       </c>
       <c r="F172" t="n">
-        <v>0.9239000000000001</v>
+        <v>0.9233</v>
       </c>
       <c r="G172" t="n">
-        <v>0.0163</v>
+        <v>0.0168</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -10215,15 +10390,16 @@
       <c r="M172" t="inlineStr"/>
       <c r="N172" t="inlineStr"/>
       <c r="O172" t="inlineStr"/>
-      <c r="P172" t="n">
-        <v>0.9402</v>
-      </c>
+      <c r="P172" t="inlineStr"/>
       <c r="Q172" t="n">
         <v>0.9402</v>
       </c>
-      <c r="R172" t="inlineStr"/>
+      <c r="R172" t="n">
+        <v>0.9402</v>
+      </c>
       <c r="S172" t="inlineStr"/>
       <c r="T172" t="inlineStr"/>
+      <c r="U172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -10269,21 +10445,22 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>The name 'FECP Comp.' closely aligns with 'Isentas ICOP FECP', despite both having all-zero evidence.</t>
+          <t>The candidate 'FECP Comp.' has the highest name confidence but lacks distinctive data evidence.</t>
         </is>
       </c>
       <c r="M173" t="inlineStr"/>
       <c r="N173" t="inlineStr"/>
       <c r="O173" t="inlineStr"/>
-      <c r="P173" t="n">
+      <c r="P173" t="inlineStr"/>
+      <c r="Q173" t="n">
+        <v>0</v>
+      </c>
+      <c r="R173" t="n">
         <v>0.8653</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0.8653</v>
-      </c>
-      <c r="R173" t="inlineStr"/>
       <c r="S173" t="inlineStr"/>
       <c r="T173" t="inlineStr"/>
+      <c r="U173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -10294,28 +10471,22 @@
           <t>Outras ICOP FECP</t>
         </is>
       </c>
-      <c r="C174" t="n">
-        <v>321</v>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>FECP Comp.</t>
-        </is>
-      </c>
+      <c r="C174" t="inlineStr"/>
+      <c r="D174" t="inlineStr"/>
       <c r="E174" t="n">
         <v>0.8799</v>
       </c>
       <c r="F174" t="n">
-        <v>0</v>
+        <v>0.8506</v>
       </c>
       <c r="G174" t="n">
-        <v>0.8799</v>
+        <v>0.0292</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
       </c>
       <c r="I174" t="n">
-        <v>0.8799</v>
+        <v>0</v>
       </c>
       <c r="J174" t="inlineStr">
         <is>
@@ -10324,26 +10495,27 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>no_match</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>The candidate 'FECP Comp.' has a high name confidence but lacks distinctive data evidence.</t>
+          <t>All candidates exhibit semantic-role conflicts or lack distinctive evidence, making them unsuitable for mapping.</t>
         </is>
       </c>
       <c r="M174" t="inlineStr"/>
       <c r="N174" t="inlineStr"/>
       <c r="O174" t="inlineStr"/>
-      <c r="P174" t="n">
-        <v>0</v>
-      </c>
+      <c r="P174" t="inlineStr"/>
       <c r="Q174" t="n">
-        <v>0.8799</v>
-      </c>
-      <c r="R174" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="R174" t="n">
+        <v>0</v>
+      </c>
       <c r="S174" t="inlineStr"/>
       <c r="T174" t="inlineStr"/>
+      <c r="U174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -10357,16 +10529,16 @@
       <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="n">
-        <v>0.7123</v>
+        <v>0.7786</v>
       </c>
       <c r="F175" t="n">
         <v>0.8415</v>
       </c>
       <c r="G175" t="n">
-        <v>-0.1292</v>
+        <v>-0.0629</v>
       </c>
       <c r="H175" t="n">
-        <v>0.7557</v>
+        <v>0.2504</v>
       </c>
       <c r="I175" t="n">
         <v>0</v>
@@ -10389,15 +10561,16 @@
       <c r="M175" t="inlineStr"/>
       <c r="N175" t="inlineStr"/>
       <c r="O175" t="inlineStr"/>
-      <c r="P175" t="n">
-        <v>0.7123</v>
-      </c>
+      <c r="P175" t="inlineStr"/>
       <c r="Q175" t="n">
-        <v>0.7123</v>
-      </c>
-      <c r="R175" t="inlineStr"/>
+        <v>0.7786</v>
+      </c>
+      <c r="R175" t="n">
+        <v>0.7786</v>
+      </c>
       <c r="S175" t="inlineStr"/>
       <c r="T175" t="inlineStr"/>
+      <c r="U175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -10411,16 +10584,16 @@
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="n">
-        <v>0.8045</v>
+        <v>0.7563</v>
       </c>
       <c r="F176" t="n">
         <v>0.8195</v>
       </c>
       <c r="G176" t="n">
-        <v>-0.015</v>
+        <v>-0.06320000000000001</v>
       </c>
       <c r="H176" t="n">
-        <v>0.7593</v>
+        <v>0.7806</v>
       </c>
       <c r="I176" t="n">
         <v>0</v>
@@ -10443,15 +10616,16 @@
       <c r="M176" t="inlineStr"/>
       <c r="N176" t="inlineStr"/>
       <c r="O176" t="inlineStr"/>
-      <c r="P176" t="n">
-        <v>0.7593</v>
-      </c>
+      <c r="P176" t="inlineStr"/>
       <c r="Q176" t="n">
-        <v>0.7894</v>
-      </c>
-      <c r="R176" t="inlineStr"/>
+        <v>0.7563</v>
+      </c>
+      <c r="R176" t="n">
+        <v>0.7563</v>
+      </c>
       <c r="S176" t="inlineStr"/>
       <c r="T176" t="inlineStr"/>
+      <c r="U176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -10497,15 +10671,16 @@
       <c r="M177" t="inlineStr"/>
       <c r="N177" t="inlineStr"/>
       <c r="O177" t="inlineStr"/>
-      <c r="P177" t="n">
-        <v>0.8299</v>
-      </c>
+      <c r="P177" t="inlineStr"/>
       <c r="Q177" t="n">
         <v>0.8299</v>
       </c>
-      <c r="R177" t="inlineStr"/>
+      <c r="R177" t="n">
+        <v>0.8299</v>
+      </c>
       <c r="S177" t="inlineStr"/>
       <c r="T177" t="inlineStr"/>
+      <c r="U177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -10519,10 +10694,10 @@
       <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr"/>
       <c r="E178" t="n">
-        <v>0.8306</v>
+        <v>0.8305</v>
       </c>
       <c r="F178" t="n">
-        <v>0.8217</v>
+        <v>0.8216</v>
       </c>
       <c r="G178" t="n">
         <v>0.0089</v>
@@ -10545,21 +10720,22 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>All candidate columns have insufficient evidence or semantic conflicts, making a valid mapping impossible.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M178" t="inlineStr"/>
       <c r="N178" t="inlineStr"/>
       <c r="O178" t="inlineStr"/>
-      <c r="P178" t="n">
-        <v>0</v>
-      </c>
+      <c r="P178" t="inlineStr"/>
       <c r="Q178" t="n">
         <v>0</v>
       </c>
-      <c r="R178" t="inlineStr"/>
+      <c r="R178" t="n">
+        <v>0.8305</v>
+      </c>
       <c r="S178" t="inlineStr"/>
       <c r="T178" t="inlineStr"/>
+      <c r="U178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -10582,7 +10758,7 @@
         <v>0.8555</v>
       </c>
       <c r="F179" t="n">
-        <v>0.8572</v>
+        <v>0.8573</v>
       </c>
       <c r="G179" t="n">
         <v>-0.0018</v>
@@ -10605,21 +10781,22 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>The 'Doc. Fiscal' column has a strong numeric profile and a high name confidence, closely matching the 'Nº documento' role.</t>
+          <t>The 'Doc. Fiscal' column has a strong numeric profile and a high non-empty count, closely matching the expected format of invoice document numbers.</t>
         </is>
       </c>
       <c r="M179" t="inlineStr"/>
       <c r="N179" t="inlineStr"/>
       <c r="O179" t="inlineStr"/>
-      <c r="P179" t="n">
-        <v>0.9</v>
-      </c>
+      <c r="P179" t="inlineStr"/>
       <c r="Q179" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="R179" t="inlineStr"/>
+        <v>0.985</v>
+      </c>
+      <c r="R179" t="n">
+        <v>0.8714</v>
+      </c>
       <c r="S179" t="inlineStr"/>
       <c r="T179" t="inlineStr"/>
+      <c r="U179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -10633,16 +10810,16 @@
       <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="n">
-        <v>0.8095</v>
+        <v>0.8144</v>
       </c>
       <c r="F180" t="n">
-        <v>0.8361</v>
+        <v>0.836</v>
       </c>
       <c r="G180" t="n">
-        <v>-0.0266</v>
+        <v>-0.0215</v>
       </c>
       <c r="H180" t="n">
-        <v>0.3993</v>
+        <v>0.375</v>
       </c>
       <c r="I180" t="n">
         <v>0</v>
@@ -10665,15 +10842,16 @@
       <c r="M180" t="inlineStr"/>
       <c r="N180" t="inlineStr"/>
       <c r="O180" t="inlineStr"/>
-      <c r="P180" t="n">
-        <v>0.8095</v>
-      </c>
+      <c r="P180" t="inlineStr"/>
       <c r="Q180" t="n">
-        <v>0.8095</v>
-      </c>
-      <c r="R180" t="inlineStr"/>
+        <v>0.8144</v>
+      </c>
+      <c r="R180" t="n">
+        <v>0.8144</v>
+      </c>
       <c r="S180" t="inlineStr"/>
       <c r="T180" t="inlineStr"/>
+      <c r="U180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -10719,15 +10897,16 @@
       <c r="M181" t="inlineStr"/>
       <c r="N181" t="inlineStr"/>
       <c r="O181" t="inlineStr"/>
-      <c r="P181" t="n">
-        <v>0</v>
-      </c>
+      <c r="P181" t="inlineStr"/>
       <c r="Q181" t="n">
         <v>0</v>
       </c>
-      <c r="R181" t="inlineStr"/>
+      <c r="R181" t="n">
+        <v>0</v>
+      </c>
       <c r="S181" t="inlineStr"/>
       <c r="T181" t="inlineStr"/>
+      <c r="U181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -10741,13 +10920,13 @@
       <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr"/>
       <c r="E182" t="n">
+        <v>0.7986</v>
+      </c>
+      <c r="F182" t="n">
         <v>0.798</v>
       </c>
-      <c r="F182" t="n">
-        <v>0.7965</v>
-      </c>
       <c r="G182" t="n">
-        <v>0.0015</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -10767,21 +10946,22 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>No suitable candidate found due to lack of relevant data evidence.</t>
+          <t>All candidates have empty evidence, making it impossible to establish a valid mapping.</t>
         </is>
       </c>
       <c r="M182" t="inlineStr"/>
       <c r="N182" t="inlineStr"/>
       <c r="O182" t="inlineStr"/>
-      <c r="P182" t="n">
-        <v>0</v>
-      </c>
+      <c r="P182" t="inlineStr"/>
       <c r="Q182" t="n">
         <v>0</v>
       </c>
-      <c r="R182" t="inlineStr"/>
+      <c r="R182" t="n">
+        <v>0.7986</v>
+      </c>
       <c r="S182" t="inlineStr"/>
       <c r="T182" t="inlineStr"/>
+      <c r="U182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -10795,13 +10975,13 @@
       <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr"/>
       <c r="E183" t="n">
-        <v>0.8256</v>
+        <v>0.8265</v>
       </c>
       <c r="F183" t="n">
-        <v>0.8266</v>
+        <v>0.8255</v>
       </c>
       <c r="G183" t="n">
-        <v>-0.001</v>
+        <v>0.001</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -10821,21 +11001,22 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>All candidates have insufficient evidence and do not align semantically with the empty model column.</t>
         </is>
       </c>
       <c r="M183" t="inlineStr"/>
       <c r="N183" t="inlineStr"/>
       <c r="O183" t="inlineStr"/>
-      <c r="P183" t="n">
-        <v>0.8256</v>
-      </c>
+      <c r="P183" t="inlineStr"/>
       <c r="Q183" t="n">
-        <v>0.8256</v>
-      </c>
-      <c r="R183" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="R183" t="n">
+        <v>0</v>
+      </c>
       <c r="S183" t="inlineStr"/>
       <c r="T183" t="inlineStr"/>
+      <c r="U183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -10849,10 +11030,10 @@
       <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr"/>
       <c r="E184" t="n">
-        <v>0.8151</v>
+        <v>0.8149</v>
       </c>
       <c r="F184" t="n">
-        <v>0.8353</v>
+        <v>0.8351</v>
       </c>
       <c r="G184" t="n">
         <v>-0.0202</v>
@@ -10881,15 +11062,16 @@
       <c r="M184" t="inlineStr"/>
       <c r="N184" t="inlineStr"/>
       <c r="O184" t="inlineStr"/>
-      <c r="P184" t="n">
-        <v>0.4286</v>
-      </c>
+      <c r="P184" t="inlineStr"/>
       <c r="Q184" t="n">
-        <v>0.8151</v>
-      </c>
-      <c r="R184" t="inlineStr"/>
+        <v>0.8149</v>
+      </c>
+      <c r="R184" t="n">
+        <v>0.8149</v>
+      </c>
       <c r="S184" t="inlineStr"/>
       <c r="T184" t="inlineStr"/>
+      <c r="U184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -10941,15 +11123,16 @@
       <c r="M185" t="inlineStr"/>
       <c r="N185" t="inlineStr"/>
       <c r="O185" t="inlineStr"/>
-      <c r="P185" t="n">
+      <c r="P185" t="inlineStr"/>
+      <c r="Q185" t="n">
         <v>0.9968</v>
       </c>
-      <c r="Q185" t="n">
-        <v>0.9883999999999999</v>
-      </c>
-      <c r="R185" t="inlineStr"/>
+      <c r="R185" t="n">
+        <v>0.989</v>
+      </c>
       <c r="S185" t="inlineStr"/>
       <c r="T185" t="inlineStr"/>
+      <c r="U185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -10966,7 +11149,7 @@
         <v>0.8228</v>
       </c>
       <c r="F186" t="n">
-        <v>0.8451</v>
+        <v>0.845</v>
       </c>
       <c r="G186" t="n">
         <v>-0.0222</v>
@@ -10995,15 +11178,16 @@
       <c r="M186" t="inlineStr"/>
       <c r="N186" t="inlineStr"/>
       <c r="O186" t="inlineStr"/>
-      <c r="P186" t="n">
-        <v>0.8228</v>
-      </c>
+      <c r="P186" t="inlineStr"/>
       <c r="Q186" t="n">
         <v>0.8228</v>
       </c>
-      <c r="R186" t="inlineStr"/>
+      <c r="R186" t="n">
+        <v>0.8228</v>
+      </c>
       <c r="S186" t="inlineStr"/>
       <c r="T186" t="inlineStr"/>
+      <c r="U186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -11017,10 +11201,10 @@
       <c r="C187" t="inlineStr"/>
       <c r="D187" t="inlineStr"/>
       <c r="E187" t="n">
-        <v>0.832</v>
+        <v>0.8319</v>
       </c>
       <c r="F187" t="n">
-        <v>0.8491</v>
+        <v>0.849</v>
       </c>
       <c r="G187" t="n">
         <v>-0.0171</v>
@@ -11049,15 +11233,16 @@
       <c r="M187" t="inlineStr"/>
       <c r="N187" t="inlineStr"/>
       <c r="O187" t="inlineStr"/>
-      <c r="P187" t="n">
-        <v>0.832</v>
-      </c>
+      <c r="P187" t="inlineStr"/>
       <c r="Q187" t="n">
-        <v>0.832</v>
-      </c>
-      <c r="R187" t="inlineStr"/>
+        <v>0.8319</v>
+      </c>
+      <c r="R187" t="n">
+        <v>0.8319</v>
+      </c>
       <c r="S187" t="inlineStr"/>
       <c r="T187" t="inlineStr"/>
+      <c r="U187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -11080,10 +11265,10 @@
         <v>0.8545</v>
       </c>
       <c r="F188" t="n">
-        <v>0.8238</v>
+        <v>0.8274</v>
       </c>
       <c r="G188" t="n">
-        <v>0.0307</v>
+        <v>0.027</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
@@ -11103,21 +11288,22 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>The column 'Doc. Fiscal' has a strong numeric profile and high name confidence, aligning well with the expected document identifier.</t>
+          <t>The column 'Doc. Fiscal' has a strong numeric profile and aligns closely with the semantic role of 'Documento de compras'.</t>
         </is>
       </c>
       <c r="M188" t="inlineStr"/>
       <c r="N188" t="inlineStr"/>
       <c r="O188" t="inlineStr"/>
-      <c r="P188" t="n">
+      <c r="P188" t="inlineStr"/>
+      <c r="Q188" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="R188" t="n">
         <v>0.8545</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0.8545</v>
-      </c>
-      <c r="R188" t="inlineStr"/>
       <c r="S188" t="inlineStr"/>
       <c r="T188" t="inlineStr"/>
+      <c r="U188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -11137,41 +11323,48 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>0.9139</v>
+        <v>0.914</v>
       </c>
       <c r="F189" t="n">
-        <v>0.8443000000000001</v>
+        <v>0.8444</v>
       </c>
       <c r="G189" t="n">
         <v>0.0696</v>
       </c>
-      <c r="H189" t="inlineStr"/>
+      <c r="H189" t="n">
+        <v>0</v>
+      </c>
       <c r="I189" t="n">
-        <v>0.9139</v>
+        <v>0.914</v>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>data</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>review</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>Accepted from header similarity with a clear lead over the runner-up.</t>
+          <t>'Inf. item' has no populated rows, so it cannot be this column's source however well the headers match. Not accepted.</t>
         </is>
       </c>
       <c r="M189" t="inlineStr"/>
       <c r="N189" t="inlineStr"/>
       <c r="O189" t="inlineStr"/>
       <c r="P189" t="inlineStr"/>
-      <c r="Q189" t="inlineStr"/>
-      <c r="R189" t="inlineStr"/>
+      <c r="Q189" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R189" t="n">
+        <v>0.8708</v>
+      </c>
       <c r="S189" t="inlineStr"/>
       <c r="T189" t="inlineStr"/>
+      <c r="U189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -11217,15 +11410,16 @@
       <c r="M190" t="inlineStr"/>
       <c r="N190" t="inlineStr"/>
       <c r="O190" t="inlineStr"/>
-      <c r="P190" t="n">
-        <v>0</v>
-      </c>
+      <c r="P190" t="inlineStr"/>
       <c r="Q190" t="n">
         <v>0</v>
       </c>
-      <c r="R190" t="inlineStr"/>
+      <c r="R190" t="n">
+        <v>0</v>
+      </c>
       <c r="S190" t="inlineStr"/>
       <c r="T190" t="inlineStr"/>
+      <c r="U190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -11280,6 +11474,7 @@
       <c r="R191" t="inlineStr"/>
       <c r="S191" t="inlineStr"/>
       <c r="T191" t="inlineStr"/>
+      <c r="U191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -11293,7 +11488,7 @@
       <c r="C192" t="inlineStr"/>
       <c r="D192" t="inlineStr"/>
       <c r="E192" t="n">
-        <v>0.8477</v>
+        <v>0.8476</v>
       </c>
       <c r="F192" t="n">
         <v>0.8431</v>
@@ -11325,15 +11520,16 @@
       <c r="M192" t="inlineStr"/>
       <c r="N192" t="inlineStr"/>
       <c r="O192" t="inlineStr"/>
-      <c r="P192" t="n">
+      <c r="P192" t="inlineStr"/>
+      <c r="Q192" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0.8477</v>
-      </c>
-      <c r="R192" t="inlineStr"/>
+      <c r="R192" t="n">
+        <v>0.8476</v>
+      </c>
       <c r="S192" t="inlineStr"/>
       <c r="T192" t="inlineStr"/>
+      <c r="U192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -11388,6 +11584,7 @@
       <c r="R193" t="inlineStr"/>
       <c r="S193" t="inlineStr"/>
       <c r="T193" t="inlineStr"/>
+      <c r="U193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -11407,10 +11604,10 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>0.8794</v>
+        <v>0.8794999999999999</v>
       </c>
       <c r="F194" t="n">
-        <v>0.9056999999999999</v>
+        <v>0.9058</v>
       </c>
       <c r="G194" t="n">
         <v>-0.0263</v>
@@ -11419,7 +11616,7 @@
         <v>0.3</v>
       </c>
       <c r="I194" t="n">
-        <v>0.8794</v>
+        <v>0.8794999999999999</v>
       </c>
       <c r="J194" t="inlineStr">
         <is>
@@ -11433,21 +11630,22 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>The name 'Trib. IPI' closely relates to 'Tipo de Imposto IPI' and has sufficient data evidence despite some numeric variance.</t>
+          <t>The name 'Trib. IPI' closely relates to 'Tipo de Imposto IPI' and has sufficient data evidence despite some numeric values.</t>
         </is>
       </c>
       <c r="M194" t="inlineStr"/>
       <c r="N194" t="inlineStr"/>
       <c r="O194" t="inlineStr"/>
-      <c r="P194" t="n">
-        <v>0.8794</v>
-      </c>
+      <c r="P194" t="inlineStr"/>
       <c r="Q194" t="n">
-        <v>0.8794</v>
-      </c>
-      <c r="R194" t="inlineStr"/>
+        <v>0.8794999999999999</v>
+      </c>
+      <c r="R194" t="n">
+        <v>0.8794999999999999</v>
+      </c>
       <c r="S194" t="inlineStr"/>
       <c r="T194" t="inlineStr"/>
+      <c r="U194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -11461,13 +11659,13 @@
       <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr"/>
       <c r="E195" t="n">
-        <v>0.832</v>
+        <v>0.8321</v>
       </c>
       <c r="F195" t="n">
-        <v>0.8087</v>
+        <v>0.848</v>
       </c>
       <c r="G195" t="n">
-        <v>0.0233</v>
+        <v>-0.0159</v>
       </c>
       <c r="H195" t="n">
         <v>0.35</v>
@@ -11493,15 +11691,16 @@
       <c r="M195" t="inlineStr"/>
       <c r="N195" t="inlineStr"/>
       <c r="O195" t="inlineStr"/>
-      <c r="P195" t="n">
-        <v>0.35</v>
-      </c>
+      <c r="P195" t="inlineStr"/>
       <c r="Q195" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R195" t="n">
         <v>0.83</v>
       </c>
-      <c r="R195" t="inlineStr"/>
       <c r="S195" t="inlineStr"/>
       <c r="T195" t="inlineStr"/>
+      <c r="U195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -11521,19 +11720,19 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>0.8816000000000001</v>
+        <v>0.8815</v>
       </c>
       <c r="F196" t="n">
         <v>0.872</v>
       </c>
       <c r="G196" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0095</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
       </c>
       <c r="I196" t="n">
-        <v>0.8816000000000001</v>
+        <v>0.8815</v>
       </c>
       <c r="J196" t="inlineStr">
         <is>
@@ -11553,15 +11752,16 @@
       <c r="M196" t="inlineStr"/>
       <c r="N196" t="inlineStr"/>
       <c r="O196" t="inlineStr"/>
-      <c r="P196" t="n">
-        <v>0</v>
-      </c>
+      <c r="P196" t="inlineStr"/>
       <c r="Q196" t="n">
         <v>0</v>
       </c>
-      <c r="R196" t="inlineStr"/>
+      <c r="R196" t="n">
+        <v>0</v>
+      </c>
       <c r="S196" t="inlineStr"/>
       <c r="T196" t="inlineStr"/>
+      <c r="U196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -11575,13 +11775,13 @@
       <c r="C197" t="inlineStr"/>
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="n">
-        <v>0.7076</v>
+        <v>0.8092</v>
       </c>
       <c r="F197" t="n">
-        <v>0.8458</v>
+        <v>0.8493000000000001</v>
       </c>
       <c r="G197" t="n">
-        <v>-0.1382</v>
+        <v>-0.0401</v>
       </c>
       <c r="H197" t="n">
         <v>0.84</v>
@@ -11607,15 +11807,16 @@
       <c r="M197" t="inlineStr"/>
       <c r="N197" t="inlineStr"/>
       <c r="O197" t="inlineStr"/>
-      <c r="P197" t="n">
-        <v>0.7076</v>
-      </c>
+      <c r="P197" t="inlineStr"/>
       <c r="Q197" t="n">
-        <v>0.7076</v>
-      </c>
-      <c r="R197" t="inlineStr"/>
+        <v>0.95</v>
+      </c>
+      <c r="R197" t="n">
+        <v>0.85</v>
+      </c>
       <c r="S197" t="inlineStr"/>
       <c r="T197" t="inlineStr"/>
+      <c r="U197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -11629,16 +11830,16 @@
       <c r="C198" t="inlineStr"/>
       <c r="D198" t="inlineStr"/>
       <c r="E198" t="n">
-        <v>0.8092</v>
+        <v>0.7927</v>
       </c>
       <c r="F198" t="n">
-        <v>0.7981</v>
+        <v>0.8121</v>
       </c>
       <c r="G198" t="n">
-        <v>0.0111</v>
+        <v>-0.0194</v>
       </c>
       <c r="H198" t="n">
-        <v>0</v>
+        <v>0.6264</v>
       </c>
       <c r="I198" t="n">
         <v>0</v>
@@ -11655,21 +11856,22 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>No suitable candidate matches the semantic role of 'Material' based on name and data evidence.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M198" t="inlineStr"/>
       <c r="N198" t="inlineStr"/>
       <c r="O198" t="inlineStr"/>
-      <c r="P198" t="n">
-        <v>0</v>
-      </c>
+      <c r="P198" t="inlineStr"/>
       <c r="Q198" t="n">
-        <v>0</v>
-      </c>
-      <c r="R198" t="inlineStr"/>
+        <v>0.6264</v>
+      </c>
+      <c r="R198" t="n">
+        <v>0.7927</v>
+      </c>
       <c r="S198" t="inlineStr"/>
       <c r="T198" t="inlineStr"/>
+      <c r="U198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -11686,10 +11888,10 @@
         <v>0.8199</v>
       </c>
       <c r="F199" t="n">
-        <v>0.7965</v>
+        <v>0.8008</v>
       </c>
       <c r="G199" t="n">
-        <v>0.0234</v>
+        <v>0.019</v>
       </c>
       <c r="H199" t="n">
         <v>0</v>
@@ -11709,21 +11911,22 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>All candidates have semantic-role conflicts with the 'Unidade de medida' header.</t>
+          <t>All candidates exhibit semantic-role conflicts with the 'Unidade de medida' header.</t>
         </is>
       </c>
       <c r="M199" t="inlineStr"/>
       <c r="N199" t="inlineStr"/>
       <c r="O199" t="inlineStr"/>
-      <c r="P199" t="n">
-        <v>0</v>
-      </c>
+      <c r="P199" t="inlineStr"/>
       <c r="Q199" t="n">
         <v>0</v>
       </c>
-      <c r="R199" t="inlineStr"/>
+      <c r="R199" t="n">
+        <v>0</v>
+      </c>
       <c r="S199" t="inlineStr"/>
       <c r="T199" t="inlineStr"/>
+      <c r="U199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -11746,10 +11949,10 @@
         <v>1</v>
       </c>
       <c r="F200" t="n">
-        <v>0.7784</v>
+        <v>0.7854</v>
       </c>
       <c r="G200" t="n">
-        <v>0.2216</v>
+        <v>0.2146</v>
       </c>
       <c r="H200" t="inlineStr"/>
       <c r="I200" t="n">
@@ -11778,6 +11981,7 @@
       <c r="R200" t="inlineStr"/>
       <c r="S200" t="inlineStr"/>
       <c r="T200" t="inlineStr"/>
+      <c r="U200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -11791,13 +11995,13 @@
       <c r="C201" t="inlineStr"/>
       <c r="D201" t="inlineStr"/>
       <c r="E201" t="n">
-        <v>0.7349</v>
+        <v>0.7345</v>
       </c>
       <c r="F201" t="n">
         <v>0.7342</v>
       </c>
       <c r="G201" t="n">
-        <v>0.0007</v>
+        <v>0.0003</v>
       </c>
       <c r="H201" t="n">
         <v>0</v>
@@ -11817,21 +12021,22 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>No viable candidates match the required semantic role for 'Município do Local de Fim'.</t>
+          <t>All candidate columns lack relevant data evidence to support a mapping.</t>
         </is>
       </c>
       <c r="M201" t="inlineStr"/>
       <c r="N201" t="inlineStr"/>
       <c r="O201" t="inlineStr"/>
-      <c r="P201" t="n">
-        <v>0</v>
-      </c>
+      <c r="P201" t="inlineStr"/>
       <c r="Q201" t="n">
         <v>0</v>
       </c>
-      <c r="R201" t="inlineStr"/>
+      <c r="R201" t="n">
+        <v>0</v>
+      </c>
       <c r="S201" t="inlineStr"/>
       <c r="T201" t="inlineStr"/>
+      <c r="U201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -11871,21 +12076,22 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>No suitable candidate matches the semantic role of 'Município do Local de Início'.</t>
+          <t>No suitable candidate matches the semantic role of 'Município do Local de Início' as all candidates pertain to tax situations rather than municipalities.</t>
         </is>
       </c>
       <c r="M202" t="inlineStr"/>
       <c r="N202" t="inlineStr"/>
       <c r="O202" t="inlineStr"/>
-      <c r="P202" t="n">
-        <v>0</v>
-      </c>
+      <c r="P202" t="inlineStr"/>
       <c r="Q202" t="n">
         <v>0</v>
       </c>
-      <c r="R202" t="inlineStr"/>
+      <c r="R202" t="n">
+        <v>0</v>
+      </c>
       <c r="S202" t="inlineStr"/>
       <c r="T202" t="inlineStr"/>
+      <c r="U202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -11905,19 +12111,19 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>0.8629</v>
+        <v>0.863</v>
       </c>
       <c r="F203" t="n">
         <v>0</v>
       </c>
       <c r="G203" t="n">
-        <v>0.8629</v>
+        <v>0.863</v>
       </c>
       <c r="H203" t="n">
         <v>0</v>
       </c>
       <c r="I203" t="n">
-        <v>0.8629</v>
+        <v>0.863</v>
       </c>
       <c r="J203" t="inlineStr">
         <is>
@@ -11937,15 +12143,16 @@
       <c r="M203" t="inlineStr"/>
       <c r="N203" t="inlineStr"/>
       <c r="O203" t="inlineStr"/>
-      <c r="P203" t="n">
-        <v>0</v>
-      </c>
+      <c r="P203" t="inlineStr"/>
       <c r="Q203" t="n">
         <v>0</v>
       </c>
-      <c r="R203" t="inlineStr"/>
+      <c r="R203" t="n">
+        <v>0</v>
+      </c>
       <c r="S203" t="inlineStr"/>
       <c r="T203" t="inlineStr"/>
+      <c r="U203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -11985,21 +12192,22 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>All candidate columns contain no relevant data, making it impossible to establish a mapping.</t>
+          <t>No suitable candidate found due to lack of non-empty values in the client columns.</t>
         </is>
       </c>
       <c r="M204" t="inlineStr"/>
       <c r="N204" t="inlineStr"/>
       <c r="O204" t="inlineStr"/>
-      <c r="P204" t="n">
-        <v>0</v>
-      </c>
+      <c r="P204" t="inlineStr"/>
       <c r="Q204" t="n">
-        <v>0.7633</v>
-      </c>
-      <c r="R204" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="R204" t="n">
+        <v>0</v>
+      </c>
       <c r="S204" t="inlineStr"/>
       <c r="T204" t="inlineStr"/>
+      <c r="U204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -12055,13 +12263,16 @@
         <v>0.9493</v>
       </c>
       <c r="O205" t="n">
-        <v>0.9493</v>
-      </c>
-      <c r="P205" t="inlineStr"/>
+        <v>0.9876</v>
+      </c>
+      <c r="P205" t="n">
+        <v>0.9876</v>
+      </c>
       <c r="Q205" t="inlineStr"/>
       <c r="R205" t="inlineStr"/>
       <c r="S205" t="inlineStr"/>
       <c r="T205" t="inlineStr"/>
+      <c r="U205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -12107,15 +12318,16 @@
       <c r="M206" t="inlineStr"/>
       <c r="N206" t="inlineStr"/>
       <c r="O206" t="inlineStr"/>
-      <c r="P206" t="n">
+      <c r="P206" t="inlineStr"/>
+      <c r="Q206" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q206" t="n">
+      <c r="R206" t="n">
         <v>0.8465</v>
       </c>
-      <c r="R206" t="inlineStr"/>
       <c r="S206" t="inlineStr"/>
       <c r="T206" t="inlineStr"/>
+      <c r="U206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -12161,21 +12373,22 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>The name 'Preço Unit.' closely aligns with 'Preço líq.' and both contain numeric values, despite some differences in sample distributions.</t>
+          <t>The candidate 'Preço Unit.' has a high name confidence and a similar numeric profile, despite being a unit price rather than a net price.</t>
         </is>
       </c>
       <c r="M207" t="inlineStr"/>
       <c r="N207" t="inlineStr"/>
       <c r="O207" t="inlineStr"/>
-      <c r="P207" t="n">
-        <v>0.8762</v>
-      </c>
+      <c r="P207" t="inlineStr"/>
       <c r="Q207" t="n">
-        <v>0.8762</v>
-      </c>
-      <c r="R207" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="R207" t="n">
+        <v>0.88</v>
+      </c>
       <c r="S207" t="inlineStr"/>
       <c r="T207" t="inlineStr"/>
+      <c r="U207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -12201,7 +12414,7 @@
         <v>0.8456</v>
       </c>
       <c r="G208" t="n">
-        <v>-0.0043</v>
+        <v>-0.0044</v>
       </c>
       <c r="H208" t="n">
         <v>0.84</v>
@@ -12221,21 +12434,22 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>The name 'Vlr Total' closely aligns with 'Valor líquido' in terms of semantic meaning, and both have similar numeric profiles.</t>
+          <t>The candidate 'Vlr Total' closely matches the semantic role of 'Valor líquido' and has similar numeric characteristics.</t>
         </is>
       </c>
       <c r="M208" t="inlineStr"/>
       <c r="N208" t="inlineStr"/>
       <c r="O208" t="inlineStr"/>
-      <c r="P208" t="n">
-        <v>0.8413</v>
-      </c>
+      <c r="P208" t="inlineStr"/>
       <c r="Q208" t="n">
         <v>0.8413</v>
       </c>
-      <c r="R208" t="inlineStr"/>
+      <c r="R208" t="n">
+        <v>0.8413</v>
+      </c>
       <c r="S208" t="inlineStr"/>
       <c r="T208" t="inlineStr"/>
+      <c r="U208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -12247,28 +12461,28 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>110</v>
+        <v>5</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>NF Eletr.</t>
+          <t>Série NF</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>0.8752</v>
+        <v>0.8829</v>
       </c>
       <c r="F209" t="n">
+        <v>0.8769</v>
+      </c>
+      <c r="G209" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="H209" t="n">
+        <v>0.1718</v>
+      </c>
+      <c r="I209" t="n">
         <v>0.8829</v>
       </c>
-      <c r="G209" t="n">
-        <v>-0.0077</v>
-      </c>
-      <c r="H209" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="I209" t="n">
-        <v>0.8752</v>
-      </c>
       <c r="J209" t="inlineStr">
         <is>
           <t>data</t>
@@ -12281,21 +12495,22 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>The column 'NF Eletr.' has a high name confidence and contains numeric values consistent with invoice numbers.</t>
+          <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
         </is>
       </c>
       <c r="M209" t="inlineStr"/>
       <c r="N209" t="inlineStr"/>
       <c r="O209" t="inlineStr"/>
-      <c r="P209" t="n">
-        <v>0.8752</v>
-      </c>
+      <c r="P209" t="inlineStr"/>
       <c r="Q209" t="n">
-        <v>0.8752</v>
-      </c>
-      <c r="R209" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="R209" t="n">
+        <v>0.868</v>
+      </c>
       <c r="S209" t="inlineStr"/>
       <c r="T209" t="inlineStr"/>
+      <c r="U209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -12312,10 +12527,10 @@
         <v>0.8401999999999999</v>
       </c>
       <c r="F210" t="n">
-        <v>0.8359</v>
+        <v>0.8817</v>
       </c>
       <c r="G210" t="n">
-        <v>0.0043</v>
+        <v>-0.0415</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
@@ -12341,15 +12556,16 @@
       <c r="M210" t="inlineStr"/>
       <c r="N210" t="inlineStr"/>
       <c r="O210" t="inlineStr"/>
-      <c r="P210" t="n">
-        <v>0.8401999999999999</v>
-      </c>
+      <c r="P210" t="inlineStr"/>
       <c r="Q210" t="n">
         <v>0.8401999999999999</v>
       </c>
-      <c r="R210" t="inlineStr"/>
+      <c r="R210" t="n">
+        <v>0.8401999999999999</v>
+      </c>
       <c r="S210" t="inlineStr"/>
       <c r="T210" t="inlineStr"/>
+      <c r="U210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -12395,21 +12611,22 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>The candidate 'Vlr Total' closely matches the semantic role and numeric characteristics of 'Valor Total do Item'.</t>
+          <t>The candidate 'Vlr Total' closely matches the canonical 'Valor Total do Item' in name and numeric profile.</t>
         </is>
       </c>
       <c r="M211" t="inlineStr"/>
       <c r="N211" t="inlineStr"/>
       <c r="O211" t="inlineStr"/>
-      <c r="P211" t="n">
-        <v>0.9</v>
-      </c>
+      <c r="P211" t="inlineStr"/>
       <c r="Q211" t="n">
-        <v>0.895</v>
-      </c>
-      <c r="R211" t="inlineStr"/>
+        <v>0.891</v>
+      </c>
+      <c r="R211" t="n">
+        <v>0.891</v>
+      </c>
       <c r="S211" t="inlineStr"/>
       <c r="T211" t="inlineStr"/>
+      <c r="U211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -12423,16 +12640,16 @@
       <c r="C212" t="inlineStr"/>
       <c r="D212" t="inlineStr"/>
       <c r="E212" t="n">
-        <v>0.7469</v>
+        <v>0.7657</v>
       </c>
       <c r="F212" t="n">
-        <v>0.7657</v>
+        <v>0.761</v>
       </c>
       <c r="G212" t="n">
-        <v>-0.0188</v>
+        <v>0.0046</v>
       </c>
       <c r="H212" t="n">
-        <v>0.1639</v>
+        <v>0</v>
       </c>
       <c r="I212" t="n">
         <v>0</v>
@@ -12449,21 +12666,22 @@
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>The candidate 'Data Entrada' does not match the expected type or content for 'Nome do Fornecedor do Local de Início', which requires a string representing supplier names.</t>
         </is>
       </c>
       <c r="M212" t="inlineStr"/>
       <c r="N212" t="inlineStr"/>
       <c r="O212" t="inlineStr"/>
-      <c r="P212" t="n">
-        <v>0.7469</v>
-      </c>
+      <c r="P212" t="inlineStr"/>
       <c r="Q212" t="n">
-        <v>0.7469</v>
-      </c>
-      <c r="R212" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="R212" t="n">
+        <v>0</v>
+      </c>
       <c r="S212" t="inlineStr"/>
       <c r="T212" t="inlineStr"/>
+      <c r="U212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -12509,21 +12727,22 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>The candidate 'Crd.Transp.' has a high name confidence but all values are zero, indicating no valid data.</t>
+          <t>The candidate 'Crd.Transp.' has a high name confidence but lacks any non-empty values, making it unsuitable for mapping.</t>
         </is>
       </c>
       <c r="M213" t="inlineStr"/>
       <c r="N213" t="inlineStr"/>
       <c r="O213" t="inlineStr"/>
-      <c r="P213" t="n">
-        <v>0</v>
-      </c>
+      <c r="P213" t="inlineStr"/>
       <c r="Q213" t="n">
+        <v>0</v>
+      </c>
+      <c r="R213" t="n">
         <v>0.8643999999999999</v>
       </c>
-      <c r="R213" t="inlineStr"/>
       <c r="S213" t="inlineStr"/>
       <c r="T213" t="inlineStr"/>
+      <c r="U213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -12569,21 +12788,22 @@
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>The candidate 'Aliq. PIS' closely matches the canonical 'Aliquota PIS' in name and has sufficient numeric evidence.</t>
+          <t>The candidate 'Aliq. PIS' closely matches the canonical 'Aliquota PIS' in name and has a strong numeric profile.</t>
         </is>
       </c>
       <c r="M214" t="inlineStr"/>
       <c r="N214" t="inlineStr"/>
       <c r="O214" t="inlineStr"/>
-      <c r="P214" t="n">
-        <v>0.98</v>
-      </c>
+      <c r="P214" t="inlineStr"/>
       <c r="Q214" t="n">
         <v>0.98</v>
       </c>
-      <c r="R214" t="inlineStr"/>
+      <c r="R214" t="n">
+        <v>0.98</v>
+      </c>
       <c r="S214" t="inlineStr"/>
       <c r="T214" t="inlineStr"/>
+      <c r="U214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -12603,7 +12823,7 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>0.8286</v>
+        <v>0.8285</v>
       </c>
       <c r="F215" t="n">
         <v>0.8292</v>
@@ -12615,7 +12835,7 @@
         <v>0.435</v>
       </c>
       <c r="I215" t="n">
-        <v>0.8286</v>
+        <v>0.8285</v>
       </c>
       <c r="J215" t="inlineStr">
         <is>
@@ -12629,21 +12849,22 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>The 'NF Original' column has a strong name match and numeric profile consistent with the 10-digit format of the 'Ref.doc.origem' values.</t>
+          <t>The column 'NF Original' has a strong name match and numeric profile consistent with invoice numbers.</t>
         </is>
       </c>
       <c r="M215" t="inlineStr"/>
       <c r="N215" t="inlineStr"/>
       <c r="O215" t="inlineStr"/>
-      <c r="P215" t="n">
+      <c r="P215" t="inlineStr"/>
+      <c r="Q215" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q215" t="n">
-        <v>0.829</v>
-      </c>
-      <c r="R215" t="inlineStr"/>
+      <c r="R215" t="n">
+        <v>0.8285</v>
+      </c>
       <c r="S215" t="inlineStr"/>
       <c r="T215" t="inlineStr"/>
+      <c r="U215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -12689,21 +12910,22 @@
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>The name 'Antecip.ICMS' closely relates to the 'Texto ICMS' column, and the profile shows a strong numeric presence without semantic conflicts.</t>
+          <t>The name 'Antecip.ICMS' closely aligns with the 'Texto ICMS' column, and the data profile indicates it contains relevant ICMS values.</t>
         </is>
       </c>
       <c r="M216" t="inlineStr"/>
       <c r="N216" t="inlineStr"/>
       <c r="O216" t="inlineStr"/>
-      <c r="P216" t="n">
-        <v>0.8954</v>
-      </c>
+      <c r="P216" t="inlineStr"/>
       <c r="Q216" t="n">
         <v>0.8954</v>
       </c>
-      <c r="R216" t="inlineStr"/>
+      <c r="R216" t="n">
+        <v>0.8954</v>
+      </c>
       <c r="S216" t="inlineStr"/>
       <c r="T216" t="inlineStr"/>
+      <c r="U216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -12723,7 +12945,7 @@
         <v>0.8954</v>
       </c>
       <c r="G217" t="n">
-        <v>-0.0129</v>
+        <v>-0.0128</v>
       </c>
       <c r="H217" t="n">
         <v>0.75</v>
@@ -12749,15 +12971,16 @@
       <c r="M217" t="inlineStr"/>
       <c r="N217" t="inlineStr"/>
       <c r="O217" t="inlineStr"/>
-      <c r="P217" t="n">
-        <v>0.8825</v>
-      </c>
+      <c r="P217" t="inlineStr"/>
       <c r="Q217" t="n">
         <v>0.8825</v>
       </c>
-      <c r="R217" t="inlineStr"/>
+      <c r="R217" t="n">
+        <v>0.8825</v>
+      </c>
       <c r="S217" t="inlineStr"/>
       <c r="T217" t="inlineStr"/>
+      <c r="U217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -12780,10 +13003,10 @@
         <v>0.8959</v>
       </c>
       <c r="F218" t="n">
-        <v>0.8431</v>
+        <v>0.8431999999999999</v>
       </c>
       <c r="G218" t="n">
-        <v>0.0528</v>
+        <v>0.0527</v>
       </c>
       <c r="H218" t="n">
         <v>0</v>
@@ -12809,15 +13032,16 @@
       <c r="M218" t="inlineStr"/>
       <c r="N218" t="inlineStr"/>
       <c r="O218" t="inlineStr"/>
-      <c r="P218" t="n">
-        <v>0.8501</v>
-      </c>
+      <c r="P218" t="inlineStr"/>
       <c r="Q218" t="n">
-        <v>0.8501</v>
-      </c>
-      <c r="R218" t="inlineStr"/>
+        <v>0.8502</v>
+      </c>
+      <c r="R218" t="n">
+        <v>0.8502</v>
+      </c>
       <c r="S218" t="inlineStr"/>
       <c r="T218" t="inlineStr"/>
+      <c r="U218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -12863,21 +13087,22 @@
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>The header 'Sit.Trib.PIS' closely matches the semantic role of 'Lei tributária PIS' and has strong numeric evidence.</t>
+          <t>The candidate 'Sit.Trib.PIS' closely matches the semantic role of 'Lei tributária PIS' with strong numeric evidence.</t>
         </is>
       </c>
       <c r="M219" t="inlineStr"/>
       <c r="N219" t="inlineStr"/>
       <c r="O219" t="inlineStr"/>
-      <c r="P219" t="n">
+      <c r="P219" t="inlineStr"/>
+      <c r="Q219" t="n">
         <v>0.95</v>
       </c>
-      <c r="Q219" t="n">
+      <c r="R219" t="n">
         <v>0.9032</v>
       </c>
-      <c r="R219" t="inlineStr"/>
       <c r="S219" t="inlineStr"/>
       <c r="T219" t="inlineStr"/>
+      <c r="U219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -12900,7 +13125,7 @@
         <v>0.8695000000000001</v>
       </c>
       <c r="F220" t="n">
-        <v>0.8888</v>
+        <v>0.8889</v>
       </c>
       <c r="G220" t="n">
         <v>-0.0193</v>
@@ -12923,7 +13148,7 @@
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>The header 'Trib. IPI' aligns closely with 'CST IPI' and has strong data evidence with a significant non-empty count and valid values.</t>
+          <t>The header 'Trib. IPI' closely matches the canonical 'CST IPI' and has strong data evidence with a significant non-empty count.</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
@@ -12934,18 +13159,19 @@
       <c r="N220" t="n">
         <v>1</v>
       </c>
-      <c r="O220" t="n">
+      <c r="O220" t="inlineStr"/>
+      <c r="P220" t="n">
         <v>0.55</v>
       </c>
-      <c r="P220" t="n">
+      <c r="Q220" t="n">
         <v>0.8695000000000001</v>
       </c>
-      <c r="Q220" t="n">
-        <v>0.8784999999999999</v>
-      </c>
-      <c r="R220" t="inlineStr"/>
+      <c r="R220" t="n">
+        <v>0.8695000000000001</v>
+      </c>
       <c r="S220" t="inlineStr"/>
       <c r="T220" t="inlineStr"/>
+      <c r="U220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -12962,7 +13188,7 @@
         <v>0.8486</v>
       </c>
       <c r="F221" t="n">
-        <v>0.8955</v>
+        <v>0.8954</v>
       </c>
       <c r="G221" t="n">
         <v>-0.0468</v>
@@ -12991,15 +13217,16 @@
       <c r="M221" t="inlineStr"/>
       <c r="N221" t="inlineStr"/>
       <c r="O221" t="inlineStr"/>
-      <c r="P221" t="n">
+      <c r="P221" t="inlineStr"/>
+      <c r="Q221" t="n">
         <v>0.95</v>
       </c>
-      <c r="Q221" t="n">
-        <v>0.8955</v>
-      </c>
-      <c r="R221" t="inlineStr"/>
+      <c r="R221" t="n">
+        <v>0.8954</v>
+      </c>
       <c r="S221" t="inlineStr"/>
       <c r="T221" t="inlineStr"/>
+      <c r="U221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -13022,10 +13249,10 @@
         <v>0.888</v>
       </c>
       <c r="F222" t="n">
-        <v>0.8862</v>
+        <v>0.8865</v>
       </c>
       <c r="G222" t="n">
-        <v>0.0018</v>
+        <v>0.0015</v>
       </c>
       <c r="H222" t="n">
         <v>0.84</v>
@@ -13045,7 +13272,7 @@
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>The column 'Sit.Trib.PIS' has a high name confidence and matches the expected format and content of 'CST PIS'.</t>
+          <t>The candidate 'Sit.Trib.PIS' has a high name confidence and matches the expected format and type for CST PIS.</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
@@ -13056,18 +13283,19 @@
       <c r="N222" t="n">
         <v>1</v>
       </c>
-      <c r="O222" t="n">
+      <c r="O222" t="inlineStr"/>
+      <c r="P222" t="n">
         <v>0.55</v>
-      </c>
-      <c r="P222" t="n">
-        <v>0.888</v>
       </c>
       <c r="Q222" t="n">
         <v>0.888</v>
       </c>
-      <c r="R222" t="inlineStr"/>
+      <c r="R222" t="n">
+        <v>0.888</v>
+      </c>
       <c r="S222" t="inlineStr"/>
       <c r="T222" t="inlineStr"/>
+      <c r="U222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -13113,15 +13341,16 @@
       <c r="M223" t="inlineStr"/>
       <c r="N223" t="inlineStr"/>
       <c r="O223" t="inlineStr"/>
-      <c r="P223" t="n">
-        <v>0</v>
-      </c>
+      <c r="P223" t="inlineStr"/>
       <c r="Q223" t="n">
+        <v>0</v>
+      </c>
+      <c r="R223" t="n">
         <v>0.8996</v>
       </c>
-      <c r="R223" t="inlineStr"/>
       <c r="S223" t="inlineStr"/>
       <c r="T223" t="inlineStr"/>
+      <c r="U223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -13161,21 +13390,22 @@
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>All candidates have empty or all-zero evidence, providing no support for a mapping.</t>
+          <t>All candidates have empty evidence, making it impossible to establish a valid mapping.</t>
         </is>
       </c>
       <c r="M224" t="inlineStr"/>
       <c r="N224" t="inlineStr"/>
       <c r="O224" t="inlineStr"/>
-      <c r="P224" t="n">
-        <v>0</v>
-      </c>
+      <c r="P224" t="inlineStr"/>
       <c r="Q224" t="n">
         <v>0</v>
       </c>
-      <c r="R224" t="inlineStr"/>
+      <c r="R224" t="n">
+        <v>0.7823</v>
+      </c>
       <c r="S224" t="inlineStr"/>
       <c r="T224" t="inlineStr"/>
+      <c r="U224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -13189,13 +13419,13 @@
       <c r="C225" t="inlineStr"/>
       <c r="D225" t="inlineStr"/>
       <c r="E225" t="n">
-        <v>0.7907999999999999</v>
+        <v>0.7909</v>
       </c>
       <c r="F225" t="n">
-        <v>0.7868000000000001</v>
+        <v>0.7872</v>
       </c>
       <c r="G225" t="n">
-        <v>0.0039</v>
+        <v>0.0037</v>
       </c>
       <c r="H225" t="n">
         <v>0</v>
@@ -13221,15 +13451,16 @@
       <c r="M225" t="inlineStr"/>
       <c r="N225" t="inlineStr"/>
       <c r="O225" t="inlineStr"/>
-      <c r="P225" t="n">
-        <v>0</v>
-      </c>
+      <c r="P225" t="inlineStr"/>
       <c r="Q225" t="n">
         <v>0</v>
       </c>
-      <c r="R225" t="inlineStr"/>
+      <c r="R225" t="n">
+        <v>0</v>
+      </c>
       <c r="S225" t="inlineStr"/>
       <c r="T225" t="inlineStr"/>
+      <c r="U225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -13243,13 +13474,13 @@
       <c r="C226" t="inlineStr"/>
       <c r="D226" t="inlineStr"/>
       <c r="E226" t="n">
-        <v>0.7548</v>
+        <v>0.7546</v>
       </c>
       <c r="F226" t="n">
-        <v>0.7716</v>
+        <v>0.7717000000000001</v>
       </c>
       <c r="G226" t="n">
-        <v>-0.0169</v>
+        <v>-0.0171</v>
       </c>
       <c r="H226" t="n">
         <v>0.45</v>
@@ -13275,15 +13506,16 @@
       <c r="M226" t="inlineStr"/>
       <c r="N226" t="inlineStr"/>
       <c r="O226" t="inlineStr"/>
-      <c r="P226" t="n">
+      <c r="P226" t="inlineStr"/>
+      <c r="Q226" t="n">
         <v>0.45</v>
       </c>
-      <c r="Q226" t="n">
-        <v>0.7548</v>
-      </c>
-      <c r="R226" t="inlineStr"/>
+      <c r="R226" t="n">
+        <v>0.7546</v>
+      </c>
       <c r="S226" t="inlineStr"/>
       <c r="T226" t="inlineStr"/>
+      <c r="U226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -13306,7 +13538,7 @@
         <v>0.008</v>
       </c>
       <c r="H227" t="n">
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="I227" t="n">
         <v>0</v>
@@ -13323,21 +13555,22 @@
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>The candidate 'Armazem' has a low name confidence and does not match the numeric format of 'Centro'.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M227" t="inlineStr"/>
       <c r="N227" t="inlineStr"/>
       <c r="O227" t="inlineStr"/>
-      <c r="P227" t="n">
-        <v>0</v>
-      </c>
+      <c r="P227" t="inlineStr"/>
       <c r="Q227" t="n">
-        <v>0</v>
-      </c>
-      <c r="R227" t="inlineStr"/>
+        <v>0.375</v>
+      </c>
+      <c r="R227" t="n">
+        <v>0.7913</v>
+      </c>
       <c r="S227" t="inlineStr"/>
       <c r="T227" t="inlineStr"/>
+      <c r="U227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -13377,21 +13610,22 @@
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>No viable candidates match the semantic role of 'Local do desembaraço aduaneiro' as all candidates are unrelated numeric identifiers.</t>
+          <t>No suitable candidate found due to lack of relevant data evidence.</t>
         </is>
       </c>
       <c r="M228" t="inlineStr"/>
       <c r="N228" t="inlineStr"/>
       <c r="O228" t="inlineStr"/>
-      <c r="P228" t="n">
-        <v>0</v>
-      </c>
+      <c r="P228" t="inlineStr"/>
       <c r="Q228" t="n">
         <v>0</v>
       </c>
-      <c r="R228" t="inlineStr"/>
+      <c r="R228" t="n">
+        <v>0</v>
+      </c>
       <c r="S228" t="inlineStr"/>
       <c r="T228" t="inlineStr"/>
+      <c r="U228" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13437,7 +13671,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-04T23:45:52.274086+00:00</t>
+          <t>2026-08-25T04:37:57.168283+00:00</t>
         </is>
       </c>
     </row>

--- a/mapping_datasul_full.xlsx
+++ b/mapping_datasul_full.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U228"/>
+  <dimension ref="A1:V228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,25 +512,30 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>arithmetic_proof</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>llm_data_confidence</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>llm_final_confidence</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>reviewer_status</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>correct_client_column</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>reviewer_note</t>
         </is>
@@ -574,22 +579,23 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>All candidates exhibit semantic conflicts or lack relevant data evidence.</t>
+          <t>All candidates exhibit semantic header conflicts or lack relevant data evidence.</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
         <v>0</v>
       </c>
-      <c r="S2" t="inlineStr"/>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -635,22 +641,23 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
+          <t>Both columns are labeled as 'Base' with similar numeric characteristics, but all values are zero, indicating no valid data.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="inlineStr"/>
+        <v>0.8787</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.8787</v>
+      </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -673,10 +680,10 @@
         <v>0.8605</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8283</v>
+        <v>0.8282</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0322</v>
+        <v>0.0323</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -703,15 +710,16 @@
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
         <v>0</v>
       </c>
-      <c r="S4" t="inlineStr"/>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -731,7 +739,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.8766</v>
+        <v>0.8764999999999999</v>
       </c>
       <c r="F5" t="n">
         <v>0.8395</v>
@@ -743,7 +751,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8766</v>
+        <v>0.8764999999999999</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -764,15 +772,16 @@
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>0.8766</v>
-      </c>
-      <c r="S5" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.8764999999999999</v>
+      </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -786,13 +795,13 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>0.8381999999999999</v>
+        <v>0.842</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8381999999999999</v>
+        <v>0.842</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -812,22 +821,23 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the tax-family context, indicating they do not align with the 'Isentas CBS' column.</t>
+          <t>All candidates have significant semantic header conflicts or lack relevant data evidence.</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
         <v>0</v>
       </c>
-      <c r="S6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -873,22 +883,23 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>The name 'Retido Outro' has a high confidence score and no semantic conflicts, despite all values being zero.</t>
+          <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="n">
-        <v>0.8437</v>
-      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="n">
-        <v>0.8437</v>
-      </c>
-      <c r="S7" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.8321</v>
+      </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -905,7 +916,7 @@
         <v>0.8495</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8389</v>
+        <v>0.839</v>
       </c>
       <c r="G8" t="n">
         <v>0.0105</v>
@@ -928,22 +939,23 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>All candidates exhibit semantic-role conflicts and lack distinctive evidence.</t>
+          <t>All candidates exhibit semantic header conflicts and lack distinctive row evidence.</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="n">
         <v>0</v>
       </c>
-      <c r="S8" t="inlineStr"/>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -957,13 +969,13 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
-        <v>0.8443000000000001</v>
+        <v>0.8444</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8443000000000001</v>
+        <v>0.8444</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -990,15 +1002,16 @@
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="n">
-        <v>0.8443000000000001</v>
-      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="n">
-        <v>0.8443000000000001</v>
-      </c>
-      <c r="S9" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.8444</v>
+      </c>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1051,15 +1064,16 @@
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="n">
         <v>0</v>
       </c>
-      <c r="S10" t="inlineStr"/>
+      <c r="S10" t="n">
+        <v>0.8832</v>
+      </c>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1079,19 +1093,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.853</v>
+        <v>0.8531</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.853</v>
+        <v>0.8531</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0.853</v>
+        <v>0.8531</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1112,15 +1126,16 @@
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="n">
         <v>0</v>
       </c>
-      <c r="S11" t="inlineStr"/>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1140,19 +1155,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.8835</v>
+        <v>0.8834</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8693</v>
+        <v>0.8692</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0143</v>
+        <v>0.0142</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8835</v>
+        <v>0.8834</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1173,15 +1188,16 @@
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="n">
         <v>0</v>
       </c>
-      <c r="S12" t="inlineStr"/>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1192,22 +1208,28 @@
           <t>Isentas IBSM</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
+      <c r="C13" t="n">
+        <v>303</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Ind Isen Prv</t>
+        </is>
+      </c>
       <c r="E13" t="n">
-        <v>0.8496</v>
+        <v>0.8535</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8496</v>
+        <v>0.8535</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>0.8535</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1216,27 +1238,28 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>review</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>All candidates have significant semantic header conflicts with the original column.</t>
+          <t>The strongest header candidate has weak row evidence; preserve the name-based mapping for review instead of replacing it with a merely similar value shape.</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="n">
         <v>0</v>
       </c>
-      <c r="S13" t="inlineStr"/>
+      <c r="S13" t="n">
+        <v>0.8514</v>
+      </c>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1247,22 +1270,28 @@
           <t>Outras IBSM</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
+      <c r="C14" t="n">
+        <v>303</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Ind Isen Prv</t>
+        </is>
+      </c>
       <c r="E14" t="n">
-        <v>0.8474</v>
+        <v>0.8512999999999999</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8474</v>
+        <v>0.8512999999999999</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>0.8512999999999999</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1271,27 +1300,28 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>review</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the tax-family context, indicating they do not align with the 'Outras IBSM' column.</t>
+          <t>The strongest header candidate has weak row evidence; preserve the name-based mapping for review instead of replacing it with a merely similar value shape.</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="n">
         <v>0</v>
       </c>
-      <c r="S14" t="inlineStr"/>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1305,13 +1335,13 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
-        <v>0.8618</v>
+        <v>0.8626</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8473000000000001</v>
+        <v>0.8477</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0145</v>
+        <v>0.0148</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1338,15 +1368,16 @@
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="n">
         <v>0</v>
       </c>
-      <c r="S15" t="inlineStr"/>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1393,15 +1424,16 @@
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="n">
         <v>0</v>
       </c>
-      <c r="S16" t="inlineStr"/>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1454,15 +1486,16 @@
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="n">
         <v>0</v>
       </c>
-      <c r="S17" t="inlineStr"/>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1515,15 +1548,16 @@
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
         <v>0.8555</v>
       </c>
-      <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1576,15 +1610,16 @@
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="n">
         <v>0</v>
       </c>
-      <c r="S19" t="inlineStr"/>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1604,19 +1639,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.8522</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.8522</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8522</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1637,15 +1672,16 @@
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="n">
-        <v>0.861</v>
-      </c>
-      <c r="S20" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1659,13 +1695,13 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
-        <v>0.8466</v>
+        <v>0.8507</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8465</v>
+        <v>0.8464</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0002</v>
+        <v>0.0042</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1685,22 +1721,23 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the tax-family context, indicating they do not align with the 'Outras IBS' column.</t>
+          <t>All candidates have semantic header conflicts with the 'Outras IBS' column, indicating incompatible tax-family roles.</t>
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="n">
         <v>0</v>
       </c>
-      <c r="S21" t="inlineStr"/>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1714,7 +1751,7 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>0.866</v>
+        <v>0.8659</v>
       </c>
       <c r="F22" t="n">
         <v>0.8485</v>
@@ -1740,22 +1777,23 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>All candidates exhibit semantic header conflicts and lack distinctive non-zero evidence.</t>
+          <t>All candidates have semantic-role conflicts and provide no valid evidence.</t>
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="n">
         <v>0</v>
       </c>
-      <c r="S22" t="inlineStr"/>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1766,22 +1804,28 @@
           <t>Tipo de Imposto IS</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
+      <c r="C23" t="n">
+        <v>157</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Sit.Trib.ISS</t>
+        </is>
+      </c>
       <c r="E23" t="n">
+        <v>0.8501</v>
+      </c>
+      <c r="F23" t="n">
         <v>0.8541</v>
       </c>
-      <c r="F23" t="n">
-        <v>0.8502</v>
-      </c>
       <c r="G23" t="n">
-        <v>0.004</v>
+        <v>-0.004</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>0.8501</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1790,27 +1834,28 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>review</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>No viable candidates due to lack of relevant data and semantic conflicts.</t>
+          <t>The header 'Sit.Trib.ISS' aligns with the tax status role, despite all-zero values.</t>
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="inlineStr"/>
+        <v>0.8501</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.8501</v>
+      </c>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1822,27 +1867,27 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Vlr Base IPI</t>
+          <t>Base Imp 2</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.8801</v>
+        <v>0.8835</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8834</v>
+        <v>0.8813</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.0033</v>
+        <v>0.0022</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8801</v>
+        <v>0.8835</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1856,22 +1901,23 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>The column 'Vlr Base IPI' has a higher name confidence and contains varied non-zero samples, indicating it may represent a base value.</t>
+          <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="n">
-        <v>0.8801</v>
-      </c>
+      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="n">
-        <v>0.8801</v>
-      </c>
-      <c r="S24" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1894,7 +1940,7 @@
         <v>0.8672</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8633</v>
+        <v>0.8633999999999999</v>
       </c>
       <c r="G25" t="n">
         <v>0.0038</v>
@@ -1917,22 +1963,23 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>The candidate 'Aliq ICMS So' has a high name confidence but lacks distinctive sample overlap and all values are zero.</t>
+          <t>The candidate 'Aliq ICMS So' has a high name confidence but both columns contain only zeros, indicating no valid data evidence.</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q25" t="inlineStr"/>
       <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
         <v>0.8672</v>
       </c>
-      <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1944,28 +1991,28 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Vlr ICMS Com</t>
+          <t>Vlr Isen ICM</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.8348</v>
+        <v>0.8721</v>
       </c>
       <c r="F26" t="n">
+        <v>0.8703</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
         <v>0.8721</v>
       </c>
-      <c r="G26" t="n">
-        <v>-0.0373</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.8348</v>
-      </c>
       <c r="J26" t="inlineStr">
         <is>
           <t>data</t>
@@ -1978,22 +2025,23 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>The name 'Vlr ICMS Com' closely relates to tax values, and while both columns show high zero fractions, the name suggests a relevant tax context.</t>
+          <t>The candidate 'Vlr Isen ICM' has a high name confidence and matches the tax exemption context, despite both having a high zero fraction.</t>
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="n">
-        <v>0.8348</v>
-      </c>
+      <c r="Q26" t="inlineStr"/>
       <c r="R26" t="n">
-        <v>0.8348</v>
-      </c>
-      <c r="S26" t="inlineStr"/>
+        <v>0.8721</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.8721</v>
+      </c>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2007,13 +2055,13 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="n">
-        <v>0.8626</v>
+        <v>0.8646</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8401</v>
+        <v>0.8401999999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0225</v>
+        <v>0.0245</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -2033,22 +2081,23 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>All candidates exhibit semantic-role conflicts or lack relevant data evidence.</t>
+          <t>All candidates have semantic-role conflicts or all-zero evidence, indicating no suitable mapping.</t>
         </is>
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q27" t="inlineStr"/>
       <c r="R27" t="n">
         <v>0</v>
       </c>
-      <c r="S27" t="inlineStr"/>
+      <c r="S27" t="n">
+        <v>0.8646</v>
+      </c>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2062,13 +2111,13 @@
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="n">
-        <v>0.8719</v>
+        <v>0.8746</v>
       </c>
       <c r="F28" t="n">
         <v>0.8588</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0131</v>
+        <v>0.0158</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -2095,15 +2144,16 @@
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q28" t="inlineStr"/>
       <c r="R28" t="n">
         <v>0</v>
       </c>
-      <c r="S28" t="inlineStr"/>
+      <c r="S28" t="n">
+        <v>0.8554</v>
+      </c>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2120,10 +2170,10 @@
         <v>0.8332000000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8326</v>
+        <v>0.8325</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0007</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -2150,15 +2200,16 @@
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q29" t="inlineStr"/>
       <c r="R29" t="n">
         <v>0</v>
       </c>
-      <c r="S29" t="inlineStr"/>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2172,13 +2223,13 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="n">
-        <v>0.7519</v>
+        <v>0.7521</v>
       </c>
       <c r="F30" t="n">
         <v>0.8106</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.0587</v>
+        <v>-0.0585</v>
       </c>
       <c r="H30" t="n">
         <v>0.84</v>
@@ -2205,15 +2256,16 @@
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="n">
-        <v>0.7519</v>
-      </c>
+      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="n">
-        <v>0.7519</v>
-      </c>
-      <c r="S30" t="inlineStr"/>
+        <v>0.7521</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.7521</v>
+      </c>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2233,10 +2285,10 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.8611</v>
+        <v>0.8612</v>
       </c>
       <c r="F31" t="n">
-        <v>0.8181</v>
+        <v>0.8182</v>
       </c>
       <c r="G31" t="n">
         <v>0.043</v>
@@ -2245,7 +2297,7 @@
         <v>0.84</v>
       </c>
       <c r="I31" t="n">
-        <v>0.8611</v>
+        <v>0.8612</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -2259,22 +2311,23 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>The header 'Data Emissão' closely matches 'Data de lançamento' in meaning, both representing dates related to document issuance.</t>
+          <t>The header 'Data Emissão' closely matches 'Data de lançamento' in meaning, both representing dates related to invoices.</t>
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="n">
-        <v>0.8611</v>
-      </c>
+      <c r="Q31" t="inlineStr"/>
       <c r="R31" t="n">
-        <v>0.8611</v>
-      </c>
-      <c r="S31" t="inlineStr"/>
+        <v>0.8612</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.8612</v>
+      </c>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2321,15 +2374,16 @@
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="n">
-        <v>0.8414</v>
-      </c>
+      <c r="Q32" t="inlineStr"/>
       <c r="R32" t="n">
         <v>0.8414</v>
       </c>
-      <c r="S32" t="inlineStr"/>
+      <c r="S32" t="n">
+        <v>0.8414</v>
+      </c>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2352,10 +2406,10 @@
         <v>0.9176</v>
       </c>
       <c r="F33" t="n">
-        <v>0.8362000000000001</v>
+        <v>0.8361</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0814</v>
+        <v>0.0815</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -2382,15 +2436,16 @@
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="n">
-        <v>0.9</v>
-      </c>
+      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="n">
         <v>0.9</v>
       </c>
-      <c r="S33" t="inlineStr"/>
+      <c r="S33" t="n">
+        <v>0.9</v>
+      </c>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2410,7 +2465,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.9112</v>
+        <v>0.9111</v>
       </c>
       <c r="F34" t="n">
         <v>0.926</v>
@@ -2443,15 +2498,16 @@
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="n">
-        <v>0.9112</v>
-      </c>
+      <c r="Q34" t="inlineStr"/>
       <c r="R34" t="n">
-        <v>0.9112</v>
-      </c>
-      <c r="S34" t="inlineStr"/>
+        <v>0.9111</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0.9111</v>
+      </c>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2474,16 +2530,16 @@
         <v>0.8519</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9101</v>
+        <v>0.9071</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.0582</v>
+        <v>-0.0552</v>
       </c>
       <c r="H35" t="n">
         <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>0.9407</v>
+        <v>0.9408</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2517,6 +2573,7 @@
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2569,15 +2626,16 @@
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q36" t="inlineStr"/>
       <c r="R36" t="n">
         <v>0</v>
       </c>
-      <c r="S36" t="inlineStr"/>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2617,22 +2675,23 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>The candidate 'ID Tributos' has a different semantic role and no distinctive sample overlap with 'ID parceiro', indicating no mapping.</t>
+          <t>No candidate column matches the semantic role of 'ID parceiro', which is a numeric identifier.</t>
         </is>
       </c>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q37" t="inlineStr"/>
       <c r="R37" t="n">
         <v>0</v>
       </c>
-      <c r="S37" t="inlineStr"/>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2655,7 +2714,7 @@
         <v>0.0032</v>
       </c>
       <c r="H38" t="n">
-        <v>0.4054</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -2672,22 +2731,23 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>No candidate column matches the semantic role of 'Nome' based on the provided evidence.</t>
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="n">
-        <v>0.8494</v>
-      </c>
-      <c r="S38" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2734,15 +2794,16 @@
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="Q39" t="inlineStr"/>
       <c r="R39" t="n">
         <v>0.5</v>
       </c>
-      <c r="S39" t="inlineStr"/>
+      <c r="S39" t="n">
+        <v>0.5</v>
+      </c>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2756,13 +2817,13 @@
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="n">
-        <v>0.7937</v>
+        <v>0.7938</v>
       </c>
       <c r="F40" t="n">
         <v>0.8041</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.0104</v>
+        <v>-0.0103</v>
       </c>
       <c r="H40" t="n">
         <v>0.45</v>
@@ -2789,15 +2850,16 @@
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="n">
-        <v>0.7937</v>
-      </c>
+      <c r="Q40" t="inlineStr"/>
       <c r="R40" t="n">
-        <v>0.7937</v>
-      </c>
-      <c r="S40" t="inlineStr"/>
+        <v>0.7938</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0.7938</v>
+      </c>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2843,22 +2905,23 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>The name 'Vlr Total' closely matches 'Val.Total NF' and the numeric profiles are compatible.</t>
+          <t>The candidate 'Vlr Total' closely matches the semantic role and numeric characteristics of 'Val.Total NF', with a high name confidence and similar numeric profiles.</t>
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="n">
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="n">
         <v>0.9</v>
       </c>
-      <c r="R41" t="n">
+      <c r="S41" t="n">
         <v>0.88</v>
       </c>
-      <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2909,11 +2972,16 @@
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>valor = base x aliquota holds for icms on 5570 rows at fit 0.998</t>
+        </is>
+      </c>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2964,11 +3032,16 @@
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>valor = base x aliquota holds for icms on 5570 rows at fit 0.998</t>
+        </is>
+      </c>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3015,15 +3088,16 @@
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="Q44" t="inlineStr"/>
       <c r="R44" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="S44" t="n">
         <v>0.9155</v>
       </c>
-      <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3070,15 +3144,16 @@
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="n">
-        <v>0.874</v>
-      </c>
+      <c r="Q45" t="inlineStr"/>
       <c r="R45" t="n">
         <v>0.874</v>
       </c>
-      <c r="S45" t="inlineStr"/>
+      <c r="S45" t="n">
+        <v>0.874</v>
+      </c>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3095,10 +3170,10 @@
         <v>0.8991</v>
       </c>
       <c r="F46" t="n">
-        <v>0.8871</v>
+        <v>0.8872</v>
       </c>
       <c r="G46" t="n">
-        <v>0.012</v>
+        <v>0.0119</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -3125,15 +3200,16 @@
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q46" t="inlineStr"/>
       <c r="R46" t="n">
         <v>0</v>
       </c>
-      <c r="S46" t="inlineStr"/>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
       <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3179,22 +3255,23 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>The candidate 'Vlr Isen ICM' has a compatible numeric type and no semantic header conflict.</t>
+          <t>The candidate 'Vlr Isen ICM' has a compatible numeric type and no semantic header conflict, making it the best match despite the presence of zeros.</t>
         </is>
       </c>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="n">
-        <v>0.8691</v>
-      </c>
+      <c r="Q47" t="inlineStr"/>
       <c r="R47" t="n">
         <v>0.8691</v>
       </c>
-      <c r="S47" t="inlineStr"/>
+      <c r="S47" t="n">
+        <v>0.8691</v>
+      </c>
       <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3247,15 +3324,16 @@
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q48" t="inlineStr"/>
       <c r="R48" t="n">
         <v>0</v>
       </c>
-      <c r="S48" t="inlineStr"/>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
       <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3308,15 +3386,20 @@
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="n">
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>valor = base x aliquota holds for ipi on 3275 rows at fit 0.9979</t>
+        </is>
+      </c>
+      <c r="R49" t="n">
         <v>0.9979</v>
       </c>
-      <c r="R49" t="n">
+      <c r="S49" t="n">
         <v>0.9491000000000001</v>
       </c>
-      <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3367,11 +3450,16 @@
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>valor = base x aliquota holds for ipi on 3275 rows at fit 0.9979</t>
+        </is>
+      </c>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3385,7 +3473,7 @@
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="n">
-        <v>0.9011</v>
+        <v>0.9012</v>
       </c>
       <c r="F51" t="n">
         <v>0.897</v>
@@ -3418,15 +3506,16 @@
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="n">
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="n">
         <v>0.091</v>
       </c>
-      <c r="R51" t="n">
-        <v>0.9011</v>
-      </c>
-      <c r="S51" t="inlineStr"/>
+      <c r="S51" t="n">
+        <v>0.9012</v>
+      </c>
       <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3449,7 +3538,7 @@
         <v>0.8981</v>
       </c>
       <c r="F52" t="n">
-        <v>0.878</v>
+        <v>0.8781</v>
       </c>
       <c r="G52" t="n">
         <v>0.02</v>
@@ -3479,15 +3568,16 @@
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="n">
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
         <v>0.8981</v>
       </c>
-      <c r="R52" t="n">
-        <v>0.8981</v>
-      </c>
-      <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3533,22 +3623,23 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>The name 'Base Pis' closely matches 'Base PIS' with high name confidence, and while the numeric evidence is weak, the profile similarity is very high.</t>
+          <t>The name 'Base Pis' closely matches 'Base PIS' with high name confidence, and while the numeric evidence is weak, the semantic role aligns.</t>
         </is>
       </c>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="n">
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="n">
         <v>0.909</v>
       </c>
-      <c r="R53" t="n">
-        <v>0.954</v>
-      </c>
-      <c r="S53" t="inlineStr"/>
+      <c r="S53" t="n">
+        <v>0.955</v>
+      </c>
       <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -3604,6 +3695,7 @@
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -3626,10 +3718,10 @@
         <v>1</v>
       </c>
       <c r="F55" t="n">
-        <v>0.9263</v>
+        <v>0.9264</v>
       </c>
       <c r="G55" t="n">
-        <v>0.0737</v>
+        <v>0.0736</v>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="n">
@@ -3659,6 +3751,7 @@
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr"/>
       <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -3681,10 +3774,10 @@
         <v>1</v>
       </c>
       <c r="F56" t="n">
-        <v>0.8995</v>
+        <v>0.8996</v>
       </c>
       <c r="G56" t="n">
-        <v>0.1005</v>
+        <v>0.1004</v>
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="n">
@@ -3714,6 +3807,7 @@
       <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3733,17 +3827,17 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.9414</v>
+        <v>0.9415</v>
       </c>
       <c r="F57" t="n">
-        <v>0.8270999999999999</v>
+        <v>0.8272</v>
       </c>
       <c r="G57" t="n">
         <v>0.1143</v>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="n">
-        <v>0.9414</v>
+        <v>0.9415</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -3769,6 +3863,7 @@
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3791,10 +3886,10 @@
         <v>0.9409</v>
       </c>
       <c r="F58" t="n">
-        <v>0.826</v>
+        <v>0.827</v>
       </c>
       <c r="G58" t="n">
-        <v>0.1149</v>
+        <v>0.1139</v>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="n">
@@ -3824,6 +3919,7 @@
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr"/>
       <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3869,22 +3965,23 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>The header 'Obs Liv. Fis' suggests observational notes, which aligns with the 'Observações' column's content.</t>
+          <t>The header 'Obs Liv. Fis' suggests observations related to fiscal documents, aligning with the 'Observações' column's content.</t>
         </is>
       </c>
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="n">
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="n">
         <v>0.8</v>
       </c>
-      <c r="R59" t="n">
+      <c r="S59" t="n">
         <v>0.826</v>
       </c>
-      <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3904,10 +4001,10 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.8768</v>
+        <v>0.8767</v>
       </c>
       <c r="F60" t="n">
-        <v>0.7951</v>
+        <v>0.795</v>
       </c>
       <c r="G60" t="n">
         <v>0.08169999999999999</v>
@@ -3930,22 +4027,23 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>The candidate 'Chave Nfe' has a high name confidence and matches the expected format and characteristics of the 'Chave de acesso'.</t>
+          <t>The candidate 'Chave Nfe' has a high name confidence and matches the expected format and characteristics of the 'Chave de acesso' with 44-digit numeric values.</t>
         </is>
       </c>
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="n">
-        <v>0.9</v>
-      </c>
+      <c r="Q60" t="inlineStr"/>
       <c r="R60" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="S60" t="inlineStr"/>
+        <v>0.95</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0.93</v>
+      </c>
       <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -3965,19 +4063,19 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.9093</v>
+        <v>0.9092</v>
       </c>
       <c r="F61" t="n">
-        <v>0.8498</v>
+        <v>0.8497</v>
       </c>
       <c r="G61" t="n">
-        <v>0.0595</v>
+        <v>0.0596</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>0.9093</v>
+        <v>0.9092</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -3998,15 +4096,16 @@
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="n">
-        <v>0.9</v>
-      </c>
+      <c r="Q61" t="inlineStr"/>
       <c r="R61" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="S61" t="inlineStr"/>
+        <v>0.8375</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0.8734</v>
+      </c>
       <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -4052,22 +4151,23 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>The header 'Data Emissão' closely matches the semantic role of 'Data documento' with strong datetime evidence.</t>
+          <t>The header 'Data Emissão' closely matches the semantic role of 'Data documento' and both have similar datetime profiles.</t>
         </is>
       </c>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="n">
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="n">
         <v>0.8752</v>
       </c>
-      <c r="R62" t="n">
+      <c r="S62" t="n">
         <v>0.8794999999999999</v>
       </c>
-      <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr"/>
+      <c r="V62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -4084,10 +4184,10 @@
         <v>0.8016</v>
       </c>
       <c r="F63" t="n">
-        <v>0.7685</v>
+        <v>0.7685999999999999</v>
       </c>
       <c r="G63" t="n">
-        <v>0.0331</v>
+        <v>0.033</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -4107,22 +4207,23 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>No suitable candidate matches the semantic role of 'Criado por'.</t>
+          <t>No candidate column provides relevant mapping evidence for 'Criado por'.</t>
         </is>
       </c>
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q63" t="inlineStr"/>
       <c r="R63" t="n">
         <v>0</v>
       </c>
-      <c r="S63" t="inlineStr"/>
+      <c r="S63" t="n">
+        <v>0</v>
+      </c>
       <c r="T63" t="inlineStr"/>
       <c r="U63" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -4136,13 +4237,13 @@
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="n">
-        <v>0.7929</v>
+        <v>0.7927999999999999</v>
       </c>
       <c r="F64" t="n">
-        <v>0.7577</v>
+        <v>0.7594</v>
       </c>
       <c r="G64" t="n">
-        <v>0.0352</v>
+        <v>0.0334</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -4162,22 +4263,23 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>No suitable candidate matches the semantic role of 'Modificado por'.</t>
+          <t>No candidate column matches the semantic role of 'Modificado por'.</t>
         </is>
       </c>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q64" t="inlineStr"/>
       <c r="R64" t="n">
         <v>0</v>
       </c>
-      <c r="S64" t="inlineStr"/>
+      <c r="S64" t="n">
+        <v>0</v>
+      </c>
       <c r="T64" t="inlineStr"/>
       <c r="U64" t="inlineStr"/>
+      <c r="V64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -4194,10 +4296,10 @@
         <v>0.8379</v>
       </c>
       <c r="F65" t="n">
-        <v>0.8155</v>
+        <v>0.8175</v>
       </c>
       <c r="G65" t="n">
-        <v>0.0224</v>
+        <v>0.0203</v>
       </c>
       <c r="H65" t="n">
         <v>0.45</v>
@@ -4224,15 +4326,16 @@
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="n">
-        <v>0.8379</v>
-      </c>
+      <c r="Q65" t="inlineStr"/>
       <c r="R65" t="n">
         <v>0.8379</v>
       </c>
-      <c r="S65" t="inlineStr"/>
+      <c r="S65" t="n">
+        <v>0.8379</v>
+      </c>
       <c r="T65" t="inlineStr"/>
       <c r="U65" t="inlineStr"/>
+      <c r="V65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -4285,15 +4388,16 @@
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="n">
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S66" t="n">
         <v>0.845</v>
       </c>
-      <c r="R66" t="n">
-        <v>0.845</v>
-      </c>
-      <c r="S66" t="inlineStr"/>
       <c r="T66" t="inlineStr"/>
       <c r="U66" t="inlineStr"/>
+      <c r="V66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -4316,7 +4420,7 @@
         <v>0.8584000000000001</v>
       </c>
       <c r="F67" t="n">
-        <v>0.8586</v>
+        <v>0.8587</v>
       </c>
       <c r="G67" t="n">
         <v>-0.0002</v>
@@ -4339,22 +4443,23 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>The candidate 'NF Original' closely matches the document ID role of 'Nº doc.original' with strong numeric evidence.</t>
+          <t>The candidate 'NF Original' has a strong name match and a numeric profile consistent with invoice numbers.</t>
         </is>
       </c>
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="n">
-        <v>0.8584000000000001</v>
-      </c>
+      <c r="Q67" t="inlineStr"/>
       <c r="R67" t="n">
         <v>0.8584000000000001</v>
       </c>
-      <c r="S67" t="inlineStr"/>
+      <c r="S67" t="n">
+        <v>0.8584000000000001</v>
+      </c>
       <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr"/>
+      <c r="V67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -4374,19 +4479,19 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.8507</v>
+        <v>0.8508</v>
       </c>
       <c r="F68" t="n">
-        <v>0.8332000000000001</v>
+        <v>0.8333</v>
       </c>
       <c r="G68" t="n">
-        <v>0.0176</v>
+        <v>0.0175</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>0.8507</v>
+        <v>0.8508</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -4400,22 +4505,23 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>The candidate column has no non-empty values, making it incompatible despite a reasonable name match.</t>
+          <t>The candidate column has no data evidence and only a weak name match.</t>
         </is>
       </c>
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q68" t="inlineStr"/>
       <c r="R68" t="n">
-        <v>0.8507</v>
-      </c>
-      <c r="S68" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="S68" t="n">
+        <v>0.8508</v>
+      </c>
       <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr"/>
+      <c r="V68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -4432,7 +4538,7 @@
         <v>0.8661</v>
       </c>
       <c r="F69" t="n">
-        <v>0.8497</v>
+        <v>0.8498</v>
       </c>
       <c r="G69" t="n">
         <v>0.0163</v>
@@ -4462,15 +4568,16 @@
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q69" t="inlineStr"/>
       <c r="R69" t="n">
         <v>0</v>
       </c>
-      <c r="S69" t="inlineStr"/>
+      <c r="S69" t="n">
+        <v>0</v>
+      </c>
       <c r="T69" t="inlineStr"/>
       <c r="U69" t="inlineStr"/>
+      <c r="V69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -4490,7 +4597,7 @@
         <v>0.7958</v>
       </c>
       <c r="G70" t="n">
-        <v>0.0083</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -4510,22 +4617,23 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>No suitable candidate matches the semantic role of 'Condições pagamento' based on the evidence provided.</t>
+          <t>No suitable candidate matches the semantic role of 'Condições pagamento' based on the available evidence.</t>
         </is>
       </c>
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q70" t="inlineStr"/>
       <c r="R70" t="n">
         <v>0</v>
       </c>
-      <c r="S70" t="inlineStr"/>
+      <c r="S70" t="n">
+        <v>0.8041</v>
+      </c>
       <c r="T70" t="inlineStr"/>
       <c r="U70" t="inlineStr"/>
+      <c r="V70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -4578,15 +4686,16 @@
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr"/>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q71" t="inlineStr"/>
       <c r="R71" t="n">
         <v>0</v>
       </c>
-      <c r="S71" t="inlineStr"/>
+      <c r="S71" t="n">
+        <v>0.8559</v>
+      </c>
       <c r="T71" t="inlineStr"/>
       <c r="U71" t="inlineStr"/>
+      <c r="V71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -4609,10 +4718,10 @@
         <v>0.8605</v>
       </c>
       <c r="F72" t="n">
-        <v>0.7678</v>
+        <v>0.7677</v>
       </c>
       <c r="G72" t="n">
-        <v>0.0927</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -4639,15 +4748,16 @@
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q72" t="inlineStr"/>
       <c r="R72" t="n">
-        <v>0.8614000000000001</v>
-      </c>
-      <c r="S72" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="S72" t="n">
+        <v>0</v>
+      </c>
       <c r="T72" t="inlineStr"/>
       <c r="U72" t="inlineStr"/>
+      <c r="V72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -4661,13 +4771,13 @@
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="n">
-        <v>0.7991</v>
+        <v>0.7998</v>
       </c>
       <c r="F73" t="n">
-        <v>0.8494</v>
+        <v>0.849</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.0503</v>
+        <v>-0.0492</v>
       </c>
       <c r="H73" t="n">
         <v>0.84</v>
@@ -4694,15 +4804,16 @@
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="n">
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="n">
         <v>0.9667</v>
       </c>
-      <c r="R73" t="n">
-        <v>0.8494</v>
-      </c>
-      <c r="S73" t="inlineStr"/>
+      <c r="S73" t="n">
+        <v>0.849</v>
+      </c>
       <c r="T73" t="inlineStr"/>
       <c r="U73" t="inlineStr"/>
+      <c r="V73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -4722,19 +4833,19 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.8758</v>
+        <v>0.8763</v>
       </c>
       <c r="F74" t="n">
         <v>0.8493000000000001</v>
       </c>
       <c r="G74" t="n">
-        <v>0.0265</v>
+        <v>0.027</v>
       </c>
       <c r="H74" t="n">
         <v>0.65</v>
       </c>
       <c r="I74" t="n">
-        <v>0.8758</v>
+        <v>0.8763</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -4748,22 +4859,23 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>The candidate 'Item NF Orig' has a high name confidence and numeric profile similarity, but lacks distinctive sample overlap.</t>
+          <t>The candidate 'Item NF Orig' has a high name confidence and a numeric profile, but lacks distinctive sample overlap with the reference.</t>
         </is>
       </c>
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="n">
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="n">
         <v>0.65</v>
       </c>
-      <c r="R74" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="S74" t="inlineStr"/>
+      <c r="S74" t="n">
+        <v>0.8763</v>
+      </c>
       <c r="T74" t="inlineStr"/>
       <c r="U74" t="inlineStr"/>
+      <c r="V74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -4810,15 +4922,16 @@
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q75" t="inlineStr"/>
       <c r="R75" t="n">
         <v>0</v>
       </c>
-      <c r="S75" t="inlineStr"/>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
       <c r="T75" t="inlineStr"/>
       <c r="U75" t="inlineStr"/>
+      <c r="V75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -4832,13 +4945,13 @@
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="n">
-        <v>0.8042</v>
+        <v>0.8075</v>
       </c>
       <c r="F76" t="n">
-        <v>0.8025</v>
+        <v>0.8024</v>
       </c>
       <c r="G76" t="n">
-        <v>0.0017</v>
+        <v>0.005</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -4858,22 +4971,23 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>All candidates have insufficient evidence or conflicting roles, making a mapping unsupported.</t>
+          <t>No suitable candidate found due to lack of relevant data evidence.</t>
         </is>
       </c>
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q76" t="inlineStr"/>
       <c r="R76" t="n">
         <v>0</v>
       </c>
-      <c r="S76" t="inlineStr"/>
+      <c r="S76" t="n">
+        <v>0</v>
+      </c>
       <c r="T76" t="inlineStr"/>
       <c r="U76" t="inlineStr"/>
+      <c r="V76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -4890,7 +5004,7 @@
         <v>0.8317</v>
       </c>
       <c r="F77" t="n">
-        <v>0.823</v>
+        <v>0.8231000000000001</v>
       </c>
       <c r="G77" t="n">
         <v>0.0086</v>
@@ -4920,15 +5034,16 @@
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q77" t="inlineStr"/>
       <c r="R77" t="n">
         <v>0</v>
       </c>
-      <c r="S77" t="inlineStr"/>
+      <c r="S77" t="n">
+        <v>0</v>
+      </c>
       <c r="T77" t="inlineStr"/>
       <c r="U77" t="inlineStr"/>
+      <c r="V77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -4951,7 +5066,7 @@
         <v>0.9081</v>
       </c>
       <c r="F78" t="n">
-        <v>0.8306</v>
+        <v>0.8305</v>
       </c>
       <c r="G78" t="n">
         <v>0.0775</v>
@@ -4981,15 +5096,16 @@
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="n">
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="n">
         <v>0.9199000000000001</v>
       </c>
-      <c r="R78" t="n">
+      <c r="S78" t="n">
         <v>0.914</v>
       </c>
-      <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr"/>
       <c r="U78" t="inlineStr"/>
+      <c r="V78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -5012,7 +5128,7 @@
         <v>0.8129</v>
       </c>
       <c r="F79" t="n">
-        <v>0.883</v>
+        <v>0.8831</v>
       </c>
       <c r="G79" t="n">
         <v>-0.0702</v>
@@ -5035,22 +5151,23 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>The header 'Num. RPS' closely aligns with the semantic role of 'Nº de serviço' and has informative data evidence.</t>
+          <t>The name 'Num. RPS' closely relates to 'Nº de serviço' and has informative data evidence.</t>
         </is>
       </c>
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="n">
-        <v>0.8129</v>
-      </c>
+      <c r="Q79" t="inlineStr"/>
       <c r="R79" t="n">
         <v>0.8129</v>
       </c>
-      <c r="S79" t="inlineStr"/>
+      <c r="S79" t="n">
+        <v>0.8129</v>
+      </c>
       <c r="T79" t="inlineStr"/>
       <c r="U79" t="inlineStr"/>
+      <c r="V79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -5070,7 +5187,7 @@
         <v>0.8035</v>
       </c>
       <c r="G80" t="n">
-        <v>0.0412</v>
+        <v>0.0411</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -5090,22 +5207,23 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>All candidate columns have insufficient evidence or semantic conflicts, making them incompatible.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q80" t="inlineStr"/>
       <c r="R80" t="n">
-        <v>0</v>
-      </c>
-      <c r="S80" t="inlineStr"/>
+        <v>0.8447</v>
+      </c>
+      <c r="S80" t="n">
+        <v>0.8447</v>
+      </c>
       <c r="T80" t="inlineStr"/>
       <c r="U80" t="inlineStr"/>
+      <c r="V80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -5119,7 +5237,7 @@
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="n">
-        <v>0.8079</v>
+        <v>0.8078</v>
       </c>
       <c r="F81" t="n">
         <v>0.842</v>
@@ -5152,15 +5270,16 @@
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="n">
-        <v>0.8079</v>
-      </c>
+      <c r="Q81" t="inlineStr"/>
       <c r="R81" t="n">
+        <v>0.8078</v>
+      </c>
+      <c r="S81" t="n">
         <v>0.825</v>
       </c>
-      <c r="S81" t="inlineStr"/>
       <c r="T81" t="inlineStr"/>
       <c r="U81" t="inlineStr"/>
+      <c r="V81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -5177,7 +5296,7 @@
         <v>0.7775</v>
       </c>
       <c r="F82" t="n">
-        <v>0.7881</v>
+        <v>0.788</v>
       </c>
       <c r="G82" t="n">
         <v>-0.0106</v>
@@ -5207,15 +5326,16 @@
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
       <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="n">
-        <v>0.7775</v>
-      </c>
+      <c r="Q82" t="inlineStr"/>
       <c r="R82" t="n">
         <v>0.7775</v>
       </c>
-      <c r="S82" t="inlineStr"/>
+      <c r="S82" t="n">
+        <v>0.7775</v>
+      </c>
       <c r="T82" t="inlineStr"/>
       <c r="U82" t="inlineStr"/>
+      <c r="V82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -5229,13 +5349,13 @@
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="n">
-        <v>0.8279</v>
+        <v>0.8278</v>
       </c>
       <c r="F83" t="n">
-        <v>0.8323</v>
+        <v>0.8322000000000001</v>
       </c>
       <c r="G83" t="n">
-        <v>-0.0044</v>
+        <v>-0.0045</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -5262,15 +5382,16 @@
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr"/>
-      <c r="Q83" t="n">
-        <v>0.8279</v>
-      </c>
+      <c r="Q83" t="inlineStr"/>
       <c r="R83" t="n">
-        <v>0.8279</v>
-      </c>
-      <c r="S83" t="inlineStr"/>
+        <v>0.8278</v>
+      </c>
+      <c r="S83" t="n">
+        <v>0.8278</v>
+      </c>
       <c r="T83" t="inlineStr"/>
       <c r="U83" t="inlineStr"/>
+      <c r="V83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -5284,13 +5405,13 @@
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="n">
-        <v>0.7961</v>
+        <v>0.7786999999999999</v>
       </c>
       <c r="F84" t="n">
-        <v>0.7911</v>
+        <v>0.7959000000000001</v>
       </c>
       <c r="G84" t="n">
-        <v>0.005</v>
+        <v>-0.0172</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -5310,22 +5431,23 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>All candidates have zero values and lack distinctive evidence to support a mapping.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
       <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q84" t="inlineStr"/>
       <c r="R84" t="n">
-        <v>0</v>
-      </c>
-      <c r="S84" t="inlineStr"/>
+        <v>0.7786999999999999</v>
+      </c>
+      <c r="S84" t="n">
+        <v>0.7786999999999999</v>
+      </c>
       <c r="T84" t="inlineStr"/>
       <c r="U84" t="inlineStr"/>
+      <c r="V84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -5339,13 +5461,13 @@
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="n">
-        <v>0.7903</v>
+        <v>0.7982</v>
       </c>
       <c r="F85" t="n">
-        <v>0.7983</v>
+        <v>0.79</v>
       </c>
       <c r="G85" t="n">
-        <v>-0.0081</v>
+        <v>0.0081</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -5365,22 +5487,23 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>All candidates have zero values and lack distinctive evidence to support a mapping.</t>
         </is>
       </c>
       <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
       <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="n">
-        <v>0.7903</v>
-      </c>
+      <c r="Q85" t="inlineStr"/>
       <c r="R85" t="n">
-        <v>0.7903</v>
-      </c>
-      <c r="S85" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="S85" t="n">
+        <v>0</v>
+      </c>
       <c r="T85" t="inlineStr"/>
       <c r="U85" t="inlineStr"/>
+      <c r="V85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -5420,22 +5543,23 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>All candidates have insufficient evidence or semantic conflicts, making a mapping unsupported.</t>
+          <t>No suitable candidate found due to lack of relevant data evidence.</t>
         </is>
       </c>
       <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
       <c r="P86" t="inlineStr"/>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q86" t="inlineStr"/>
       <c r="R86" t="n">
         <v>0</v>
       </c>
-      <c r="S86" t="inlineStr"/>
+      <c r="S86" t="n">
+        <v>0</v>
+      </c>
       <c r="T86" t="inlineStr"/>
       <c r="U86" t="inlineStr"/>
+      <c r="V86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -5455,19 +5579,19 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.8826000000000001</v>
+        <v>0.8827</v>
       </c>
       <c r="F87" t="n">
         <v>0.8787</v>
       </c>
       <c r="G87" t="n">
-        <v>0.0039</v>
+        <v>0.004</v>
       </c>
       <c r="H87" t="n">
         <v>0.84</v>
       </c>
       <c r="I87" t="n">
-        <v>0.8826000000000001</v>
+        <v>0.8827</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -5481,22 +5605,23 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>The name 'Antecip.ICMS' aligns closely with the tax type, and the profile shows valid numeric data without semantic conflicts.</t>
+          <t>The name 'Antecip.ICMS' aligns closely with the tax type, and there is no semantic conflict.</t>
         </is>
       </c>
       <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
       <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="n">
-        <v>0.8826000000000001</v>
-      </c>
+      <c r="Q87" t="inlineStr"/>
       <c r="R87" t="n">
-        <v>0.8826000000000001</v>
-      </c>
-      <c r="S87" t="inlineStr"/>
+        <v>0.8827</v>
+      </c>
+      <c r="S87" t="n">
+        <v>0.8827</v>
+      </c>
       <c r="T87" t="inlineStr"/>
       <c r="U87" t="inlineStr"/>
+      <c r="V87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -5542,22 +5667,23 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>The name 'Antecip.ICMS' closely relates to the 'Base Reduzida ICMS' and has a high name confidence, despite limited numeric evidence.</t>
+          <t>The name 'Antecip.ICMS' closely relates to ICMS tax, but lacks sufficient distinctive sample overlap and has a lower numeric range compared to 'Base Reduzida ICMS'.</t>
         </is>
       </c>
       <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr"/>
       <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="n">
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="S88" t="n">
         <v>0.8724</v>
       </c>
-      <c r="R88" t="n">
-        <v>0.8724</v>
-      </c>
-      <c r="S88" t="inlineStr"/>
       <c r="T88" t="inlineStr"/>
       <c r="U88" t="inlineStr"/>
+      <c r="V88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -5571,10 +5697,10 @@
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="n">
-        <v>0.8306</v>
+        <v>0.8307</v>
       </c>
       <c r="F89" t="n">
-        <v>0.8294</v>
+        <v>0.8295</v>
       </c>
       <c r="G89" t="n">
         <v>0.0012</v>
@@ -5604,15 +5730,16 @@
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr"/>
       <c r="P89" t="inlineStr"/>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q89" t="inlineStr"/>
       <c r="R89" t="n">
         <v>0</v>
       </c>
-      <c r="S89" t="inlineStr"/>
+      <c r="S89" t="n">
+        <v>0</v>
+      </c>
       <c r="T89" t="inlineStr"/>
       <c r="U89" t="inlineStr"/>
+      <c r="V89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -5626,13 +5753,13 @@
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="n">
-        <v>0.8544</v>
+        <v>0.8431999999999999</v>
       </c>
       <c r="F90" t="n">
-        <v>0.8524</v>
+        <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>0.002</v>
+        <v>0.8431999999999999</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -5652,22 +5779,23 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>All candidates exhibit semantic header conflicts or lack relevant data evidence.</t>
         </is>
       </c>
       <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr"/>
       <c r="P90" t="inlineStr"/>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q90" t="inlineStr"/>
       <c r="R90" t="n">
-        <v>0.8544</v>
-      </c>
-      <c r="S90" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="S90" t="n">
+        <v>0</v>
+      </c>
       <c r="T90" t="inlineStr"/>
       <c r="U90" t="inlineStr"/>
+      <c r="V90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -5681,13 +5809,13 @@
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="n">
-        <v>0.8675</v>
+        <v>0.8456</v>
       </c>
       <c r="F91" t="n">
-        <v>0.8672</v>
+        <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>0.0003</v>
+        <v>0.8456</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -5707,22 +5835,23 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the original column and provide no distinctive or valid data evidence.</t>
+          <t>All candidates have a tax-family conflict with ICAP vs ICMS, indicating incompatible semantic roles.</t>
         </is>
       </c>
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr"/>
       <c r="P91" t="inlineStr"/>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q91" t="inlineStr"/>
       <c r="R91" t="n">
         <v>0</v>
       </c>
-      <c r="S91" t="inlineStr"/>
+      <c r="S91" t="n">
+        <v>0</v>
+      </c>
       <c r="T91" t="inlineStr"/>
       <c r="U91" t="inlineStr"/>
+      <c r="V91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -5769,15 +5898,16 @@
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr"/>
       <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q92" t="inlineStr"/>
       <c r="R92" t="n">
         <v>0</v>
       </c>
-      <c r="S92" t="inlineStr"/>
+      <c r="S92" t="n">
+        <v>0</v>
+      </c>
       <c r="T92" t="inlineStr"/>
       <c r="U92" t="inlineStr"/>
+      <c r="V92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -5817,22 +5947,23 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>All candidates exhibit semantic header conflicts with the expected tax type, and the evidence quality is insufficient.</t>
+          <t>All candidates have significant semantic header conflicts with the expected tax type.</t>
         </is>
       </c>
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr"/>
       <c r="P93" t="inlineStr"/>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q93" t="inlineStr"/>
       <c r="R93" t="n">
         <v>0</v>
       </c>
-      <c r="S93" t="inlineStr"/>
+      <c r="S93" t="n">
+        <v>0</v>
+      </c>
       <c r="T93" t="inlineStr"/>
       <c r="U93" t="inlineStr"/>
+      <c r="V93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -5885,15 +6016,16 @@
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr"/>
       <c r="P94" t="inlineStr"/>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q94" t="inlineStr"/>
       <c r="R94" t="n">
         <v>0</v>
       </c>
-      <c r="S94" t="inlineStr"/>
+      <c r="S94" t="n">
+        <v>0</v>
+      </c>
       <c r="T94" t="inlineStr"/>
       <c r="U94" t="inlineStr"/>
+      <c r="V94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -5907,10 +6039,10 @@
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="n">
-        <v>0.8618</v>
+        <v>0.8617</v>
       </c>
       <c r="F95" t="n">
-        <v>0.8552</v>
+        <v>0.8551</v>
       </c>
       <c r="G95" t="n">
         <v>0.0066</v>
@@ -5940,15 +6072,16 @@
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr"/>
       <c r="P95" t="inlineStr"/>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q95" t="inlineStr"/>
       <c r="R95" t="n">
-        <v>0.8618</v>
-      </c>
-      <c r="S95" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="S95" t="n">
+        <v>0.8617</v>
+      </c>
       <c r="T95" t="inlineStr"/>
       <c r="U95" t="inlineStr"/>
+      <c r="V95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -5959,22 +6092,28 @@
           <t>Isentas ICEP</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr"/>
-      <c r="D96" t="inlineStr"/>
+      <c r="C96" t="n">
+        <v>303</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Ind Isen Prv</t>
+        </is>
+      </c>
       <c r="E96" t="n">
-        <v>0.8482</v>
+        <v>0.851</v>
       </c>
       <c r="F96" t="n">
         <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>0.8482</v>
+        <v>0.851</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>0.851</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -5983,27 +6122,28 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>review</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>All candidates exhibit semantic header conflicts and lack distinctive row evidence.</t>
+          <t>The strongest header candidate has weak row evidence; preserve the name-based mapping for review instead of replacing it with a merely similar value shape.</t>
         </is>
       </c>
       <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr"/>
       <c r="P96" t="inlineStr"/>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q96" t="inlineStr"/>
       <c r="R96" t="n">
         <v>0</v>
       </c>
-      <c r="S96" t="inlineStr"/>
+      <c r="S96" t="n">
+        <v>0</v>
+      </c>
       <c r="T96" t="inlineStr"/>
       <c r="U96" t="inlineStr"/>
+      <c r="V96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -6023,19 +6163,19 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.8552999999999999</v>
+        <v>0.8583</v>
       </c>
       <c r="F97" t="n">
         <v>0</v>
       </c>
       <c r="G97" t="n">
-        <v>0.8552999999999999</v>
+        <v>0.8583</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
       </c>
       <c r="I97" t="n">
-        <v>0.8552999999999999</v>
+        <v>0.8583</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
@@ -6056,15 +6196,16 @@
       <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr"/>
       <c r="P97" t="inlineStr"/>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q97" t="inlineStr"/>
       <c r="R97" t="n">
         <v>0</v>
       </c>
-      <c r="S97" t="inlineStr"/>
+      <c r="S97" t="n">
+        <v>0</v>
+      </c>
       <c r="T97" t="inlineStr"/>
       <c r="U97" t="inlineStr"/>
+      <c r="V97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -6078,13 +6219,13 @@
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="n">
-        <v>0.8419</v>
+        <v>0.8421999999999999</v>
       </c>
       <c r="F98" t="n">
-        <v>0.8405</v>
+        <v>0.8409</v>
       </c>
       <c r="G98" t="n">
-        <v>0.0014</v>
+        <v>0.0013</v>
       </c>
       <c r="H98" t="n">
         <v>0</v>
@@ -6104,22 +6245,23 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>All candidates exhibit semantic header conflicts and lack distinctive non-zero evidence.</t>
+          <t>All candidates exhibit semantic header conflicts and lack distinctive row evidence.</t>
         </is>
       </c>
       <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr"/>
       <c r="O98" t="inlineStr"/>
       <c r="P98" t="inlineStr"/>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q98" t="inlineStr"/>
       <c r="R98" t="n">
         <v>0</v>
       </c>
-      <c r="S98" t="inlineStr"/>
+      <c r="S98" t="n">
+        <v>0</v>
+      </c>
       <c r="T98" t="inlineStr"/>
       <c r="U98" t="inlineStr"/>
+      <c r="V98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -6136,7 +6278,7 @@
         <v>0.839</v>
       </c>
       <c r="F99" t="n">
-        <v>0.8258</v>
+        <v>0.8259</v>
       </c>
       <c r="G99" t="n">
         <v>0.0131</v>
@@ -6159,22 +6301,23 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>All candidates have a tax-family conflict with ICMS, indicating they do not semantically match the required ICSP type.</t>
+          <t>All candidates have a tax-family conflict with ICMS, and the evidence is insufficient to support a mapping.</t>
         </is>
       </c>
       <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr"/>
       <c r="O99" t="inlineStr"/>
       <c r="P99" t="inlineStr"/>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q99" t="inlineStr"/>
       <c r="R99" t="n">
         <v>0</v>
       </c>
-      <c r="S99" t="inlineStr"/>
+      <c r="S99" t="n">
+        <v>0</v>
+      </c>
       <c r="T99" t="inlineStr"/>
       <c r="U99" t="inlineStr"/>
+      <c r="V99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -6227,15 +6370,16 @@
       <c r="N100" t="inlineStr"/>
       <c r="O100" t="inlineStr"/>
       <c r="P100" t="inlineStr"/>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q100" t="inlineStr"/>
       <c r="R100" t="n">
         <v>0</v>
       </c>
-      <c r="S100" t="inlineStr"/>
+      <c r="S100" t="n">
+        <v>0</v>
+      </c>
       <c r="T100" t="inlineStr"/>
       <c r="U100" t="inlineStr"/>
+      <c r="V100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -6255,19 +6399,19 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.8713</v>
+        <v>0.8712</v>
       </c>
       <c r="F101" t="n">
         <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>0.8713</v>
+        <v>0.8712</v>
       </c>
       <c r="H101" t="n">
         <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>0.8713</v>
+        <v>0.8712</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -6288,15 +6432,16 @@
       <c r="N101" t="inlineStr"/>
       <c r="O101" t="inlineStr"/>
       <c r="P101" t="inlineStr"/>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q101" t="inlineStr"/>
       <c r="R101" t="n">
         <v>0</v>
       </c>
-      <c r="S101" t="inlineStr"/>
+      <c r="S101" t="n">
+        <v>0</v>
+      </c>
       <c r="T101" t="inlineStr"/>
       <c r="U101" t="inlineStr"/>
+      <c r="V101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -6342,22 +6487,23 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>The candidate 'Vlr Isen ICM' has a high name confidence and no semantic header conflict, despite the weak data evidence.</t>
+          <t>The name 'Vlr Isen ICM' is the closest match to 'Valor ICSP' despite both having high zero fractions.</t>
         </is>
       </c>
       <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr"/>
       <c r="O102" t="inlineStr"/>
       <c r="P102" t="inlineStr"/>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q102" t="inlineStr"/>
       <c r="R102" t="n">
         <v>0.8829</v>
       </c>
-      <c r="S102" t="inlineStr"/>
+      <c r="S102" t="n">
+        <v>0.8829</v>
+      </c>
       <c r="T102" t="inlineStr"/>
       <c r="U102" t="inlineStr"/>
+      <c r="V102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -6368,22 +6514,28 @@
           <t>Isentas ICSP</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr"/>
-      <c r="D103" t="inlineStr"/>
+      <c r="C103" t="n">
+        <v>303</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Ind Isen Prv</t>
+        </is>
+      </c>
       <c r="E103" t="n">
-        <v>0.8486</v>
+        <v>0.8505</v>
       </c>
       <c r="F103" t="n">
         <v>0</v>
       </c>
       <c r="G103" t="n">
-        <v>0.8486</v>
+        <v>0.8505</v>
       </c>
       <c r="H103" t="n">
         <v>0</v>
       </c>
       <c r="I103" t="n">
-        <v>0</v>
+        <v>0.8505</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -6392,27 +6544,28 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>review</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>All candidates exhibit semantic header conflicts or all-zero evidence, indicating no suitable mapping.</t>
+          <t>The strongest header candidate has weak row evidence; preserve the name-based mapping for review instead of replacing it with a merely similar value shape.</t>
         </is>
       </c>
       <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr"/>
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="inlineStr"/>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q103" t="inlineStr"/>
       <c r="R103" t="n">
         <v>0</v>
       </c>
-      <c r="S103" t="inlineStr"/>
+      <c r="S103" t="n">
+        <v>0.8507</v>
+      </c>
       <c r="T103" t="inlineStr"/>
       <c r="U103" t="inlineStr"/>
+      <c r="V103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -6432,19 +6585,19 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.8534</v>
+        <v>0.8557</v>
       </c>
       <c r="F104" t="n">
         <v>0</v>
       </c>
       <c r="G104" t="n">
-        <v>0.8534</v>
+        <v>0.8557</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
       </c>
       <c r="I104" t="n">
-        <v>0.8534</v>
+        <v>0.8557</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -6465,15 +6618,16 @@
       <c r="N104" t="inlineStr"/>
       <c r="O104" t="inlineStr"/>
       <c r="P104" t="inlineStr"/>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q104" t="inlineStr"/>
       <c r="R104" t="n">
         <v>0</v>
       </c>
-      <c r="S104" t="inlineStr"/>
+      <c r="S104" t="n">
+        <v>0</v>
+      </c>
       <c r="T104" t="inlineStr"/>
       <c r="U104" t="inlineStr"/>
+      <c r="V104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -6487,13 +6641,13 @@
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="n">
-        <v>0.8405</v>
+        <v>0.8407</v>
       </c>
       <c r="F105" t="n">
-        <v>0.84</v>
+        <v>0.8401</v>
       </c>
       <c r="G105" t="n">
-        <v>0.0004</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -6513,22 +6667,23 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>All candidates exhibit semantic header conflicts and lack distinctive row evidence.</t>
+          <t>All candidates exhibit semantic header conflicts and contain only zeros, providing no valid mapping evidence.</t>
         </is>
       </c>
       <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr"/>
       <c r="P105" t="inlineStr"/>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q105" t="inlineStr"/>
       <c r="R105" t="n">
         <v>0</v>
       </c>
-      <c r="S105" t="inlineStr"/>
+      <c r="S105" t="n">
+        <v>0</v>
+      </c>
       <c r="T105" t="inlineStr"/>
       <c r="U105" t="inlineStr"/>
+      <c r="V105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -6575,15 +6730,16 @@
       <c r="N106" t="inlineStr"/>
       <c r="O106" t="inlineStr"/>
       <c r="P106" t="inlineStr"/>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q106" t="inlineStr"/>
       <c r="R106" t="n">
         <v>0</v>
       </c>
-      <c r="S106" t="inlineStr"/>
+      <c r="S106" t="n">
+        <v>0</v>
+      </c>
       <c r="T106" t="inlineStr"/>
       <c r="U106" t="inlineStr"/>
+      <c r="V106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -6630,15 +6786,16 @@
       <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr"/>
       <c r="P107" t="inlineStr"/>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q107" t="inlineStr"/>
       <c r="R107" t="n">
         <v>0</v>
       </c>
-      <c r="S107" t="inlineStr"/>
+      <c r="S107" t="n">
+        <v>0</v>
+      </c>
       <c r="T107" t="inlineStr"/>
       <c r="U107" t="inlineStr"/>
+      <c r="V107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -6658,10 +6815,10 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.856</v>
+        <v>0.8559</v>
       </c>
       <c r="F108" t="n">
-        <v>0.8836000000000001</v>
+        <v>0.8835</v>
       </c>
       <c r="G108" t="n">
         <v>-0.0276</v>
@@ -6670,7 +6827,7 @@
         <v>0</v>
       </c>
       <c r="I108" t="n">
-        <v>0.856</v>
+        <v>0.8559</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
@@ -6684,22 +6841,23 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>The candidate 'Difal ICMS' does not match the expected role of 'Aliquota DIF_ALIQ' as it represents a different tax type.</t>
+          <t>Distinctive content evidence indicates 'Difal ICMS' is a relevant tax rate, aligning with the 'Aliquota DIF_ALIQ' context.</t>
         </is>
       </c>
       <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr"/>
       <c r="O108" t="inlineStr"/>
       <c r="P108" t="inlineStr"/>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q108" t="inlineStr"/>
       <c r="R108" t="n">
-        <v>0.856</v>
-      </c>
-      <c r="S108" t="inlineStr"/>
+        <v>0.8559</v>
+      </c>
+      <c r="S108" t="n">
+        <v>0.8559</v>
+      </c>
       <c r="T108" t="inlineStr"/>
       <c r="U108" t="inlineStr"/>
+      <c r="V108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -6719,7 +6877,7 @@
         <v>0.8637</v>
       </c>
       <c r="G109" t="n">
-        <v>-0.0236</v>
+        <v>-0.0237</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -6746,15 +6904,16 @@
       <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr"/>
       <c r="P109" t="inlineStr"/>
-      <c r="Q109" t="n">
-        <v>0.84</v>
-      </c>
+      <c r="Q109" t="inlineStr"/>
       <c r="R109" t="n">
         <v>0.84</v>
       </c>
-      <c r="S109" t="inlineStr"/>
+      <c r="S109" t="n">
+        <v>0.84</v>
+      </c>
       <c r="T109" t="inlineStr"/>
       <c r="U109" t="inlineStr"/>
+      <c r="V109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -6774,19 +6933,19 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.8536</v>
+        <v>0.8522</v>
       </c>
       <c r="F110" t="n">
         <v>0</v>
       </c>
       <c r="G110" t="n">
-        <v>0.8536</v>
+        <v>0.8522</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
       </c>
       <c r="I110" t="n">
-        <v>0.8536</v>
+        <v>0.8522</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
@@ -6807,15 +6966,16 @@
       <c r="N110" t="inlineStr"/>
       <c r="O110" t="inlineStr"/>
       <c r="P110" t="inlineStr"/>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q110" t="inlineStr"/>
       <c r="R110" t="n">
         <v>0</v>
       </c>
-      <c r="S110" t="inlineStr"/>
+      <c r="S110" t="n">
+        <v>0</v>
+      </c>
       <c r="T110" t="inlineStr"/>
       <c r="U110" t="inlineStr"/>
+      <c r="V110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -6829,10 +6989,10 @@
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="n">
-        <v>0.8688</v>
+        <v>0.8681</v>
       </c>
       <c r="F111" t="n">
-        <v>0.861</v>
+        <v>0.8603</v>
       </c>
       <c r="G111" t="n">
         <v>0.0078</v>
@@ -6862,15 +7022,16 @@
       <c r="N111" t="inlineStr"/>
       <c r="O111" t="inlineStr"/>
       <c r="P111" t="inlineStr"/>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q111" t="inlineStr"/>
       <c r="R111" t="n">
         <v>0</v>
       </c>
-      <c r="S111" t="inlineStr"/>
+      <c r="S111" t="n">
+        <v>0</v>
+      </c>
       <c r="T111" t="inlineStr"/>
       <c r="U111" t="inlineStr"/>
+      <c r="V111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -6910,22 +7071,23 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>All candidates exhibit semantic-role conflicts with the target column, indicating incompatible mappings.</t>
+          <t>All candidates exhibit semantic-role conflicts with the target column.</t>
         </is>
       </c>
       <c r="M112" t="inlineStr"/>
       <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr"/>
       <c r="P112" t="inlineStr"/>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q112" t="inlineStr"/>
       <c r="R112" t="n">
         <v>0</v>
       </c>
-      <c r="S112" t="inlineStr"/>
+      <c r="S112" t="n">
+        <v>0</v>
+      </c>
       <c r="T112" t="inlineStr"/>
       <c r="U112" t="inlineStr"/>
+      <c r="V112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -6948,7 +7110,7 @@
         <v>0.893</v>
       </c>
       <c r="F113" t="n">
-        <v>0.8851</v>
+        <v>0.885</v>
       </c>
       <c r="G113" t="n">
         <v>0.007900000000000001</v>
@@ -6971,22 +7133,23 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>The candidate 'Base FCP Cmp' has a high name confidence and no semantic header conflict, despite all-zero evidence.</t>
+          <t>The name 'Base FCP Cmp' closely aligns with 'Base ICMS_FECP' and has no semantic conflicts.</t>
         </is>
       </c>
       <c r="M113" t="inlineStr"/>
       <c r="N113" t="inlineStr"/>
       <c r="O113" t="inlineStr"/>
       <c r="P113" t="inlineStr"/>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q113" t="inlineStr"/>
       <c r="R113" t="n">
         <v>0.893</v>
       </c>
-      <c r="S113" t="inlineStr"/>
+      <c r="S113" t="n">
+        <v>0.893</v>
+      </c>
       <c r="T113" t="inlineStr"/>
       <c r="U113" t="inlineStr"/>
+      <c r="V113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -7032,22 +7195,23 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>The candidate 'Aliq FECP' closely matches the semantic role of 'Aliquota ICMS_FECP' with high name confidence, despite all values being zero.</t>
+          <t>The candidate 'Aliq FECP' has a high name confidence and matches the expected semantic role despite all-zero evidence.</t>
         </is>
       </c>
       <c r="M114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
       <c r="O114" t="inlineStr"/>
       <c r="P114" t="inlineStr"/>
-      <c r="Q114" t="n">
+      <c r="Q114" t="inlineStr"/>
+      <c r="R114" t="n">
+        <v>0</v>
+      </c>
+      <c r="S114" t="n">
         <v>0.8905999999999999</v>
       </c>
-      <c r="R114" t="n">
-        <v>0.8905999999999999</v>
-      </c>
-      <c r="S114" t="inlineStr"/>
       <c r="T114" t="inlineStr"/>
       <c r="U114" t="inlineStr"/>
+      <c r="V114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -7073,7 +7237,7 @@
         <v>0.9392</v>
       </c>
       <c r="G115" t="n">
-        <v>-0.0444</v>
+        <v>-0.0443</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
@@ -7093,22 +7257,23 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>The name 'Vlr ICMS Com' closely relates to the tax value context of 'Valor ICMS_FECP', and it has a higher unique count and informative evidence.</t>
+          <t>The name 'Vlr ICMS Com' closely relates to the tax value context, and it has a higher unique count and informative evidence compared to other candidates.</t>
         </is>
       </c>
       <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr"/>
       <c r="O115" t="inlineStr"/>
       <c r="P115" t="inlineStr"/>
-      <c r="Q115" t="n">
-        <v>0.8948</v>
-      </c>
+      <c r="Q115" t="inlineStr"/>
       <c r="R115" t="n">
         <v>0.8948</v>
       </c>
-      <c r="S115" t="inlineStr"/>
+      <c r="S115" t="n">
+        <v>0.8948</v>
+      </c>
       <c r="T115" t="inlineStr"/>
       <c r="U115" t="inlineStr"/>
+      <c r="V115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -7155,15 +7320,16 @@
       <c r="N116" t="inlineStr"/>
       <c r="O116" t="inlineStr"/>
       <c r="P116" t="inlineStr"/>
-      <c r="Q116" t="n">
-        <v>0.8522999999999999</v>
-      </c>
+      <c r="Q116" t="inlineStr"/>
       <c r="R116" t="n">
         <v>0.8522999999999999</v>
       </c>
-      <c r="S116" t="inlineStr"/>
+      <c r="S116" t="n">
+        <v>0.8522999999999999</v>
+      </c>
       <c r="T116" t="inlineStr"/>
       <c r="U116" t="inlineStr"/>
+      <c r="V116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -7183,19 +7349,19 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0.8747</v>
+        <v>0.8759</v>
       </c>
       <c r="F117" t="n">
-        <v>0.872</v>
+        <v>0.8731</v>
       </c>
       <c r="G117" t="n">
-        <v>0.0026</v>
+        <v>0.0028</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
       </c>
       <c r="I117" t="n">
-        <v>0.8747</v>
+        <v>0.8759</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -7209,22 +7375,23 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>The name 'BC ICMS Efet' aligns with the tax context, and there is no semantic conflict.</t>
+          <t>The header 'BC ICMS Efet' aligns with the tax base context, despite all-zero evidence.</t>
         </is>
       </c>
       <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr"/>
       <c r="P117" t="inlineStr"/>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q117" t="inlineStr"/>
       <c r="R117" t="n">
-        <v>0.8747</v>
-      </c>
-      <c r="S117" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.8759</v>
+      </c>
       <c r="T117" t="inlineStr"/>
       <c r="U117" t="inlineStr"/>
+      <c r="V117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -7241,7 +7408,7 @@
         <v>0.8608</v>
       </c>
       <c r="F118" t="n">
-        <v>0.851</v>
+        <v>0.8511</v>
       </c>
       <c r="G118" t="n">
         <v>0.0097</v>
@@ -7264,22 +7431,23 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>All candidates exhibit semantic-role conflicts and lack distinctive row evidence.</t>
+          <t>All candidates exhibit semantic-role conflicts and lack distinctive non-zero evidence.</t>
         </is>
       </c>
       <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr"/>
       <c r="O118" t="inlineStr"/>
       <c r="P118" t="inlineStr"/>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q118" t="inlineStr"/>
       <c r="R118" t="n">
         <v>0</v>
       </c>
-      <c r="S118" t="inlineStr"/>
+      <c r="S118" t="n">
+        <v>0</v>
+      </c>
       <c r="T118" t="inlineStr"/>
       <c r="U118" t="inlineStr"/>
+      <c r="V118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -7325,22 +7493,23 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>The candidate 'IPI Pauta' has a high name confidence but lacks distinctive data evidence, making it a weak match.</t>
+          <t>The candidate 'IPI Pauta' has a strong name match but lacks distinctive data evidence.</t>
         </is>
       </c>
       <c r="M119" t="inlineStr"/>
       <c r="N119" t="inlineStr"/>
       <c r="O119" t="inlineStr"/>
       <c r="P119" t="inlineStr"/>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q119" t="inlineStr"/>
       <c r="R119" t="n">
+        <v>0</v>
+      </c>
+      <c r="S119" t="n">
         <v>0.8718</v>
       </c>
-      <c r="S119" t="inlineStr"/>
       <c r="T119" t="inlineStr"/>
       <c r="U119" t="inlineStr"/>
+      <c r="V119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -7360,19 +7529,19 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.8934</v>
+        <v>0.8935</v>
       </c>
       <c r="F120" t="n">
         <v>0.8421</v>
       </c>
       <c r="G120" t="n">
-        <v>0.0513</v>
+        <v>0.0514</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
       </c>
       <c r="I120" t="n">
-        <v>0.8934</v>
+        <v>0.8935</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
@@ -7393,15 +7562,16 @@
       <c r="N120" t="inlineStr"/>
       <c r="O120" t="inlineStr"/>
       <c r="P120" t="inlineStr"/>
-      <c r="Q120" t="n">
-        <v>0.8358</v>
-      </c>
+      <c r="Q120" t="inlineStr"/>
       <c r="R120" t="n">
         <v>0.8358</v>
       </c>
-      <c r="S120" t="inlineStr"/>
+      <c r="S120" t="n">
+        <v>0.8358</v>
+      </c>
       <c r="T120" t="inlineStr"/>
       <c r="U120" t="inlineStr"/>
+      <c r="V120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -7424,10 +7594,10 @@
         <v>0.8784999999999999</v>
       </c>
       <c r="F121" t="n">
-        <v>0.8517</v>
+        <v>0.8556</v>
       </c>
       <c r="G121" t="n">
-        <v>0.0268</v>
+        <v>0.0229</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -7447,22 +7617,23 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>The name 'Cofins Pauta' closely matches 'Isentas COFINS' and both contain only zeros, indicating they may represent the same exempt COFINS values.</t>
+          <t>The name 'Cofins Pauta' closely matches 'Isentas COFINS' and both have all-zero values, indicating they may represent the same exempt COFINS amount.</t>
         </is>
       </c>
       <c r="M121" t="inlineStr"/>
       <c r="N121" t="inlineStr"/>
       <c r="O121" t="inlineStr"/>
       <c r="P121" t="inlineStr"/>
-      <c r="Q121" t="n">
-        <v>0.8784999999999999</v>
-      </c>
+      <c r="Q121" t="inlineStr"/>
       <c r="R121" t="n">
         <v>0.8784999999999999</v>
       </c>
-      <c r="S121" t="inlineStr"/>
+      <c r="S121" t="n">
+        <v>0.8784999999999999</v>
+      </c>
       <c r="T121" t="inlineStr"/>
       <c r="U121" t="inlineStr"/>
+      <c r="V121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -7488,7 +7659,7 @@
         <v>0.8625</v>
       </c>
       <c r="G122" t="n">
-        <v>0.0247</v>
+        <v>0.0248</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
@@ -7515,15 +7686,16 @@
       <c r="N122" t="inlineStr"/>
       <c r="O122" t="inlineStr"/>
       <c r="P122" t="inlineStr"/>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q122" t="inlineStr"/>
       <c r="R122" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" t="n">
         <v>0.8872</v>
       </c>
-      <c r="S122" t="inlineStr"/>
       <c r="T122" t="inlineStr"/>
       <c r="U122" t="inlineStr"/>
+      <c r="V122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -7543,19 +7715,19 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0.8559</v>
+        <v>0.856</v>
       </c>
       <c r="F123" t="n">
         <v>0</v>
       </c>
       <c r="G123" t="n">
-        <v>0.8559</v>
+        <v>0.856</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
       </c>
       <c r="I123" t="n">
-        <v>0.8559</v>
+        <v>0.856</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
@@ -7569,22 +7741,23 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>The strongest header candidate has weak row evidence; preserve the name-based mapping for review instead of replacing it with a merely similar value shape.</t>
+          <t>The candidate 'Cofins Pauta' has a matching semantic role without conflicting evidence, despite all-zero data.</t>
         </is>
       </c>
       <c r="M123" t="inlineStr"/>
       <c r="N123" t="inlineStr"/>
       <c r="O123" t="inlineStr"/>
       <c r="P123" t="inlineStr"/>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q123" t="inlineStr"/>
       <c r="R123" t="n">
         <v>0</v>
       </c>
-      <c r="S123" t="inlineStr"/>
+      <c r="S123" t="n">
+        <v>0.856</v>
+      </c>
       <c r="T123" t="inlineStr"/>
       <c r="U123" t="inlineStr"/>
+      <c r="V123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -7595,10 +7768,16 @@
           <t>Isentas PIS</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr"/>
-      <c r="D124" t="inlineStr"/>
+      <c r="C124" t="n">
+        <v>150</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>PIS Pauta</t>
+        </is>
+      </c>
       <c r="E124" t="n">
-        <v>0.8847</v>
+        <v>0.8848</v>
       </c>
       <c r="F124" t="n">
         <v>0.8728</v>
@@ -7610,7 +7789,7 @@
         <v>0</v>
       </c>
       <c r="I124" t="n">
-        <v>0</v>
+        <v>0.8848</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
@@ -7619,27 +7798,28 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>review</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>All candidates exhibit semantic-role conflicts or all-zero evidence, indicating no suitable mapping.</t>
+          <t>The column 'PIS Pauta' has a high name confidence but all values are zero, indicating it may not represent actual data.</t>
         </is>
       </c>
       <c r="M124" t="inlineStr"/>
       <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr"/>
       <c r="P124" t="inlineStr"/>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q124" t="inlineStr"/>
       <c r="R124" t="n">
         <v>0</v>
       </c>
-      <c r="S124" t="inlineStr"/>
+      <c r="S124" t="n">
+        <v>0.8848</v>
+      </c>
       <c r="T124" t="inlineStr"/>
       <c r="U124" t="inlineStr"/>
+      <c r="V124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -7659,7 +7839,7 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>0.8867</v>
+        <v>0.8868</v>
       </c>
       <c r="F125" t="n">
         <v>0.8735000000000001</v>
@@ -7671,7 +7851,7 @@
         <v>0</v>
       </c>
       <c r="I125" t="n">
-        <v>0.8867</v>
+        <v>0.8868</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
@@ -7692,15 +7872,16 @@
       <c r="N125" t="inlineStr"/>
       <c r="O125" t="inlineStr"/>
       <c r="P125" t="inlineStr"/>
-      <c r="Q125" t="n">
-        <v>0.8867</v>
-      </c>
+      <c r="Q125" t="inlineStr"/>
       <c r="R125" t="n">
-        <v>0.8867</v>
-      </c>
-      <c r="S125" t="inlineStr"/>
+        <v>0.8868</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.8868</v>
+      </c>
       <c r="T125" t="inlineStr"/>
       <c r="U125" t="inlineStr"/>
+      <c r="V125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -7747,15 +7928,16 @@
       <c r="N126" t="inlineStr"/>
       <c r="O126" t="inlineStr"/>
       <c r="P126" t="inlineStr"/>
-      <c r="Q126" t="n">
-        <v>0.8502</v>
-      </c>
+      <c r="Q126" t="inlineStr"/>
       <c r="R126" t="n">
         <v>0.8502</v>
       </c>
-      <c r="S126" t="inlineStr"/>
+      <c r="S126" t="n">
+        <v>0.8502</v>
+      </c>
       <c r="T126" t="inlineStr"/>
       <c r="U126" t="inlineStr"/>
+      <c r="V126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -7769,13 +7951,13 @@
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="n">
-        <v>0.9</v>
+        <v>0.8591</v>
       </c>
       <c r="F127" t="n">
-        <v>0.8962</v>
+        <v>0.8387</v>
       </c>
       <c r="G127" t="n">
-        <v>0.0038</v>
+        <v>0.0204</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -7795,22 +7977,23 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>All candidates exhibit semantic-role conflicts or lack distinctive evidence, making them unsuitable for mapping.</t>
         </is>
       </c>
       <c r="M127" t="inlineStr"/>
       <c r="N127" t="inlineStr"/>
       <c r="O127" t="inlineStr"/>
       <c r="P127" t="inlineStr"/>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q127" t="inlineStr"/>
       <c r="R127" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="S127" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0</v>
+      </c>
       <c r="T127" t="inlineStr"/>
       <c r="U127" t="inlineStr"/>
+      <c r="V127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -7856,22 +8039,23 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>The candidate 'Recolhe ISS' has the highest name confidence and aligns with the tax type, despite the lack of distinctive sample overlap.</t>
+          <t>The header 'Recolhe ISS' closely relates to the tax type 'Tipo de Imposto ISS' despite the lack of numeric evidence.</t>
         </is>
       </c>
       <c r="M128" t="inlineStr"/>
       <c r="N128" t="inlineStr"/>
       <c r="O128" t="inlineStr"/>
       <c r="P128" t="inlineStr"/>
-      <c r="Q128" t="n">
-        <v>0.882</v>
-      </c>
+      <c r="Q128" t="inlineStr"/>
       <c r="R128" t="n">
         <v>0.882</v>
       </c>
-      <c r="S128" t="inlineStr"/>
+      <c r="S128" t="n">
+        <v>0.882</v>
+      </c>
       <c r="T128" t="inlineStr"/>
       <c r="U128" t="inlineStr"/>
+      <c r="V128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -7894,7 +8078,7 @@
         <v>0.8771</v>
       </c>
       <c r="F129" t="n">
-        <v>0.8798</v>
+        <v>0.8797</v>
       </c>
       <c r="G129" t="n">
         <v>-0.0027</v>
@@ -7917,22 +8101,23 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>The name 'ISS Mat.' closely aligns with 'Base ISS' and both have identical numeric profiles, despite all values being zero.</t>
+          <t>The column 'ISS Mat.' has a similar numeric profile and name context to 'Base ISS', despite both having all-zero values.</t>
         </is>
       </c>
       <c r="M129" t="inlineStr"/>
       <c r="N129" t="inlineStr"/>
       <c r="O129" t="inlineStr"/>
       <c r="P129" t="inlineStr"/>
-      <c r="Q129" t="n">
-        <v>0.8771</v>
-      </c>
+      <c r="Q129" t="inlineStr"/>
       <c r="R129" t="n">
         <v>0.8771</v>
       </c>
-      <c r="S129" t="inlineStr"/>
+      <c r="S129" t="n">
+        <v>0.8771</v>
+      </c>
       <c r="T129" t="inlineStr"/>
       <c r="U129" t="inlineStr"/>
+      <c r="V129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -7958,7 +8143,7 @@
         <v>0.8915999999999999</v>
       </c>
       <c r="G130" t="n">
-        <v>0.0022</v>
+        <v>0.0023</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -7978,22 +8163,23 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>Both columns represent ISS tax rates, but all values are zero, limiting evidence for a strong mapping.</t>
+          <t>The candidate 'Alq.ISS CPM' has a high name confidence and matches the expected integer type, despite all values being zero.</t>
         </is>
       </c>
       <c r="M130" t="inlineStr"/>
       <c r="N130" t="inlineStr"/>
       <c r="O130" t="inlineStr"/>
       <c r="P130" t="inlineStr"/>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q130" t="inlineStr"/>
       <c r="R130" t="n">
+        <v>0</v>
+      </c>
+      <c r="S130" t="n">
         <v>0.8938</v>
       </c>
-      <c r="S130" t="inlineStr"/>
       <c r="T130" t="inlineStr"/>
       <c r="U130" t="inlineStr"/>
+      <c r="V130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -8046,15 +8232,16 @@
       <c r="N131" t="inlineStr"/>
       <c r="O131" t="inlineStr"/>
       <c r="P131" t="inlineStr"/>
-      <c r="Q131" t="n">
-        <v>0.8663</v>
-      </c>
+      <c r="Q131" t="inlineStr"/>
       <c r="R131" t="n">
         <v>0.8663</v>
       </c>
-      <c r="S131" t="inlineStr"/>
+      <c r="S131" t="n">
+        <v>0.8663</v>
+      </c>
       <c r="T131" t="inlineStr"/>
       <c r="U131" t="inlineStr"/>
+      <c r="V131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -8077,7 +8264,7 @@
         <v>0.8718</v>
       </c>
       <c r="F132" t="n">
-        <v>0.8815</v>
+        <v>0.8816000000000001</v>
       </c>
       <c r="G132" t="n">
         <v>-0.0097</v>
@@ -8107,15 +8294,16 @@
       <c r="N132" t="inlineStr"/>
       <c r="O132" t="inlineStr"/>
       <c r="P132" t="inlineStr"/>
-      <c r="Q132" t="n">
-        <v>0.8718</v>
-      </c>
+      <c r="Q132" t="inlineStr"/>
       <c r="R132" t="n">
         <v>0.8718</v>
       </c>
-      <c r="S132" t="inlineStr"/>
+      <c r="S132" t="n">
+        <v>0.8718</v>
+      </c>
       <c r="T132" t="inlineStr"/>
       <c r="U132" t="inlineStr"/>
+      <c r="V132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -8126,19 +8314,13 @@
           <t>Outras ISS</t>
         </is>
       </c>
-      <c r="C133" t="n">
-        <v>115</v>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>Recolhe ISS</t>
-        </is>
-      </c>
+      <c r="C133" t="inlineStr"/>
+      <c r="D133" t="inlineStr"/>
       <c r="E133" t="n">
-        <v>0.8919</v>
+        <v>0.892</v>
       </c>
       <c r="F133" t="n">
-        <v>0.8754999999999999</v>
+        <v>0.8756</v>
       </c>
       <c r="G133" t="n">
         <v>0.0164</v>
@@ -8147,7 +8329,7 @@
         <v>0</v>
       </c>
       <c r="I133" t="n">
-        <v>0.8919</v>
+        <v>0</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -8156,27 +8338,28 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>no_match</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>The candidate 'Recolhe ISS' has a high name confidence but lacks any numeric evidence, making it incompatible with 'Outras ISS'.</t>
+          <t>All candidates have significant semantic conflicts or lack relevant data evidence.</t>
         </is>
       </c>
       <c r="M133" t="inlineStr"/>
       <c r="N133" t="inlineStr"/>
       <c r="O133" t="inlineStr"/>
       <c r="P133" t="inlineStr"/>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q133" t="inlineStr"/>
       <c r="R133" t="n">
-        <v>0.8919</v>
-      </c>
-      <c r="S133" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0</v>
+      </c>
       <c r="T133" t="inlineStr"/>
       <c r="U133" t="inlineStr"/>
+      <c r="V133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -8190,13 +8373,13 @@
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="n">
-        <v>0.8457</v>
+        <v>0.8769</v>
       </c>
       <c r="F134" t="n">
-        <v>0.8774</v>
+        <v>0.8484</v>
       </c>
       <c r="G134" t="n">
-        <v>-0.0317</v>
+        <v>0.0284</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -8216,22 +8399,23 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>All candidates exhibit semantic-role conflicts or lack relevant data evidence.</t>
         </is>
       </c>
       <c r="M134" t="inlineStr"/>
       <c r="N134" t="inlineStr"/>
       <c r="O134" t="inlineStr"/>
       <c r="P134" t="inlineStr"/>
-      <c r="Q134" t="n">
-        <v>0.8457</v>
-      </c>
+      <c r="Q134" t="inlineStr"/>
       <c r="R134" t="n">
-        <v>0.8457</v>
-      </c>
-      <c r="S134" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0</v>
+      </c>
       <c r="T134" t="inlineStr"/>
       <c r="U134" t="inlineStr"/>
+      <c r="V134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -8284,15 +8468,16 @@
       <c r="N135" t="inlineStr"/>
       <c r="O135" t="inlineStr"/>
       <c r="P135" t="inlineStr"/>
-      <c r="Q135" t="n">
-        <v>0.9431</v>
-      </c>
+      <c r="Q135" t="inlineStr"/>
       <c r="R135" t="n">
         <v>0.9431</v>
       </c>
-      <c r="S135" t="inlineStr"/>
+      <c r="S135" t="n">
+        <v>0.9431</v>
+      </c>
       <c r="T135" t="inlineStr"/>
       <c r="U135" t="inlineStr"/>
+      <c r="V135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -8338,22 +8523,23 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>The candidate 'Aliq. FCP ST' has a high name confidence and no semantic header conflict.</t>
+          <t>The name 'Aliq. FCP ST' closely matches the canonical 'Aliquota FECP_ST' without semantic conflicts.</t>
         </is>
       </c>
       <c r="M136" t="inlineStr"/>
       <c r="N136" t="inlineStr"/>
       <c r="O136" t="inlineStr"/>
       <c r="P136" t="inlineStr"/>
-      <c r="Q136" t="n">
-        <v>0.8806</v>
-      </c>
+      <c r="Q136" t="inlineStr"/>
       <c r="R136" t="n">
         <v>0.8806</v>
       </c>
-      <c r="S136" t="inlineStr"/>
+      <c r="S136" t="n">
+        <v>0.8806</v>
+      </c>
       <c r="T136" t="inlineStr"/>
       <c r="U136" t="inlineStr"/>
+      <c r="V136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -8393,22 +8579,23 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>All candidates exhibit a tax-qualifier conflict and contain only zeros, providing no valid mapping evidence.</t>
+          <t>All candidates have a semantic header conflict and provide no distinctive sample evidence.</t>
         </is>
       </c>
       <c r="M137" t="inlineStr"/>
       <c r="N137" t="inlineStr"/>
       <c r="O137" t="inlineStr"/>
       <c r="P137" t="inlineStr"/>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q137" t="inlineStr"/>
       <c r="R137" t="n">
         <v>0</v>
       </c>
-      <c r="S137" t="inlineStr"/>
+      <c r="S137" t="n">
+        <v>0</v>
+      </c>
       <c r="T137" t="inlineStr"/>
       <c r="U137" t="inlineStr"/>
+      <c r="V137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -8454,22 +8641,23 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>The candidate 'V.FECP-ST/MT' has a high name confidence and no semantic conflicts, but both columns contain only zeros, limiting data evidence.</t>
+          <t>The candidate 'V.FECP-ST/MT' has a high name confidence and no semantic conflicts, despite all-zero evidence.</t>
         </is>
       </c>
       <c r="M138" t="inlineStr"/>
       <c r="N138" t="inlineStr"/>
       <c r="O138" t="inlineStr"/>
       <c r="P138" t="inlineStr"/>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q138" t="inlineStr"/>
       <c r="R138" t="n">
+        <v>0</v>
+      </c>
+      <c r="S138" t="n">
         <v>0.8653999999999999</v>
       </c>
-      <c r="S138" t="inlineStr"/>
       <c r="T138" t="inlineStr"/>
       <c r="U138" t="inlineStr"/>
+      <c r="V138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -8480,8 +8668,14 @@
           <t>Outras FECP_ST</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr"/>
-      <c r="D139" t="inlineStr"/>
+      <c r="C139" t="n">
+        <v>214</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>V.FECP-ST/MT</t>
+        </is>
+      </c>
       <c r="E139" t="n">
         <v>0.886</v>
       </c>
@@ -8495,7 +8689,7 @@
         <v>0</v>
       </c>
       <c r="I139" t="n">
-        <v>0</v>
+        <v>0.886</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
@@ -8504,27 +8698,28 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>review</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>All candidates have semantic conflicts or lack distinctive evidence.</t>
+          <t>The candidate 'V.FECP-ST/MT' has a strong name match and no semantic header conflict.</t>
         </is>
       </c>
       <c r="M139" t="inlineStr"/>
       <c r="N139" t="inlineStr"/>
       <c r="O139" t="inlineStr"/>
       <c r="P139" t="inlineStr"/>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q139" t="inlineStr"/>
       <c r="R139" t="n">
         <v>0</v>
       </c>
-      <c r="S139" t="inlineStr"/>
+      <c r="S139" t="n">
+        <v>0.886</v>
+      </c>
       <c r="T139" t="inlineStr"/>
       <c r="U139" t="inlineStr"/>
+      <c r="V139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -8564,22 +8759,23 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>All candidates exhibit semantic header conflicts and lack distinctive sample evidence.</t>
+          <t>All candidates exhibit semantic header conflicts and provide no distinctive sample evidence.</t>
         </is>
       </c>
       <c r="M140" t="inlineStr"/>
       <c r="N140" t="inlineStr"/>
       <c r="O140" t="inlineStr"/>
       <c r="P140" t="inlineStr"/>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q140" t="inlineStr"/>
       <c r="R140" t="n">
         <v>0</v>
       </c>
-      <c r="S140" t="inlineStr"/>
+      <c r="S140" t="n">
+        <v>0</v>
+      </c>
       <c r="T140" t="inlineStr"/>
       <c r="U140" t="inlineStr"/>
+      <c r="V140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -8632,15 +8828,16 @@
       <c r="N141" t="inlineStr"/>
       <c r="O141" t="inlineStr"/>
       <c r="P141" t="inlineStr"/>
-      <c r="Q141" t="n">
-        <v>0.8672</v>
-      </c>
+      <c r="Q141" t="inlineStr"/>
       <c r="R141" t="n">
         <v>0.8672</v>
       </c>
-      <c r="S141" t="inlineStr"/>
+      <c r="S141" t="n">
+        <v>0.8672</v>
+      </c>
       <c r="T141" t="inlineStr"/>
       <c r="U141" t="inlineStr"/>
+      <c r="V141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -8693,15 +8890,16 @@
       <c r="N142" t="inlineStr"/>
       <c r="O142" t="inlineStr"/>
       <c r="P142" t="inlineStr"/>
-      <c r="Q142" t="n">
-        <v>0.99</v>
-      </c>
+      <c r="Q142" t="inlineStr"/>
       <c r="R142" t="n">
         <v>0.8951</v>
       </c>
-      <c r="S142" t="inlineStr"/>
+      <c r="S142" t="n">
+        <v>0.8951</v>
+      </c>
       <c r="T142" t="inlineStr"/>
       <c r="U142" t="inlineStr"/>
+      <c r="V142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -8754,15 +8952,16 @@
       <c r="N143" t="inlineStr"/>
       <c r="O143" t="inlineStr"/>
       <c r="P143" t="inlineStr"/>
-      <c r="Q143" t="n">
-        <v>0.8941</v>
-      </c>
+      <c r="Q143" t="inlineStr"/>
       <c r="R143" t="n">
         <v>0.8941</v>
       </c>
-      <c r="S143" t="inlineStr"/>
+      <c r="S143" t="n">
+        <v>0.8941</v>
+      </c>
       <c r="T143" t="inlineStr"/>
       <c r="U143" t="inlineStr"/>
+      <c r="V143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -8808,22 +9007,23 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>The candidate 'B.ICMS ST An' has a high name confidence and no semantic conflicts, aligning with the tax situation of ICMS ST.</t>
+          <t>The candidate 'B.ICMS ST An' has the highest name confidence and no semantic conflicts.</t>
         </is>
       </c>
       <c r="M144" t="inlineStr"/>
       <c r="N144" t="inlineStr"/>
       <c r="O144" t="inlineStr"/>
       <c r="P144" t="inlineStr"/>
-      <c r="Q144" t="n">
-        <v>0.8847</v>
-      </c>
+      <c r="Q144" t="inlineStr"/>
       <c r="R144" t="n">
         <v>0.8847</v>
       </c>
-      <c r="S144" t="inlineStr"/>
+      <c r="S144" t="n">
+        <v>0.8847</v>
+      </c>
       <c r="T144" t="inlineStr"/>
       <c r="U144" t="inlineStr"/>
+      <c r="V144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -8834,22 +9034,28 @@
           <t>Outras ICMS_ST</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr"/>
-      <c r="D145" t="inlineStr"/>
+      <c r="C145" t="n">
+        <v>239</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>B.ICMS ST An</t>
+        </is>
+      </c>
       <c r="E145" t="n">
-        <v>0.882</v>
+        <v>0.8801</v>
       </c>
       <c r="F145" t="n">
-        <v>0.8981</v>
+        <v>0.8717</v>
       </c>
       <c r="G145" t="n">
-        <v>-0.016</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
       </c>
       <c r="I145" t="n">
-        <v>0</v>
+        <v>0.8801</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
@@ -8858,27 +9064,28 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>review</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Despite the tax-qualifier conflict, 'B.ICMS ST An' aligns closely with 'Outras ICMS_ST' in naming and type.</t>
         </is>
       </c>
       <c r="M145" t="inlineStr"/>
       <c r="N145" t="inlineStr"/>
       <c r="O145" t="inlineStr"/>
       <c r="P145" t="inlineStr"/>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q145" t="inlineStr"/>
       <c r="R145" t="n">
-        <v>0.882</v>
-      </c>
-      <c r="S145" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="S145" t="n">
+        <v>0.8801</v>
+      </c>
       <c r="T145" t="inlineStr"/>
       <c r="U145" t="inlineStr"/>
+      <c r="V145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -8918,22 +9125,23 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts and lack distinctive sample overlap, indicating no suitable mapping.</t>
+          <t>All candidates have semantic header conflicts and insufficient distinctive sample evidence.</t>
         </is>
       </c>
       <c r="M146" t="inlineStr"/>
       <c r="N146" t="inlineStr"/>
       <c r="O146" t="inlineStr"/>
       <c r="P146" t="inlineStr"/>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q146" t="inlineStr"/>
       <c r="R146" t="n">
-        <v>0.8487</v>
-      </c>
-      <c r="S146" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="S146" t="n">
+        <v>0</v>
+      </c>
       <c r="T146" t="inlineStr"/>
       <c r="U146" t="inlineStr"/>
+      <c r="V146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -8980,15 +9188,16 @@
       <c r="N147" t="inlineStr"/>
       <c r="O147" t="inlineStr"/>
       <c r="P147" t="inlineStr"/>
-      <c r="Q147" t="n">
+      <c r="Q147" t="inlineStr"/>
+      <c r="R147" t="n">
         <v>0.8</v>
       </c>
-      <c r="R147" t="n">
+      <c r="S147" t="n">
         <v>0.8248</v>
       </c>
-      <c r="S147" t="inlineStr"/>
       <c r="T147" t="inlineStr"/>
       <c r="U147" t="inlineStr"/>
+      <c r="V147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -9005,10 +9214,10 @@
         <v>0.7876</v>
       </c>
       <c r="F148" t="n">
-        <v>0.7801</v>
+        <v>0.7837</v>
       </c>
       <c r="G148" t="n">
-        <v>0.0075</v>
+        <v>0.0039</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
@@ -9028,22 +9237,23 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>No viable candidates match the semantic role of 'Municipio Inicio' as all candidates pertain to tax situations or codes.</t>
+          <t>All candidate columns contain no relevant data or evidence to support a mapping.</t>
         </is>
       </c>
       <c r="M148" t="inlineStr"/>
       <c r="N148" t="inlineStr"/>
       <c r="O148" t="inlineStr"/>
       <c r="P148" t="inlineStr"/>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q148" t="inlineStr"/>
       <c r="R148" t="n">
         <v>0</v>
       </c>
-      <c r="S148" t="inlineStr"/>
+      <c r="S148" t="n">
+        <v>0</v>
+      </c>
       <c r="T148" t="inlineStr"/>
       <c r="U148" t="inlineStr"/>
+      <c r="V148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -9090,15 +9300,16 @@
       <c r="N149" t="inlineStr"/>
       <c r="O149" t="inlineStr"/>
       <c r="P149" t="inlineStr"/>
-      <c r="Q149" t="n">
-        <v>0.8372000000000001</v>
-      </c>
+      <c r="Q149" t="inlineStr"/>
       <c r="R149" t="n">
         <v>0.8372000000000001</v>
       </c>
-      <c r="S149" t="inlineStr"/>
+      <c r="S149" t="n">
+        <v>0.8372000000000001</v>
+      </c>
       <c r="T149" t="inlineStr"/>
       <c r="U149" t="inlineStr"/>
+      <c r="V149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -9118,7 +9329,7 @@
         <v>0.768</v>
       </c>
       <c r="G150" t="n">
-        <v>-0.0567</v>
+        <v>-0.0568</v>
       </c>
       <c r="H150" t="n">
         <v>0.1633</v>
@@ -9145,15 +9356,16 @@
       <c r="N150" t="inlineStr"/>
       <c r="O150" t="inlineStr"/>
       <c r="P150" t="inlineStr"/>
-      <c r="Q150" t="n">
-        <v>0.7113</v>
-      </c>
+      <c r="Q150" t="inlineStr"/>
       <c r="R150" t="n">
         <v>0.7113</v>
       </c>
-      <c r="S150" t="inlineStr"/>
+      <c r="S150" t="n">
+        <v>0.7113</v>
+      </c>
       <c r="T150" t="inlineStr"/>
       <c r="U150" t="inlineStr"/>
+      <c r="V150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -9167,13 +9379,13 @@
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="n">
-        <v>0.8584000000000001</v>
+        <v>0.8583</v>
       </c>
       <c r="F151" t="n">
         <v>0.8366</v>
       </c>
       <c r="G151" t="n">
-        <v>0.0218</v>
+        <v>0.0217</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
@@ -9193,22 +9405,23 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>All candidates have insufficient evidence and do not align semantically with the 'Exercício' column.</t>
+          <t>All candidates have insufficient evidence or are empty, making a mapping impossible.</t>
         </is>
       </c>
       <c r="M151" t="inlineStr"/>
       <c r="N151" t="inlineStr"/>
       <c r="O151" t="inlineStr"/>
       <c r="P151" t="inlineStr"/>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q151" t="inlineStr"/>
       <c r="R151" t="n">
         <v>0</v>
       </c>
-      <c r="S151" t="inlineStr"/>
+      <c r="S151" t="n">
+        <v>0</v>
+      </c>
       <c r="T151" t="inlineStr"/>
       <c r="U151" t="inlineStr"/>
+      <c r="V151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -9225,7 +9438,7 @@
         <v>0.8034</v>
       </c>
       <c r="F152" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8161</v>
       </c>
       <c r="G152" t="n">
         <v>-0.0127</v>
@@ -9255,15 +9468,16 @@
       <c r="N152" t="inlineStr"/>
       <c r="O152" t="inlineStr"/>
       <c r="P152" t="inlineStr"/>
-      <c r="Q152" t="n">
-        <v>0.8</v>
-      </c>
+      <c r="Q152" t="inlineStr"/>
       <c r="R152" t="n">
         <v>0.8034</v>
       </c>
-      <c r="S152" t="inlineStr"/>
+      <c r="S152" t="n">
+        <v>0.8034</v>
+      </c>
       <c r="T152" t="inlineStr"/>
       <c r="U152" t="inlineStr"/>
+      <c r="V152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -9280,7 +9494,7 @@
         <v>0.7963</v>
       </c>
       <c r="F153" t="n">
-        <v>0.7881</v>
+        <v>0.7882</v>
       </c>
       <c r="G153" t="n">
         <v>0.008200000000000001</v>
@@ -9310,15 +9524,16 @@
       <c r="N153" t="inlineStr"/>
       <c r="O153" t="inlineStr"/>
       <c r="P153" t="inlineStr"/>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q153" t="inlineStr"/>
       <c r="R153" t="n">
+        <v>0</v>
+      </c>
+      <c r="S153" t="n">
         <v>0.7963</v>
       </c>
-      <c r="S153" t="inlineStr"/>
       <c r="T153" t="inlineStr"/>
       <c r="U153" t="inlineStr"/>
+      <c r="V153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -9332,10 +9547,10 @@
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="n">
-        <v>0.8688</v>
+        <v>0.8689</v>
       </c>
       <c r="F154" t="n">
-        <v>0.832</v>
+        <v>0.8321</v>
       </c>
       <c r="G154" t="n">
         <v>0.0368</v>
@@ -9358,22 +9573,23 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>All candidate columns have empty profiles and lack distinctive content to support a mapping.</t>
+          <t>All candidate columns are empty with no distinctive content or evidence to support a mapping.</t>
         </is>
       </c>
       <c r="M154" t="inlineStr"/>
       <c r="N154" t="inlineStr"/>
       <c r="O154" t="inlineStr"/>
       <c r="P154" t="inlineStr"/>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q154" t="inlineStr"/>
       <c r="R154" t="n">
         <v>0</v>
       </c>
-      <c r="S154" t="inlineStr"/>
+      <c r="S154" t="n">
+        <v>0</v>
+      </c>
       <c r="T154" t="inlineStr"/>
       <c r="U154" t="inlineStr"/>
+      <c r="V154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -9413,22 +9629,23 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>All candidate columns lack sufficient non-empty data to establish a meaningful mapping.</t>
+          <t>All candidate columns lack meaningful data evidence, making a mapping unsupported.</t>
         </is>
       </c>
       <c r="M155" t="inlineStr"/>
       <c r="N155" t="inlineStr"/>
       <c r="O155" t="inlineStr"/>
       <c r="P155" t="inlineStr"/>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q155" t="inlineStr"/>
       <c r="R155" t="n">
         <v>0</v>
       </c>
-      <c r="S155" t="inlineStr"/>
+      <c r="S155" t="n">
+        <v>0</v>
+      </c>
       <c r="T155" t="inlineStr"/>
       <c r="U155" t="inlineStr"/>
+      <c r="V155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -9475,15 +9692,16 @@
       <c r="N156" t="inlineStr"/>
       <c r="O156" t="inlineStr"/>
       <c r="P156" t="inlineStr"/>
-      <c r="Q156" t="n">
-        <v>0.8388</v>
-      </c>
+      <c r="Q156" t="inlineStr"/>
       <c r="R156" t="n">
         <v>0.8388</v>
       </c>
-      <c r="S156" t="inlineStr"/>
+      <c r="S156" t="n">
+        <v>0.8388</v>
+      </c>
       <c r="T156" t="inlineStr"/>
       <c r="U156" t="inlineStr"/>
+      <c r="V156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -9503,7 +9721,7 @@
         <v>0.8413</v>
       </c>
       <c r="G157" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0089</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -9523,22 +9741,23 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>No suitable candidate matches the semantic role of 'ID do consumidor final' based on the provided evidence.</t>
+          <t>No suitable candidate matches the semantic role of 'ID do consumidor final'.</t>
         </is>
       </c>
       <c r="M157" t="inlineStr"/>
       <c r="N157" t="inlineStr"/>
       <c r="O157" t="inlineStr"/>
       <c r="P157" t="inlineStr"/>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q157" t="inlineStr"/>
       <c r="R157" t="n">
         <v>0</v>
       </c>
-      <c r="S157" t="inlineStr"/>
+      <c r="S157" t="n">
+        <v>0</v>
+      </c>
       <c r="T157" t="inlineStr"/>
       <c r="U157" t="inlineStr"/>
+      <c r="V157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -9549,28 +9768,22 @@
           <t>Dest.</t>
         </is>
       </c>
-      <c r="C158" t="n">
-        <v>252</v>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>Cliente Dest</t>
-        </is>
-      </c>
+      <c r="C158" t="inlineStr"/>
+      <c r="D158" t="inlineStr"/>
       <c r="E158" t="n">
+        <v>0.772</v>
+      </c>
+      <c r="F158" t="n">
         <v>0.8815</v>
       </c>
-      <c r="F158" t="n">
-        <v>0.8586</v>
-      </c>
       <c r="G158" t="n">
-        <v>0.0229</v>
+        <v>-0.1095</v>
       </c>
       <c r="H158" t="n">
-        <v>0.325</v>
+        <v>0.84</v>
       </c>
       <c r="I158" t="n">
-        <v>0.8815</v>
+        <v>0</v>
       </c>
       <c r="J158" t="inlineStr">
         <is>
@@ -9579,27 +9792,28 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>no_match</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>The header 'Cliente Dest' suggests a destination client, aligning with the numeric values indicating a destination code.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M158" t="inlineStr"/>
       <c r="N158" t="inlineStr"/>
       <c r="O158" t="inlineStr"/>
       <c r="P158" t="inlineStr"/>
-      <c r="Q158" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="Q158" t="inlineStr"/>
       <c r="R158" t="n">
-        <v>0.8815</v>
-      </c>
-      <c r="S158" t="inlineStr"/>
+        <v>0.772</v>
+      </c>
+      <c r="S158" t="n">
+        <v>0.772</v>
+      </c>
       <c r="T158" t="inlineStr"/>
       <c r="U158" t="inlineStr"/>
+      <c r="V158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -9622,7 +9836,7 @@
         <v>0.8584000000000001</v>
       </c>
       <c r="F159" t="n">
-        <v>0.8558</v>
+        <v>0.8557</v>
       </c>
       <c r="G159" t="n">
         <v>0.0026</v>
@@ -9652,15 +9866,16 @@
       <c r="N159" t="inlineStr"/>
       <c r="O159" t="inlineStr"/>
       <c r="P159" t="inlineStr"/>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q159" t="inlineStr"/>
       <c r="R159" t="n">
         <v>0</v>
       </c>
-      <c r="S159" t="inlineStr"/>
+      <c r="S159" t="n">
+        <v>0</v>
+      </c>
       <c r="T159" t="inlineStr"/>
       <c r="U159" t="inlineStr"/>
+      <c r="V159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -9674,13 +9889,13 @@
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="n">
-        <v>0.8309</v>
+        <v>0.8312</v>
       </c>
       <c r="F160" t="n">
-        <v>0.8465</v>
+        <v>0.8464</v>
       </c>
       <c r="G160" t="n">
-        <v>-0.0157</v>
+        <v>-0.0153</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -9707,15 +9922,16 @@
       <c r="N160" t="inlineStr"/>
       <c r="O160" t="inlineStr"/>
       <c r="P160" t="inlineStr"/>
-      <c r="Q160" t="n">
-        <v>0.8309</v>
-      </c>
+      <c r="Q160" t="inlineStr"/>
       <c r="R160" t="n">
-        <v>0.8309</v>
-      </c>
-      <c r="S160" t="inlineStr"/>
+        <v>0.8312</v>
+      </c>
+      <c r="S160" t="n">
+        <v>0.8312</v>
+      </c>
       <c r="T160" t="inlineStr"/>
       <c r="U160" t="inlineStr"/>
+      <c r="V160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -9729,13 +9945,13 @@
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="n">
-        <v>0.8152</v>
+        <v>0.8154</v>
       </c>
       <c r="F161" t="n">
-        <v>0.8121</v>
+        <v>0.8153</v>
       </c>
       <c r="G161" t="n">
-        <v>0.0031</v>
+        <v>0.0002</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -9755,22 +9971,23 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>No candidate columns provide relevant data evidence to support a mapping.</t>
         </is>
       </c>
       <c r="M161" t="inlineStr"/>
       <c r="N161" t="inlineStr"/>
       <c r="O161" t="inlineStr"/>
       <c r="P161" t="inlineStr"/>
-      <c r="Q161" t="n">
-        <v>0.8</v>
-      </c>
+      <c r="Q161" t="inlineStr"/>
       <c r="R161" t="n">
-        <v>0.8152</v>
-      </c>
-      <c r="S161" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="S161" t="n">
+        <v>0</v>
+      </c>
       <c r="T161" t="inlineStr"/>
       <c r="U161" t="inlineStr"/>
+      <c r="V161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -9826,6 +10043,7 @@
       <c r="S162" t="inlineStr"/>
       <c r="T162" t="inlineStr"/>
       <c r="U162" t="inlineStr"/>
+      <c r="V162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -9872,15 +10090,16 @@
       <c r="N163" t="inlineStr"/>
       <c r="O163" t="inlineStr"/>
       <c r="P163" t="inlineStr"/>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q163" t="inlineStr"/>
       <c r="R163" t="n">
         <v>0</v>
       </c>
-      <c r="S163" t="inlineStr"/>
+      <c r="S163" t="n">
+        <v>0</v>
+      </c>
       <c r="T163" t="inlineStr"/>
       <c r="U163" t="inlineStr"/>
+      <c r="V163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -9927,15 +10146,16 @@
       <c r="N164" t="inlineStr"/>
       <c r="O164" t="inlineStr"/>
       <c r="P164" t="inlineStr"/>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q164" t="inlineStr"/>
       <c r="R164" t="n">
+        <v>0</v>
+      </c>
+      <c r="S164" t="n">
         <v>0.8007</v>
       </c>
-      <c r="S164" t="inlineStr"/>
       <c r="T164" t="inlineStr"/>
       <c r="U164" t="inlineStr"/>
+      <c r="V164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -9949,7 +10169,7 @@
       <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="n">
-        <v>0.7877</v>
+        <v>0.7876</v>
       </c>
       <c r="F165" t="n">
         <v>0.7975</v>
@@ -9982,15 +10202,16 @@
       <c r="N165" t="inlineStr"/>
       <c r="O165" t="inlineStr"/>
       <c r="P165" t="inlineStr"/>
-      <c r="Q165" t="n">
-        <v>0.7877</v>
-      </c>
+      <c r="Q165" t="inlineStr"/>
       <c r="R165" t="n">
-        <v>0.7877</v>
-      </c>
-      <c r="S165" t="inlineStr"/>
+        <v>0.7876</v>
+      </c>
+      <c r="S165" t="n">
+        <v>0.7876</v>
+      </c>
       <c r="T165" t="inlineStr"/>
       <c r="U165" t="inlineStr"/>
+      <c r="V165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -10046,6 +10267,7 @@
       <c r="S166" t="inlineStr"/>
       <c r="T166" t="inlineStr"/>
       <c r="U166" t="inlineStr"/>
+      <c r="V166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -10085,22 +10307,23 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>All candidates have empty evidence with no distinctive samples or valid data.</t>
+          <t>All candidates have empty evidence quality, indicating no valid data to support a mapping.</t>
         </is>
       </c>
       <c r="M167" t="inlineStr"/>
       <c r="N167" t="inlineStr"/>
       <c r="O167" t="inlineStr"/>
       <c r="P167" t="inlineStr"/>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q167" t="inlineStr"/>
       <c r="R167" t="n">
         <v>0</v>
       </c>
-      <c r="S167" t="inlineStr"/>
+      <c r="S167" t="n">
+        <v>0</v>
+      </c>
       <c r="T167" t="inlineStr"/>
       <c r="U167" t="inlineStr"/>
+      <c r="V167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -10147,15 +10370,16 @@
       <c r="N168" t="inlineStr"/>
       <c r="O168" t="inlineStr"/>
       <c r="P168" t="inlineStr"/>
-      <c r="Q168" t="n">
+      <c r="Q168" t="inlineStr"/>
+      <c r="R168" t="n">
         <v>0.97</v>
       </c>
-      <c r="R168" t="n">
+      <c r="S168" t="n">
         <v>0.83</v>
       </c>
-      <c r="S168" t="inlineStr"/>
       <c r="T168" t="inlineStr"/>
       <c r="U168" t="inlineStr"/>
+      <c r="V168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -10208,15 +10432,16 @@
       <c r="N169" t="inlineStr"/>
       <c r="O169" t="inlineStr"/>
       <c r="P169" t="inlineStr"/>
-      <c r="Q169" t="n">
-        <v>0.8512999999999999</v>
-      </c>
+      <c r="Q169" t="inlineStr"/>
       <c r="R169" t="n">
         <v>0.8512999999999999</v>
       </c>
-      <c r="S169" t="inlineStr"/>
+      <c r="S169" t="n">
+        <v>0.8512999999999999</v>
+      </c>
       <c r="T169" t="inlineStr"/>
       <c r="U169" t="inlineStr"/>
+      <c r="V169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -10269,15 +10494,16 @@
       <c r="N170" t="inlineStr"/>
       <c r="O170" t="inlineStr"/>
       <c r="P170" t="inlineStr"/>
-      <c r="Q170" t="n">
-        <v>0.9036</v>
-      </c>
+      <c r="Q170" t="inlineStr"/>
       <c r="R170" t="n">
         <v>0.9036</v>
       </c>
-      <c r="S170" t="inlineStr"/>
+      <c r="S170" t="n">
+        <v>0.9036</v>
+      </c>
       <c r="T170" t="inlineStr"/>
       <c r="U170" t="inlineStr"/>
+      <c r="V170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -10323,22 +10549,23 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>The candidate 'Aliq FECP' closely matches the semantic role of 'Alíquota ICOP FECP' with a high name confidence and no conflicting evidence.</t>
+          <t>The candidate 'Aliq FECP' closely matches the semantic role of 'Alíquota ICOP FECP' with a high name confidence and no semantic conflicts.</t>
         </is>
       </c>
       <c r="M171" t="inlineStr"/>
       <c r="N171" t="inlineStr"/>
       <c r="O171" t="inlineStr"/>
       <c r="P171" t="inlineStr"/>
-      <c r="Q171" t="n">
-        <v>0.8787</v>
-      </c>
+      <c r="Q171" t="inlineStr"/>
       <c r="R171" t="n">
         <v>0.8787</v>
       </c>
-      <c r="S171" t="inlineStr"/>
+      <c r="S171" t="n">
+        <v>0.8787</v>
+      </c>
       <c r="T171" t="inlineStr"/>
       <c r="U171" t="inlineStr"/>
+      <c r="V171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -10361,10 +10588,10 @@
         <v>0.9402</v>
       </c>
       <c r="F172" t="n">
-        <v>0.9233</v>
+        <v>0.9239000000000001</v>
       </c>
       <c r="G172" t="n">
-        <v>0.0168</v>
+        <v>0.0163</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -10391,15 +10618,16 @@
       <c r="N172" t="inlineStr"/>
       <c r="O172" t="inlineStr"/>
       <c r="P172" t="inlineStr"/>
-      <c r="Q172" t="n">
-        <v>0.9402</v>
-      </c>
+      <c r="Q172" t="inlineStr"/>
       <c r="R172" t="n">
         <v>0.9402</v>
       </c>
-      <c r="S172" t="inlineStr"/>
+      <c r="S172" t="n">
+        <v>0.9402</v>
+      </c>
       <c r="T172" t="inlineStr"/>
       <c r="U172" t="inlineStr"/>
+      <c r="V172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -10422,10 +10650,10 @@
         <v>0.8653</v>
       </c>
       <c r="F173" t="n">
-        <v>0.844</v>
+        <v>0.847</v>
       </c>
       <c r="G173" t="n">
-        <v>0.0213</v>
+        <v>0.0183</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -10445,22 +10673,23 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>The candidate 'FECP Comp.' has the highest name confidence but lacks distinctive data evidence.</t>
+          <t>The name 'FECP Comp.' has a high confidence score, but all values are zero, indicating no valid data.</t>
         </is>
       </c>
       <c r="M173" t="inlineStr"/>
       <c r="N173" t="inlineStr"/>
       <c r="O173" t="inlineStr"/>
       <c r="P173" t="inlineStr"/>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q173" t="inlineStr"/>
       <c r="R173" t="n">
+        <v>0</v>
+      </c>
+      <c r="S173" t="n">
         <v>0.8653</v>
       </c>
-      <c r="S173" t="inlineStr"/>
       <c r="T173" t="inlineStr"/>
       <c r="U173" t="inlineStr"/>
+      <c r="V173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -10471,22 +10700,28 @@
           <t>Outras ICOP FECP</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr"/>
-      <c r="D174" t="inlineStr"/>
+      <c r="C174" t="n">
+        <v>321</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>FECP Comp.</t>
+        </is>
+      </c>
       <c r="E174" t="n">
         <v>0.8799</v>
       </c>
       <c r="F174" t="n">
-        <v>0.8506</v>
+        <v>0</v>
       </c>
       <c r="G174" t="n">
-        <v>0.0292</v>
+        <v>0.8799</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
       </c>
       <c r="I174" t="n">
-        <v>0</v>
+        <v>0.8799</v>
       </c>
       <c r="J174" t="inlineStr">
         <is>
@@ -10495,27 +10730,28 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>review</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>All candidates exhibit semantic-role conflicts or lack distinctive evidence, making them unsuitable for mapping.</t>
+          <t>The candidate 'FECP Comp.' has a high name confidence but lacks distinctive data evidence.</t>
         </is>
       </c>
       <c r="M174" t="inlineStr"/>
       <c r="N174" t="inlineStr"/>
       <c r="O174" t="inlineStr"/>
       <c r="P174" t="inlineStr"/>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q174" t="inlineStr"/>
       <c r="R174" t="n">
         <v>0</v>
       </c>
-      <c r="S174" t="inlineStr"/>
+      <c r="S174" t="n">
+        <v>0.8799</v>
+      </c>
       <c r="T174" t="inlineStr"/>
       <c r="U174" t="inlineStr"/>
+      <c r="V174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -10529,16 +10765,16 @@
       <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="n">
-        <v>0.7786</v>
+        <v>0.7421</v>
       </c>
       <c r="F175" t="n">
         <v>0.8415</v>
       </c>
       <c r="G175" t="n">
-        <v>-0.0629</v>
+        <v>-0.0994</v>
       </c>
       <c r="H175" t="n">
-        <v>0.2504</v>
+        <v>0.7558</v>
       </c>
       <c r="I175" t="n">
         <v>0</v>
@@ -10562,15 +10798,16 @@
       <c r="N175" t="inlineStr"/>
       <c r="O175" t="inlineStr"/>
       <c r="P175" t="inlineStr"/>
-      <c r="Q175" t="n">
-        <v>0.7786</v>
-      </c>
+      <c r="Q175" t="inlineStr"/>
       <c r="R175" t="n">
-        <v>0.7786</v>
-      </c>
-      <c r="S175" t="inlineStr"/>
+        <v>0.7421</v>
+      </c>
+      <c r="S175" t="n">
+        <v>0.7421</v>
+      </c>
       <c r="T175" t="inlineStr"/>
       <c r="U175" t="inlineStr"/>
+      <c r="V175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -10584,16 +10821,16 @@
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="n">
-        <v>0.7563</v>
+        <v>0.7985</v>
       </c>
       <c r="F176" t="n">
         <v>0.8195</v>
       </c>
       <c r="G176" t="n">
-        <v>-0.06320000000000001</v>
+        <v>-0.021</v>
       </c>
       <c r="H176" t="n">
-        <v>0.7806</v>
+        <v>0.681</v>
       </c>
       <c r="I176" t="n">
         <v>0</v>
@@ -10617,15 +10854,16 @@
       <c r="N176" t="inlineStr"/>
       <c r="O176" t="inlineStr"/>
       <c r="P176" t="inlineStr"/>
-      <c r="Q176" t="n">
-        <v>0.7563</v>
-      </c>
+      <c r="Q176" t="inlineStr"/>
       <c r="R176" t="n">
-        <v>0.7563</v>
-      </c>
-      <c r="S176" t="inlineStr"/>
+        <v>0.7985</v>
+      </c>
+      <c r="S176" t="n">
+        <v>0.7985</v>
+      </c>
       <c r="T176" t="inlineStr"/>
       <c r="U176" t="inlineStr"/>
+      <c r="V176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -10672,15 +10910,16 @@
       <c r="N177" t="inlineStr"/>
       <c r="O177" t="inlineStr"/>
       <c r="P177" t="inlineStr"/>
-      <c r="Q177" t="n">
+      <c r="Q177" t="inlineStr"/>
+      <c r="R177" t="n">
+        <v>0.7872</v>
+      </c>
+      <c r="S177" t="n">
         <v>0.8299</v>
       </c>
-      <c r="R177" t="n">
-        <v>0.8299</v>
-      </c>
-      <c r="S177" t="inlineStr"/>
       <c r="T177" t="inlineStr"/>
       <c r="U177" t="inlineStr"/>
+      <c r="V177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -10697,10 +10936,10 @@
         <v>0.8305</v>
       </c>
       <c r="F178" t="n">
-        <v>0.8216</v>
+        <v>0.8217</v>
       </c>
       <c r="G178" t="n">
-        <v>0.0089</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -10720,22 +10959,23 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>No viable candidates due to lack of evidence and semantic conflicts.</t>
         </is>
       </c>
       <c r="M178" t="inlineStr"/>
       <c r="N178" t="inlineStr"/>
       <c r="O178" t="inlineStr"/>
       <c r="P178" t="inlineStr"/>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q178" t="inlineStr"/>
       <c r="R178" t="n">
-        <v>0.8305</v>
-      </c>
-      <c r="S178" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="S178" t="n">
+        <v>0</v>
+      </c>
       <c r="T178" t="inlineStr"/>
       <c r="U178" t="inlineStr"/>
+      <c r="V178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -10755,10 +10995,10 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>0.8555</v>
+        <v>0.8554</v>
       </c>
       <c r="F179" t="n">
-        <v>0.8573</v>
+        <v>0.8572</v>
       </c>
       <c r="G179" t="n">
         <v>-0.0018</v>
@@ -10767,7 +11007,7 @@
         <v>0.84</v>
       </c>
       <c r="I179" t="n">
-        <v>0.8555</v>
+        <v>0.8554</v>
       </c>
       <c r="J179" t="inlineStr">
         <is>
@@ -10781,22 +11021,23 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>The 'Doc. Fiscal' column has a strong numeric profile and a high non-empty count, closely matching the expected format of invoice document numbers.</t>
+          <t>The 'Doc. Fiscal' column has a strong numeric profile with a fixed width of 9 digits, closely matching the 10-digit format of 'Nº documento'.</t>
         </is>
       </c>
       <c r="M179" t="inlineStr"/>
       <c r="N179" t="inlineStr"/>
       <c r="O179" t="inlineStr"/>
       <c r="P179" t="inlineStr"/>
-      <c r="Q179" t="n">
-        <v>0.985</v>
-      </c>
+      <c r="Q179" t="inlineStr"/>
       <c r="R179" t="n">
-        <v>0.8714</v>
-      </c>
-      <c r="S179" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="S179" t="n">
+        <v>0.88</v>
+      </c>
       <c r="T179" t="inlineStr"/>
       <c r="U179" t="inlineStr"/>
+      <c r="V179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -10810,16 +11051,16 @@
       <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="n">
-        <v>0.8144</v>
+        <v>0.836</v>
       </c>
       <c r="F180" t="n">
-        <v>0.836</v>
+        <v>0.8279</v>
       </c>
       <c r="G180" t="n">
-        <v>-0.0215</v>
+        <v>0.0081</v>
       </c>
       <c r="H180" t="n">
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="I180" t="n">
         <v>0</v>
@@ -10836,22 +11077,23 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>No candidate column matches the expected numeric format and semantic role for 'Empresa'.</t>
         </is>
       </c>
       <c r="M180" t="inlineStr"/>
       <c r="N180" t="inlineStr"/>
       <c r="O180" t="inlineStr"/>
       <c r="P180" t="inlineStr"/>
-      <c r="Q180" t="n">
-        <v>0.8144</v>
-      </c>
+      <c r="Q180" t="inlineStr"/>
       <c r="R180" t="n">
-        <v>0.8144</v>
-      </c>
-      <c r="S180" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="S180" t="n">
+        <v>0</v>
+      </c>
       <c r="T180" t="inlineStr"/>
       <c r="U180" t="inlineStr"/>
+      <c r="V180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -10868,10 +11110,10 @@
         <v>0.8176</v>
       </c>
       <c r="F181" t="n">
-        <v>0.8137</v>
+        <v>0.8175</v>
       </c>
       <c r="G181" t="n">
-        <v>0.0039</v>
+        <v>0</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
@@ -10891,22 +11133,23 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>No suitable candidate found due to lack of evidence in the 'Exportador' column.</t>
+          <t>The 'Exportador' column is empty, providing no evidence to support a mapping.</t>
         </is>
       </c>
       <c r="M181" t="inlineStr"/>
       <c r="N181" t="inlineStr"/>
       <c r="O181" t="inlineStr"/>
       <c r="P181" t="inlineStr"/>
-      <c r="Q181" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q181" t="inlineStr"/>
       <c r="R181" t="n">
         <v>0</v>
       </c>
-      <c r="S181" t="inlineStr"/>
+      <c r="S181" t="n">
+        <v>0.8115</v>
+      </c>
       <c r="T181" t="inlineStr"/>
       <c r="U181" t="inlineStr"/>
+      <c r="V181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -10920,7 +11163,7 @@
       <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr"/>
       <c r="E182" t="n">
-        <v>0.7986</v>
+        <v>0.7987</v>
       </c>
       <c r="F182" t="n">
         <v>0.798</v>
@@ -10946,22 +11189,23 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>All candidates have empty evidence, making it impossible to establish a valid mapping.</t>
+          <t>All candidate columns are empty or lack distinctive content, making it impossible to establish a valid mapping.</t>
         </is>
       </c>
       <c r="M182" t="inlineStr"/>
       <c r="N182" t="inlineStr"/>
       <c r="O182" t="inlineStr"/>
       <c r="P182" t="inlineStr"/>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q182" t="inlineStr"/>
       <c r="R182" t="n">
-        <v>0.7986</v>
-      </c>
-      <c r="S182" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="S182" t="n">
+        <v>0.7987</v>
+      </c>
       <c r="T182" t="inlineStr"/>
       <c r="U182" t="inlineStr"/>
+      <c r="V182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -10975,13 +11219,13 @@
       <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr"/>
       <c r="E183" t="n">
-        <v>0.8265</v>
+        <v>0.8205</v>
       </c>
       <c r="F183" t="n">
-        <v>0.8255</v>
+        <v>0.8266</v>
       </c>
       <c r="G183" t="n">
-        <v>0.001</v>
+        <v>-0.0061</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -11001,22 +11245,23 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>All candidates have insufficient evidence and do not align semantically with the empty model column.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M183" t="inlineStr"/>
       <c r="N183" t="inlineStr"/>
       <c r="O183" t="inlineStr"/>
       <c r="P183" t="inlineStr"/>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q183" t="inlineStr"/>
       <c r="R183" t="n">
-        <v>0</v>
-      </c>
-      <c r="S183" t="inlineStr"/>
+        <v>0.993</v>
+      </c>
+      <c r="S183" t="n">
+        <v>0.8205</v>
+      </c>
       <c r="T183" t="inlineStr"/>
       <c r="U183" t="inlineStr"/>
+      <c r="V183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -11030,16 +11275,16 @@
       <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr"/>
       <c r="E184" t="n">
-        <v>0.8149</v>
+        <v>0.8353</v>
       </c>
       <c r="F184" t="n">
-        <v>0.8351</v>
+        <v>0.8231000000000001</v>
       </c>
       <c r="G184" t="n">
-        <v>-0.0202</v>
+        <v>0.0122</v>
       </c>
       <c r="H184" t="n">
-        <v>0.4286</v>
+        <v>0</v>
       </c>
       <c r="I184" t="n">
         <v>0</v>
@@ -11056,22 +11301,23 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>No viable candidates match the semantic role of 'Código Fornecedor Início' based on the provided evidence.</t>
         </is>
       </c>
       <c r="M184" t="inlineStr"/>
       <c r="N184" t="inlineStr"/>
       <c r="O184" t="inlineStr"/>
       <c r="P184" t="inlineStr"/>
-      <c r="Q184" t="n">
-        <v>0.8149</v>
-      </c>
+      <c r="Q184" t="inlineStr"/>
       <c r="R184" t="n">
-        <v>0.8149</v>
-      </c>
-      <c r="S184" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="S184" t="n">
+        <v>0</v>
+      </c>
       <c r="T184" t="inlineStr"/>
       <c r="U184" t="inlineStr"/>
+      <c r="V184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -11124,15 +11370,16 @@
       <c r="N185" t="inlineStr"/>
       <c r="O185" t="inlineStr"/>
       <c r="P185" t="inlineStr"/>
-      <c r="Q185" t="n">
+      <c r="Q185" t="inlineStr"/>
+      <c r="R185" t="n">
         <v>0.9968</v>
       </c>
-      <c r="R185" t="n">
-        <v>0.989</v>
-      </c>
-      <c r="S185" t="inlineStr"/>
+      <c r="S185" t="n">
+        <v>0.9968</v>
+      </c>
       <c r="T185" t="inlineStr"/>
       <c r="U185" t="inlineStr"/>
+      <c r="V185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -11149,7 +11396,7 @@
         <v>0.8228</v>
       </c>
       <c r="F186" t="n">
-        <v>0.845</v>
+        <v>0.8451</v>
       </c>
       <c r="G186" t="n">
         <v>-0.0222</v>
@@ -11179,15 +11426,16 @@
       <c r="N186" t="inlineStr"/>
       <c r="O186" t="inlineStr"/>
       <c r="P186" t="inlineStr"/>
-      <c r="Q186" t="n">
-        <v>0.8228</v>
-      </c>
+      <c r="Q186" t="inlineStr"/>
       <c r="R186" t="n">
         <v>0.8228</v>
       </c>
-      <c r="S186" t="inlineStr"/>
+      <c r="S186" t="n">
+        <v>0.8228</v>
+      </c>
       <c r="T186" t="inlineStr"/>
       <c r="U186" t="inlineStr"/>
+      <c r="V186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -11201,10 +11449,10 @@
       <c r="C187" t="inlineStr"/>
       <c r="D187" t="inlineStr"/>
       <c r="E187" t="n">
-        <v>0.8319</v>
+        <v>0.832</v>
       </c>
       <c r="F187" t="n">
-        <v>0.849</v>
+        <v>0.8491</v>
       </c>
       <c r="G187" t="n">
         <v>-0.0171</v>
@@ -11234,15 +11482,16 @@
       <c r="N187" t="inlineStr"/>
       <c r="O187" t="inlineStr"/>
       <c r="P187" t="inlineStr"/>
-      <c r="Q187" t="n">
-        <v>0.8319</v>
-      </c>
+      <c r="Q187" t="inlineStr"/>
       <c r="R187" t="n">
-        <v>0.8319</v>
-      </c>
-      <c r="S187" t="inlineStr"/>
+        <v>0.832</v>
+      </c>
+      <c r="S187" t="n">
+        <v>0.832</v>
+      </c>
       <c r="T187" t="inlineStr"/>
       <c r="U187" t="inlineStr"/>
+      <c r="V187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -11268,7 +11517,7 @@
         <v>0.8274</v>
       </c>
       <c r="G188" t="n">
-        <v>0.027</v>
+        <v>0.0271</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
@@ -11288,22 +11537,23 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>The column 'Doc. Fiscal' has a strong numeric profile and aligns closely with the semantic role of 'Documento de compras'.</t>
+          <t>The header 'Doc. Fiscal' closely aligns with the semantic role of 'Documento de compras' and has substantial numeric data evidence.</t>
         </is>
       </c>
       <c r="M188" t="inlineStr"/>
       <c r="N188" t="inlineStr"/>
       <c r="O188" t="inlineStr"/>
       <c r="P188" t="inlineStr"/>
-      <c r="Q188" t="n">
+      <c r="Q188" t="inlineStr"/>
+      <c r="R188" t="n">
         <v>0.9</v>
       </c>
-      <c r="R188" t="n">
+      <c r="S188" t="n">
         <v>0.8545</v>
       </c>
-      <c r="S188" t="inlineStr"/>
       <c r="T188" t="inlineStr"/>
       <c r="U188" t="inlineStr"/>
+      <c r="V188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -11323,10 +11573,10 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>0.914</v>
+        <v>0.9139</v>
       </c>
       <c r="F189" t="n">
-        <v>0.8444</v>
+        <v>0.8443000000000001</v>
       </c>
       <c r="G189" t="n">
         <v>0.0696</v>
@@ -11335,7 +11585,7 @@
         <v>0</v>
       </c>
       <c r="I189" t="n">
-        <v>0.914</v>
+        <v>0.9139</v>
       </c>
       <c r="J189" t="inlineStr">
         <is>
@@ -11356,15 +11606,16 @@
       <c r="N189" t="inlineStr"/>
       <c r="O189" t="inlineStr"/>
       <c r="P189" t="inlineStr"/>
-      <c r="Q189" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="Q189" t="inlineStr"/>
       <c r="R189" t="n">
-        <v>0.8708</v>
-      </c>
-      <c r="S189" t="inlineStr"/>
+        <v>0.8725000000000001</v>
+      </c>
+      <c r="S189" t="n">
+        <v>0.8725000000000001</v>
+      </c>
       <c r="T189" t="inlineStr"/>
       <c r="U189" t="inlineStr"/>
+      <c r="V189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -11404,22 +11655,23 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>All candidates have empty or all-zero evidence, providing no support for a mapping.</t>
+          <t>All candidates have empty or all-zero evidence, making them unsuitable for mapping.</t>
         </is>
       </c>
       <c r="M190" t="inlineStr"/>
       <c r="N190" t="inlineStr"/>
       <c r="O190" t="inlineStr"/>
       <c r="P190" t="inlineStr"/>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q190" t="inlineStr"/>
       <c r="R190" t="n">
         <v>0</v>
       </c>
-      <c r="S190" t="inlineStr"/>
+      <c r="S190" t="n">
+        <v>0</v>
+      </c>
       <c r="T190" t="inlineStr"/>
       <c r="U190" t="inlineStr"/>
+      <c r="V190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -11470,11 +11722,16 @@
       <c r="N191" t="inlineStr"/>
       <c r="O191" t="inlineStr"/>
       <c r="P191" t="inlineStr"/>
-      <c r="Q191" t="inlineStr"/>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>valor = base x aliquota holds for icms on 5570 rows at fit 0.998</t>
+        </is>
+      </c>
       <c r="R191" t="inlineStr"/>
       <c r="S191" t="inlineStr"/>
       <c r="T191" t="inlineStr"/>
       <c r="U191" t="inlineStr"/>
+      <c r="V191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -11488,7 +11745,7 @@
       <c r="C192" t="inlineStr"/>
       <c r="D192" t="inlineStr"/>
       <c r="E192" t="n">
-        <v>0.8476</v>
+        <v>0.8477</v>
       </c>
       <c r="F192" t="n">
         <v>0.8431</v>
@@ -11521,15 +11778,16 @@
       <c r="N192" t="inlineStr"/>
       <c r="O192" t="inlineStr"/>
       <c r="P192" t="inlineStr"/>
-      <c r="Q192" t="n">
+      <c r="Q192" t="inlineStr"/>
+      <c r="R192" t="n">
         <v>0.5</v>
       </c>
-      <c r="R192" t="n">
-        <v>0.8476</v>
-      </c>
-      <c r="S192" t="inlineStr"/>
+      <c r="S192" t="n">
+        <v>0.8179999999999999</v>
+      </c>
       <c r="T192" t="inlineStr"/>
       <c r="U192" t="inlineStr"/>
+      <c r="V192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -11580,11 +11838,16 @@
       <c r="N193" t="inlineStr"/>
       <c r="O193" t="inlineStr"/>
       <c r="P193" t="inlineStr"/>
-      <c r="Q193" t="inlineStr"/>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>valor = base x aliquota holds for ipi on 3275 rows at fit 0.9979</t>
+        </is>
+      </c>
       <c r="R193" t="inlineStr"/>
       <c r="S193" t="inlineStr"/>
       <c r="T193" t="inlineStr"/>
       <c r="U193" t="inlineStr"/>
+      <c r="V193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -11604,10 +11867,10 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>0.8794999999999999</v>
+        <v>0.8794</v>
       </c>
       <c r="F194" t="n">
-        <v>0.9058</v>
+        <v>0.9056999999999999</v>
       </c>
       <c r="G194" t="n">
         <v>-0.0263</v>
@@ -11616,7 +11879,7 @@
         <v>0.3</v>
       </c>
       <c r="I194" t="n">
-        <v>0.8794999999999999</v>
+        <v>0.8794</v>
       </c>
       <c r="J194" t="inlineStr">
         <is>
@@ -11630,22 +11893,23 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>The name 'Trib. IPI' closely relates to 'Tipo de Imposto IPI' and has sufficient data evidence despite some numeric values.</t>
+          <t>The candidate 'Trib. IPI' has a high name confidence and aligns with the expected tax type for IPI.</t>
         </is>
       </c>
       <c r="M194" t="inlineStr"/>
       <c r="N194" t="inlineStr"/>
       <c r="O194" t="inlineStr"/>
       <c r="P194" t="inlineStr"/>
-      <c r="Q194" t="n">
-        <v>0.8794999999999999</v>
-      </c>
+      <c r="Q194" t="inlineStr"/>
       <c r="R194" t="n">
-        <v>0.8794999999999999</v>
-      </c>
-      <c r="S194" t="inlineStr"/>
+        <v>0.8794</v>
+      </c>
+      <c r="S194" t="n">
+        <v>0.8794</v>
+      </c>
       <c r="T194" t="inlineStr"/>
       <c r="U194" t="inlineStr"/>
+      <c r="V194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -11659,13 +11923,13 @@
       <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr"/>
       <c r="E195" t="n">
-        <v>0.8321</v>
+        <v>0.832</v>
       </c>
       <c r="F195" t="n">
-        <v>0.848</v>
+        <v>0.8479</v>
       </c>
       <c r="G195" t="n">
-        <v>-0.0159</v>
+        <v>-0.016</v>
       </c>
       <c r="H195" t="n">
         <v>0.35</v>
@@ -11692,15 +11956,16 @@
       <c r="N195" t="inlineStr"/>
       <c r="O195" t="inlineStr"/>
       <c r="P195" t="inlineStr"/>
-      <c r="Q195" t="n">
-        <v>0.8</v>
-      </c>
+      <c r="Q195" t="inlineStr"/>
       <c r="R195" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="S195" t="n">
         <v>0.83</v>
       </c>
-      <c r="S195" t="inlineStr"/>
       <c r="T195" t="inlineStr"/>
       <c r="U195" t="inlineStr"/>
+      <c r="V195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -11753,15 +12018,16 @@
       <c r="N196" t="inlineStr"/>
       <c r="O196" t="inlineStr"/>
       <c r="P196" t="inlineStr"/>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q196" t="inlineStr"/>
       <c r="R196" t="n">
         <v>0</v>
       </c>
-      <c r="S196" t="inlineStr"/>
+      <c r="S196" t="n">
+        <v>0</v>
+      </c>
       <c r="T196" t="inlineStr"/>
       <c r="U196" t="inlineStr"/>
+      <c r="V196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -11775,16 +12041,16 @@
       <c r="C197" t="inlineStr"/>
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="n">
-        <v>0.8092</v>
+        <v>0.7688</v>
       </c>
       <c r="F197" t="n">
-        <v>0.8493000000000001</v>
+        <v>0.8464</v>
       </c>
       <c r="G197" t="n">
-        <v>-0.0401</v>
+        <v>-0.0776</v>
       </c>
       <c r="H197" t="n">
-        <v>0.84</v>
+        <v>0.8316</v>
       </c>
       <c r="I197" t="n">
         <v>0</v>
@@ -11808,15 +12074,16 @@
       <c r="N197" t="inlineStr"/>
       <c r="O197" t="inlineStr"/>
       <c r="P197" t="inlineStr"/>
-      <c r="Q197" t="n">
-        <v>0.95</v>
-      </c>
+      <c r="Q197" t="inlineStr"/>
       <c r="R197" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="S197" t="inlineStr"/>
+        <v>0.7688</v>
+      </c>
+      <c r="S197" t="n">
+        <v>0.7688</v>
+      </c>
       <c r="T197" t="inlineStr"/>
       <c r="U197" t="inlineStr"/>
+      <c r="V197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -11863,15 +12130,16 @@
       <c r="N198" t="inlineStr"/>
       <c r="O198" t="inlineStr"/>
       <c r="P198" t="inlineStr"/>
-      <c r="Q198" t="n">
+      <c r="Q198" t="inlineStr"/>
+      <c r="R198" t="n">
         <v>0.6264</v>
       </c>
-      <c r="R198" t="n">
+      <c r="S198" t="n">
         <v>0.7927</v>
       </c>
-      <c r="S198" t="inlineStr"/>
       <c r="T198" t="inlineStr"/>
       <c r="U198" t="inlineStr"/>
+      <c r="V198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -11911,22 +12179,23 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>All candidates exhibit semantic-role conflicts with the 'Unidade de medida' header.</t>
+          <t>All candidates exhibit semantic-role conflicts or lack relevant data evidence.</t>
         </is>
       </c>
       <c r="M199" t="inlineStr"/>
       <c r="N199" t="inlineStr"/>
       <c r="O199" t="inlineStr"/>
       <c r="P199" t="inlineStr"/>
-      <c r="Q199" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q199" t="inlineStr"/>
       <c r="R199" t="n">
         <v>0</v>
       </c>
-      <c r="S199" t="inlineStr"/>
+      <c r="S199" t="n">
+        <v>0</v>
+      </c>
       <c r="T199" t="inlineStr"/>
       <c r="U199" t="inlineStr"/>
+      <c r="V199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -11982,6 +12251,7 @@
       <c r="S200" t="inlineStr"/>
       <c r="T200" t="inlineStr"/>
       <c r="U200" t="inlineStr"/>
+      <c r="V200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -12021,22 +12291,23 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>All candidate columns lack relevant data evidence to support a mapping.</t>
+          <t>No viable candidates due to lack of non-empty values in the client column.</t>
         </is>
       </c>
       <c r="M201" t="inlineStr"/>
       <c r="N201" t="inlineStr"/>
       <c r="O201" t="inlineStr"/>
       <c r="P201" t="inlineStr"/>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q201" t="inlineStr"/>
       <c r="R201" t="n">
         <v>0</v>
       </c>
-      <c r="S201" t="inlineStr"/>
+      <c r="S201" t="n">
+        <v>0</v>
+      </c>
       <c r="T201" t="inlineStr"/>
       <c r="U201" t="inlineStr"/>
+      <c r="V201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -12076,22 +12347,23 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>No suitable candidate matches the semantic role of 'Município do Local de Início' as all candidates pertain to tax situations rather than municipalities.</t>
+          <t>No suitable candidate matches the semantic role of 'Município do Local de Início'.</t>
         </is>
       </c>
       <c r="M202" t="inlineStr"/>
       <c r="N202" t="inlineStr"/>
       <c r="O202" t="inlineStr"/>
       <c r="P202" t="inlineStr"/>
-      <c r="Q202" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q202" t="inlineStr"/>
       <c r="R202" t="n">
         <v>0</v>
       </c>
-      <c r="S202" t="inlineStr"/>
+      <c r="S202" t="n">
+        <v>0</v>
+      </c>
       <c r="T202" t="inlineStr"/>
       <c r="U202" t="inlineStr"/>
+      <c r="V202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -12111,19 +12383,19 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>0.863</v>
+        <v>0.8629</v>
       </c>
       <c r="F203" t="n">
         <v>0</v>
       </c>
       <c r="G203" t="n">
-        <v>0.863</v>
+        <v>0.8629</v>
       </c>
       <c r="H203" t="n">
         <v>0</v>
       </c>
       <c r="I203" t="n">
-        <v>0.863</v>
+        <v>0.8629</v>
       </c>
       <c r="J203" t="inlineStr">
         <is>
@@ -12144,15 +12416,16 @@
       <c r="N203" t="inlineStr"/>
       <c r="O203" t="inlineStr"/>
       <c r="P203" t="inlineStr"/>
-      <c r="Q203" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q203" t="inlineStr"/>
       <c r="R203" t="n">
         <v>0</v>
       </c>
-      <c r="S203" t="inlineStr"/>
+      <c r="S203" t="n">
+        <v>0</v>
+      </c>
       <c r="T203" t="inlineStr"/>
       <c r="U203" t="inlineStr"/>
+      <c r="V203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -12192,22 +12465,23 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>No suitable candidate found due to lack of non-empty values in the client columns.</t>
+          <t>No viable candidates match the required semantic role for 'Nome Transportadora'.</t>
         </is>
       </c>
       <c r="M204" t="inlineStr"/>
       <c r="N204" t="inlineStr"/>
       <c r="O204" t="inlineStr"/>
       <c r="P204" t="inlineStr"/>
-      <c r="Q204" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q204" t="inlineStr"/>
       <c r="R204" t="n">
         <v>0</v>
       </c>
-      <c r="S204" t="inlineStr"/>
+      <c r="S204" t="n">
+        <v>0</v>
+      </c>
       <c r="T204" t="inlineStr"/>
       <c r="U204" t="inlineStr"/>
+      <c r="V204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -12227,7 +12501,7 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>0.9467</v>
+        <v>0.9466</v>
       </c>
       <c r="F205" t="n">
         <v>0.8237</v>
@@ -12237,7 +12511,7 @@
       </c>
       <c r="H205" t="inlineStr"/>
       <c r="I205" t="n">
-        <v>0.9467</v>
+        <v>0.9466</v>
       </c>
       <c r="J205" t="inlineStr">
         <is>
@@ -12273,6 +12547,7 @@
       <c r="S205" t="inlineStr"/>
       <c r="T205" t="inlineStr"/>
       <c r="U205" t="inlineStr"/>
+      <c r="V205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -12319,15 +12594,16 @@
       <c r="N206" t="inlineStr"/>
       <c r="O206" t="inlineStr"/>
       <c r="P206" t="inlineStr"/>
-      <c r="Q206" t="n">
-        <v>0.8</v>
-      </c>
+      <c r="Q206" t="inlineStr"/>
       <c r="R206" t="n">
-        <v>0.8465</v>
-      </c>
-      <c r="S206" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="S206" t="n">
+        <v>0.85</v>
+      </c>
       <c r="T206" t="inlineStr"/>
       <c r="U206" t="inlineStr"/>
+      <c r="V206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -12373,22 +12649,23 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>The candidate 'Preço Unit.' has a high name confidence and a similar numeric profile, despite being a unit price rather than a net price.</t>
+          <t>The name 'Preço Unit.' closely aligns with 'Preço líq.' and both contain numeric values, despite some differences in sample distributions.</t>
         </is>
       </c>
       <c r="M207" t="inlineStr"/>
       <c r="N207" t="inlineStr"/>
       <c r="O207" t="inlineStr"/>
       <c r="P207" t="inlineStr"/>
-      <c r="Q207" t="n">
+      <c r="Q207" t="inlineStr"/>
+      <c r="R207" t="n">
         <v>0.9</v>
       </c>
-      <c r="R207" t="n">
+      <c r="S207" t="n">
         <v>0.88</v>
       </c>
-      <c r="S207" t="inlineStr"/>
       <c r="T207" t="inlineStr"/>
       <c r="U207" t="inlineStr"/>
+      <c r="V207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -12414,7 +12691,7 @@
         <v>0.8456</v>
       </c>
       <c r="G208" t="n">
-        <v>-0.0044</v>
+        <v>-0.0043</v>
       </c>
       <c r="H208" t="n">
         <v>0.84</v>
@@ -12434,22 +12711,23 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>The candidate 'Vlr Total' closely matches the semantic role of 'Valor líquido' and has similar numeric characteristics.</t>
+          <t>The candidate 'Vlr Total' closely matches the semantic role of 'Valor líquido' and has a similar numeric profile.</t>
         </is>
       </c>
       <c r="M208" t="inlineStr"/>
       <c r="N208" t="inlineStr"/>
       <c r="O208" t="inlineStr"/>
       <c r="P208" t="inlineStr"/>
-      <c r="Q208" t="n">
-        <v>0.8413</v>
-      </c>
+      <c r="Q208" t="inlineStr"/>
       <c r="R208" t="n">
         <v>0.8413</v>
       </c>
-      <c r="S208" t="inlineStr"/>
+      <c r="S208" t="n">
+        <v>0.8413</v>
+      </c>
       <c r="T208" t="inlineStr"/>
       <c r="U208" t="inlineStr"/>
+      <c r="V208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -12461,27 +12739,27 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>5</v>
+        <v>110</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Série NF</t>
+          <t>NF Eletr.</t>
         </is>
       </c>
       <c r="E209" t="n">
+        <v>0.8753</v>
+      </c>
+      <c r="F209" t="n">
         <v>0.8829</v>
       </c>
-      <c r="F209" t="n">
-        <v>0.8769</v>
-      </c>
       <c r="G209" t="n">
-        <v>0.006</v>
+        <v>-0.0076</v>
       </c>
       <c r="H209" t="n">
-        <v>0.1718</v>
+        <v>0.16</v>
       </c>
       <c r="I209" t="n">
-        <v>0.8829</v>
+        <v>0.8753</v>
       </c>
       <c r="J209" t="inlineStr">
         <is>
@@ -12495,22 +12773,23 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
+          <t>The column 'NF Eletr.' has a high name confidence and contains numeric values consistent with invoice numbers.</t>
         </is>
       </c>
       <c r="M209" t="inlineStr"/>
       <c r="N209" t="inlineStr"/>
       <c r="O209" t="inlineStr"/>
       <c r="P209" t="inlineStr"/>
-      <c r="Q209" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q209" t="inlineStr"/>
       <c r="R209" t="n">
-        <v>0.868</v>
-      </c>
-      <c r="S209" t="inlineStr"/>
+        <v>0.8753</v>
+      </c>
+      <c r="S209" t="n">
+        <v>0.8753</v>
+      </c>
       <c r="T209" t="inlineStr"/>
       <c r="U209" t="inlineStr"/>
+      <c r="V209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -12557,15 +12836,16 @@
       <c r="N210" t="inlineStr"/>
       <c r="O210" t="inlineStr"/>
       <c r="P210" t="inlineStr"/>
-      <c r="Q210" t="n">
-        <v>0.8401999999999999</v>
-      </c>
+      <c r="Q210" t="inlineStr"/>
       <c r="R210" t="n">
         <v>0.8401999999999999</v>
       </c>
-      <c r="S210" t="inlineStr"/>
+      <c r="S210" t="n">
+        <v>0.8401999999999999</v>
+      </c>
       <c r="T210" t="inlineStr"/>
       <c r="U210" t="inlineStr"/>
+      <c r="V210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -12611,22 +12891,23 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>The candidate 'Vlr Total' closely matches the canonical 'Valor Total do Item' in name and numeric profile.</t>
+          <t>The candidate 'Vlr Total' closely matches the semantic role and numeric characteristics of 'Valor Total do Item'.</t>
         </is>
       </c>
       <c r="M211" t="inlineStr"/>
       <c r="N211" t="inlineStr"/>
       <c r="O211" t="inlineStr"/>
       <c r="P211" t="inlineStr"/>
-      <c r="Q211" t="n">
-        <v>0.891</v>
-      </c>
+      <c r="Q211" t="inlineStr"/>
       <c r="R211" t="n">
-        <v>0.891</v>
-      </c>
-      <c r="S211" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="S211" t="n">
+        <v>0.895</v>
+      </c>
       <c r="T211" t="inlineStr"/>
       <c r="U211" t="inlineStr"/>
+      <c r="V211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -12640,13 +12921,13 @@
       <c r="C212" t="inlineStr"/>
       <c r="D212" t="inlineStr"/>
       <c r="E212" t="n">
-        <v>0.7657</v>
+        <v>0.7659</v>
       </c>
       <c r="F212" t="n">
-        <v>0.761</v>
+        <v>0.7628</v>
       </c>
       <c r="G212" t="n">
-        <v>0.0046</v>
+        <v>0.0031</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
@@ -12666,22 +12947,23 @@
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>The candidate 'Data Entrada' does not match the expected type or content for 'Nome do Fornecedor do Local de Início', which requires a string representing supplier names.</t>
+          <t>The candidate 'Data Entrada' does not match the expected type or content for 'Nome do Fornecedor do Local de Início'.</t>
         </is>
       </c>
       <c r="M212" t="inlineStr"/>
       <c r="N212" t="inlineStr"/>
       <c r="O212" t="inlineStr"/>
       <c r="P212" t="inlineStr"/>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q212" t="inlineStr"/>
       <c r="R212" t="n">
         <v>0</v>
       </c>
-      <c r="S212" t="inlineStr"/>
+      <c r="S212" t="n">
+        <v>0</v>
+      </c>
       <c r="T212" t="inlineStr"/>
       <c r="U212" t="inlineStr"/>
+      <c r="V212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -12701,7 +12983,7 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>0.8643999999999999</v>
+        <v>0.8645</v>
       </c>
       <c r="F213" t="n">
         <v>0.8337</v>
@@ -12713,7 +12995,7 @@
         <v>0</v>
       </c>
       <c r="I213" t="n">
-        <v>0.8643999999999999</v>
+        <v>0.8645</v>
       </c>
       <c r="J213" t="inlineStr">
         <is>
@@ -12727,22 +13009,23 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>The candidate 'Crd.Transp.' has a high name confidence but lacks any non-empty values, making it unsuitable for mapping.</t>
+          <t>The candidate 'Crd.Transp.' has a high name confidence but all values are zero, indicating no valid data.</t>
         </is>
       </c>
       <c r="M213" t="inlineStr"/>
       <c r="N213" t="inlineStr"/>
       <c r="O213" t="inlineStr"/>
       <c r="P213" t="inlineStr"/>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q213" t="inlineStr"/>
       <c r="R213" t="n">
-        <v>0.8643999999999999</v>
-      </c>
-      <c r="S213" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="S213" t="n">
+        <v>0.8645</v>
+      </c>
       <c r="T213" t="inlineStr"/>
       <c r="U213" t="inlineStr"/>
+      <c r="V213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -12795,15 +13078,20 @@
       <c r="N214" t="inlineStr"/>
       <c r="O214" t="inlineStr"/>
       <c r="P214" t="inlineStr"/>
-      <c r="Q214" t="n">
-        <v>0.98</v>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>valor = base x aliquota holds for pis on 5501 rows at fit 0.9996</t>
+        </is>
       </c>
       <c r="R214" t="n">
         <v>0.98</v>
       </c>
-      <c r="S214" t="inlineStr"/>
+      <c r="S214" t="n">
+        <v>0.98</v>
+      </c>
       <c r="T214" t="inlineStr"/>
       <c r="U214" t="inlineStr"/>
+      <c r="V214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -12814,28 +13102,22 @@
           <t>Ref.doc.origem</t>
         </is>
       </c>
-      <c r="C215" t="n">
-        <v>92</v>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>NF Original</t>
-        </is>
-      </c>
+      <c r="C215" t="inlineStr"/>
+      <c r="D215" t="inlineStr"/>
       <c r="E215" t="n">
-        <v>0.8285</v>
+        <v>0.8292</v>
       </c>
       <c r="F215" t="n">
-        <v>0.8292</v>
+        <v>0.8302</v>
       </c>
       <c r="G215" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0009</v>
       </c>
       <c r="H215" t="n">
         <v>0.435</v>
       </c>
       <c r="I215" t="n">
-        <v>0.8285</v>
+        <v>0</v>
       </c>
       <c r="J215" t="inlineStr">
         <is>
@@ -12844,27 +13126,28 @@
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>no_match</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>The column 'NF Original' has a strong name match and numeric profile consistent with invoice numbers.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M215" t="inlineStr"/>
       <c r="N215" t="inlineStr"/>
       <c r="O215" t="inlineStr"/>
       <c r="P215" t="inlineStr"/>
-      <c r="Q215" t="n">
+      <c r="Q215" t="inlineStr"/>
+      <c r="R215" t="n">
         <v>0.8</v>
       </c>
-      <c r="R215" t="n">
-        <v>0.8285</v>
-      </c>
-      <c r="S215" t="inlineStr"/>
+      <c r="S215" t="n">
+        <v>0.8149999999999999</v>
+      </c>
       <c r="T215" t="inlineStr"/>
       <c r="U215" t="inlineStr"/>
+      <c r="V215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -12910,22 +13193,23 @@
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>The name 'Antecip.ICMS' closely aligns with the 'Texto ICMS' column, and the data profile indicates it contains relevant ICMS values.</t>
+          <t>The name 'Antecip.ICMS' closely relates to the tax context of 'Texto ICMS' and has a strong numeric profile.</t>
         </is>
       </c>
       <c r="M216" t="inlineStr"/>
       <c r="N216" t="inlineStr"/>
       <c r="O216" t="inlineStr"/>
       <c r="P216" t="inlineStr"/>
-      <c r="Q216" t="n">
-        <v>0.8954</v>
-      </c>
+      <c r="Q216" t="inlineStr"/>
       <c r="R216" t="n">
         <v>0.8954</v>
       </c>
-      <c r="S216" t="inlineStr"/>
+      <c r="S216" t="n">
+        <v>0.8954</v>
+      </c>
       <c r="T216" t="inlineStr"/>
       <c r="U216" t="inlineStr"/>
+      <c r="V216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -12972,15 +13256,16 @@
       <c r="N217" t="inlineStr"/>
       <c r="O217" t="inlineStr"/>
       <c r="P217" t="inlineStr"/>
-      <c r="Q217" t="n">
-        <v>0.8825</v>
-      </c>
+      <c r="Q217" t="inlineStr"/>
       <c r="R217" t="n">
         <v>0.8825</v>
       </c>
-      <c r="S217" t="inlineStr"/>
+      <c r="S217" t="n">
+        <v>0.8825</v>
+      </c>
       <c r="T217" t="inlineStr"/>
       <c r="U217" t="inlineStr"/>
+      <c r="V217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -13003,10 +13288,10 @@
         <v>0.8959</v>
       </c>
       <c r="F218" t="n">
-        <v>0.8431999999999999</v>
+        <v>0.8431</v>
       </c>
       <c r="G218" t="n">
-        <v>0.0527</v>
+        <v>0.0528</v>
       </c>
       <c r="H218" t="n">
         <v>0</v>
@@ -13033,15 +13318,16 @@
       <c r="N218" t="inlineStr"/>
       <c r="O218" t="inlineStr"/>
       <c r="P218" t="inlineStr"/>
-      <c r="Q218" t="n">
-        <v>0.8502</v>
-      </c>
+      <c r="Q218" t="inlineStr"/>
       <c r="R218" t="n">
-        <v>0.8502</v>
-      </c>
-      <c r="S218" t="inlineStr"/>
+        <v>0.8501</v>
+      </c>
+      <c r="S218" t="n">
+        <v>0.8501</v>
+      </c>
       <c r="T218" t="inlineStr"/>
       <c r="U218" t="inlineStr"/>
+      <c r="V218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -13087,22 +13373,23 @@
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>The candidate 'Sit.Trib.PIS' closely matches the semantic role of 'Lei tributária PIS' with strong numeric evidence.</t>
+          <t>The name 'Sit.Trib.PIS' closely matches the tax situation of 'Lei tributária PIS' with strong numeric evidence.</t>
         </is>
       </c>
       <c r="M219" t="inlineStr"/>
       <c r="N219" t="inlineStr"/>
       <c r="O219" t="inlineStr"/>
       <c r="P219" t="inlineStr"/>
-      <c r="Q219" t="n">
+      <c r="Q219" t="inlineStr"/>
+      <c r="R219" t="n">
         <v>0.95</v>
       </c>
-      <c r="R219" t="n">
+      <c r="S219" t="n">
         <v>0.9032</v>
       </c>
-      <c r="S219" t="inlineStr"/>
       <c r="T219" t="inlineStr"/>
       <c r="U219" t="inlineStr"/>
+      <c r="V219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -13125,7 +13412,7 @@
         <v>0.8695000000000001</v>
       </c>
       <c r="F220" t="n">
-        <v>0.8889</v>
+        <v>0.8888</v>
       </c>
       <c r="G220" t="n">
         <v>-0.0193</v>
@@ -13148,7 +13435,7 @@
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>The header 'Trib. IPI' closely matches the canonical 'CST IPI' and has strong data evidence with a significant non-empty count.</t>
+          <t>The candidate 'Trib. IPI' has a strong name match and aligns well with the expected format and values for CST IPI.</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
@@ -13163,15 +13450,16 @@
       <c r="P220" t="n">
         <v>0.55</v>
       </c>
-      <c r="Q220" t="n">
-        <v>0.8695000000000001</v>
-      </c>
+      <c r="Q220" t="inlineStr"/>
       <c r="R220" t="n">
         <v>0.8695000000000001</v>
       </c>
-      <c r="S220" t="inlineStr"/>
+      <c r="S220" t="n">
+        <v>0.8788</v>
+      </c>
       <c r="T220" t="inlineStr"/>
       <c r="U220" t="inlineStr"/>
+      <c r="V220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -13188,7 +13476,7 @@
         <v>0.8486</v>
       </c>
       <c r="F221" t="n">
-        <v>0.8954</v>
+        <v>0.8955</v>
       </c>
       <c r="G221" t="n">
         <v>-0.0468</v>
@@ -13218,15 +13506,16 @@
       <c r="N221" t="inlineStr"/>
       <c r="O221" t="inlineStr"/>
       <c r="P221" t="inlineStr"/>
-      <c r="Q221" t="n">
+      <c r="Q221" t="inlineStr"/>
+      <c r="R221" t="n">
         <v>0.95</v>
       </c>
-      <c r="R221" t="n">
-        <v>0.8954</v>
-      </c>
-      <c r="S221" t="inlineStr"/>
+      <c r="S221" t="n">
+        <v>0.8955</v>
+      </c>
       <c r="T221" t="inlineStr"/>
       <c r="U221" t="inlineStr"/>
+      <c r="V221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -13249,10 +13538,10 @@
         <v>0.888</v>
       </c>
       <c r="F222" t="n">
-        <v>0.8865</v>
+        <v>0.8862</v>
       </c>
       <c r="G222" t="n">
-        <v>0.0015</v>
+        <v>0.0018</v>
       </c>
       <c r="H222" t="n">
         <v>0.84</v>
@@ -13287,15 +13576,16 @@
       <c r="P222" t="n">
         <v>0.55</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0.888</v>
-      </c>
+      <c r="Q222" t="inlineStr"/>
       <c r="R222" t="n">
         <v>0.888</v>
       </c>
-      <c r="S222" t="inlineStr"/>
+      <c r="S222" t="n">
+        <v>0.888</v>
+      </c>
       <c r="T222" t="inlineStr"/>
       <c r="U222" t="inlineStr"/>
+      <c r="V222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -13342,15 +13632,16 @@
       <c r="N223" t="inlineStr"/>
       <c r="O223" t="inlineStr"/>
       <c r="P223" t="inlineStr"/>
-      <c r="Q223" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q223" t="inlineStr"/>
       <c r="R223" t="n">
+        <v>0</v>
+      </c>
+      <c r="S223" t="n">
         <v>0.8996</v>
       </c>
-      <c r="S223" t="inlineStr"/>
       <c r="T223" t="inlineStr"/>
       <c r="U223" t="inlineStr"/>
+      <c r="V223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -13390,22 +13681,23 @@
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>All candidates have empty evidence, making it impossible to establish a valid mapping.</t>
+          <t>All candidates have empty or non-informative data, making it impossible to establish a valid mapping.</t>
         </is>
       </c>
       <c r="M224" t="inlineStr"/>
       <c r="N224" t="inlineStr"/>
       <c r="O224" t="inlineStr"/>
       <c r="P224" t="inlineStr"/>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q224" t="inlineStr"/>
       <c r="R224" t="n">
-        <v>0.7823</v>
-      </c>
-      <c r="S224" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="S224" t="n">
+        <v>0</v>
+      </c>
       <c r="T224" t="inlineStr"/>
       <c r="U224" t="inlineStr"/>
+      <c r="V224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -13452,15 +13744,16 @@
       <c r="N225" t="inlineStr"/>
       <c r="O225" t="inlineStr"/>
       <c r="P225" t="inlineStr"/>
-      <c r="Q225" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q225" t="inlineStr"/>
       <c r="R225" t="n">
         <v>0</v>
       </c>
-      <c r="S225" t="inlineStr"/>
+      <c r="S225" t="n">
+        <v>0</v>
+      </c>
       <c r="T225" t="inlineStr"/>
       <c r="U225" t="inlineStr"/>
+      <c r="V225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -13474,16 +13767,16 @@
       <c r="C226" t="inlineStr"/>
       <c r="D226" t="inlineStr"/>
       <c r="E226" t="n">
-        <v>0.7546</v>
+        <v>0.7717000000000001</v>
       </c>
       <c r="F226" t="n">
-        <v>0.7717000000000001</v>
+        <v>0.7645999999999999</v>
       </c>
       <c r="G226" t="n">
-        <v>-0.0171</v>
+        <v>0.0071</v>
       </c>
       <c r="H226" t="n">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="I226" t="n">
         <v>0</v>
@@ -13500,22 +13793,23 @@
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>No suitable candidate matches the expected string format and content for 'UF do Local de Início'.</t>
         </is>
       </c>
       <c r="M226" t="inlineStr"/>
       <c r="N226" t="inlineStr"/>
       <c r="O226" t="inlineStr"/>
       <c r="P226" t="inlineStr"/>
-      <c r="Q226" t="n">
-        <v>0.45</v>
-      </c>
+      <c r="Q226" t="inlineStr"/>
       <c r="R226" t="n">
-        <v>0.7546</v>
-      </c>
-      <c r="S226" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="S226" t="n">
+        <v>0</v>
+      </c>
       <c r="T226" t="inlineStr"/>
       <c r="U226" t="inlineStr"/>
+      <c r="V226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -13529,16 +13823,16 @@
       <c r="C227" t="inlineStr"/>
       <c r="D227" t="inlineStr"/>
       <c r="E227" t="n">
+        <v>0.7107</v>
+      </c>
+      <c r="F227" t="n">
         <v>0.7913</v>
       </c>
-      <c r="F227" t="n">
-        <v>0.7833</v>
-      </c>
       <c r="G227" t="n">
-        <v>0.008</v>
+        <v>-0.0806</v>
       </c>
       <c r="H227" t="n">
-        <v>0.375</v>
+        <v>0.84</v>
       </c>
       <c r="I227" t="n">
         <v>0</v>
@@ -13562,15 +13856,16 @@
       <c r="N227" t="inlineStr"/>
       <c r="O227" t="inlineStr"/>
       <c r="P227" t="inlineStr"/>
-      <c r="Q227" t="n">
-        <v>0.375</v>
-      </c>
+      <c r="Q227" t="inlineStr"/>
       <c r="R227" t="n">
-        <v>0.7913</v>
-      </c>
-      <c r="S227" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="S227" t="n">
+        <v>0.85</v>
+      </c>
       <c r="T227" t="inlineStr"/>
       <c r="U227" t="inlineStr"/>
+      <c r="V227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -13617,15 +13912,16 @@
       <c r="N228" t="inlineStr"/>
       <c r="O228" t="inlineStr"/>
       <c r="P228" t="inlineStr"/>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q228" t="inlineStr"/>
       <c r="R228" t="n">
         <v>0</v>
       </c>
-      <c r="S228" t="inlineStr"/>
+      <c r="S228" t="n">
+        <v>0</v>
+      </c>
       <c r="T228" t="inlineStr"/>
       <c r="U228" t="inlineStr"/>
+      <c r="V228" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13671,7 +13967,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25T04:37:57.168283+00:00</t>
+          <t>2026-08-25T05:09:02.963531+00:00</t>
         </is>
       </c>
     </row>

--- a/mapping_datasul_full.xlsx
+++ b/mapping_datasul_full.xlsx
@@ -641,7 +641,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Both columns are labeled as 'Base' with similar numeric characteristics, but all values are zero, indicating no valid data.</t>
+          <t>The name 'Base CPRB' closely matches 'Base CBS' with high name confidence, despite both being all zeros.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.8605</v>
+        <v>0.8604000000000001</v>
       </c>
       <c r="F4" t="n">
         <v>0.8282</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0323</v>
+        <v>0.0322</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8605</v>
+        <v>0.8604000000000001</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.8764999999999999</v>
+        <v>0.8766</v>
       </c>
       <c r="F5" t="n">
         <v>0.8395</v>
@@ -751,7 +751,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8764999999999999</v>
+        <v>0.8766</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Both columns are numeric and contain only zeros, but 'Valor CPRB' conflicts with the tax family of 'Valor CBS'.</t>
+          <t>Both columns are numeric and have all-zero samples, but 'Valor CPRB' is a tax value, conflicting with the expected role of 'Valor CBS'.</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -777,7 +777,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8764999999999999</v>
+        <v>0.8766</v>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
@@ -792,22 +792,28 @@
           <t>Isentas CBS</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+      <c r="C6" t="n">
+        <v>303</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Ind Isen Prv</t>
+        </is>
+      </c>
       <c r="E6" t="n">
-        <v>0.842</v>
+        <v>0.8421</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.8381999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>0.842</v>
+        <v>0.0039</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.8421</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -816,12 +822,12 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>review</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>All candidates have significant semantic header conflicts or lack relevant data evidence.</t>
+          <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -895,7 +901,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8321</v>
+        <v>0.8322000000000001</v>
       </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
@@ -916,10 +922,10 @@
         <v>0.8495</v>
       </c>
       <c r="F8" t="n">
-        <v>0.839</v>
+        <v>0.8389</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0105</v>
+        <v>0.0106</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -939,7 +945,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>All candidates exhibit semantic header conflicts and lack distinctive row evidence.</t>
+          <t>All candidates exhibit semantic-role conflicts and lack distinctive non-zero evidence.</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -969,13 +975,13 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
-        <v>0.8444</v>
+        <v>0.8443000000000001</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8444</v>
+        <v>0.8443000000000001</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1004,10 +1010,10 @@
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.8443000000000001</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8444</v>
+        <v>0.8443000000000001</v>
       </c>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
@@ -1069,7 +1075,7 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.8832</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
@@ -1093,19 +1099,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.8531</v>
+        <v>0.853</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8531</v>
+        <v>0.853</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8531</v>
+        <v>0.853</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1147,27 +1153,27 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Vlr Isen ICM</t>
+          <t>Valor IRRF</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.8834</v>
+        <v>0.8693</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8692</v>
+        <v>0.8585</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0142</v>
+        <v>0.0108</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8834</v>
+        <v>0.8693</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1217,19 +1223,19 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.8535</v>
+        <v>0.8536</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>0.8465</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8535</v>
+        <v>0.0071</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8535</v>
+        <v>0.8536</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1243,7 +1249,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>The strongest header candidate has weak row evidence; preserve the name-based mapping for review instead of replacing it with a merely similar value shape.</t>
+          <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
@@ -1255,7 +1261,7 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8514</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
@@ -1270,28 +1276,22 @@
           <t>Outras IBSM</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>303</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Ind Isen Prv</t>
-        </is>
-      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
-        <v>0.8512999999999999</v>
+        <v>0.8546</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>0.8514</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8512999999999999</v>
+        <v>0.0032</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8512999999999999</v>
+        <v>0</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>no_match</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>The strongest header candidate has weak row evidence; preserve the name-based mapping for review instead of replacing it with a merely similar value shape.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -1335,13 +1335,13 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
-        <v>0.8626</v>
+        <v>0.8617</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8477</v>
+        <v>0.8473000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0148</v>
+        <v>0.0145</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>All candidates exhibit semantic-role conflicts and lack distinctive non-zero evidence.</t>
+          <t>All candidates exhibit semantic-role conflicts and provide no useful row evidence.</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -1515,19 +1515,19 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.8489</v>
+        <v>0.849</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8489</v>
+        <v>0.849</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8489</v>
+        <v>0.849</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8555</v>
+        <v>0.848</v>
       </c>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
@@ -1580,10 +1580,10 @@
         <v>0.8856000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8799</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0057</v>
+        <v>0.8856000000000001</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1642,10 +1642,10 @@
         <v>0.8564000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>0.8438</v>
       </c>
       <c r="G20" t="n">
-        <v>0.8564000000000001</v>
+        <v>0.0126</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>The strongest header candidate has weak row evidence; preserve the name-based mapping for review instead of replacing it with a merely similar value shape.</t>
+          <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
@@ -1692,22 +1692,28 @@
           <t>Outras IBS</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
+      <c r="C21" t="n">
+        <v>118</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Retido Outro</t>
+        </is>
+      </c>
       <c r="E21" t="n">
-        <v>0.8507</v>
+        <v>0.8464</v>
       </c>
       <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
         <v>0.8464</v>
       </c>
-      <c r="G21" t="n">
-        <v>0.0042</v>
-      </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>0.8464</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1716,12 +1722,12 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>review</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts with the 'Outras IBS' column, indicating incompatible tax-family roles.</t>
+          <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
@@ -1777,7 +1783,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>All candidates have semantic-role conflicts and provide no valid evidence.</t>
+          <t>All candidates exhibit semantic header conflicts and lack distinctive non-zero evidence.</t>
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
@@ -1804,28 +1810,22 @@
           <t>Tipo de Imposto IS</t>
         </is>
       </c>
-      <c r="C23" t="n">
-        <v>157</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Sit.Trib.ISS</t>
-        </is>
-      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
+        <v>0.8541</v>
+      </c>
+      <c r="F23" t="n">
         <v>0.8501</v>
       </c>
-      <c r="F23" t="n">
-        <v>0.8541</v>
-      </c>
       <c r="G23" t="n">
-        <v>-0.004</v>
+        <v>0.004</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8501</v>
+        <v>0</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1834,12 +1834,12 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>no_match</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>The header 'Sit.Trib.ISS' aligns with the tax status role, despite all-zero values.</t>
+          <t>All candidates exhibit significant semantic-role conflicts or lack sufficient evidence.</t>
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
@@ -1848,10 +1848,10 @@
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="n">
-        <v>0.8501</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.8501</v>
+        <v>0</v>
       </c>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
@@ -1867,27 +1867,27 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Base Imp 2</t>
+          <t>Vlr Base IPI</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.8835</v>
+        <v>0.8801</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8813</v>
+        <v>0.8834</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0022</v>
+        <v>-0.0033</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8835</v>
+        <v>0.8801</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
+          <t>The name 'Vlr Base IPI' suggests a base value for IPI tax, which aligns with the role of 'Base IS' despite both having all-zero evidence.</t>
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
@@ -1910,10 +1910,10 @@
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>0.8801</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>0.8801</v>
       </c>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
@@ -1937,19 +1937,19 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.8672</v>
+        <v>0.8671</v>
       </c>
       <c r="F25" t="n">
         <v>0.8633999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0038</v>
+        <v>0.0037</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>0.8672</v>
+        <v>0.8671</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>The candidate 'Aliq ICMS So' has a high name confidence but both columns contain only zeros, indicating no valid data evidence.</t>
+          <t>The candidate 'Aliq ICMS So' has a high name confidence but both columns contain only zeros, indicating no valid mapping.</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
@@ -1975,7 +1975,7 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0.8672</v>
+        <v>0.8671</v>
       </c>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
@@ -1991,27 +1991,27 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>15</v>
+        <v>82</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Vlr Isen ICM</t>
+          <t>Valor INSS</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.8721</v>
+        <v>0.8487</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8703</v>
+        <v>0.844</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0018</v>
+        <v>0.0047</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0.8721</v>
+        <v>0.8487</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>The candidate 'Vlr Isen ICM' has a high name confidence and matches the tax exemption context, despite both having a high zero fraction.</t>
+          <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
@@ -2034,10 +2034,10 @@
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="n">
-        <v>0.8721</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0.8721</v>
+        <v>0</v>
       </c>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
@@ -2052,22 +2052,28 @@
           <t>Isentas IS</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
+      <c r="C27" t="n">
+        <v>19</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Vlr Isen IPI</t>
+        </is>
+      </c>
       <c r="E27" t="n">
+        <v>0.8502</v>
+      </c>
+      <c r="F27" t="n">
         <v>0.8646</v>
       </c>
-      <c r="F27" t="n">
-        <v>0.8401999999999999</v>
-      </c>
       <c r="G27" t="n">
-        <v>0.0245</v>
+        <v>-0.0144</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>0.8502</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2076,12 +2082,12 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>review</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>All candidates have semantic-role conflicts or all-zero evidence, indicating no suitable mapping.</t>
+          <t>The candidate 'Vlr Isen IPI' has a strong name match and numeric values indicating it relates to exempt values.</t>
         </is>
       </c>
       <c r="M27" t="inlineStr"/>
@@ -2090,10 +2096,10 @@
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>0.993</v>
       </c>
       <c r="S27" t="n">
-        <v>0.8646</v>
+        <v>0.8502</v>
       </c>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
@@ -2108,22 +2114,28 @@
           <t>Outras IS</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
+      <c r="C28" t="n">
+        <v>20</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Vlr Outr IPI</t>
+        </is>
+      </c>
       <c r="E28" t="n">
-        <v>0.8746</v>
+        <v>0.8611</v>
       </c>
       <c r="F28" t="n">
         <v>0.8588</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0158</v>
+        <v>0.0023</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>0.8611</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2132,12 +2144,12 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>review</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>All candidates exhibit semantic-role conflicts or all-zero evidence, indicating no suitable mapping.</t>
+          <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
@@ -2149,7 +2161,7 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0.8554</v>
+        <v>0.8552999999999999</v>
       </c>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
@@ -2167,13 +2179,13 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="n">
-        <v>0.8332000000000001</v>
+        <v>0.8331</v>
       </c>
       <c r="F29" t="n">
         <v>0.8325</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0007</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -2311,7 +2323,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>The header 'Data Emissão' closely matches 'Data de lançamento' in meaning, both representing dates related to invoices.</t>
+          <t>The column 'Data Emissão' has a high name confidence and matches the datetime type of 'Data de lançamento'.</t>
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
@@ -2530,10 +2542,10 @@
         <v>0.8519</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9071</v>
+        <v>0.9101</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.0552</v>
+        <v>-0.0582</v>
       </c>
       <c r="H35" t="n">
         <v>1</v>
@@ -2675,7 +2687,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>No candidate column matches the semantic role of 'ID parceiro', which is a numeric identifier.</t>
+          <t>No suitable candidate matches the semantic role of 'ID parceiro' based on name and data evidence.</t>
         </is>
       </c>
       <c r="M37" t="inlineStr"/>
@@ -2731,7 +2743,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>No candidate column matches the semantic role of 'Nome' based on the provided evidence.</t>
+          <t>No suitable candidate matches the semantic role of 'Nome' as all candidates are unrelated or empty.</t>
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
@@ -2743,7 +2755,7 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>0.8269</v>
       </c>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
@@ -2764,10 +2776,10 @@
         <v>0.8285</v>
       </c>
       <c r="F39" t="n">
-        <v>0.8581</v>
+        <v>0.858</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.0296</v>
+        <v>-0.0295</v>
       </c>
       <c r="H39" t="n">
         <v>0.4227</v>
@@ -2796,10 +2808,10 @@
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="S39" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
@@ -2882,7 +2894,7 @@
         <v>0.8653999999999999</v>
       </c>
       <c r="F41" t="n">
-        <v>0.8493000000000001</v>
+        <v>0.8492</v>
       </c>
       <c r="G41" t="n">
         <v>0.0162</v>
@@ -2905,7 +2917,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>The candidate 'Vlr Total' closely matches the semantic role and numeric characteristics of 'Val.Total NF', with a high name confidence and similar numeric profiles.</t>
+          <t>The candidate 'Vlr Total' closely matches the semantic role and numeric characteristics of 'Val.Total NF'.</t>
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
@@ -2914,10 +2926,10 @@
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="n">
-        <v>0.9</v>
+        <v>0.9278999999999999</v>
       </c>
       <c r="S41" t="n">
-        <v>0.88</v>
+        <v>0.8666</v>
       </c>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr"/>
@@ -3004,10 +3016,10 @@
         <v>1</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9357</v>
+        <v>0.9358</v>
       </c>
       <c r="G43" t="n">
-        <v>0.0643</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
@@ -3061,7 +3073,7 @@
         <v>0.9122</v>
       </c>
       <c r="G44" t="n">
-        <v>0.0033</v>
+        <v>0.0032</v>
       </c>
       <c r="H44" t="n">
         <v>0.84</v>
@@ -3108,22 +3120,28 @@
           <t>Isentas ICMS</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
+      <c r="C45" t="n">
+        <v>15</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Vlr Isen ICM</t>
+        </is>
+      </c>
       <c r="E45" t="n">
-        <v>0.874</v>
+        <v>0.87</v>
       </c>
       <c r="F45" t="n">
-        <v>0.8932</v>
+        <v>0.8895</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.0192</v>
+        <v>-0.0195</v>
       </c>
       <c r="H45" t="n">
-        <v>0.7623</v>
+        <v>0.84</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -3132,12 +3150,12 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>review</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>The name 'Vlr Isen ICM' closely aligns with 'Isentas ICMS' and has no semantic conflicts, supported by a strong numeric profile.</t>
         </is>
       </c>
       <c r="M45" t="inlineStr"/>
@@ -3146,10 +3164,10 @@
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="n">
-        <v>0.874</v>
+        <v>0.8999</v>
       </c>
       <c r="S45" t="n">
-        <v>0.874</v>
+        <v>0.8999</v>
       </c>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
@@ -3164,22 +3182,28 @@
           <t>Outras ICMS</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
+      <c r="C46" t="n">
+        <v>16</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Vlr Out ICMS</t>
+        </is>
+      </c>
       <c r="E46" t="n">
+        <v>0.9164</v>
+      </c>
+      <c r="F46" t="n">
         <v>0.8991</v>
       </c>
-      <c r="F46" t="n">
-        <v>0.8872</v>
-      </c>
       <c r="G46" t="n">
-        <v>0.0119</v>
+        <v>0.0173</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>0.8999</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -3188,12 +3212,12 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>review</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>The candidate 'Vlr Out ICMS' has a semantic header conflict and does not align with the expected role of 'Outras ICMS'.</t>
+          <t>The name 'Vlr Out ICMS' closely matches 'Outras ICMS' and both contain numeric values, despite a high zero fraction.</t>
         </is>
       </c>
       <c r="M46" t="inlineStr"/>
@@ -3202,10 +3226,10 @@
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>0.9164</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>0.9164</v>
       </c>
       <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr"/>
@@ -3221,28 +3245,28 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>15</v>
+        <v>255</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Vlr Isen ICM</t>
+          <t>Val.Desc.ICM</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.8691</v>
+        <v>0.8531</v>
       </c>
       <c r="F47" t="n">
+        <v>0.8232</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.0299</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
         <v>0.8531</v>
       </c>
-      <c r="G47" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0.8691</v>
-      </c>
       <c r="J47" t="inlineStr">
         <is>
           <t>data</t>
@@ -3255,7 +3279,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>The candidate 'Vlr Isen ICM' has a compatible numeric type and no semantic header conflict, making it the best match despite the presence of zeros.</t>
+          <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
         </is>
       </c>
       <c r="M47" t="inlineStr"/>
@@ -3264,10 +3288,10 @@
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="n">
-        <v>0.8691</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>0.8691</v>
+        <v>0</v>
       </c>
       <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr"/>
@@ -3283,27 +3307,27 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>15</v>
+        <v>244</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Vlr Isen ICM</t>
+          <t>Valor CPRB</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.8731</v>
+        <v>0.853</v>
       </c>
       <c r="F48" t="n">
-        <v>0.8529</v>
+        <v>0.8457</v>
       </c>
       <c r="G48" t="n">
-        <v>0.0202</v>
+        <v>0.0072</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>0.8731</v>
+        <v>0.853</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -3395,7 +3419,7 @@
         <v>0.9979</v>
       </c>
       <c r="S49" t="n">
-        <v>0.9491000000000001</v>
+        <v>0.973</v>
       </c>
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr"/>
@@ -3422,10 +3446,10 @@
         <v>1</v>
       </c>
       <c r="F50" t="n">
-        <v>0.9267</v>
+        <v>0.9105</v>
       </c>
       <c r="G50" t="n">
-        <v>0.0733</v>
+        <v>0.0895</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
@@ -3470,13 +3494,19 @@
           <t>Isentas IPI</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
+      <c r="C51" t="n">
+        <v>19</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Vlr Isen IPI</t>
+        </is>
+      </c>
       <c r="E51" t="n">
         <v>0.9012</v>
       </c>
       <c r="F51" t="n">
-        <v>0.897</v>
+        <v>0.8971</v>
       </c>
       <c r="G51" t="n">
         <v>0.0041</v>
@@ -3485,7 +3515,7 @@
         <v>0.84</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>0.8999</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -3494,12 +3524,12 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>review</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>The candidate 'Vlr Isen IPI' closely matches the semantic role of 'Isentas IPI' and has a high name confidence, despite some zero values.</t>
         </is>
       </c>
       <c r="M51" t="inlineStr"/>
@@ -3508,10 +3538,10 @@
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="n">
-        <v>0.091</v>
+        <v>0.9</v>
       </c>
       <c r="S51" t="n">
-        <v>0.9012</v>
+        <v>0.895</v>
       </c>
       <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr"/>
@@ -3527,27 +3557,27 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>152</v>
+        <v>20</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>IPI Pauta</t>
+          <t>Vlr Outr IPI</t>
         </is>
       </c>
       <c r="E52" t="n">
+        <v>0.911</v>
+      </c>
+      <c r="F52" t="n">
         <v>0.8981</v>
       </c>
-      <c r="F52" t="n">
-        <v>0.8781</v>
-      </c>
       <c r="G52" t="n">
-        <v>0.02</v>
+        <v>0.013</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>0.8981</v>
+        <v>0.8999</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -3561,7 +3591,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>The header 'IPI Pauta' aligns with the tax context of 'Outras IPI', despite both having all-zero evidence.</t>
+          <t>The name 'Vlr Outr IPI' closely matches 'Outras IPI', but both columns contain mostly zeros, limiting data evidence.</t>
         </is>
       </c>
       <c r="M52" t="inlineStr"/>
@@ -3570,10 +3600,10 @@
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="S52" t="n">
-        <v>0.8981</v>
+        <v>0.911</v>
       </c>
       <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr"/>
@@ -3635,7 +3665,7 @@
         <v>0.909</v>
       </c>
       <c r="S53" t="n">
-        <v>0.955</v>
+        <v>0.954</v>
       </c>
       <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr"/>
@@ -3827,17 +3857,17 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.9415</v>
+        <v>0.9414</v>
       </c>
       <c r="F57" t="n">
-        <v>0.8272</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="G57" t="n">
         <v>0.1143</v>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="n">
-        <v>0.9415</v>
+        <v>0.9414</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -3886,7 +3916,7 @@
         <v>0.9409</v>
       </c>
       <c r="F58" t="n">
-        <v>0.827</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="G58" t="n">
         <v>0.1139</v>
@@ -4001,13 +4031,13 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.8767</v>
+        <v>0.8768</v>
       </c>
       <c r="F60" t="n">
         <v>0.795</v>
       </c>
       <c r="G60" t="n">
-        <v>0.08169999999999999</v>
+        <v>0.0818</v>
       </c>
       <c r="H60" t="n">
         <v>1</v>
@@ -4027,7 +4057,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>The candidate 'Chave Nfe' has a high name confidence and matches the expected format and characteristics of the 'Chave de acesso' with 44-digit numeric values.</t>
+          <t>The candidate 'Chave Nfe' has a high name confidence and matches the expected format and characteristics of the 'Chave de acesso'.</t>
         </is>
       </c>
       <c r="M60" t="inlineStr"/>
@@ -4036,10 +4066,10 @@
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="n">
-        <v>0.95</v>
+        <v>0.8768</v>
       </c>
       <c r="S60" t="n">
-        <v>0.93</v>
+        <v>0.8768</v>
       </c>
       <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr"/>
@@ -4063,10 +4093,10 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.9092</v>
+        <v>0.9094</v>
       </c>
       <c r="F61" t="n">
-        <v>0.8497</v>
+        <v>0.8498</v>
       </c>
       <c r="G61" t="n">
         <v>0.0596</v>
@@ -4075,7 +4105,7 @@
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>0.9092</v>
+        <v>0.9094</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -4098,10 +4128,10 @@
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="n">
-        <v>0.8375</v>
+        <v>0.9</v>
       </c>
       <c r="S61" t="n">
-        <v>0.8734</v>
+        <v>0.9</v>
       </c>
       <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr"/>
@@ -4128,7 +4158,7 @@
         <v>0.8752</v>
       </c>
       <c r="F62" t="n">
-        <v>0.8837</v>
+        <v>0.8838</v>
       </c>
       <c r="G62" t="n">
         <v>-0.008500000000000001</v>
@@ -4163,7 +4193,7 @@
         <v>0.8752</v>
       </c>
       <c r="S62" t="n">
-        <v>0.8794999999999999</v>
+        <v>0.8752</v>
       </c>
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr"/>
@@ -4184,10 +4214,10 @@
         <v>0.8016</v>
       </c>
       <c r="F63" t="n">
-        <v>0.7685999999999999</v>
+        <v>0.7685</v>
       </c>
       <c r="G63" t="n">
-        <v>0.033</v>
+        <v>0.0331</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -4207,7 +4237,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>No candidate column provides relevant mapping evidence for 'Criado por'.</t>
+          <t>No suitable candidate matches the semantic role of 'Criado por' based on the evidence provided.</t>
         </is>
       </c>
       <c r="M63" t="inlineStr"/>
@@ -4219,7 +4249,7 @@
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="T63" t="inlineStr"/>
       <c r="U63" t="inlineStr"/>
@@ -4246,7 +4276,7 @@
         <v>0.0334</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>0.43</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
@@ -4263,7 +4293,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>No candidate column matches the semantic role of 'Modificado por'.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M64" t="inlineStr"/>
@@ -4275,7 +4305,7 @@
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>0</v>
+        <v>0.7927999999999999</v>
       </c>
       <c r="T64" t="inlineStr"/>
       <c r="U64" t="inlineStr"/>
@@ -4299,7 +4329,7 @@
         <v>0.8175</v>
       </c>
       <c r="G65" t="n">
-        <v>0.0203</v>
+        <v>0.0204</v>
       </c>
       <c r="H65" t="n">
         <v>0.45</v>
@@ -4361,7 +4391,7 @@
         <v>0.8373</v>
       </c>
       <c r="G66" t="n">
-        <v>0.0077</v>
+        <v>0.0076</v>
       </c>
       <c r="H66" t="n">
         <v>0.3167</v>
@@ -4381,7 +4411,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>The column 'NF Original' has a high name confidence and matches the numeric format of invoice document numbers.</t>
+          <t>The header 'NF Original' closely matches the semantic role of 'Nº doc.original Cabeçalho' and has a high name confidence.</t>
         </is>
       </c>
       <c r="M66" t="inlineStr"/>
@@ -4390,7 +4420,7 @@
       <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="n">
-        <v>0.5</v>
+        <v>0.845</v>
       </c>
       <c r="S66" t="n">
         <v>0.845</v>
@@ -4420,10 +4450,10 @@
         <v>0.8584000000000001</v>
       </c>
       <c r="F67" t="n">
-        <v>0.8587</v>
+        <v>0.8586</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.0002</v>
+        <v>-0.0003</v>
       </c>
       <c r="H67" t="n">
         <v>0.3167</v>
@@ -4443,7 +4473,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>The candidate 'NF Original' has a strong name match and a numeric profile consistent with invoice numbers.</t>
+          <t>The candidate 'NF Original' has a strong name match and numeric profile consistent with invoice document numbers.</t>
         </is>
       </c>
       <c r="M67" t="inlineStr"/>
@@ -4452,10 +4482,10 @@
       <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="n">
-        <v>0.8584000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="S67" t="n">
-        <v>0.8584000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr"/>
@@ -4479,19 +4509,19 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.8508</v>
+        <v>0.8512</v>
       </c>
       <c r="F68" t="n">
-        <v>0.8333</v>
+        <v>0.8332000000000001</v>
       </c>
       <c r="G68" t="n">
-        <v>0.0175</v>
+        <v>0.0181</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>0.8508</v>
+        <v>0.8512</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -4505,7 +4535,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>The candidate column has no data evidence and only a weak name match.</t>
+          <t>The candidate 'Cód Sit SN' has a high name confidence but lacks any row evidence.</t>
         </is>
       </c>
       <c r="M68" t="inlineStr"/>
@@ -4517,7 +4547,7 @@
         <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>0.8508</v>
+        <v>0.8512</v>
       </c>
       <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr"/>
@@ -4538,7 +4568,7 @@
         <v>0.8661</v>
       </c>
       <c r="F69" t="n">
-        <v>0.8498</v>
+        <v>0.8497</v>
       </c>
       <c r="G69" t="n">
         <v>0.0163</v>
@@ -4561,7 +4591,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>All candidates have empty or all-zero evidence, providing no support for a mapping.</t>
+          <t>All candidates have empty or all-zero evidence, making them unsuitable for mapping.</t>
         </is>
       </c>
       <c r="M69" t="inlineStr"/>
@@ -4597,7 +4627,7 @@
         <v>0.7958</v>
       </c>
       <c r="G70" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.0083</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -4617,7 +4647,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>No suitable candidate matches the semantic role of 'Condições pagamento' based on the available evidence.</t>
+          <t>No suitable candidate matches the semantic role of 'Condições pagamento' based on the evidence.</t>
         </is>
       </c>
       <c r="M70" t="inlineStr"/>
@@ -4629,7 +4659,7 @@
         <v>0</v>
       </c>
       <c r="S70" t="n">
-        <v>0.8041</v>
+        <v>0</v>
       </c>
       <c r="T70" t="inlineStr"/>
       <c r="U70" t="inlineStr"/>
@@ -4691,7 +4721,7 @@
         <v>0</v>
       </c>
       <c r="S71" t="n">
-        <v>0.8559</v>
+        <v>0</v>
       </c>
       <c r="T71" t="inlineStr"/>
       <c r="U71" t="inlineStr"/>
@@ -4718,10 +4748,10 @@
         <v>0.8605</v>
       </c>
       <c r="F72" t="n">
-        <v>0.7677</v>
+        <v>0.7678</v>
       </c>
       <c r="G72" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.0926</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -4771,13 +4801,13 @@
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="n">
-        <v>0.7998</v>
+        <v>0.7992</v>
       </c>
       <c r="F73" t="n">
-        <v>0.849</v>
+        <v>0.8494</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.0492</v>
+        <v>-0.0503</v>
       </c>
       <c r="H73" t="n">
         <v>0.84</v>
@@ -4809,7 +4839,7 @@
         <v>0.9667</v>
       </c>
       <c r="S73" t="n">
-        <v>0.849</v>
+        <v>0.8494</v>
       </c>
       <c r="T73" t="inlineStr"/>
       <c r="U73" t="inlineStr"/>
@@ -4833,19 +4863,19 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.8763</v>
+        <v>0.8758</v>
       </c>
       <c r="F74" t="n">
         <v>0.8493000000000001</v>
       </c>
       <c r="G74" t="n">
-        <v>0.027</v>
+        <v>0.0265</v>
       </c>
       <c r="H74" t="n">
         <v>0.65</v>
       </c>
       <c r="I74" t="n">
-        <v>0.8763</v>
+        <v>0.8758</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -4859,7 +4889,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>The candidate 'Item NF Orig' has a high name confidence and a numeric profile, but lacks distinctive sample overlap with the reference.</t>
+          <t>The candidate 'Item NF Orig' has a similar numeric profile but lacks distinctive sample overlap with 'Item referência NF'.</t>
         </is>
       </c>
       <c r="M74" t="inlineStr"/>
@@ -4871,7 +4901,7 @@
         <v>0.65</v>
       </c>
       <c r="S74" t="n">
-        <v>0.8763</v>
+        <v>0.75</v>
       </c>
       <c r="T74" t="inlineStr"/>
       <c r="U74" t="inlineStr"/>
@@ -4889,13 +4919,13 @@
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="n">
-        <v>0.8007</v>
+        <v>0.8006</v>
       </c>
       <c r="F75" t="n">
         <v>0.7974</v>
       </c>
       <c r="G75" t="n">
-        <v>0.0033</v>
+        <v>0.0032</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -4951,7 +4981,7 @@
         <v>0.8024</v>
       </c>
       <c r="G76" t="n">
-        <v>0.005</v>
+        <v>0.0051</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -4971,7 +5001,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>No suitable candidate found due to lack of relevant data evidence.</t>
+          <t>No suitable candidate found with relevant data evidence.</t>
         </is>
       </c>
       <c r="M76" t="inlineStr"/>
@@ -5007,7 +5037,7 @@
         <v>0.8231000000000001</v>
       </c>
       <c r="G77" t="n">
-        <v>0.0086</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -5066,7 +5096,7 @@
         <v>0.9081</v>
       </c>
       <c r="F78" t="n">
-        <v>0.8305</v>
+        <v>0.8306</v>
       </c>
       <c r="G78" t="n">
         <v>0.0775</v>
@@ -5128,10 +5158,10 @@
         <v>0.8129</v>
       </c>
       <c r="F79" t="n">
-        <v>0.8831</v>
+        <v>0.883</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.0702</v>
+        <v>-0.0701</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
@@ -5151,7 +5181,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>The name 'Num. RPS' closely relates to 'Nº de serviço' and has informative data evidence.</t>
+          <t>The header 'Num. RPS' closely aligns with the semantic role of 'Nº de serviço' and has informative data evidence.</t>
         </is>
       </c>
       <c r="M79" t="inlineStr"/>
@@ -5181,7 +5211,7 @@
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="n">
-        <v>0.8447</v>
+        <v>0.8446</v>
       </c>
       <c r="F80" t="n">
         <v>0.8035</v>
@@ -5207,7 +5237,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>The candidate columns contain numeric values, but the source column is empty, providing no evidence for a mapping.</t>
         </is>
       </c>
       <c r="M80" t="inlineStr"/>
@@ -5216,10 +5246,10 @@
       <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="n">
-        <v>0.8447</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
-        <v>0.8447</v>
+        <v>0.8446</v>
       </c>
       <c r="T80" t="inlineStr"/>
       <c r="U80" t="inlineStr"/>
@@ -5237,10 +5267,10 @@
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="n">
-        <v>0.8078</v>
+        <v>0.8079</v>
       </c>
       <c r="F81" t="n">
-        <v>0.842</v>
+        <v>0.8421</v>
       </c>
       <c r="G81" t="n">
         <v>-0.0342</v>
@@ -5272,10 +5302,10 @@
       <c r="P81" t="inlineStr"/>
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="n">
-        <v>0.8078</v>
+        <v>0.8079</v>
       </c>
       <c r="S81" t="n">
-        <v>0.825</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="T81" t="inlineStr"/>
       <c r="U81" t="inlineStr"/>
@@ -5293,16 +5323,16 @@
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="n">
-        <v>0.7775</v>
+        <v>0.788</v>
       </c>
       <c r="F82" t="n">
-        <v>0.788</v>
+        <v>0.7871</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.0106</v>
+        <v>0.001</v>
       </c>
       <c r="H82" t="n">
-        <v>0.7266</v>
+        <v>0</v>
       </c>
       <c r="I82" t="n">
         <v>0</v>
@@ -5319,7 +5349,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>No suitable candidate matches the semantic role or provides sufficient evidence.</t>
         </is>
       </c>
       <c r="M82" t="inlineStr"/>
@@ -5328,10 +5358,10 @@
       <c r="P82" t="inlineStr"/>
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="n">
-        <v>0.7775</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
-        <v>0.7775</v>
+        <v>0</v>
       </c>
       <c r="T82" t="inlineStr"/>
       <c r="U82" t="inlineStr"/>
@@ -5349,13 +5379,13 @@
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="n">
-        <v>0.8278</v>
+        <v>0.8112</v>
       </c>
       <c r="F83" t="n">
         <v>0.8322000000000001</v>
       </c>
       <c r="G83" t="n">
-        <v>-0.0045</v>
+        <v>-0.021</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -5384,10 +5414,10 @@
       <c r="P83" t="inlineStr"/>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="n">
-        <v>0.8278</v>
+        <v>0.8112</v>
       </c>
       <c r="S83" t="n">
-        <v>0.8278</v>
+        <v>0.8112</v>
       </c>
       <c r="T83" t="inlineStr"/>
       <c r="U83" t="inlineStr"/>
@@ -5405,13 +5435,13 @@
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="n">
-        <v>0.7786999999999999</v>
+        <v>0.7959000000000001</v>
       </c>
       <c r="F84" t="n">
-        <v>0.7959000000000001</v>
+        <v>0.7909</v>
       </c>
       <c r="G84" t="n">
-        <v>-0.0172</v>
+        <v>0.005</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -5431,7 +5461,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>All candidates have zero values and lack distinctive evidence to support a mapping.</t>
         </is>
       </c>
       <c r="M84" t="inlineStr"/>
@@ -5440,10 +5470,10 @@
       <c r="P84" t="inlineStr"/>
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="n">
-        <v>0.7786999999999999</v>
+        <v>0</v>
       </c>
       <c r="S84" t="n">
-        <v>0.7786999999999999</v>
+        <v>0</v>
       </c>
       <c r="T84" t="inlineStr"/>
       <c r="U84" t="inlineStr"/>
@@ -5467,7 +5497,7 @@
         <v>0.79</v>
       </c>
       <c r="G85" t="n">
-        <v>0.0081</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -5517,7 +5547,7 @@
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="n">
-        <v>0.8458</v>
+        <v>0.8457</v>
       </c>
       <c r="F86" t="n">
         <v>0.8383</v>
@@ -5555,7 +5585,7 @@
         <v>0</v>
       </c>
       <c r="S86" t="n">
-        <v>0</v>
+        <v>0.8457</v>
       </c>
       <c r="T86" t="inlineStr"/>
       <c r="U86" t="inlineStr"/>
@@ -5723,7 +5753,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>All candidates have a tax-family conflict with ICAP and ICMS, indicating incompatible semantic roles.</t>
+          <t>All candidates conflict with the tax-family context of ICAP, indicating they do not represent the same business meaning.</t>
         </is>
       </c>
       <c r="M89" t="inlineStr"/>
@@ -5750,22 +5780,28 @@
           <t>Isentas ICAP</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr"/>
-      <c r="D90" t="inlineStr"/>
+      <c r="C90" t="n">
+        <v>15</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Vlr Isen ICM</t>
+        </is>
+      </c>
       <c r="E90" t="n">
+        <v>0.8545</v>
+      </c>
+      <c r="F90" t="n">
         <v>0.8431999999999999</v>
       </c>
-      <c r="F90" t="n">
-        <v>0</v>
-      </c>
       <c r="G90" t="n">
-        <v>0.8431999999999999</v>
+        <v>0.0113</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>0</v>
+        <v>0.8545</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -5774,12 +5810,12 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>review</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>All candidates exhibit semantic header conflicts or lack relevant data evidence.</t>
+          <t>The candidate 'Vlr Isen ICM' has a high name confidence and matches the semantic role of tax exemption, despite a high zero fraction.</t>
         </is>
       </c>
       <c r="M90" t="inlineStr"/>
@@ -5788,10 +5824,10 @@
       <c r="P90" t="inlineStr"/>
       <c r="Q90" t="inlineStr"/>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="S90" t="n">
-        <v>0</v>
+        <v>0.8545</v>
       </c>
       <c r="T90" t="inlineStr"/>
       <c r="U90" t="inlineStr"/>
@@ -5809,13 +5845,13 @@
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="n">
-        <v>0.8456</v>
+        <v>0.8675</v>
       </c>
       <c r="F91" t="n">
-        <v>0</v>
+        <v>0.8671</v>
       </c>
       <c r="G91" t="n">
-        <v>0.8456</v>
+        <v>0.0004</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -5835,7 +5871,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>All candidates have a tax-family conflict with ICAP vs ICMS, indicating incompatible semantic roles.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M91" t="inlineStr"/>
@@ -5891,7 +5927,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>All candidates exhibit semantic header conflicts and lack distinctive row evidence.</t>
+          <t>All candidates exhibit semantic header conflicts and lack distinctive non-zero evidence.</t>
         </is>
       </c>
       <c r="M92" t="inlineStr"/>
@@ -6036,22 +6072,28 @@
           <t>Aliquota ICEP</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr"/>
-      <c r="D95" t="inlineStr"/>
+      <c r="C95" t="n">
+        <v>245</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Alíquota CPR</t>
+        </is>
+      </c>
       <c r="E95" t="n">
-        <v>0.8617</v>
+        <v>0.8474</v>
       </c>
       <c r="F95" t="n">
-        <v>0.8551</v>
+        <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>0.0066</v>
+        <v>0.8474</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>0</v>
+        <v>0.8474</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -6060,12 +6102,12 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>review</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
         </is>
       </c>
       <c r="M95" t="inlineStr"/>
@@ -6077,7 +6119,7 @@
         <v>0</v>
       </c>
       <c r="S95" t="n">
-        <v>0.8617</v>
+        <v>0</v>
       </c>
       <c r="T95" t="inlineStr"/>
       <c r="U95" t="inlineStr"/>
@@ -6104,10 +6146,10 @@
         <v>0.851</v>
       </c>
       <c r="F96" t="n">
-        <v>0</v>
+        <v>0.8479</v>
       </c>
       <c r="G96" t="n">
-        <v>0.851</v>
+        <v>0.0031</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -6127,7 +6169,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>The strongest header candidate has weak row evidence; preserve the name-based mapping for review instead of replacing it with a merely similar value shape.</t>
+          <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
         </is>
       </c>
       <c r="M96" t="inlineStr"/>
@@ -6154,28 +6196,22 @@
           <t>Outras ICEP</t>
         </is>
       </c>
-      <c r="C97" t="n">
-        <v>303</v>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Ind Isen Prv</t>
-        </is>
-      </c>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="inlineStr"/>
       <c r="E97" t="n">
         <v>0.8583</v>
       </c>
       <c r="F97" t="n">
-        <v>0</v>
+        <v>0.8529</v>
       </c>
       <c r="G97" t="n">
-        <v>0.8583</v>
+        <v>0.0054</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
       </c>
       <c r="I97" t="n">
-        <v>0.8583</v>
+        <v>0</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
@@ -6184,12 +6220,12 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>no_match</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>The strongest header candidate has weak row evidence; preserve the name-based mapping for review instead of replacing it with a merely similar value shape.</t>
+          <t>All candidates exhibit semantic header conflicts and lack distinctive row evidence.</t>
         </is>
       </c>
       <c r="M97" t="inlineStr"/>
@@ -6219,10 +6255,10 @@
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="n">
-        <v>0.8421999999999999</v>
+        <v>0.8421</v>
       </c>
       <c r="F98" t="n">
-        <v>0.8409</v>
+        <v>0.8408</v>
       </c>
       <c r="G98" t="n">
         <v>0.0013</v>
@@ -6245,7 +6281,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>All candidates exhibit semantic header conflicts and lack distinctive row evidence.</t>
+          <t>All candidates exhibit semantic-role conflicts or lack distinctive evidence, making them unsuitable for mapping.</t>
         </is>
       </c>
       <c r="M98" t="inlineStr"/>
@@ -6278,7 +6314,7 @@
         <v>0.839</v>
       </c>
       <c r="F99" t="n">
-        <v>0.8259</v>
+        <v>0.8258</v>
       </c>
       <c r="G99" t="n">
         <v>0.0131</v>
@@ -6452,28 +6488,22 @@
           <t>Valor ICSP</t>
         </is>
       </c>
-      <c r="C102" t="n">
-        <v>15</v>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>Vlr Isen ICM</t>
-        </is>
-      </c>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr"/>
       <c r="E102" t="n">
-        <v>0.8829</v>
+        <v>0.883</v>
       </c>
       <c r="F102" t="n">
-        <v>0</v>
+        <v>0.8804999999999999</v>
       </c>
       <c r="G102" t="n">
-        <v>0.8829</v>
+        <v>0.0025</v>
       </c>
       <c r="H102" t="n">
         <v>0</v>
       </c>
       <c r="I102" t="n">
-        <v>0.8829</v>
+        <v>0</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -6482,12 +6512,12 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>no_match</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>The name 'Vlr Isen ICM' is the closest match to 'Valor ICSP' despite both having high zero fractions.</t>
+          <t>All candidates exhibit semantic header conflicts and lack distinctive non-zero evidence.</t>
         </is>
       </c>
       <c r="M102" t="inlineStr"/>
@@ -6496,10 +6526,10 @@
       <c r="P102" t="inlineStr"/>
       <c r="Q102" t="inlineStr"/>
       <c r="R102" t="n">
-        <v>0.8829</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
-        <v>0.8829</v>
+        <v>0</v>
       </c>
       <c r="T102" t="inlineStr"/>
       <c r="U102" t="inlineStr"/>
@@ -6515,27 +6545,27 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>303</v>
+        <v>15</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Ind Isen Prv</t>
+          <t>Vlr Isen ICM</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.8505</v>
+        <v>0.8508</v>
       </c>
       <c r="F103" t="n">
-        <v>0</v>
+        <v>0.8504</v>
       </c>
       <c r="G103" t="n">
-        <v>0.8505</v>
+        <v>0.0004</v>
       </c>
       <c r="H103" t="n">
         <v>0</v>
       </c>
       <c r="I103" t="n">
-        <v>0.8505</v>
+        <v>0.8508</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -6549,7 +6579,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>The strongest header candidate has weak row evidence; preserve the name-based mapping for review instead of replacing it with a merely similar value shape.</t>
+          <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
         </is>
       </c>
       <c r="M103" t="inlineStr"/>
@@ -6561,7 +6591,7 @@
         <v>0</v>
       </c>
       <c r="S103" t="n">
-        <v>0.8507</v>
+        <v>0</v>
       </c>
       <c r="T103" t="inlineStr"/>
       <c r="U103" t="inlineStr"/>
@@ -6576,28 +6606,22 @@
           <t>Outras ICSP</t>
         </is>
       </c>
-      <c r="C104" t="n">
-        <v>303</v>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>Ind Isen Prv</t>
-        </is>
-      </c>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr"/>
       <c r="E104" t="n">
-        <v>0.8557</v>
+        <v>0.8588</v>
       </c>
       <c r="F104" t="n">
-        <v>0</v>
+        <v>0.8657</v>
       </c>
       <c r="G104" t="n">
-        <v>0.8557</v>
+        <v>-0.0069</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
       </c>
       <c r="I104" t="n">
-        <v>0.8557</v>
+        <v>0</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -6606,12 +6630,12 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>no_match</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>The strongest header candidate has weak row evidence; preserve the name-based mapping for review instead of replacing it with a merely similar value shape.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M104" t="inlineStr"/>
@@ -6620,10 +6644,10 @@
       <c r="P104" t="inlineStr"/>
       <c r="Q104" t="inlineStr"/>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>0.8588</v>
       </c>
       <c r="S104" t="n">
-        <v>0</v>
+        <v>0.8588</v>
       </c>
       <c r="T104" t="inlineStr"/>
       <c r="U104" t="inlineStr"/>
@@ -6641,13 +6665,13 @@
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="n">
-        <v>0.8407</v>
+        <v>0.8404</v>
       </c>
       <c r="F105" t="n">
-        <v>0.8401</v>
+        <v>0.84</v>
       </c>
       <c r="G105" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0004</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -6667,7 +6691,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>All candidates exhibit semantic header conflicts and contain only zeros, providing no valid mapping evidence.</t>
+          <t>All candidates exhibit semantic conflicts and lack distinctive evidence.</t>
         </is>
       </c>
       <c r="M105" t="inlineStr"/>
@@ -6723,7 +6747,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>All candidates exhibit semantic-role conflicts and insufficient evidence to support a mapping.</t>
+          <t>All candidates have semantic-role conflicts and no distinctive row evidence.</t>
         </is>
       </c>
       <c r="M106" t="inlineStr"/>
@@ -6735,7 +6759,7 @@
         <v>0</v>
       </c>
       <c r="S106" t="n">
-        <v>0</v>
+        <v>0.8607</v>
       </c>
       <c r="T106" t="inlineStr"/>
       <c r="U106" t="inlineStr"/>
@@ -6815,7 +6839,7 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.8559</v>
+        <v>0.856</v>
       </c>
       <c r="F108" t="n">
         <v>0.8835</v>
@@ -6827,7 +6851,7 @@
         <v>0</v>
       </c>
       <c r="I108" t="n">
-        <v>0.8559</v>
+        <v>0.856</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
@@ -6841,7 +6865,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>Distinctive content evidence indicates 'Difal ICMS' is a relevant tax rate, aligning with the 'Aliquota DIF_ALIQ' context.</t>
+          <t>The candidate 'Difal ICMS' has a relevant name match and a profile indicating mixed numeric values, unlike the all-zero profile of the model column.</t>
         </is>
       </c>
       <c r="M108" t="inlineStr"/>
@@ -6850,10 +6874,10 @@
       <c r="P108" t="inlineStr"/>
       <c r="Q108" t="inlineStr"/>
       <c r="R108" t="n">
-        <v>0.8559</v>
+        <v>0</v>
       </c>
       <c r="S108" t="n">
-        <v>0.8559</v>
+        <v>0.856</v>
       </c>
       <c r="T108" t="inlineStr"/>
       <c r="U108" t="inlineStr"/>
@@ -6933,19 +6957,19 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.8522</v>
+        <v>0.8536</v>
       </c>
       <c r="F110" t="n">
         <v>0</v>
       </c>
       <c r="G110" t="n">
-        <v>0.8522</v>
+        <v>0.8536</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
       </c>
       <c r="I110" t="n">
-        <v>0.8522</v>
+        <v>0.8536</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
@@ -6989,10 +7013,10 @@
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="n">
-        <v>0.8681</v>
+        <v>0.8688</v>
       </c>
       <c r="F111" t="n">
-        <v>0.8603</v>
+        <v>0.861</v>
       </c>
       <c r="G111" t="n">
         <v>0.0078</v>
@@ -7045,13 +7069,13 @@
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="n">
-        <v>0.8270999999999999</v>
+        <v>0.827</v>
       </c>
       <c r="F112" t="n">
         <v>0</v>
       </c>
       <c r="G112" t="n">
-        <v>0.8270999999999999</v>
+        <v>0.827</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -7071,7 +7095,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>All candidates exhibit semantic-role conflicts with the target column.</t>
+          <t>All candidates have semantic-role conflicts and provide no distinctive evidence.</t>
         </is>
       </c>
       <c r="M112" t="inlineStr"/>
@@ -7110,7 +7134,7 @@
         <v>0.893</v>
       </c>
       <c r="F113" t="n">
-        <v>0.885</v>
+        <v>0.8851</v>
       </c>
       <c r="G113" t="n">
         <v>0.007900000000000001</v>
@@ -7133,7 +7157,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>The name 'Base FCP Cmp' closely aligns with 'Base ICMS_FECP' and has no semantic conflicts.</t>
+          <t>The candidate 'Base FCP Cmp' has a high name confidence but all values are zero, indicating no valid mapping.</t>
         </is>
       </c>
       <c r="M113" t="inlineStr"/>
@@ -7142,7 +7166,7 @@
       <c r="P113" t="inlineStr"/>
       <c r="Q113" t="inlineStr"/>
       <c r="R113" t="n">
-        <v>0.893</v>
+        <v>0</v>
       </c>
       <c r="S113" t="n">
         <v>0.893</v>
@@ -7195,7 +7219,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>The candidate 'Aliq FECP' has a high name confidence and matches the expected semantic role despite all-zero evidence.</t>
+          <t>The column 'Aliq FECP' closely matches the semantic role of 'Aliquota ICMS_FECP' with a high name confidence.</t>
         </is>
       </c>
       <c r="M114" t="inlineStr"/>
@@ -7204,7 +7228,7 @@
       <c r="P114" t="inlineStr"/>
       <c r="Q114" t="inlineStr"/>
       <c r="R114" t="n">
-        <v>0</v>
+        <v>0.8905999999999999</v>
       </c>
       <c r="S114" t="n">
         <v>0.8905999999999999</v>
@@ -7223,27 +7247,27 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>25</v>
+        <v>126</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Vlr ICMS Com</t>
+          <t>Valor FECP</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>0.8948</v>
+        <v>0.9391</v>
       </c>
       <c r="F115" t="n">
-        <v>0.9392</v>
+        <v>0.9272</v>
       </c>
       <c r="G115" t="n">
-        <v>-0.0443</v>
+        <v>0.0118</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
       </c>
       <c r="I115" t="n">
-        <v>0.8948</v>
+        <v>0.8999</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
@@ -7257,7 +7281,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>The name 'Vlr ICMS Com' closely relates to the tax value context, and it has a higher unique count and informative evidence compared to other candidates.</t>
+          <t>The name 'Valor FECP' closely matches 'Valor ICMS_FECP' and both have all-zero values, indicating they refer to the same concept.</t>
         </is>
       </c>
       <c r="M115" t="inlineStr"/>
@@ -7266,10 +7290,10 @@
       <c r="P115" t="inlineStr"/>
       <c r="Q115" t="inlineStr"/>
       <c r="R115" t="n">
-        <v>0.8948</v>
+        <v>0.9391</v>
       </c>
       <c r="S115" t="n">
-        <v>0.8948</v>
+        <v>0.9391</v>
       </c>
       <c r="T115" t="inlineStr"/>
       <c r="U115" t="inlineStr"/>
@@ -7284,23 +7308,29 @@
           <t>Isentas ICMS_FECP</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr"/>
-      <c r="D116" t="inlineStr"/>
+      <c r="C116" t="n">
+        <v>331</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>BC ICMS Efet</t>
+        </is>
+      </c>
       <c r="E116" t="n">
-        <v>0.8522999999999999</v>
+        <v>0.8747</v>
       </c>
       <c r="F116" t="n">
+        <v>0.8636</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0.0111</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" t="n">
         <v>0.8747</v>
       </c>
-      <c r="G116" t="n">
-        <v>-0.0224</v>
-      </c>
-      <c r="H116" t="n">
-        <v>0</v>
-      </c>
-      <c r="I116" t="n">
-        <v>0</v>
-      </c>
       <c r="J116" t="inlineStr">
         <is>
           <t>data</t>
@@ -7308,12 +7338,12 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>review</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
         </is>
       </c>
       <c r="M116" t="inlineStr"/>
@@ -7340,28 +7370,22 @@
           <t>Outras ICMS_FECP</t>
         </is>
       </c>
-      <c r="C117" t="n">
-        <v>331</v>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>BC ICMS Efet</t>
-        </is>
-      </c>
+      <c r="C117" t="inlineStr"/>
+      <c r="D117" t="inlineStr"/>
       <c r="E117" t="n">
-        <v>0.8759</v>
+        <v>0.8617</v>
       </c>
       <c r="F117" t="n">
-        <v>0.8731</v>
+        <v>0.8835</v>
       </c>
       <c r="G117" t="n">
-        <v>0.0028</v>
+        <v>-0.0218</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
       </c>
       <c r="I117" t="n">
-        <v>0.8759</v>
+        <v>0</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -7370,12 +7394,12 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>no_match</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>The header 'BC ICMS Efet' aligns with the tax base context, despite all-zero evidence.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M117" t="inlineStr"/>
@@ -7384,10 +7408,10 @@
       <c r="P117" t="inlineStr"/>
       <c r="Q117" t="inlineStr"/>
       <c r="R117" t="n">
-        <v>0</v>
+        <v>0.8617</v>
       </c>
       <c r="S117" t="n">
-        <v>0.8759</v>
+        <v>0.8617</v>
       </c>
       <c r="T117" t="inlineStr"/>
       <c r="U117" t="inlineStr"/>
@@ -7431,7 +7455,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>All candidates exhibit semantic-role conflicts and lack distinctive non-zero evidence.</t>
+          <t>All candidates exhibit semantic-role conflicts or lack distinctive evidence, making them unsuitable for mapping.</t>
         </is>
       </c>
       <c r="M118" t="inlineStr"/>
@@ -7617,7 +7641,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>The name 'Cofins Pauta' closely matches 'Isentas COFINS' and both have all-zero values, indicating they may represent the same exempt COFINS amount.</t>
+          <t>The header 'Cofins Pauta' is closely related to 'Isentas COFINS', but both contain only zeros, indicating no valid data.</t>
         </is>
       </c>
       <c r="M121" t="inlineStr"/>
@@ -7626,7 +7650,7 @@
       <c r="P121" t="inlineStr"/>
       <c r="Q121" t="inlineStr"/>
       <c r="R121" t="n">
-        <v>0.8784999999999999</v>
+        <v>0</v>
       </c>
       <c r="S121" t="n">
         <v>0.8784999999999999</v>
@@ -7659,7 +7683,7 @@
         <v>0.8625</v>
       </c>
       <c r="G122" t="n">
-        <v>0.0248</v>
+        <v>0.0247</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
@@ -7715,19 +7739,19 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0.856</v>
+        <v>0.8562</v>
       </c>
       <c r="F123" t="n">
         <v>0</v>
       </c>
       <c r="G123" t="n">
-        <v>0.856</v>
+        <v>0.8562</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
       </c>
       <c r="I123" t="n">
-        <v>0.856</v>
+        <v>0.8562</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
@@ -7741,7 +7765,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>The candidate 'Cofins Pauta' has a matching semantic role without conflicting evidence, despite all-zero data.</t>
+          <t>The strongest header candidate has weak row evidence; preserve the name-based mapping for review instead of replacing it with a merely similar value shape.</t>
         </is>
       </c>
       <c r="M123" t="inlineStr"/>
@@ -7753,7 +7777,7 @@
         <v>0</v>
       </c>
       <c r="S123" t="n">
-        <v>0.856</v>
+        <v>0</v>
       </c>
       <c r="T123" t="inlineStr"/>
       <c r="U123" t="inlineStr"/>
@@ -7780,7 +7804,7 @@
         <v>0.8848</v>
       </c>
       <c r="F124" t="n">
-        <v>0.8728</v>
+        <v>0.8729</v>
       </c>
       <c r="G124" t="n">
         <v>0.0119</v>
@@ -7803,7 +7827,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>The column 'PIS Pauta' has a high name confidence but all values are zero, indicating it may not represent actual data.</t>
+          <t>The header 'PIS Pauta' suggests a tax-related context, but both columns contain only zeros, indicating no valid data to support a mapping.</t>
         </is>
       </c>
       <c r="M124" t="inlineStr"/>
@@ -7839,7 +7863,7 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>0.8868</v>
+        <v>0.8867</v>
       </c>
       <c r="F125" t="n">
         <v>0.8735000000000001</v>
@@ -7851,7 +7875,7 @@
         <v>0</v>
       </c>
       <c r="I125" t="n">
-        <v>0.8868</v>
+        <v>0.8867</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
@@ -7874,10 +7898,10 @@
       <c r="P125" t="inlineStr"/>
       <c r="Q125" t="inlineStr"/>
       <c r="R125" t="n">
-        <v>0.8868</v>
+        <v>0.8867</v>
       </c>
       <c r="S125" t="n">
-        <v>0.8868</v>
+        <v>0.8867</v>
       </c>
       <c r="T125" t="inlineStr"/>
       <c r="U125" t="inlineStr"/>
@@ -7895,13 +7919,13 @@
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="n">
-        <v>0.8502</v>
+        <v>0.8501</v>
       </c>
       <c r="F126" t="n">
         <v>0.894</v>
       </c>
       <c r="G126" t="n">
-        <v>-0.0438</v>
+        <v>-0.0439</v>
       </c>
       <c r="H126" t="n">
         <v>0.0601</v>
@@ -7930,10 +7954,10 @@
       <c r="P126" t="inlineStr"/>
       <c r="Q126" t="inlineStr"/>
       <c r="R126" t="n">
-        <v>0.8502</v>
+        <v>0.8501</v>
       </c>
       <c r="S126" t="n">
-        <v>0.8502</v>
+        <v>0.8501</v>
       </c>
       <c r="T126" t="inlineStr"/>
       <c r="U126" t="inlineStr"/>
@@ -7951,13 +7975,13 @@
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="n">
-        <v>0.8591</v>
+        <v>0.8962</v>
       </c>
       <c r="F127" t="n">
-        <v>0.8387</v>
+        <v>0.8999</v>
       </c>
       <c r="G127" t="n">
-        <v>0.0204</v>
+        <v>-0.0037</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -7977,7 +8001,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>All candidates exhibit semantic-role conflicts or lack distinctive evidence, making them unsuitable for mapping.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M127" t="inlineStr"/>
@@ -7986,10 +8010,10 @@
       <c r="P127" t="inlineStr"/>
       <c r="Q127" t="inlineStr"/>
       <c r="R127" t="n">
-        <v>0</v>
+        <v>0.8962</v>
       </c>
       <c r="S127" t="n">
-        <v>0</v>
+        <v>0.8962</v>
       </c>
       <c r="T127" t="inlineStr"/>
       <c r="U127" t="inlineStr"/>
@@ -8039,7 +8063,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>The header 'Recolhe ISS' closely relates to the tax type 'Tipo de Imposto ISS' despite the lack of numeric evidence.</t>
+          <t>The column 'Recolhe ISS' has a high name confidence and contains relevant non-empty values indicating a tax type.</t>
         </is>
       </c>
       <c r="M128" t="inlineStr"/>
@@ -8075,19 +8099,19 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>0.8771</v>
+        <v>0.877</v>
       </c>
       <c r="F129" t="n">
-        <v>0.8797</v>
+        <v>0.8798</v>
       </c>
       <c r="G129" t="n">
-        <v>-0.0027</v>
+        <v>-0.0028</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
       </c>
       <c r="I129" t="n">
-        <v>0.8771</v>
+        <v>0.877</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
@@ -8101,7 +8125,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>The column 'ISS Mat.' has a similar numeric profile and name context to 'Base ISS', despite both having all-zero values.</t>
+          <t>The name 'ISS Mat.' closely aligns with 'Base ISS' and both have similar numeric profiles, despite all values being zero.</t>
         </is>
       </c>
       <c r="M129" t="inlineStr"/>
@@ -8110,10 +8134,10 @@
       <c r="P129" t="inlineStr"/>
       <c r="Q129" t="inlineStr"/>
       <c r="R129" t="n">
-        <v>0.8771</v>
+        <v>0.877</v>
       </c>
       <c r="S129" t="n">
-        <v>0.8771</v>
+        <v>0.877</v>
       </c>
       <c r="T129" t="inlineStr"/>
       <c r="U129" t="inlineStr"/>
@@ -8143,7 +8167,7 @@
         <v>0.8915999999999999</v>
       </c>
       <c r="G130" t="n">
-        <v>0.0023</v>
+        <v>0.0022</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -8163,7 +8187,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>The candidate 'Alq.ISS CPM' has a high name confidence and matches the expected integer type, despite all values being zero.</t>
+          <t>Both columns represent ISS tax rates, but all values are zero, limiting evidence for a strong mapping.</t>
         </is>
       </c>
       <c r="M130" t="inlineStr"/>
@@ -8199,19 +8223,19 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>0.8663</v>
+        <v>0.8662</v>
       </c>
       <c r="F131" t="n">
         <v>0.8939</v>
       </c>
       <c r="G131" t="n">
-        <v>-0.0276</v>
+        <v>-0.0277</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
       </c>
       <c r="I131" t="n">
-        <v>0.8663</v>
+        <v>0.8662</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
@@ -8225,7 +8249,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>The header 'ISS Mat.' aligns with the tax type and has similar numeric characteristics despite all-zero values.</t>
+          <t>The header 'ISS Mat.' closely matches 'Valor ISS' and both have all-zero values, indicating a potential mapping despite the lack of distinctive sample overlap.</t>
         </is>
       </c>
       <c r="M131" t="inlineStr"/>
@@ -8234,10 +8258,10 @@
       <c r="P131" t="inlineStr"/>
       <c r="Q131" t="inlineStr"/>
       <c r="R131" t="n">
-        <v>0.8663</v>
+        <v>0.8662</v>
       </c>
       <c r="S131" t="n">
-        <v>0.8663</v>
+        <v>0.8662</v>
       </c>
       <c r="T131" t="inlineStr"/>
       <c r="U131" t="inlineStr"/>
@@ -8267,7 +8291,7 @@
         <v>0.8816000000000001</v>
       </c>
       <c r="G132" t="n">
-        <v>-0.0097</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -8317,7 +8341,7 @@
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="n">
-        <v>0.892</v>
+        <v>0.8921</v>
       </c>
       <c r="F133" t="n">
         <v>0.8756</v>
@@ -8373,13 +8397,13 @@
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="n">
+        <v>0.8449</v>
+      </c>
+      <c r="F134" t="n">
         <v>0.8769</v>
       </c>
-      <c r="F134" t="n">
-        <v>0.8484</v>
-      </c>
       <c r="G134" t="n">
-        <v>0.0284</v>
+        <v>-0.0319</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -8399,7 +8423,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>All candidates exhibit semantic-role conflicts or lack relevant data evidence.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M134" t="inlineStr"/>
@@ -8408,10 +8432,10 @@
       <c r="P134" t="inlineStr"/>
       <c r="Q134" t="inlineStr"/>
       <c r="R134" t="n">
-        <v>0</v>
+        <v>0.8449</v>
       </c>
       <c r="S134" t="n">
-        <v>0</v>
+        <v>0.8449</v>
       </c>
       <c r="T134" t="inlineStr"/>
       <c r="U134" t="inlineStr"/>
@@ -8523,7 +8547,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>The name 'Aliq. FCP ST' closely matches the canonical 'Aliquota FECP_ST' without semantic conflicts.</t>
+          <t>The candidate 'Aliq. FCP ST' has a high name confidence and no semantic header conflict.</t>
         </is>
       </c>
       <c r="M136" t="inlineStr"/>
@@ -8559,7 +8583,7 @@
         <v>0.8781</v>
       </c>
       <c r="G137" t="n">
-        <v>0.0081</v>
+        <v>0.008</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
@@ -8579,7 +8603,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>All candidates have a semantic header conflict and provide no distinctive sample evidence.</t>
+          <t>All candidates exhibit a tax-qualifier conflict and contain only zeros, providing no valid mapping evidence.</t>
         </is>
       </c>
       <c r="M137" t="inlineStr"/>
@@ -8641,7 +8665,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>The candidate 'V.FECP-ST/MT' has a high name confidence and no semantic conflicts, despite all-zero evidence.</t>
+          <t>The candidate 'V.FECP-ST/MT' has a high name confidence and no semantic conflicts, but all values are zero, indicating no actual data support.</t>
         </is>
       </c>
       <c r="M138" t="inlineStr"/>
@@ -8703,7 +8727,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>The candidate 'V.FECP-ST/MT' has a strong name match and no semantic header conflict.</t>
+          <t>The candidate 'V.FECP-ST/MT' has the highest name confidence and no semantic header conflict.</t>
         </is>
       </c>
       <c r="M139" t="inlineStr"/>
@@ -8759,7 +8783,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>All candidates exhibit semantic header conflicts and provide no distinctive sample evidence.</t>
+          <t>All candidates exhibit semantic-role conflicts and provide no distinctive evidence.</t>
         </is>
       </c>
       <c r="M140" t="inlineStr"/>
@@ -8795,10 +8819,10 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>0.8672</v>
+        <v>0.8673</v>
       </c>
       <c r="F141" t="n">
-        <v>0.8736</v>
+        <v>0.8737</v>
       </c>
       <c r="G141" t="n">
         <v>-0.0064</v>
@@ -8807,7 +8831,7 @@
         <v>0</v>
       </c>
       <c r="I141" t="n">
-        <v>0.8672</v>
+        <v>0.8673</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
@@ -8830,10 +8854,10 @@
       <c r="P141" t="inlineStr"/>
       <c r="Q141" t="inlineStr"/>
       <c r="R141" t="n">
-        <v>0.8672</v>
+        <v>0.8673</v>
       </c>
       <c r="S141" t="n">
-        <v>0.8672</v>
+        <v>0.8673</v>
       </c>
       <c r="T141" t="inlineStr"/>
       <c r="U141" t="inlineStr"/>
@@ -8848,28 +8872,22 @@
           <t>Base ICMS_ST</t>
         </is>
       </c>
-      <c r="C142" t="n">
-        <v>240</v>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>ICMS ST Ant.</t>
-        </is>
-      </c>
+      <c r="C142" t="inlineStr"/>
+      <c r="D142" t="inlineStr"/>
       <c r="E142" t="n">
-        <v>0.8951</v>
+        <v>0.8897</v>
       </c>
       <c r="F142" t="n">
         <v>0.908</v>
       </c>
       <c r="G142" t="n">
-        <v>-0.0128</v>
+        <v>-0.0183</v>
       </c>
       <c r="H142" t="n">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="I142" t="n">
-        <v>0.8951</v>
+        <v>0</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
@@ -8878,12 +8896,12 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>no_match</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>The name 'ICMS ST Ant.' closely matches 'Base ICMS_ST' and has no semantic conflicts.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M142" t="inlineStr"/>
@@ -8892,10 +8910,10 @@
       <c r="P142" t="inlineStr"/>
       <c r="Q142" t="inlineStr"/>
       <c r="R142" t="n">
-        <v>0.8951</v>
+        <v>0.8897</v>
       </c>
       <c r="S142" t="n">
-        <v>0.8951</v>
+        <v>0.898</v>
       </c>
       <c r="T142" t="inlineStr"/>
       <c r="U142" t="inlineStr"/>
@@ -8925,7 +8943,7 @@
         <v>0.8922</v>
       </c>
       <c r="G143" t="n">
-        <v>0.002</v>
+        <v>0.0019</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -8945,7 +8963,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>The name 'ICMS ST Ant.' closely aligns with 'Aliquota ICMS_ST' and has no semantic conflicts.</t>
+          <t>The name 'ICMS ST Ant.' closely aligns with 'Aliquota ICMS_ST' despite a lack of distinctive sample overlap, and no semantic header conflict.</t>
         </is>
       </c>
       <c r="M143" t="inlineStr"/>
@@ -9007,7 +9025,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>The candidate 'B.ICMS ST An' has the highest name confidence and no semantic conflicts.</t>
+          <t>The name 'B.ICMS ST An' closely matches the tax type 'Isentas ICMS_ST' with no semantic conflicts.</t>
         </is>
       </c>
       <c r="M144" t="inlineStr"/>
@@ -9034,28 +9052,22 @@
           <t>Outras ICMS_ST</t>
         </is>
       </c>
-      <c r="C145" t="n">
-        <v>239</v>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>B.ICMS ST An</t>
-        </is>
-      </c>
+      <c r="C145" t="inlineStr"/>
+      <c r="D145" t="inlineStr"/>
       <c r="E145" t="n">
-        <v>0.8801</v>
+        <v>0.882</v>
       </c>
       <c r="F145" t="n">
-        <v>0.8717</v>
+        <v>0.8981</v>
       </c>
       <c r="G145" t="n">
-        <v>0.008399999999999999</v>
+        <v>-0.016</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
       </c>
       <c r="I145" t="n">
-        <v>0.8801</v>
+        <v>0</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
@@ -9064,12 +9076,12 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>no_match</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>Despite the tax-qualifier conflict, 'B.ICMS ST An' aligns closely with 'Outras ICMS_ST' in naming and type.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M145" t="inlineStr"/>
@@ -9081,7 +9093,7 @@
         <v>0</v>
       </c>
       <c r="S145" t="n">
-        <v>0.8801</v>
+        <v>0.882</v>
       </c>
       <c r="T145" t="inlineStr"/>
       <c r="U145" t="inlineStr"/>
@@ -9125,7 +9137,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>All candidates have semantic header conflicts and insufficient distinctive sample evidence.</t>
+          <t>All candidates exhibit semantic header conflicts and lack distinctive sample overlap or strong relationship evidence.</t>
         </is>
       </c>
       <c r="M146" t="inlineStr"/>
@@ -9158,10 +9170,10 @@
         <v>0.8248</v>
       </c>
       <c r="F147" t="n">
-        <v>0.8243</v>
+        <v>0.8241000000000001</v>
       </c>
       <c r="G147" t="n">
-        <v>0.0005</v>
+        <v>0.0007</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
@@ -9190,7 +9202,7 @@
       <c r="P147" t="inlineStr"/>
       <c r="Q147" t="inlineStr"/>
       <c r="R147" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="S147" t="n">
         <v>0.8248</v>
@@ -9237,7 +9249,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>All candidate columns contain no relevant data or evidence to support a mapping.</t>
+          <t>All candidates have insufficient evidence and do not align semantically with 'Municipio Inicio'.</t>
         </is>
       </c>
       <c r="M148" t="inlineStr"/>
@@ -9329,7 +9341,7 @@
         <v>0.768</v>
       </c>
       <c r="G150" t="n">
-        <v>-0.0568</v>
+        <v>-0.0567</v>
       </c>
       <c r="H150" t="n">
         <v>0.1633</v>
@@ -9379,13 +9391,13 @@
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="n">
-        <v>0.8583</v>
+        <v>0.8584000000000001</v>
       </c>
       <c r="F151" t="n">
         <v>0.8366</v>
       </c>
       <c r="G151" t="n">
-        <v>0.0217</v>
+        <v>0.0218</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
@@ -9405,7 +9417,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>All candidates have insufficient evidence or are empty, making a mapping impossible.</t>
+          <t>All candidate columns contain no relevant data or evidence to support a mapping.</t>
         </is>
       </c>
       <c r="M151" t="inlineStr"/>
@@ -9435,10 +9447,10 @@
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="n">
-        <v>0.8034</v>
+        <v>0.8033</v>
       </c>
       <c r="F152" t="n">
-        <v>0.8161</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="G152" t="n">
         <v>-0.0127</v>
@@ -9470,10 +9482,10 @@
       <c r="P152" t="inlineStr"/>
       <c r="Q152" t="inlineStr"/>
       <c r="R152" t="n">
-        <v>0.8034</v>
+        <v>0</v>
       </c>
       <c r="S152" t="n">
-        <v>0.8034</v>
+        <v>0.8033</v>
       </c>
       <c r="T152" t="inlineStr"/>
       <c r="U152" t="inlineStr"/>
@@ -9494,7 +9506,7 @@
         <v>0.7963</v>
       </c>
       <c r="F153" t="n">
-        <v>0.7882</v>
+        <v>0.7881</v>
       </c>
       <c r="G153" t="n">
         <v>0.008200000000000001</v>
@@ -9547,13 +9559,13 @@
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="n">
-        <v>0.8689</v>
+        <v>0.8688</v>
       </c>
       <c r="F154" t="n">
-        <v>0.8321</v>
+        <v>0.8325</v>
       </c>
       <c r="G154" t="n">
-        <v>0.0368</v>
+        <v>0.0364</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -9603,13 +9615,13 @@
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="n">
-        <v>0.8409</v>
+        <v>0.841</v>
       </c>
       <c r="F155" t="n">
         <v>0.8302</v>
       </c>
       <c r="G155" t="n">
-        <v>0.0107</v>
+        <v>0.0108</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -9629,7 +9641,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>All candidate columns lack meaningful data evidence, making a mapping unsupported.</t>
+          <t>All candidate columns contain no valid data, making them incompatible with the 'Domicílio Fiscal' requirement.</t>
         </is>
       </c>
       <c r="M155" t="inlineStr"/>
@@ -9662,10 +9674,10 @@
         <v>0.8388</v>
       </c>
       <c r="F156" t="n">
-        <v>0.8841</v>
+        <v>0.8837</v>
       </c>
       <c r="G156" t="n">
-        <v>-0.0453</v>
+        <v>-0.045</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -9718,7 +9730,7 @@
         <v>0.8502999999999999</v>
       </c>
       <c r="F157" t="n">
-        <v>0.8413</v>
+        <v>0.8414</v>
       </c>
       <c r="G157" t="n">
         <v>0.0089</v>
@@ -9741,7 +9753,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>No suitable candidate matches the semantic role of 'ID do consumidor final'.</t>
+          <t>The candidate columns do not match the expected format or content of 'ID do consumidor final', which is numeric and has a fixed width of 1.</t>
         </is>
       </c>
       <c r="M157" t="inlineStr"/>
@@ -9753,7 +9765,7 @@
         <v>0</v>
       </c>
       <c r="S157" t="n">
-        <v>0</v>
+        <v>0.8153</v>
       </c>
       <c r="T157" t="inlineStr"/>
       <c r="U157" t="inlineStr"/>
@@ -9771,7 +9783,7 @@
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="n">
-        <v>0.772</v>
+        <v>0.7721</v>
       </c>
       <c r="F158" t="n">
         <v>0.8815</v>
@@ -9806,10 +9818,10 @@
       <c r="P158" t="inlineStr"/>
       <c r="Q158" t="inlineStr"/>
       <c r="R158" t="n">
-        <v>0.772</v>
+        <v>0.7721</v>
       </c>
       <c r="S158" t="n">
-        <v>0.772</v>
+        <v>0.7771</v>
       </c>
       <c r="T158" t="inlineStr"/>
       <c r="U158" t="inlineStr"/>
@@ -9836,7 +9848,7 @@
         <v>0.8584000000000001</v>
       </c>
       <c r="F159" t="n">
-        <v>0.8557</v>
+        <v>0.8558</v>
       </c>
       <c r="G159" t="n">
         <v>0.0026</v>
@@ -9871,7 +9883,7 @@
         <v>0</v>
       </c>
       <c r="S159" t="n">
-        <v>0</v>
+        <v>0.8584000000000001</v>
       </c>
       <c r="T159" t="inlineStr"/>
       <c r="U159" t="inlineStr"/>
@@ -9889,13 +9901,13 @@
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="n">
-        <v>0.8312</v>
+        <v>0.8465</v>
       </c>
       <c r="F160" t="n">
-        <v>0.8464</v>
+        <v>0.8465</v>
       </c>
       <c r="G160" t="n">
-        <v>-0.0153</v>
+        <v>0</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -9915,7 +9927,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>All candidate columns lack sufficient non-empty data to support a mapping.</t>
         </is>
       </c>
       <c r="M160" t="inlineStr"/>
@@ -9924,10 +9936,10 @@
       <c r="P160" t="inlineStr"/>
       <c r="Q160" t="inlineStr"/>
       <c r="R160" t="n">
-        <v>0.8312</v>
+        <v>0</v>
       </c>
       <c r="S160" t="n">
-        <v>0.8312</v>
+        <v>0</v>
       </c>
       <c r="T160" t="inlineStr"/>
       <c r="U160" t="inlineStr"/>
@@ -9948,7 +9960,7 @@
         <v>0.8154</v>
       </c>
       <c r="F161" t="n">
-        <v>0.8153</v>
+        <v>0.8152</v>
       </c>
       <c r="G161" t="n">
         <v>0.0002</v>
@@ -9971,7 +9983,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>No candidate columns provide relevant data evidence to support a mapping.</t>
+          <t>All candidate columns contain no relevant data to support a mapping.</t>
         </is>
       </c>
       <c r="M161" t="inlineStr"/>
@@ -10010,10 +10022,10 @@
         <v>0.9295</v>
       </c>
       <c r="F162" t="n">
-        <v>0.8118</v>
+        <v>0.8164</v>
       </c>
       <c r="G162" t="n">
-        <v>0.1177</v>
+        <v>0.1131</v>
       </c>
       <c r="H162" t="inlineStr"/>
       <c r="I162" t="n">
@@ -10169,13 +10181,13 @@
       <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="n">
-        <v>0.7876</v>
+        <v>0.7975</v>
       </c>
       <c r="F165" t="n">
-        <v>0.7975</v>
+        <v>0.7904</v>
       </c>
       <c r="G165" t="n">
-        <v>-0.009900000000000001</v>
+        <v>0.0071</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -10195,7 +10207,7 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>All candidate columns contain no non-empty values, making them unsuitable for mapping.</t>
         </is>
       </c>
       <c r="M165" t="inlineStr"/>
@@ -10204,10 +10216,10 @@
       <c r="P165" t="inlineStr"/>
       <c r="Q165" t="inlineStr"/>
       <c r="R165" t="n">
-        <v>0.7876</v>
+        <v>0</v>
       </c>
       <c r="S165" t="n">
-        <v>0.7876</v>
+        <v>0</v>
       </c>
       <c r="T165" t="inlineStr"/>
       <c r="U165" t="inlineStr"/>
@@ -10287,7 +10299,7 @@
         <v>0.8205</v>
       </c>
       <c r="G167" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0089</v>
       </c>
       <c r="H167" t="n">
         <v>0</v>
@@ -10307,7 +10319,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>All candidates have empty evidence quality, indicating no valid data to support a mapping.</t>
+          <t>All candidates have empty evidence with no distinctive samples or valid data.</t>
         </is>
       </c>
       <c r="M167" t="inlineStr"/>
@@ -10375,7 +10387,7 @@
         <v>0.97</v>
       </c>
       <c r="S168" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="T168" t="inlineStr"/>
       <c r="U168" t="inlineStr"/>
@@ -10390,28 +10402,22 @@
           <t>Valor da isenção de ICMS</t>
         </is>
       </c>
-      <c r="C169" t="n">
-        <v>15</v>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>Vlr Isen ICM</t>
-        </is>
-      </c>
+      <c r="C169" t="inlineStr"/>
+      <c r="D169" t="inlineStr"/>
       <c r="E169" t="n">
-        <v>0.8512999999999999</v>
+        <v>0.8512</v>
       </c>
       <c r="F169" t="n">
-        <v>0.874</v>
+        <v>0.8741</v>
       </c>
       <c r="G169" t="n">
-        <v>-0.0227</v>
+        <v>-0.0229</v>
       </c>
       <c r="H169" t="n">
         <v>0.0007</v>
       </c>
       <c r="I169" t="n">
-        <v>0.8512999999999999</v>
+        <v>0</v>
       </c>
       <c r="J169" t="inlineStr">
         <is>
@@ -10420,12 +10426,12 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>no_match</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>A high-coverage fiscal equation strongly contradicts this proposal; keep it for review instead of accepting it automatically.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M169" t="inlineStr"/>
@@ -10434,10 +10440,10 @@
       <c r="P169" t="inlineStr"/>
       <c r="Q169" t="inlineStr"/>
       <c r="R169" t="n">
-        <v>0.8512999999999999</v>
+        <v>0.8512</v>
       </c>
       <c r="S169" t="n">
-        <v>0.8512999999999999</v>
+        <v>0.8512</v>
       </c>
       <c r="T169" t="inlineStr"/>
       <c r="U169" t="inlineStr"/>
@@ -10487,7 +10493,7 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>The name 'Base FCP Cmp' closely aligns with 'Base de Cálculo ICOP FECP' and both have all-zero evidence, but the name confidence is the highest among candidates.</t>
+          <t>The candidate 'Base FCP Cmp' has the highest name confidence and no semantic conflicts.</t>
         </is>
       </c>
       <c r="M170" t="inlineStr"/>
@@ -10549,7 +10555,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>The candidate 'Aliq FECP' closely matches the semantic role of 'Alíquota ICOP FECP' with a high name confidence and no semantic conflicts.</t>
+          <t>The candidate 'Aliq FECP' closely matches the semantic role of 'Alíquota ICOP FECP' with a high name confidence and no conflicting evidence.</t>
         </is>
       </c>
       <c r="M171" t="inlineStr"/>
@@ -10588,10 +10594,10 @@
         <v>0.9402</v>
       </c>
       <c r="F172" t="n">
-        <v>0.9239000000000001</v>
+        <v>0.9234</v>
       </c>
       <c r="G172" t="n">
-        <v>0.0163</v>
+        <v>0.0168</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -10639,27 +10645,27 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>321</v>
+        <v>15</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>FECP Comp.</t>
+          <t>Vlr Isen ICM</t>
         </is>
       </c>
       <c r="E173" t="n">
+        <v>0.8556</v>
+      </c>
+      <c r="F173" t="n">
         <v>0.8653</v>
       </c>
-      <c r="F173" t="n">
-        <v>0.847</v>
-      </c>
       <c r="G173" t="n">
-        <v>0.0183</v>
+        <v>-0.0097</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
       </c>
       <c r="I173" t="n">
-        <v>0.8653</v>
+        <v>0.8556</v>
       </c>
       <c r="J173" t="inlineStr">
         <is>
@@ -10673,7 +10679,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>The name 'FECP Comp.' has a high confidence score, but all values are zero, indicating no valid data.</t>
+          <t>The name 'Vlr Isen ICM' closely relates to tax exemptions, aligning with the 'Isentas ICOP FECP' context despite some numeric discrepancies.</t>
         </is>
       </c>
       <c r="M173" t="inlineStr"/>
@@ -10682,10 +10688,10 @@
       <c r="P173" t="inlineStr"/>
       <c r="Q173" t="inlineStr"/>
       <c r="R173" t="n">
-        <v>0</v>
+        <v>0.8556</v>
       </c>
       <c r="S173" t="n">
-        <v>0.8653</v>
+        <v>0.8556</v>
       </c>
       <c r="T173" t="inlineStr"/>
       <c r="U173" t="inlineStr"/>
@@ -10700,28 +10706,22 @@
           <t>Outras ICOP FECP</t>
         </is>
       </c>
-      <c r="C174" t="n">
-        <v>321</v>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>FECP Comp.</t>
-        </is>
-      </c>
+      <c r="C174" t="inlineStr"/>
+      <c r="D174" t="inlineStr"/>
       <c r="E174" t="n">
         <v>0.8799</v>
       </c>
       <c r="F174" t="n">
-        <v>0</v>
+        <v>0.8506</v>
       </c>
       <c r="G174" t="n">
-        <v>0.8799</v>
+        <v>0.0292</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
       </c>
       <c r="I174" t="n">
-        <v>0.8799</v>
+        <v>0</v>
       </c>
       <c r="J174" t="inlineStr">
         <is>
@@ -10730,12 +10730,12 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>no_match</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>The candidate 'FECP Comp.' has a high name confidence but lacks distinctive data evidence.</t>
+          <t>All candidates have semantic conflicts or all-zero evidence, indicating no suitable mapping.</t>
         </is>
       </c>
       <c r="M174" t="inlineStr"/>
@@ -10747,7 +10747,7 @@
         <v>0</v>
       </c>
       <c r="S174" t="n">
-        <v>0.8799</v>
+        <v>0.8582</v>
       </c>
       <c r="T174" t="inlineStr"/>
       <c r="U174" t="inlineStr"/>
@@ -10765,16 +10765,16 @@
       <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="n">
-        <v>0.7421</v>
+        <v>0.7786</v>
       </c>
       <c r="F175" t="n">
         <v>0.8415</v>
       </c>
       <c r="G175" t="n">
-        <v>-0.0994</v>
+        <v>-0.0629</v>
       </c>
       <c r="H175" t="n">
-        <v>0.7558</v>
+        <v>0.2504</v>
       </c>
       <c r="I175" t="n">
         <v>0</v>
@@ -10800,10 +10800,10 @@
       <c r="P175" t="inlineStr"/>
       <c r="Q175" t="inlineStr"/>
       <c r="R175" t="n">
-        <v>0.7421</v>
+        <v>0.7121</v>
       </c>
       <c r="S175" t="n">
-        <v>0.7421</v>
+        <v>0.7121</v>
       </c>
       <c r="T175" t="inlineStr"/>
       <c r="U175" t="inlineStr"/>
@@ -10939,7 +10939,7 @@
         <v>0.8217</v>
       </c>
       <c r="G178" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0089</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -10959,7 +10959,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>No viable candidates due to lack of evidence and semantic conflicts.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M178" t="inlineStr"/>
@@ -10971,7 +10971,7 @@
         <v>0</v>
       </c>
       <c r="S178" t="n">
-        <v>0</v>
+        <v>0.8305</v>
       </c>
       <c r="T178" t="inlineStr"/>
       <c r="U178" t="inlineStr"/>
@@ -10995,10 +10995,10 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>0.8554</v>
+        <v>0.8555</v>
       </c>
       <c r="F179" t="n">
-        <v>0.8572</v>
+        <v>0.8573</v>
       </c>
       <c r="G179" t="n">
         <v>-0.0018</v>
@@ -11007,7 +11007,7 @@
         <v>0.84</v>
       </c>
       <c r="I179" t="n">
-        <v>0.8554</v>
+        <v>0.8555</v>
       </c>
       <c r="J179" t="inlineStr">
         <is>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>The 'Doc. Fiscal' column has a strong numeric profile with a fixed width of 9 digits, closely matching the 10-digit format of 'Nº documento'.</t>
+          <t>The 'Doc. Fiscal' column has a strong numeric profile and a high non-empty count, closely matching the expected format of invoice document numbers.</t>
         </is>
       </c>
       <c r="M179" t="inlineStr"/>
@@ -11030,10 +11030,10 @@
       <c r="P179" t="inlineStr"/>
       <c r="Q179" t="inlineStr"/>
       <c r="R179" t="n">
-        <v>0.9</v>
+        <v>0.985</v>
       </c>
       <c r="S179" t="n">
-        <v>0.88</v>
+        <v>0.8714</v>
       </c>
       <c r="T179" t="inlineStr"/>
       <c r="U179" t="inlineStr"/>
@@ -11077,7 +11077,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>No candidate column matches the expected numeric format and semantic role for 'Empresa'.</t>
+          <t>No candidate column matches the semantic role of 'Empresa' with sufficient evidence.</t>
         </is>
       </c>
       <c r="M180" t="inlineStr"/>
@@ -11107,7 +11107,7 @@
       <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr"/>
       <c r="E181" t="n">
-        <v>0.8176</v>
+        <v>0.8175</v>
       </c>
       <c r="F181" t="n">
         <v>0.8175</v>
@@ -11133,7 +11133,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>The 'Exportador' column is empty, providing no evidence to support a mapping.</t>
+          <t>No suitable candidate found due to lack of non-empty values in the 'Exportador' column.</t>
         </is>
       </c>
       <c r="M181" t="inlineStr"/>
@@ -11166,10 +11166,10 @@
         <v>0.7987</v>
       </c>
       <c r="F182" t="n">
-        <v>0.798</v>
+        <v>0.7981</v>
       </c>
       <c r="G182" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0007</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -11189,7 +11189,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>All candidate columns are empty or lack distinctive content, making it impossible to establish a valid mapping.</t>
+          <t>All candidate columns are empty, providing no evidence for a mapping.</t>
         </is>
       </c>
       <c r="M182" t="inlineStr"/>
@@ -11281,7 +11281,7 @@
         <v>0.8231000000000001</v>
       </c>
       <c r="G184" t="n">
-        <v>0.0122</v>
+        <v>0.0121</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -11301,7 +11301,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>No viable candidates match the semantic role of 'Código Fornecedor Início' based on the provided evidence.</t>
+          <t>No viable candidates match the semantic role or provide sufficient data evidence.</t>
         </is>
       </c>
       <c r="M184" t="inlineStr"/>
@@ -11375,7 +11375,7 @@
         <v>0.9968</v>
       </c>
       <c r="S185" t="n">
-        <v>0.9968</v>
+        <v>0.9883999999999999</v>
       </c>
       <c r="T185" t="inlineStr"/>
       <c r="U185" t="inlineStr"/>
@@ -11537,7 +11537,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>The header 'Doc. Fiscal' closely aligns with the semantic role of 'Documento de compras' and has substantial numeric data evidence.</t>
+          <t>The 'Doc. Fiscal' column has a strong numeric profile and high name confidence, aligning well with the expected format for purchase documents.</t>
         </is>
       </c>
       <c r="M188" t="inlineStr"/>
@@ -11549,7 +11549,7 @@
         <v>0.9</v>
       </c>
       <c r="S188" t="n">
-        <v>0.8545</v>
+        <v>0.872</v>
       </c>
       <c r="T188" t="inlineStr"/>
       <c r="U188" t="inlineStr"/>
@@ -11608,10 +11608,10 @@
       <c r="P189" t="inlineStr"/>
       <c r="Q189" t="inlineStr"/>
       <c r="R189" t="n">
-        <v>0.8725000000000001</v>
+        <v>0.8708</v>
       </c>
       <c r="S189" t="n">
-        <v>0.8725000000000001</v>
+        <v>0.8708</v>
       </c>
       <c r="T189" t="inlineStr"/>
       <c r="U189" t="inlineStr"/>
@@ -11655,7 +11655,7 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>All candidates have empty or all-zero evidence, making them unsuitable for mapping.</t>
+          <t>All candidates have empty or all-zero evidence, providing no support for a mapping.</t>
         </is>
       </c>
       <c r="M190" t="inlineStr"/>
@@ -11745,7 +11745,7 @@
       <c r="C192" t="inlineStr"/>
       <c r="D192" t="inlineStr"/>
       <c r="E192" t="n">
-        <v>0.8477</v>
+        <v>0.8476</v>
       </c>
       <c r="F192" t="n">
         <v>0.8431</v>
@@ -11783,7 +11783,7 @@
         <v>0.5</v>
       </c>
       <c r="S192" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.8476</v>
       </c>
       <c r="T192" t="inlineStr"/>
       <c r="U192" t="inlineStr"/>
@@ -11893,7 +11893,7 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>The candidate 'Trib. IPI' has a high name confidence and aligns with the expected tax type for IPI.</t>
+          <t>The name 'Trib. IPI' closely relates to 'Tipo de Imposto IPI' and the data profile shows a mix of numeric values consistent with tax types.</t>
         </is>
       </c>
       <c r="M194" t="inlineStr"/>
@@ -11923,16 +11923,16 @@
       <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr"/>
       <c r="E195" t="n">
+        <v>0.8479</v>
+      </c>
+      <c r="F195" t="n">
         <v>0.832</v>
       </c>
-      <c r="F195" t="n">
-        <v>0.8479</v>
-      </c>
       <c r="G195" t="n">
-        <v>-0.016</v>
+        <v>0.0159</v>
       </c>
       <c r="H195" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="I195" t="n">
         <v>0</v>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>No suitable candidate found due to semantic conflicts and lack of evidence.</t>
         </is>
       </c>
       <c r="M195" t="inlineStr"/>
@@ -11958,10 +11958,10 @@
       <c r="P195" t="inlineStr"/>
       <c r="Q195" t="inlineStr"/>
       <c r="R195" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="S195" t="n">
-        <v>0.83</v>
+        <v>0</v>
       </c>
       <c r="T195" t="inlineStr"/>
       <c r="U195" t="inlineStr"/>
@@ -12047,7 +12047,7 @@
         <v>0.8464</v>
       </c>
       <c r="G197" t="n">
-        <v>-0.0776</v>
+        <v>-0.0775</v>
       </c>
       <c r="H197" t="n">
         <v>0.8316</v>
@@ -12076,10 +12076,10 @@
       <c r="P197" t="inlineStr"/>
       <c r="Q197" t="inlineStr"/>
       <c r="R197" t="n">
-        <v>0.7688</v>
+        <v>0.8</v>
       </c>
       <c r="S197" t="n">
-        <v>0.7688</v>
+        <v>0.8</v>
       </c>
       <c r="T197" t="inlineStr"/>
       <c r="U197" t="inlineStr"/>
@@ -12097,16 +12097,16 @@
       <c r="C198" t="inlineStr"/>
       <c r="D198" t="inlineStr"/>
       <c r="E198" t="n">
-        <v>0.7927</v>
+        <v>0.8121</v>
       </c>
       <c r="F198" t="n">
-        <v>0.8121</v>
+        <v>0.8092</v>
       </c>
       <c r="G198" t="n">
-        <v>-0.0194</v>
+        <v>0.0029</v>
       </c>
       <c r="H198" t="n">
-        <v>0.6264</v>
+        <v>0</v>
       </c>
       <c r="I198" t="n">
         <v>0</v>
@@ -12123,7 +12123,7 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>No suitable candidate matches the semantic role and data evidence for the 'Material' column.</t>
         </is>
       </c>
       <c r="M198" t="inlineStr"/>
@@ -12132,10 +12132,10 @@
       <c r="P198" t="inlineStr"/>
       <c r="Q198" t="inlineStr"/>
       <c r="R198" t="n">
-        <v>0.6264</v>
+        <v>0</v>
       </c>
       <c r="S198" t="n">
-        <v>0.7927</v>
+        <v>0</v>
       </c>
       <c r="T198" t="inlineStr"/>
       <c r="U198" t="inlineStr"/>
@@ -12159,7 +12159,7 @@
         <v>0.8008</v>
       </c>
       <c r="G199" t="n">
-        <v>0.019</v>
+        <v>0.0191</v>
       </c>
       <c r="H199" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>All candidates exhibit semantic-role conflicts or lack relevant data evidence.</t>
+          <t>All candidates have semantic-role conflicts or insufficient evidence to support a mapping.</t>
         </is>
       </c>
       <c r="M199" t="inlineStr"/>
@@ -12265,13 +12265,13 @@
       <c r="C201" t="inlineStr"/>
       <c r="D201" t="inlineStr"/>
       <c r="E201" t="n">
-        <v>0.7345</v>
+        <v>0.7349</v>
       </c>
       <c r="F201" t="n">
         <v>0.7342</v>
       </c>
       <c r="G201" t="n">
-        <v>0.0003</v>
+        <v>0.0007</v>
       </c>
       <c r="H201" t="n">
         <v>0</v>
@@ -12291,7 +12291,7 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>No viable candidates due to lack of non-empty values in the client column.</t>
+          <t>No viable candidates due to lack of non-empty values in the client columns.</t>
         </is>
       </c>
       <c r="M201" t="inlineStr"/>
@@ -12383,19 +12383,19 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>0.8629</v>
+        <v>0.8633</v>
       </c>
       <c r="F203" t="n">
         <v>0</v>
       </c>
       <c r="G203" t="n">
-        <v>0.8629</v>
+        <v>0.8633</v>
       </c>
       <c r="H203" t="n">
         <v>0</v>
       </c>
       <c r="I203" t="n">
-        <v>0.8629</v>
+        <v>0.8633</v>
       </c>
       <c r="J203" t="inlineStr">
         <is>
@@ -12409,7 +12409,7 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>The strongest header candidate has weak row evidence; preserve the name-based mapping for review instead of replacing it with a merely similar value shape.</t>
+          <t>The header 'Vlr Isen ICM' has no semantic conflict and shows informative numeric data, while 'IVA' is a tax type that aligns with the context.</t>
         </is>
       </c>
       <c r="M203" t="inlineStr"/>
@@ -12418,10 +12418,10 @@
       <c r="P203" t="inlineStr"/>
       <c r="Q203" t="inlineStr"/>
       <c r="R203" t="n">
-        <v>0</v>
+        <v>0.8633</v>
       </c>
       <c r="S203" t="n">
-        <v>0</v>
+        <v>0.8633</v>
       </c>
       <c r="T203" t="inlineStr"/>
       <c r="U203" t="inlineStr"/>
@@ -12439,13 +12439,13 @@
       <c r="C204" t="inlineStr"/>
       <c r="D204" t="inlineStr"/>
       <c r="E204" t="n">
-        <v>0.8383</v>
+        <v>0.8384</v>
       </c>
       <c r="F204" t="n">
         <v>0.8028999999999999</v>
       </c>
       <c r="G204" t="n">
-        <v>0.0354</v>
+        <v>0.0355</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -12465,7 +12465,7 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>No viable candidates match the required semantic role for 'Nome Transportadora'.</t>
+          <t>All candidate columns contain no relevant data, making it impossible to establish a mapping.</t>
         </is>
       </c>
       <c r="M204" t="inlineStr"/>
@@ -12477,7 +12477,7 @@
         <v>0</v>
       </c>
       <c r="S204" t="n">
-        <v>0</v>
+        <v>0.7633</v>
       </c>
       <c r="T204" t="inlineStr"/>
       <c r="U204" t="inlineStr"/>
@@ -12507,7 +12507,7 @@
         <v>0.8237</v>
       </c>
       <c r="G205" t="n">
-        <v>0.123</v>
+        <v>0.1229</v>
       </c>
       <c r="H205" t="inlineStr"/>
       <c r="I205" t="n">
@@ -12626,10 +12626,10 @@
         <v>0.8762</v>
       </c>
       <c r="F207" t="n">
-        <v>0.7989000000000001</v>
+        <v>0.7997</v>
       </c>
       <c r="G207" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.0764</v>
       </c>
       <c r="H207" t="n">
         <v>0.84</v>
@@ -12649,7 +12649,7 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>The name 'Preço Unit.' closely aligns with 'Preço líq.' and both contain numeric values, despite some differences in sample distributions.</t>
+          <t>The column 'Preço Unit.' has a high name confidence and a similar numeric profile, despite being a unit price rather than a net price.</t>
         </is>
       </c>
       <c r="M207" t="inlineStr"/>
@@ -12685,19 +12685,19 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>0.8413</v>
+        <v>0.8411999999999999</v>
       </c>
       <c r="F208" t="n">
         <v>0.8456</v>
       </c>
       <c r="G208" t="n">
-        <v>-0.0043</v>
+        <v>-0.0044</v>
       </c>
       <c r="H208" t="n">
         <v>0.84</v>
       </c>
       <c r="I208" t="n">
-        <v>0.8413</v>
+        <v>0.8411999999999999</v>
       </c>
       <c r="J208" t="inlineStr">
         <is>
@@ -12720,10 +12720,10 @@
       <c r="P208" t="inlineStr"/>
       <c r="Q208" t="inlineStr"/>
       <c r="R208" t="n">
-        <v>0.8413</v>
+        <v>0.8411999999999999</v>
       </c>
       <c r="S208" t="n">
-        <v>0.8413</v>
+        <v>0.8411999999999999</v>
       </c>
       <c r="T208" t="inlineStr"/>
       <c r="U208" t="inlineStr"/>
@@ -12773,7 +12773,7 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>The column 'NF Eletr.' has a high name confidence and contains numeric values consistent with invoice numbers.</t>
+          <t>The column 'NF Eletr.' closely aligns with the 'NF/NF-e do serviço' based on name similarity and inferred type, despite the numeric profile.</t>
         </is>
       </c>
       <c r="M209" t="inlineStr"/>
@@ -12871,7 +12871,7 @@
         <v>0.8334</v>
       </c>
       <c r="G211" t="n">
-        <v>0.0576</v>
+        <v>0.0575</v>
       </c>
       <c r="H211" t="n">
         <v>0.84</v>
@@ -12903,7 +12903,7 @@
         <v>0.9</v>
       </c>
       <c r="S211" t="n">
-        <v>0.895</v>
+        <v>0.89</v>
       </c>
       <c r="T211" t="inlineStr"/>
       <c r="U211" t="inlineStr"/>
@@ -12921,13 +12921,13 @@
       <c r="C212" t="inlineStr"/>
       <c r="D212" t="inlineStr"/>
       <c r="E212" t="n">
-        <v>0.7659</v>
+        <v>0.7657</v>
       </c>
       <c r="F212" t="n">
-        <v>0.7628</v>
+        <v>0.7627</v>
       </c>
       <c r="G212" t="n">
-        <v>0.0031</v>
+        <v>0.003</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
@@ -13071,7 +13071,7 @@
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>The candidate 'Aliq. PIS' closely matches the canonical 'Aliquota PIS' in name and has a strong numeric profile.</t>
+          <t>The candidate 'Aliq. PIS' closely matches the canonical 'Aliquota PIS' in both name and numeric profile.</t>
         </is>
       </c>
       <c r="M214" t="inlineStr"/>
@@ -13102,22 +13102,28 @@
           <t>Ref.doc.origem</t>
         </is>
       </c>
-      <c r="C215" t="inlineStr"/>
-      <c r="D215" t="inlineStr"/>
+      <c r="C215" t="n">
+        <v>92</v>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>NF Original</t>
+        </is>
+      </c>
       <c r="E215" t="n">
+        <v>0.8286</v>
+      </c>
+      <c r="F215" t="n">
         <v>0.8292</v>
       </c>
-      <c r="F215" t="n">
-        <v>0.8302</v>
-      </c>
       <c r="G215" t="n">
-        <v>-0.0009</v>
+        <v>-0.0007</v>
       </c>
       <c r="H215" t="n">
         <v>0.435</v>
       </c>
       <c r="I215" t="n">
-        <v>0</v>
+        <v>0.8286</v>
       </c>
       <c r="J215" t="inlineStr">
         <is>
@@ -13126,12 +13132,12 @@
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>review</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>The column 'NF Original' has a strong name match and numeric profile consistent with invoice document numbers.</t>
         </is>
       </c>
       <c r="M215" t="inlineStr"/>
@@ -13143,7 +13149,7 @@
         <v>0.8</v>
       </c>
       <c r="S215" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8143</v>
       </c>
       <c r="T215" t="inlineStr"/>
       <c r="U215" t="inlineStr"/>
@@ -13173,7 +13179,7 @@
         <v>0.9198</v>
       </c>
       <c r="G216" t="n">
-        <v>-0.0244</v>
+        <v>-0.0245</v>
       </c>
       <c r="H216" t="n">
         <v>0.84</v>
@@ -13193,7 +13199,7 @@
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>The name 'Antecip.ICMS' closely relates to the tax context of 'Texto ICMS' and has a strong numeric profile.</t>
+          <t>The name 'Antecip.ICMS' closely relates to the 'Texto ICMS' column, and the numeric profile indicates valid data.</t>
         </is>
       </c>
       <c r="M216" t="inlineStr"/>
@@ -13320,10 +13326,10 @@
       <c r="P218" t="inlineStr"/>
       <c r="Q218" t="inlineStr"/>
       <c r="R218" t="n">
-        <v>0.8501</v>
+        <v>0.8669</v>
       </c>
       <c r="S218" t="n">
-        <v>0.8501</v>
+        <v>0.8669</v>
       </c>
       <c r="T218" t="inlineStr"/>
       <c r="U218" t="inlineStr"/>
@@ -13373,7 +13379,7 @@
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>The name 'Sit.Trib.PIS' closely matches the tax situation of 'Lei tributária PIS' with strong numeric evidence.</t>
+          <t>The header 'Sit.Trib.PIS' closely matches the semantic role of 'Lei tributária PIS' and has strong numeric evidence.</t>
         </is>
       </c>
       <c r="M219" t="inlineStr"/>
@@ -13435,7 +13441,7 @@
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>The candidate 'Trib. IPI' has a strong name match and aligns well with the expected format and values for CST IPI.</t>
+          <t>The candidate 'Trib. IPI' has a strong name match and a profile that aligns closely with the expected format for CST IPI.</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
@@ -13599,13 +13605,13 @@
       <c r="C223" t="inlineStr"/>
       <c r="D223" t="inlineStr"/>
       <c r="E223" t="n">
-        <v>0.8996</v>
+        <v>0.8997000000000001</v>
       </c>
       <c r="F223" t="n">
         <v>0.8939</v>
       </c>
       <c r="G223" t="n">
-        <v>0.0057</v>
+        <v>0.0058</v>
       </c>
       <c r="H223" t="n">
         <v>0</v>
@@ -13637,7 +13643,7 @@
         <v>0</v>
       </c>
       <c r="S223" t="n">
-        <v>0.8996</v>
+        <v>0.8997000000000001</v>
       </c>
       <c r="T223" t="inlineStr"/>
       <c r="U223" t="inlineStr"/>
@@ -13681,7 +13687,7 @@
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>All candidates have empty or non-informative data, making it impossible to establish a valid mapping.</t>
+          <t>All candidates have empty or all-zero evidence, providing no support for a mapping.</t>
         </is>
       </c>
       <c r="M224" t="inlineStr"/>
@@ -13711,10 +13717,10 @@
       <c r="C225" t="inlineStr"/>
       <c r="D225" t="inlineStr"/>
       <c r="E225" t="n">
-        <v>0.7909</v>
+        <v>0.7905</v>
       </c>
       <c r="F225" t="n">
-        <v>0.7872</v>
+        <v>0.7868000000000001</v>
       </c>
       <c r="G225" t="n">
         <v>0.0037</v>
@@ -13737,7 +13743,7 @@
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>All candidates have zero or empty evidence, making them unsuitable for mapping.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M225" t="inlineStr"/>
@@ -13749,7 +13755,7 @@
         <v>0</v>
       </c>
       <c r="S225" t="n">
-        <v>0</v>
+        <v>0.7905</v>
       </c>
       <c r="T225" t="inlineStr"/>
       <c r="U225" t="inlineStr"/>
@@ -13767,16 +13773,16 @@
       <c r="C226" t="inlineStr"/>
       <c r="D226" t="inlineStr"/>
       <c r="E226" t="n">
-        <v>0.7717000000000001</v>
+        <v>0.7548</v>
       </c>
       <c r="F226" t="n">
-        <v>0.7645999999999999</v>
+        <v>0.7724</v>
       </c>
       <c r="G226" t="n">
-        <v>0.0071</v>
+        <v>-0.0176</v>
       </c>
       <c r="H226" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="I226" t="n">
         <v>0</v>
@@ -13793,7 +13799,7 @@
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>No suitable candidate matches the expected string format and content for 'UF do Local de Início'.</t>
+          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
       <c r="M226" t="inlineStr"/>
@@ -13802,10 +13808,10 @@
       <c r="P226" t="inlineStr"/>
       <c r="Q226" t="inlineStr"/>
       <c r="R226" t="n">
-        <v>0</v>
+        <v>0.7548</v>
       </c>
       <c r="S226" t="n">
-        <v>0</v>
+        <v>0.7548</v>
       </c>
       <c r="T226" t="inlineStr"/>
       <c r="U226" t="inlineStr"/>
@@ -13823,16 +13829,16 @@
       <c r="C227" t="inlineStr"/>
       <c r="D227" t="inlineStr"/>
       <c r="E227" t="n">
-        <v>0.7107</v>
+        <v>0.7597</v>
       </c>
       <c r="F227" t="n">
-        <v>0.7913</v>
+        <v>0.7914</v>
       </c>
       <c r="G227" t="n">
-        <v>-0.0806</v>
+        <v>-0.0317</v>
       </c>
       <c r="H227" t="n">
-        <v>0.84</v>
+        <v>0.8064</v>
       </c>
       <c r="I227" t="n">
         <v>0</v>
@@ -13858,10 +13864,10 @@
       <c r="P227" t="inlineStr"/>
       <c r="Q227" t="inlineStr"/>
       <c r="R227" t="n">
-        <v>0.9</v>
+        <v>0.8064</v>
       </c>
       <c r="S227" t="n">
-        <v>0.85</v>
+        <v>0.795</v>
       </c>
       <c r="T227" t="inlineStr"/>
       <c r="U227" t="inlineStr"/>
@@ -13967,7 +13973,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25T05:09:02.963531+00:00</t>
+          <t>2026-08-25T05:39:54.996848+00:00</t>
         </is>
       </c>
     </row>
